--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,8 +107,35 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001A2733"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -140,8 +167,33 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="56">
+  <borders count="119">
     <border>
       <left/>
       <right/>
@@ -722,11 +774,722 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1045,6 +1808,353 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="60" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="93" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="100" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="98" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="99" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="64" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="56" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="60" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="62" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1119,6 +2229,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1456,1167 +2656,1230 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="55" t="n"/>
-      <c r="B1" s="120" t="n"/>
-      <c r="C1" s="120" t="n"/>
-      <c r="D1" s="120" t="n"/>
-      <c r="E1" s="120" t="n"/>
-      <c r="F1" s="120" t="n"/>
-      <c r="G1" s="120" t="n"/>
-      <c r="H1" s="120" t="n"/>
-      <c r="I1" s="57" t="inlineStr">
+      <c r="A1" s="165" t="n"/>
+      <c r="B1" s="166" t="n"/>
+      <c r="C1" s="166" t="n"/>
+      <c r="D1" s="166" t="n"/>
+      <c r="E1" s="166" t="n"/>
+      <c r="F1" s="166" t="n"/>
+      <c r="G1" s="166" t="n"/>
+      <c r="H1" s="167" t="n"/>
+      <c r="I1" s="168" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW</t>
         </is>
       </c>
-      <c r="J1" s="120" t="n"/>
-      <c r="K1" s="120" t="n"/>
-      <c r="L1" s="120" t="n"/>
-      <c r="M1" s="120" t="n"/>
-      <c r="N1" s="120" t="n"/>
-      <c r="O1" s="120" t="n"/>
-      <c r="P1" s="120" t="n"/>
-      <c r="Q1" s="120" t="n"/>
-      <c r="R1" s="120" t="n"/>
-      <c r="S1" s="120" t="n"/>
-      <c r="T1" s="120" t="n"/>
-      <c r="U1" s="120" t="n"/>
-      <c r="V1" s="120" t="n"/>
-      <c r="W1" s="120" t="n"/>
-      <c r="X1" s="120" t="n"/>
-      <c r="Y1" s="120" t="n"/>
-      <c r="Z1" s="120" t="n"/>
-      <c r="AA1" s="120" t="n"/>
-      <c r="AB1" s="120" t="n"/>
-      <c r="AC1" s="120" t="n"/>
-      <c r="AD1" s="120" t="n"/>
-      <c r="AE1" s="58" t="inlineStr">
+      <c r="J1" s="169" t="n"/>
+      <c r="K1" s="169" t="n"/>
+      <c r="L1" s="169" t="n"/>
+      <c r="M1" s="169" t="n"/>
+      <c r="N1" s="169" t="n"/>
+      <c r="O1" s="169" t="n"/>
+      <c r="P1" s="169" t="n"/>
+      <c r="Q1" s="169" t="n"/>
+      <c r="R1" s="169" t="n"/>
+      <c r="S1" s="169" t="n"/>
+      <c r="T1" s="169" t="n"/>
+      <c r="U1" s="169" t="n"/>
+      <c r="V1" s="169" t="n"/>
+      <c r="W1" s="169" t="n"/>
+      <c r="X1" s="169" t="n"/>
+      <c r="Y1" s="169" t="n"/>
+      <c r="Z1" s="169" t="n"/>
+      <c r="AA1" s="169" t="n"/>
+      <c r="AB1" s="169" t="n"/>
+      <c r="AC1" s="169" t="n"/>
+      <c r="AD1" s="170" t="n"/>
+      <c r="AE1" s="171" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="121" t="n"/>
-      <c r="AG1" s="121" t="n"/>
-      <c r="AH1" s="122" t="n"/>
-      <c r="AI1" s="61" t="inlineStr">
+      <c r="AF1" s="172" t="n"/>
+      <c r="AG1" s="172" t="n"/>
+      <c r="AH1" s="173" t="n"/>
+      <c r="AI1" s="174" t="inlineStr">
         <is>
           <t>FRM-111</t>
         </is>
       </c>
-      <c r="AJ1" s="121" t="n"/>
-      <c r="AK1" s="121" t="n"/>
-      <c r="AL1" s="121" t="n"/>
-      <c r="AM1" s="121" t="n"/>
-      <c r="AN1" s="122" t="n"/>
+      <c r="AJ1" s="175" t="n"/>
+      <c r="AK1" s="175" t="n"/>
+      <c r="AL1" s="175" t="n"/>
+      <c r="AM1" s="175" t="n"/>
+      <c r="AN1" s="176" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="123" t="n"/>
-      <c r="I2" s="123" t="n"/>
-      <c r="AE2" s="64" t="inlineStr">
+      <c r="A2" s="177" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="178" t="n"/>
+      <c r="I2" s="179" t="n"/>
+      <c r="J2" s="180" t="n"/>
+      <c r="K2" s="180" t="n"/>
+      <c r="L2" s="180" t="n"/>
+      <c r="M2" s="180" t="n"/>
+      <c r="N2" s="180" t="n"/>
+      <c r="O2" s="180" t="n"/>
+      <c r="P2" s="180" t="n"/>
+      <c r="Q2" s="180" t="n"/>
+      <c r="R2" s="180" t="n"/>
+      <c r="S2" s="180" t="n"/>
+      <c r="T2" s="180" t="n"/>
+      <c r="U2" s="180" t="n"/>
+      <c r="V2" s="180" t="n"/>
+      <c r="W2" s="180" t="n"/>
+      <c r="X2" s="180" t="n"/>
+      <c r="Y2" s="180" t="n"/>
+      <c r="Z2" s="180" t="n"/>
+      <c r="AA2" s="180" t="n"/>
+      <c r="AB2" s="180" t="n"/>
+      <c r="AC2" s="180" t="n"/>
+      <c r="AD2" s="181" t="n"/>
+      <c r="AE2" s="182" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="124" t="n"/>
-      <c r="AG2" s="124" t="n"/>
-      <c r="AH2" s="125" t="n"/>
-      <c r="AI2" s="67" t="inlineStr">
+      <c r="AF2" s="183" t="n"/>
+      <c r="AG2" s="183" t="n"/>
+      <c r="AH2" s="184" t="n"/>
+      <c r="AI2" s="185" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="124" t="n"/>
-      <c r="AK2" s="124" t="n"/>
-      <c r="AL2" s="124" t="n"/>
-      <c r="AM2" s="124" t="n"/>
-      <c r="AN2" s="125" t="n"/>
+      <c r="AJ2" s="186" t="n"/>
+      <c r="AK2" s="186" t="n"/>
+      <c r="AL2" s="186" t="n"/>
+      <c r="AM2" s="186" t="n"/>
+      <c r="AN2" s="187" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="123" t="n"/>
-      <c r="I3" s="126" t="n"/>
-      <c r="J3" s="124" t="n"/>
-      <c r="K3" s="124" t="n"/>
-      <c r="L3" s="124" t="n"/>
-      <c r="M3" s="124" t="n"/>
-      <c r="N3" s="124" t="n"/>
-      <c r="O3" s="124" t="n"/>
-      <c r="P3" s="124" t="n"/>
-      <c r="Q3" s="124" t="n"/>
-      <c r="R3" s="124" t="n"/>
-      <c r="S3" s="124" t="n"/>
-      <c r="T3" s="124" t="n"/>
-      <c r="U3" s="124" t="n"/>
-      <c r="V3" s="124" t="n"/>
-      <c r="W3" s="124" t="n"/>
-      <c r="X3" s="124" t="n"/>
-      <c r="Y3" s="124" t="n"/>
-      <c r="Z3" s="124" t="n"/>
-      <c r="AA3" s="124" t="n"/>
-      <c r="AB3" s="124" t="n"/>
-      <c r="AC3" s="124" t="n"/>
-      <c r="AD3" s="124" t="n"/>
-      <c r="AE3" s="64" t="inlineStr">
+      <c r="A3" s="177" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="178" t="n"/>
+      <c r="I3" s="179" t="n"/>
+      <c r="J3" s="180" t="n"/>
+      <c r="K3" s="180" t="n"/>
+      <c r="L3" s="180" t="n"/>
+      <c r="M3" s="180" t="n"/>
+      <c r="N3" s="180" t="n"/>
+      <c r="O3" s="180" t="n"/>
+      <c r="P3" s="180" t="n"/>
+      <c r="Q3" s="180" t="n"/>
+      <c r="R3" s="180" t="n"/>
+      <c r="S3" s="180" t="n"/>
+      <c r="T3" s="180" t="n"/>
+      <c r="U3" s="180" t="n"/>
+      <c r="V3" s="180" t="n"/>
+      <c r="W3" s="180" t="n"/>
+      <c r="X3" s="180" t="n"/>
+      <c r="Y3" s="180" t="n"/>
+      <c r="Z3" s="180" t="n"/>
+      <c r="AA3" s="180" t="n"/>
+      <c r="AB3" s="180" t="n"/>
+      <c r="AC3" s="180" t="n"/>
+      <c r="AD3" s="181" t="n"/>
+      <c r="AE3" s="182" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="124" t="n"/>
-      <c r="AG3" s="124" t="n"/>
-      <c r="AH3" s="125" t="n"/>
-      <c r="AI3" s="67" t="inlineStr">
+      <c r="AF3" s="183" t="n"/>
+      <c r="AG3" s="183" t="n"/>
+      <c r="AH3" s="184" t="n"/>
+      <c r="AI3" s="185" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="124" t="n"/>
-      <c r="AK3" s="124" t="n"/>
-      <c r="AL3" s="124" t="n"/>
-      <c r="AM3" s="124" t="n"/>
-      <c r="AN3" s="125" t="n"/>
+      <c r="AJ3" s="186" t="n"/>
+      <c r="AK3" s="186" t="n"/>
+      <c r="AL3" s="186" t="n"/>
+      <c r="AM3" s="186" t="n"/>
+      <c r="AN3" s="187" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="123" t="n"/>
-      <c r="I4" s="69" t="inlineStr">
+      <c r="A4" s="177" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="178" t="n"/>
+      <c r="I4" s="188" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="64" t="inlineStr">
+      <c r="J4" s="189" t="n"/>
+      <c r="K4" s="189" t="n"/>
+      <c r="L4" s="189" t="n"/>
+      <c r="M4" s="189" t="n"/>
+      <c r="N4" s="189" t="n"/>
+      <c r="O4" s="189" t="n"/>
+      <c r="P4" s="189" t="n"/>
+      <c r="Q4" s="189" t="n"/>
+      <c r="R4" s="189" t="n"/>
+      <c r="S4" s="189" t="n"/>
+      <c r="T4" s="189" t="n"/>
+      <c r="U4" s="189" t="n"/>
+      <c r="V4" s="189" t="n"/>
+      <c r="W4" s="189" t="n"/>
+      <c r="X4" s="189" t="n"/>
+      <c r="Y4" s="189" t="n"/>
+      <c r="Z4" s="189" t="n"/>
+      <c r="AA4" s="189" t="n"/>
+      <c r="AB4" s="189" t="n"/>
+      <c r="AC4" s="189" t="n"/>
+      <c r="AD4" s="190" t="n"/>
+      <c r="AE4" s="182" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="124" t="n"/>
-      <c r="AG4" s="124" t="n"/>
-      <c r="AH4" s="125" t="n"/>
-      <c r="AI4" s="67" t="inlineStr">
+      <c r="AF4" s="183" t="n"/>
+      <c r="AG4" s="183" t="n"/>
+      <c r="AH4" s="184" t="n"/>
+      <c r="AI4" s="185" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AJ4" s="124" t="n"/>
-      <c r="AK4" s="124" t="n"/>
-      <c r="AL4" s="124" t="n"/>
-      <c r="AM4" s="124" t="n"/>
-      <c r="AN4" s="125" t="n"/>
+      <c r="AJ4" s="186" t="n"/>
+      <c r="AK4" s="186" t="n"/>
+      <c r="AL4" s="186" t="n"/>
+      <c r="AM4" s="186" t="n"/>
+      <c r="AN4" s="187" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="126" t="n"/>
-      <c r="B5" s="124" t="n"/>
-      <c r="C5" s="124" t="n"/>
-      <c r="D5" s="124" t="n"/>
-      <c r="E5" s="124" t="n"/>
-      <c r="F5" s="124" t="n"/>
-      <c r="G5" s="124" t="n"/>
-      <c r="H5" s="124" t="n"/>
-      <c r="I5" s="70" t="inlineStr">
+      <c r="A5" s="191" t="n"/>
+      <c r="B5" s="192" t="n"/>
+      <c r="C5" s="192" t="n"/>
+      <c r="D5" s="192" t="n"/>
+      <c r="E5" s="192" t="n"/>
+      <c r="F5" s="192" t="n"/>
+      <c r="G5" s="192" t="n"/>
+      <c r="H5" s="193" t="n"/>
+      <c r="I5" s="194" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="124" t="n"/>
-      <c r="K5" s="124" t="n"/>
-      <c r="L5" s="124" t="n"/>
-      <c r="M5" s="124" t="n"/>
-      <c r="N5" s="124" t="n"/>
-      <c r="O5" s="124" t="n"/>
-      <c r="P5" s="124" t="n"/>
-      <c r="Q5" s="124" t="n"/>
-      <c r="R5" s="124" t="n"/>
-      <c r="S5" s="124" t="n"/>
-      <c r="T5" s="124" t="n"/>
-      <c r="U5" s="124" t="n"/>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
-      <c r="X5" s="124" t="n"/>
-      <c r="Y5" s="124" t="n"/>
-      <c r="Z5" s="124" t="n"/>
-      <c r="AA5" s="124" t="n"/>
-      <c r="AB5" s="124" t="n"/>
-      <c r="AC5" s="124" t="n"/>
-      <c r="AD5" s="124" t="n"/>
-      <c r="AE5" s="64" t="inlineStr">
+      <c r="J5" s="195" t="n"/>
+      <c r="K5" s="195" t="n"/>
+      <c r="L5" s="195" t="n"/>
+      <c r="M5" s="195" t="n"/>
+      <c r="N5" s="195" t="n"/>
+      <c r="O5" s="195" t="n"/>
+      <c r="P5" s="195" t="n"/>
+      <c r="Q5" s="195" t="n"/>
+      <c r="R5" s="195" t="n"/>
+      <c r="S5" s="195" t="n"/>
+      <c r="T5" s="195" t="n"/>
+      <c r="U5" s="195" t="n"/>
+      <c r="V5" s="195" t="n"/>
+      <c r="W5" s="195" t="n"/>
+      <c r="X5" s="195" t="n"/>
+      <c r="Y5" s="195" t="n"/>
+      <c r="Z5" s="195" t="n"/>
+      <c r="AA5" s="195" t="n"/>
+      <c r="AB5" s="195" t="n"/>
+      <c r="AC5" s="195" t="n"/>
+      <c r="AD5" s="196" t="n"/>
+      <c r="AE5" s="197" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="124" t="n"/>
-      <c r="AG5" s="124" t="n"/>
-      <c r="AH5" s="125" t="n"/>
-      <c r="AI5" s="67" t="inlineStr">
+      <c r="AF5" s="198" t="n"/>
+      <c r="AG5" s="198" t="n"/>
+      <c r="AH5" s="199" t="n"/>
+      <c r="AI5" s="200" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AJ5" s="124" t="n"/>
-      <c r="AK5" s="124" t="n"/>
-      <c r="AL5" s="124" t="n"/>
-      <c r="AM5" s="124" t="n"/>
-      <c r="AN5" s="125" t="n"/>
+      <c r="AJ5" s="201" t="n"/>
+      <c r="AK5" s="201" t="n"/>
+      <c r="AL5" s="201" t="n"/>
+      <c r="AM5" s="201" t="n"/>
+      <c r="AN5" s="202" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="71" t="n"/>
-      <c r="B6" s="119" t="n"/>
-      <c r="C6" s="119" t="n"/>
-      <c r="D6" s="119" t="n"/>
-      <c r="E6" s="119" t="n"/>
-      <c r="F6" s="119" t="n"/>
-      <c r="G6" s="119" t="n"/>
-      <c r="H6" s="119" t="n"/>
-      <c r="I6" s="119" t="n"/>
-      <c r="J6" s="119" t="n"/>
-      <c r="K6" s="119" t="n"/>
-      <c r="L6" s="119" t="n"/>
-      <c r="M6" s="119" t="n"/>
-      <c r="N6" s="119" t="n"/>
-      <c r="O6" s="119" t="n"/>
-      <c r="P6" s="119" t="n"/>
-      <c r="Q6" s="119" t="n"/>
-      <c r="R6" s="119" t="n"/>
-      <c r="S6" s="119" t="n"/>
-      <c r="T6" s="119" t="n"/>
-      <c r="U6" s="119" t="n"/>
-      <c r="V6" s="119" t="n"/>
-      <c r="W6" s="119" t="n"/>
-      <c r="X6" s="119" t="n"/>
-      <c r="Y6" s="119" t="n"/>
-      <c r="Z6" s="119" t="n"/>
-      <c r="AA6" s="119" t="n"/>
-      <c r="AB6" s="119" t="n"/>
-      <c r="AC6" s="119" t="n"/>
-      <c r="AD6" s="119" t="n"/>
-      <c r="AE6" s="119" t="n"/>
-      <c r="AF6" s="119" t="n"/>
-      <c r="AG6" s="119" t="n"/>
-      <c r="AH6" s="119" t="n"/>
-      <c r="AI6" s="119" t="n"/>
-      <c r="AJ6" s="119" t="n"/>
-      <c r="AK6" s="119" t="n"/>
-      <c r="AL6" s="119" t="n"/>
-      <c r="AM6" s="119" t="n"/>
-      <c r="AN6" s="119" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="203" t="n"/>
+      <c r="B6" s="203" t="n"/>
+      <c r="C6" s="203" t="n"/>
+      <c r="D6" s="203" t="n"/>
+      <c r="E6" s="203" t="n"/>
+      <c r="F6" s="203" t="n"/>
+      <c r="G6" s="203" t="n"/>
+      <c r="H6" s="203" t="n"/>
+      <c r="I6" s="203" t="n"/>
+      <c r="J6" s="203" t="n"/>
+      <c r="K6" s="203" t="n"/>
+      <c r="L6" s="203" t="n"/>
+      <c r="M6" s="203" t="n"/>
+      <c r="N6" s="203" t="n"/>
+      <c r="O6" s="203" t="n"/>
+      <c r="P6" s="203" t="n"/>
+      <c r="Q6" s="203" t="n"/>
+      <c r="R6" s="203" t="n"/>
+      <c r="S6" s="203" t="n"/>
+      <c r="T6" s="203" t="n"/>
+      <c r="U6" s="203" t="n"/>
+      <c r="V6" s="203" t="n"/>
+      <c r="W6" s="203" t="n"/>
+      <c r="X6" s="203" t="n"/>
+      <c r="Y6" s="203" t="n"/>
+      <c r="Z6" s="203" t="n"/>
+      <c r="AA6" s="203" t="n"/>
+      <c r="AB6" s="203" t="n"/>
+      <c r="AC6" s="203" t="n"/>
+      <c r="AD6" s="203" t="n"/>
+      <c r="AE6" s="203" t="n"/>
+      <c r="AF6" s="203" t="n"/>
+      <c r="AG6" s="203" t="n"/>
+      <c r="AH6" s="203" t="n"/>
+      <c r="AI6" s="203" t="n"/>
+      <c r="AJ6" s="203" t="n"/>
+      <c r="AK6" s="203" t="n"/>
+      <c r="AL6" s="203" t="n"/>
+      <c r="AM6" s="203" t="n"/>
+      <c r="AN6" s="203" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="72" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REVIEW HEADER</t>
         </is>
       </c>
-      <c r="B7" s="121" t="n"/>
-      <c r="C7" s="121" t="n"/>
-      <c r="D7" s="121" t="n"/>
-      <c r="E7" s="121" t="n"/>
-      <c r="F7" s="121" t="n"/>
-      <c r="G7" s="121" t="n"/>
-      <c r="H7" s="121" t="n"/>
-      <c r="I7" s="121" t="n"/>
-      <c r="J7" s="121" t="n"/>
-      <c r="K7" s="121" t="n"/>
-      <c r="L7" s="121" t="n"/>
-      <c r="M7" s="121" t="n"/>
-      <c r="N7" s="121" t="n"/>
-      <c r="O7" s="121" t="n"/>
-      <c r="P7" s="121" t="n"/>
-      <c r="Q7" s="121" t="n"/>
-      <c r="R7" s="121" t="n"/>
-      <c r="S7" s="121" t="n"/>
-      <c r="T7" s="121" t="n"/>
-      <c r="U7" s="121" t="n"/>
-      <c r="V7" s="121" t="n"/>
-      <c r="W7" s="121" t="n"/>
-      <c r="X7" s="121" t="n"/>
-      <c r="Y7" s="121" t="n"/>
-      <c r="Z7" s="121" t="n"/>
-      <c r="AA7" s="121" t="n"/>
-      <c r="AB7" s="121" t="n"/>
-      <c r="AC7" s="121" t="n"/>
-      <c r="AD7" s="121" t="n"/>
-      <c r="AE7" s="121" t="n"/>
-      <c r="AF7" s="121" t="n"/>
-      <c r="AG7" s="121" t="n"/>
-      <c r="AH7" s="121" t="n"/>
-      <c r="AI7" s="121" t="n"/>
-      <c r="AJ7" s="121" t="n"/>
-      <c r="AK7" s="121" t="n"/>
-      <c r="AL7" s="121" t="n"/>
-      <c r="AM7" s="121" t="n"/>
-      <c r="AN7" s="122" t="n"/>
+      <c r="B7" s="205" t="n"/>
+      <c r="C7" s="205" t="n"/>
+      <c r="D7" s="205" t="n"/>
+      <c r="E7" s="205" t="n"/>
+      <c r="F7" s="205" t="n"/>
+      <c r="G7" s="205" t="n"/>
+      <c r="H7" s="205" t="n"/>
+      <c r="I7" s="205" t="n"/>
+      <c r="J7" s="205" t="n"/>
+      <c r="K7" s="205" t="n"/>
+      <c r="L7" s="205" t="n"/>
+      <c r="M7" s="205" t="n"/>
+      <c r="N7" s="205" t="n"/>
+      <c r="O7" s="205" t="n"/>
+      <c r="P7" s="205" t="n"/>
+      <c r="Q7" s="205" t="n"/>
+      <c r="R7" s="205" t="n"/>
+      <c r="S7" s="205" t="n"/>
+      <c r="T7" s="205" t="n"/>
+      <c r="U7" s="205" t="n"/>
+      <c r="V7" s="205" t="n"/>
+      <c r="W7" s="205" t="n"/>
+      <c r="X7" s="205" t="n"/>
+      <c r="Y7" s="205" t="n"/>
+      <c r="Z7" s="205" t="n"/>
+      <c r="AA7" s="205" t="n"/>
+      <c r="AB7" s="205" t="n"/>
+      <c r="AC7" s="205" t="n"/>
+      <c r="AD7" s="205" t="n"/>
+      <c r="AE7" s="205" t="n"/>
+      <c r="AF7" s="205" t="n"/>
+      <c r="AG7" s="205" t="n"/>
+      <c r="AH7" s="205" t="n"/>
+      <c r="AI7" s="205" t="n"/>
+      <c r="AJ7" s="205" t="n"/>
+      <c r="AK7" s="205" t="n"/>
+      <c r="AL7" s="205" t="n"/>
+      <c r="AM7" s="205" t="n"/>
+      <c r="AN7" s="206" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="207" t="inlineStr">
         <is>
           <t>Access Review ID</t>
         </is>
       </c>
-      <c r="B8" s="107" t="n"/>
-      <c r="C8" s="107" t="n"/>
-      <c r="D8" s="107" t="n"/>
-      <c r="E8" s="107" t="n"/>
-      <c r="F8" s="107" t="n"/>
-      <c r="G8" s="108" t="n"/>
-      <c r="H8" s="76" t="n"/>
-      <c r="I8" s="109" t="n"/>
-      <c r="J8" s="109" t="n"/>
-      <c r="K8" s="109" t="n"/>
-      <c r="L8" s="109" t="n"/>
-      <c r="M8" s="109" t="n"/>
-      <c r="N8" s="109" t="n"/>
-      <c r="O8" s="109" t="n"/>
-      <c r="P8" s="109" t="n"/>
-      <c r="Q8" s="109" t="n"/>
-      <c r="R8" s="109" t="n"/>
-      <c r="S8" s="109" t="n"/>
-      <c r="T8" s="110" t="n"/>
-      <c r="U8" s="73" t="inlineStr">
+      <c r="B8" s="208" t="n"/>
+      <c r="C8" s="208" t="n"/>
+      <c r="D8" s="208" t="n"/>
+      <c r="E8" s="208" t="n"/>
+      <c r="F8" s="208" t="n"/>
+      <c r="G8" s="208" t="n"/>
+      <c r="H8" s="129" t="n"/>
+      <c r="I8" s="209" t="n"/>
+      <c r="J8" s="209" t="n"/>
+      <c r="K8" s="209" t="n"/>
+      <c r="L8" s="209" t="n"/>
+      <c r="M8" s="209" t="n"/>
+      <c r="N8" s="209" t="n"/>
+      <c r="O8" s="209" t="n"/>
+      <c r="P8" s="209" t="n"/>
+      <c r="Q8" s="209" t="n"/>
+      <c r="R8" s="209" t="n"/>
+      <c r="S8" s="209" t="n"/>
+      <c r="T8" s="209" t="n"/>
+      <c r="U8" s="210" t="inlineStr">
         <is>
           <t>System / Area</t>
         </is>
       </c>
-      <c r="V8" s="107" t="n"/>
-      <c r="W8" s="107" t="n"/>
-      <c r="X8" s="107" t="n"/>
-      <c r="Y8" s="107" t="n"/>
-      <c r="Z8" s="107" t="n"/>
-      <c r="AA8" s="108" t="n"/>
-      <c r="AB8" s="76" t="n"/>
-      <c r="AC8" s="109" t="n"/>
-      <c r="AD8" s="109" t="n"/>
-      <c r="AE8" s="109" t="n"/>
-      <c r="AF8" s="109" t="n"/>
-      <c r="AG8" s="109" t="n"/>
-      <c r="AH8" s="109" t="n"/>
-      <c r="AI8" s="109" t="n"/>
-      <c r="AJ8" s="109" t="n"/>
-      <c r="AK8" s="109" t="n"/>
-      <c r="AL8" s="109" t="n"/>
-      <c r="AM8" s="109" t="n"/>
-      <c r="AN8" s="110" t="n"/>
+      <c r="V8" s="208" t="n"/>
+      <c r="W8" s="208" t="n"/>
+      <c r="X8" s="208" t="n"/>
+      <c r="Y8" s="208" t="n"/>
+      <c r="Z8" s="208" t="n"/>
+      <c r="AA8" s="208" t="n"/>
+      <c r="AB8" s="129" t="n"/>
+      <c r="AC8" s="209" t="n"/>
+      <c r="AD8" s="209" t="n"/>
+      <c r="AE8" s="209" t="n"/>
+      <c r="AF8" s="209" t="n"/>
+      <c r="AG8" s="209" t="n"/>
+      <c r="AH8" s="209" t="n"/>
+      <c r="AI8" s="209" t="n"/>
+      <c r="AJ8" s="209" t="n"/>
+      <c r="AK8" s="209" t="n"/>
+      <c r="AL8" s="209" t="n"/>
+      <c r="AM8" s="209" t="n"/>
+      <c r="AN8" s="211" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="212" t="inlineStr">
         <is>
           <t>Reviewer / Process Owner</t>
         </is>
       </c>
-      <c r="B9" s="107" t="n"/>
-      <c r="C9" s="107" t="n"/>
-      <c r="D9" s="107" t="n"/>
-      <c r="E9" s="107" t="n"/>
-      <c r="F9" s="107" t="n"/>
-      <c r="G9" s="108" t="n"/>
-      <c r="H9" s="76" t="n"/>
-      <c r="I9" s="109" t="n"/>
-      <c r="J9" s="109" t="n"/>
-      <c r="K9" s="109" t="n"/>
-      <c r="L9" s="109" t="n"/>
-      <c r="M9" s="109" t="n"/>
-      <c r="N9" s="109" t="n"/>
-      <c r="O9" s="109" t="n"/>
-      <c r="P9" s="109" t="n"/>
-      <c r="Q9" s="109" t="n"/>
-      <c r="R9" s="109" t="n"/>
-      <c r="S9" s="109" t="n"/>
-      <c r="T9" s="110" t="n"/>
-      <c r="U9" s="73" t="inlineStr">
+      <c r="B9" s="213" t="n"/>
+      <c r="C9" s="213" t="n"/>
+      <c r="D9" s="213" t="n"/>
+      <c r="E9" s="213" t="n"/>
+      <c r="F9" s="213" t="n"/>
+      <c r="G9" s="213" t="n"/>
+      <c r="H9" s="214" t="n"/>
+      <c r="I9" s="215" t="n"/>
+      <c r="J9" s="215" t="n"/>
+      <c r="K9" s="215" t="n"/>
+      <c r="L9" s="215" t="n"/>
+      <c r="M9" s="215" t="n"/>
+      <c r="N9" s="215" t="n"/>
+      <c r="O9" s="215" t="n"/>
+      <c r="P9" s="215" t="n"/>
+      <c r="Q9" s="215" t="n"/>
+      <c r="R9" s="215" t="n"/>
+      <c r="S9" s="215" t="n"/>
+      <c r="T9" s="215" t="n"/>
+      <c r="U9" s="216" t="inlineStr">
         <is>
           <t>Review Period</t>
         </is>
       </c>
-      <c r="V9" s="107" t="n"/>
-      <c r="W9" s="107" t="n"/>
-      <c r="X9" s="107" t="n"/>
-      <c r="Y9" s="107" t="n"/>
-      <c r="Z9" s="107" t="n"/>
-      <c r="AA9" s="108" t="n"/>
-      <c r="AB9" s="76" t="n"/>
-      <c r="AC9" s="109" t="n"/>
-      <c r="AD9" s="109" t="n"/>
-      <c r="AE9" s="109" t="n"/>
-      <c r="AF9" s="109" t="n"/>
-      <c r="AG9" s="109" t="n"/>
-      <c r="AH9" s="109" t="n"/>
-      <c r="AI9" s="109" t="n"/>
-      <c r="AJ9" s="109" t="n"/>
-      <c r="AK9" s="109" t="n"/>
-      <c r="AL9" s="109" t="n"/>
-      <c r="AM9" s="109" t="n"/>
-      <c r="AN9" s="110" t="n"/>
+      <c r="V9" s="213" t="n"/>
+      <c r="W9" s="213" t="n"/>
+      <c r="X9" s="213" t="n"/>
+      <c r="Y9" s="213" t="n"/>
+      <c r="Z9" s="213" t="n"/>
+      <c r="AA9" s="213" t="n"/>
+      <c r="AB9" s="214" t="n"/>
+      <c r="AC9" s="215" t="n"/>
+      <c r="AD9" s="215" t="n"/>
+      <c r="AE9" s="215" t="n"/>
+      <c r="AF9" s="215" t="n"/>
+      <c r="AG9" s="215" t="n"/>
+      <c r="AH9" s="215" t="n"/>
+      <c r="AI9" s="215" t="n"/>
+      <c r="AJ9" s="215" t="n"/>
+      <c r="AK9" s="215" t="n"/>
+      <c r="AL9" s="215" t="n"/>
+      <c r="AM9" s="215" t="n"/>
+      <c r="AN9" s="217" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. REVIEW SCOPE AND BASIS</t>
         </is>
       </c>
-      <c r="B10" s="107" t="n"/>
-      <c r="C10" s="107" t="n"/>
-      <c r="D10" s="107" t="n"/>
-      <c r="E10" s="107" t="n"/>
-      <c r="F10" s="107" t="n"/>
-      <c r="G10" s="107" t="n"/>
-      <c r="H10" s="107" t="n"/>
-      <c r="I10" s="107" t="n"/>
-      <c r="J10" s="107" t="n"/>
-      <c r="K10" s="107" t="n"/>
-      <c r="L10" s="107" t="n"/>
-      <c r="M10" s="107" t="n"/>
-      <c r="N10" s="107" t="n"/>
-      <c r="O10" s="107" t="n"/>
-      <c r="P10" s="107" t="n"/>
-      <c r="Q10" s="107" t="n"/>
-      <c r="R10" s="107" t="n"/>
-      <c r="S10" s="107" t="n"/>
-      <c r="T10" s="107" t="n"/>
-      <c r="U10" s="107" t="n"/>
-      <c r="V10" s="107" t="n"/>
-      <c r="W10" s="107" t="n"/>
-      <c r="X10" s="107" t="n"/>
-      <c r="Y10" s="107" t="n"/>
-      <c r="Z10" s="107" t="n"/>
-      <c r="AA10" s="107" t="n"/>
-      <c r="AB10" s="107" t="n"/>
-      <c r="AC10" s="107" t="n"/>
-      <c r="AD10" s="107" t="n"/>
-      <c r="AE10" s="107" t="n"/>
-      <c r="AF10" s="107" t="n"/>
-      <c r="AG10" s="107" t="n"/>
-      <c r="AH10" s="107" t="n"/>
-      <c r="AI10" s="107" t="n"/>
-      <c r="AJ10" s="107" t="n"/>
-      <c r="AK10" s="107" t="n"/>
-      <c r="AL10" s="107" t="n"/>
-      <c r="AM10" s="107" t="n"/>
-      <c r="AN10" s="108" t="n"/>
+      <c r="B10" s="205" t="n"/>
+      <c r="C10" s="205" t="n"/>
+      <c r="D10" s="205" t="n"/>
+      <c r="E10" s="205" t="n"/>
+      <c r="F10" s="205" t="n"/>
+      <c r="G10" s="205" t="n"/>
+      <c r="H10" s="205" t="n"/>
+      <c r="I10" s="205" t="n"/>
+      <c r="J10" s="205" t="n"/>
+      <c r="K10" s="205" t="n"/>
+      <c r="L10" s="205" t="n"/>
+      <c r="M10" s="205" t="n"/>
+      <c r="N10" s="205" t="n"/>
+      <c r="O10" s="205" t="n"/>
+      <c r="P10" s="205" t="n"/>
+      <c r="Q10" s="205" t="n"/>
+      <c r="R10" s="205" t="n"/>
+      <c r="S10" s="205" t="n"/>
+      <c r="T10" s="205" t="n"/>
+      <c r="U10" s="205" t="n"/>
+      <c r="V10" s="205" t="n"/>
+      <c r="W10" s="205" t="n"/>
+      <c r="X10" s="205" t="n"/>
+      <c r="Y10" s="205" t="n"/>
+      <c r="Z10" s="205" t="n"/>
+      <c r="AA10" s="205" t="n"/>
+      <c r="AB10" s="205" t="n"/>
+      <c r="AC10" s="205" t="n"/>
+      <c r="AD10" s="205" t="n"/>
+      <c r="AE10" s="205" t="n"/>
+      <c r="AF10" s="205" t="n"/>
+      <c r="AG10" s="205" t="n"/>
+      <c r="AH10" s="205" t="n"/>
+      <c r="AI10" s="205" t="n"/>
+      <c r="AJ10" s="205" t="n"/>
+      <c r="AK10" s="205" t="n"/>
+      <c r="AL10" s="205" t="n"/>
+      <c r="AM10" s="205" t="n"/>
+      <c r="AN10" s="206" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="73" t="inlineStr">
+      <c r="A11" s="218" t="inlineStr">
         <is>
           <t>Account Population / Role Scope</t>
         </is>
       </c>
-      <c r="B11" s="107" t="n"/>
-      <c r="C11" s="107" t="n"/>
-      <c r="D11" s="107" t="n"/>
-      <c r="E11" s="107" t="n"/>
-      <c r="F11" s="107" t="n"/>
-      <c r="G11" s="108" t="n"/>
-      <c r="H11" s="76" t="n"/>
-      <c r="I11" s="109" t="n"/>
-      <c r="J11" s="109" t="n"/>
-      <c r="K11" s="109" t="n"/>
-      <c r="L11" s="109" t="n"/>
-      <c r="M11" s="109" t="n"/>
-      <c r="N11" s="109" t="n"/>
-      <c r="O11" s="109" t="n"/>
-      <c r="P11" s="109" t="n"/>
-      <c r="Q11" s="109" t="n"/>
-      <c r="R11" s="109" t="n"/>
-      <c r="S11" s="109" t="n"/>
-      <c r="T11" s="110" t="n"/>
-      <c r="U11" s="73" t="inlineStr">
+      <c r="B11" s="219" t="n"/>
+      <c r="C11" s="219" t="n"/>
+      <c r="D11" s="219" t="n"/>
+      <c r="E11" s="219" t="n"/>
+      <c r="F11" s="219" t="n"/>
+      <c r="G11" s="219" t="n"/>
+      <c r="H11" s="220" t="n"/>
+      <c r="I11" s="221" t="n"/>
+      <c r="J11" s="221" t="n"/>
+      <c r="K11" s="221" t="n"/>
+      <c r="L11" s="221" t="n"/>
+      <c r="M11" s="221" t="n"/>
+      <c r="N11" s="221" t="n"/>
+      <c r="O11" s="221" t="n"/>
+      <c r="P11" s="221" t="n"/>
+      <c r="Q11" s="221" t="n"/>
+      <c r="R11" s="221" t="n"/>
+      <c r="S11" s="221" t="n"/>
+      <c r="T11" s="221" t="n"/>
+      <c r="U11" s="222" t="inlineStr">
         <is>
           <t>Source-of-Truth Date</t>
         </is>
       </c>
-      <c r="V11" s="107" t="n"/>
-      <c r="W11" s="107" t="n"/>
-      <c r="X11" s="107" t="n"/>
-      <c r="Y11" s="107" t="n"/>
-      <c r="Z11" s="107" t="n"/>
-      <c r="AA11" s="108" t="n"/>
-      <c r="AB11" s="76" t="n"/>
-      <c r="AC11" s="109" t="n"/>
-      <c r="AD11" s="109" t="n"/>
-      <c r="AE11" s="109" t="n"/>
-      <c r="AF11" s="109" t="n"/>
-      <c r="AG11" s="109" t="n"/>
-      <c r="AH11" s="109" t="n"/>
-      <c r="AI11" s="109" t="n"/>
-      <c r="AJ11" s="109" t="n"/>
-      <c r="AK11" s="109" t="n"/>
-      <c r="AL11" s="109" t="n"/>
-      <c r="AM11" s="109" t="n"/>
-      <c r="AN11" s="110" t="n"/>
+      <c r="V11" s="219" t="n"/>
+      <c r="W11" s="219" t="n"/>
+      <c r="X11" s="219" t="n"/>
+      <c r="Y11" s="219" t="n"/>
+      <c r="Z11" s="219" t="n"/>
+      <c r="AA11" s="219" t="n"/>
+      <c r="AB11" s="220" t="n"/>
+      <c r="AC11" s="221" t="n"/>
+      <c r="AD11" s="221" t="n"/>
+      <c r="AE11" s="221" t="n"/>
+      <c r="AF11" s="221" t="n"/>
+      <c r="AG11" s="221" t="n"/>
+      <c r="AH11" s="221" t="n"/>
+      <c r="AI11" s="221" t="n"/>
+      <c r="AJ11" s="221" t="n"/>
+      <c r="AK11" s="221" t="n"/>
+      <c r="AL11" s="221" t="n"/>
+      <c r="AM11" s="221" t="n"/>
+      <c r="AN11" s="223" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="72" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. FINDINGS, ACTION AND ESCALATION</t>
         </is>
       </c>
-      <c r="B12" s="107" t="n"/>
-      <c r="C12" s="107" t="n"/>
-      <c r="D12" s="107" t="n"/>
-      <c r="E12" s="107" t="n"/>
-      <c r="F12" s="107" t="n"/>
-      <c r="G12" s="107" t="n"/>
-      <c r="H12" s="107" t="n"/>
-      <c r="I12" s="107" t="n"/>
-      <c r="J12" s="107" t="n"/>
-      <c r="K12" s="107" t="n"/>
-      <c r="L12" s="107" t="n"/>
-      <c r="M12" s="107" t="n"/>
-      <c r="N12" s="107" t="n"/>
-      <c r="O12" s="107" t="n"/>
-      <c r="P12" s="107" t="n"/>
-      <c r="Q12" s="107" t="n"/>
-      <c r="R12" s="107" t="n"/>
-      <c r="S12" s="107" t="n"/>
-      <c r="T12" s="107" t="n"/>
-      <c r="U12" s="107" t="n"/>
-      <c r="V12" s="107" t="n"/>
-      <c r="W12" s="107" t="n"/>
-      <c r="X12" s="107" t="n"/>
-      <c r="Y12" s="107" t="n"/>
-      <c r="Z12" s="107" t="n"/>
-      <c r="AA12" s="107" t="n"/>
-      <c r="AB12" s="107" t="n"/>
-      <c r="AC12" s="107" t="n"/>
-      <c r="AD12" s="107" t="n"/>
-      <c r="AE12" s="107" t="n"/>
-      <c r="AF12" s="107" t="n"/>
-      <c r="AG12" s="107" t="n"/>
-      <c r="AH12" s="107" t="n"/>
-      <c r="AI12" s="107" t="n"/>
-      <c r="AJ12" s="107" t="n"/>
-      <c r="AK12" s="107" t="n"/>
-      <c r="AL12" s="107" t="n"/>
-      <c r="AM12" s="107" t="n"/>
-      <c r="AN12" s="108" t="n"/>
+      <c r="B12" s="205" t="n"/>
+      <c r="C12" s="205" t="n"/>
+      <c r="D12" s="205" t="n"/>
+      <c r="E12" s="205" t="n"/>
+      <c r="F12" s="205" t="n"/>
+      <c r="G12" s="205" t="n"/>
+      <c r="H12" s="205" t="n"/>
+      <c r="I12" s="205" t="n"/>
+      <c r="J12" s="205" t="n"/>
+      <c r="K12" s="205" t="n"/>
+      <c r="L12" s="205" t="n"/>
+      <c r="M12" s="205" t="n"/>
+      <c r="N12" s="205" t="n"/>
+      <c r="O12" s="205" t="n"/>
+      <c r="P12" s="205" t="n"/>
+      <c r="Q12" s="205" t="n"/>
+      <c r="R12" s="205" t="n"/>
+      <c r="S12" s="205" t="n"/>
+      <c r="T12" s="205" t="n"/>
+      <c r="U12" s="205" t="n"/>
+      <c r="V12" s="205" t="n"/>
+      <c r="W12" s="205" t="n"/>
+      <c r="X12" s="205" t="n"/>
+      <c r="Y12" s="205" t="n"/>
+      <c r="Z12" s="205" t="n"/>
+      <c r="AA12" s="205" t="n"/>
+      <c r="AB12" s="205" t="n"/>
+      <c r="AC12" s="205" t="n"/>
+      <c r="AD12" s="205" t="n"/>
+      <c r="AE12" s="205" t="n"/>
+      <c r="AF12" s="205" t="n"/>
+      <c r="AG12" s="205" t="n"/>
+      <c r="AH12" s="205" t="n"/>
+      <c r="AI12" s="205" t="n"/>
+      <c r="AJ12" s="205" t="n"/>
+      <c r="AK12" s="205" t="n"/>
+      <c r="AL12" s="205" t="n"/>
+      <c r="AM12" s="205" t="n"/>
+      <c r="AN12" s="206" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
+      <c r="A13" s="218" t="inlineStr">
         <is>
           <t>Privilege / SoD Exceptions</t>
         </is>
       </c>
-      <c r="B13" s="107" t="n"/>
-      <c r="C13" s="107" t="n"/>
-      <c r="D13" s="107" t="n"/>
-      <c r="E13" s="107" t="n"/>
-      <c r="F13" s="107" t="n"/>
-      <c r="G13" s="108" t="n"/>
-      <c r="H13" s="76" t="n"/>
-      <c r="I13" s="109" t="n"/>
-      <c r="J13" s="109" t="n"/>
-      <c r="K13" s="109" t="n"/>
-      <c r="L13" s="109" t="n"/>
-      <c r="M13" s="109" t="n"/>
-      <c r="N13" s="109" t="n"/>
-      <c r="O13" s="109" t="n"/>
-      <c r="P13" s="109" t="n"/>
-      <c r="Q13" s="109" t="n"/>
-      <c r="R13" s="109" t="n"/>
-      <c r="S13" s="109" t="n"/>
-      <c r="T13" s="110" t="n"/>
-      <c r="U13" s="73" t="inlineStr">
+      <c r="B13" s="219" t="n"/>
+      <c r="C13" s="219" t="n"/>
+      <c r="D13" s="219" t="n"/>
+      <c r="E13" s="219" t="n"/>
+      <c r="F13" s="219" t="n"/>
+      <c r="G13" s="219" t="n"/>
+      <c r="H13" s="220" t="n"/>
+      <c r="I13" s="221" t="n"/>
+      <c r="J13" s="221" t="n"/>
+      <c r="K13" s="221" t="n"/>
+      <c r="L13" s="221" t="n"/>
+      <c r="M13" s="221" t="n"/>
+      <c r="N13" s="221" t="n"/>
+      <c r="O13" s="221" t="n"/>
+      <c r="P13" s="221" t="n"/>
+      <c r="Q13" s="221" t="n"/>
+      <c r="R13" s="221" t="n"/>
+      <c r="S13" s="221" t="n"/>
+      <c r="T13" s="221" t="n"/>
+      <c r="U13" s="222" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="V13" s="107" t="n"/>
-      <c r="W13" s="107" t="n"/>
-      <c r="X13" s="107" t="n"/>
-      <c r="Y13" s="107" t="n"/>
-      <c r="Z13" s="107" t="n"/>
-      <c r="AA13" s="108" t="n"/>
-      <c r="AB13" s="76" t="n"/>
-      <c r="AC13" s="109" t="n"/>
-      <c r="AD13" s="109" t="n"/>
-      <c r="AE13" s="109" t="n"/>
-      <c r="AF13" s="109" t="n"/>
-      <c r="AG13" s="109" t="n"/>
-      <c r="AH13" s="109" t="n"/>
-      <c r="AI13" s="109" t="n"/>
-      <c r="AJ13" s="109" t="n"/>
-      <c r="AK13" s="109" t="n"/>
-      <c r="AL13" s="109" t="n"/>
-      <c r="AM13" s="109" t="n"/>
-      <c r="AN13" s="110" t="n"/>
+      <c r="V13" s="219" t="n"/>
+      <c r="W13" s="219" t="n"/>
+      <c r="X13" s="219" t="n"/>
+      <c r="Y13" s="219" t="n"/>
+      <c r="Z13" s="219" t="n"/>
+      <c r="AA13" s="219" t="n"/>
+      <c r="AB13" s="220" t="n"/>
+      <c r="AC13" s="221" t="n"/>
+      <c r="AD13" s="221" t="n"/>
+      <c r="AE13" s="221" t="n"/>
+      <c r="AF13" s="221" t="n"/>
+      <c r="AG13" s="221" t="n"/>
+      <c r="AH13" s="221" t="n"/>
+      <c r="AI13" s="221" t="n"/>
+      <c r="AJ13" s="221" t="n"/>
+      <c r="AK13" s="221" t="n"/>
+      <c r="AL13" s="221" t="n"/>
+      <c r="AM13" s="221" t="n"/>
+      <c r="AN13" s="223" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="72" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DECISION AND CLOSEOUT</t>
         </is>
       </c>
-      <c r="B14" s="107" t="n"/>
-      <c r="C14" s="107" t="n"/>
-      <c r="D14" s="107" t="n"/>
-      <c r="E14" s="107" t="n"/>
-      <c r="F14" s="107" t="n"/>
-      <c r="G14" s="107" t="n"/>
-      <c r="H14" s="107" t="n"/>
-      <c r="I14" s="107" t="n"/>
-      <c r="J14" s="107" t="n"/>
-      <c r="K14" s="107" t="n"/>
-      <c r="L14" s="107" t="n"/>
-      <c r="M14" s="107" t="n"/>
-      <c r="N14" s="107" t="n"/>
-      <c r="O14" s="107" t="n"/>
-      <c r="P14" s="107" t="n"/>
-      <c r="Q14" s="107" t="n"/>
-      <c r="R14" s="107" t="n"/>
-      <c r="S14" s="107" t="n"/>
-      <c r="T14" s="107" t="n"/>
-      <c r="U14" s="107" t="n"/>
-      <c r="V14" s="107" t="n"/>
-      <c r="W14" s="107" t="n"/>
-      <c r="X14" s="107" t="n"/>
-      <c r="Y14" s="107" t="n"/>
-      <c r="Z14" s="107" t="n"/>
-      <c r="AA14" s="107" t="n"/>
-      <c r="AB14" s="107" t="n"/>
-      <c r="AC14" s="107" t="n"/>
-      <c r="AD14" s="107" t="n"/>
-      <c r="AE14" s="107" t="n"/>
-      <c r="AF14" s="107" t="n"/>
-      <c r="AG14" s="107" t="n"/>
-      <c r="AH14" s="107" t="n"/>
-      <c r="AI14" s="107" t="n"/>
-      <c r="AJ14" s="107" t="n"/>
-      <c r="AK14" s="107" t="n"/>
-      <c r="AL14" s="107" t="n"/>
-      <c r="AM14" s="107" t="n"/>
-      <c r="AN14" s="108" t="n"/>
+      <c r="B14" s="205" t="n"/>
+      <c r="C14" s="205" t="n"/>
+      <c r="D14" s="205" t="n"/>
+      <c r="E14" s="205" t="n"/>
+      <c r="F14" s="205" t="n"/>
+      <c r="G14" s="205" t="n"/>
+      <c r="H14" s="205" t="n"/>
+      <c r="I14" s="205" t="n"/>
+      <c r="J14" s="205" t="n"/>
+      <c r="K14" s="205" t="n"/>
+      <c r="L14" s="205" t="n"/>
+      <c r="M14" s="205" t="n"/>
+      <c r="N14" s="205" t="n"/>
+      <c r="O14" s="205" t="n"/>
+      <c r="P14" s="205" t="n"/>
+      <c r="Q14" s="205" t="n"/>
+      <c r="R14" s="205" t="n"/>
+      <c r="S14" s="205" t="n"/>
+      <c r="T14" s="205" t="n"/>
+      <c r="U14" s="205" t="n"/>
+      <c r="V14" s="205" t="n"/>
+      <c r="W14" s="205" t="n"/>
+      <c r="X14" s="205" t="n"/>
+      <c r="Y14" s="205" t="n"/>
+      <c r="Z14" s="205" t="n"/>
+      <c r="AA14" s="205" t="n"/>
+      <c r="AB14" s="205" t="n"/>
+      <c r="AC14" s="205" t="n"/>
+      <c r="AD14" s="205" t="n"/>
+      <c r="AE14" s="205" t="n"/>
+      <c r="AF14" s="205" t="n"/>
+      <c r="AG14" s="205" t="n"/>
+      <c r="AH14" s="205" t="n"/>
+      <c r="AI14" s="205" t="n"/>
+      <c r="AJ14" s="205" t="n"/>
+      <c r="AK14" s="205" t="n"/>
+      <c r="AL14" s="205" t="n"/>
+      <c r="AM14" s="205" t="n"/>
+      <c r="AN14" s="206" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="73" t="inlineStr">
+      <c r="A15" s="207" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B15" s="107" t="n"/>
-      <c r="C15" s="107" t="n"/>
-      <c r="D15" s="107" t="n"/>
-      <c r="E15" s="107" t="n"/>
-      <c r="F15" s="107" t="n"/>
-      <c r="G15" s="108" t="n"/>
-      <c r="H15" s="76" t="n"/>
-      <c r="I15" s="109" t="n"/>
-      <c r="J15" s="109" t="n"/>
-      <c r="K15" s="109" t="n"/>
-      <c r="L15" s="109" t="n"/>
-      <c r="M15" s="109" t="n"/>
-      <c r="N15" s="109" t="n"/>
-      <c r="O15" s="109" t="n"/>
-      <c r="P15" s="109" t="n"/>
-      <c r="Q15" s="109" t="n"/>
-      <c r="R15" s="109" t="n"/>
-      <c r="S15" s="109" t="n"/>
-      <c r="T15" s="110" t="n"/>
-      <c r="U15" s="73" t="inlineStr">
+      <c r="B15" s="208" t="n"/>
+      <c r="C15" s="208" t="n"/>
+      <c r="D15" s="208" t="n"/>
+      <c r="E15" s="208" t="n"/>
+      <c r="F15" s="208" t="n"/>
+      <c r="G15" s="208" t="n"/>
+      <c r="H15" s="129" t="n"/>
+      <c r="I15" s="209" t="n"/>
+      <c r="J15" s="209" t="n"/>
+      <c r="K15" s="209" t="n"/>
+      <c r="L15" s="209" t="n"/>
+      <c r="M15" s="209" t="n"/>
+      <c r="N15" s="224" t="n"/>
+      <c r="O15" s="209" t="n"/>
+      <c r="P15" s="209" t="n"/>
+      <c r="Q15" s="209" t="n"/>
+      <c r="R15" s="209" t="n"/>
+      <c r="S15" s="209" t="n"/>
+      <c r="T15" s="209" t="n"/>
+      <c r="U15" s="210" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="V15" s="107" t="n"/>
-      <c r="W15" s="107" t="n"/>
-      <c r="X15" s="107" t="n"/>
-      <c r="Y15" s="107" t="n"/>
-      <c r="Z15" s="107" t="n"/>
-      <c r="AA15" s="108" t="n"/>
-      <c r="AB15" s="76" t="n"/>
-      <c r="AC15" s="109" t="n"/>
-      <c r="AD15" s="109" t="n"/>
-      <c r="AE15" s="109" t="n"/>
-      <c r="AF15" s="109" t="n"/>
-      <c r="AG15" s="109" t="n"/>
-      <c r="AH15" s="109" t="n"/>
-      <c r="AI15" s="109" t="n"/>
-      <c r="AJ15" s="109" t="n"/>
-      <c r="AK15" s="109" t="n"/>
-      <c r="AL15" s="109" t="n"/>
-      <c r="AM15" s="109" t="n"/>
-      <c r="AN15" s="110" t="n"/>
+      <c r="V15" s="208" t="n"/>
+      <c r="W15" s="208" t="n"/>
+      <c r="X15" s="208" t="n"/>
+      <c r="Y15" s="208" t="n"/>
+      <c r="Z15" s="208" t="n"/>
+      <c r="AA15" s="225" t="n"/>
+      <c r="AB15" s="129" t="n"/>
+      <c r="AC15" s="209" t="n"/>
+      <c r="AD15" s="209" t="n"/>
+      <c r="AE15" s="209" t="n"/>
+      <c r="AF15" s="209" t="n"/>
+      <c r="AG15" s="209" t="n"/>
+      <c r="AH15" s="209" t="n"/>
+      <c r="AI15" s="209" t="n"/>
+      <c r="AJ15" s="209" t="n"/>
+      <c r="AK15" s="209" t="n"/>
+      <c r="AL15" s="209" t="n"/>
+      <c r="AM15" s="209" t="n"/>
+      <c r="AN15" s="211" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
+      <c r="A16" s="226" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B16" s="107" t="n"/>
-      <c r="C16" s="107" t="n"/>
-      <c r="D16" s="107" t="n"/>
-      <c r="E16" s="107" t="n"/>
-      <c r="F16" s="107" t="n"/>
-      <c r="G16" s="108" t="n"/>
-      <c r="H16" s="76" t="n"/>
-      <c r="I16" s="109" t="n"/>
-      <c r="J16" s="109" t="n"/>
-      <c r="K16" s="109" t="n"/>
-      <c r="L16" s="109" t="n"/>
-      <c r="M16" s="109" t="n"/>
-      <c r="N16" s="109" t="n"/>
-      <c r="O16" s="109" t="n"/>
-      <c r="P16" s="109" t="n"/>
-      <c r="Q16" s="109" t="n"/>
-      <c r="R16" s="109" t="n"/>
-      <c r="S16" s="109" t="n"/>
-      <c r="T16" s="110" t="n"/>
-      <c r="U16" s="73" t="inlineStr">
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="59" t="n"/>
+      <c r="G16" s="59" t="n"/>
+      <c r="H16" s="137" t="n"/>
+      <c r="I16" s="227" t="n"/>
+      <c r="J16" s="227" t="n"/>
+      <c r="K16" s="227" t="n"/>
+      <c r="L16" s="227" t="n"/>
+      <c r="M16" s="227" t="n"/>
+      <c r="N16" s="228" t="n"/>
+      <c r="O16" s="227" t="n"/>
+      <c r="P16" s="227" t="n"/>
+      <c r="Q16" s="227" t="n"/>
+      <c r="R16" s="227" t="n"/>
+      <c r="S16" s="227" t="n"/>
+      <c r="T16" s="227" t="n"/>
+      <c r="U16" s="229" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="V16" s="107" t="n"/>
-      <c r="W16" s="107" t="n"/>
-      <c r="X16" s="107" t="n"/>
-      <c r="Y16" s="107" t="n"/>
-      <c r="Z16" s="107" t="n"/>
-      <c r="AA16" s="108" t="n"/>
-      <c r="AB16" s="76" t="n"/>
-      <c r="AC16" s="109" t="n"/>
-      <c r="AD16" s="109" t="n"/>
-      <c r="AE16" s="109" t="n"/>
-      <c r="AF16" s="109" t="n"/>
-      <c r="AG16" s="109" t="n"/>
-      <c r="AH16" s="109" t="n"/>
-      <c r="AI16" s="109" t="n"/>
-      <c r="AJ16" s="109" t="n"/>
-      <c r="AK16" s="109" t="n"/>
-      <c r="AL16" s="109" t="n"/>
-      <c r="AM16" s="109" t="n"/>
-      <c r="AN16" s="110" t="n"/>
+      <c r="V16" s="59" t="n"/>
+      <c r="W16" s="59" t="n"/>
+      <c r="X16" s="59" t="n"/>
+      <c r="Y16" s="59" t="n"/>
+      <c r="Z16" s="59" t="n"/>
+      <c r="AA16" s="230" t="n"/>
+      <c r="AB16" s="137" t="n"/>
+      <c r="AC16" s="227" t="n"/>
+      <c r="AD16" s="227" t="n"/>
+      <c r="AE16" s="227" t="n"/>
+      <c r="AF16" s="227" t="n"/>
+      <c r="AG16" s="227" t="n"/>
+      <c r="AH16" s="227" t="n"/>
+      <c r="AI16" s="227" t="n"/>
+      <c r="AJ16" s="227" t="n"/>
+      <c r="AK16" s="227" t="n"/>
+      <c r="AL16" s="227" t="n"/>
+      <c r="AM16" s="227" t="n"/>
+      <c r="AN16" s="231" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
+      <c r="A17" s="226" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="B17" s="107" t="n"/>
-      <c r="C17" s="107" t="n"/>
-      <c r="D17" s="107" t="n"/>
-      <c r="E17" s="107" t="n"/>
-      <c r="F17" s="107" t="n"/>
-      <c r="G17" s="108" t="n"/>
-      <c r="H17" s="76" t="n"/>
-      <c r="I17" s="109" t="n"/>
-      <c r="J17" s="109" t="n"/>
-      <c r="K17" s="109" t="n"/>
-      <c r="L17" s="109" t="n"/>
-      <c r="M17" s="109" t="n"/>
-      <c r="N17" s="109" t="n"/>
-      <c r="O17" s="109" t="n"/>
-      <c r="P17" s="109" t="n"/>
-      <c r="Q17" s="109" t="n"/>
-      <c r="R17" s="109" t="n"/>
-      <c r="S17" s="109" t="n"/>
-      <c r="T17" s="110" t="n"/>
-      <c r="U17" s="73" t="inlineStr">
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="59" t="n"/>
+      <c r="G17" s="59" t="n"/>
+      <c r="H17" s="137" t="n"/>
+      <c r="I17" s="227" t="n"/>
+      <c r="J17" s="227" t="n"/>
+      <c r="K17" s="227" t="n"/>
+      <c r="L17" s="227" t="n"/>
+      <c r="M17" s="227" t="n"/>
+      <c r="N17" s="228" t="n"/>
+      <c r="O17" s="227" t="n"/>
+      <c r="P17" s="227" t="n"/>
+      <c r="Q17" s="227" t="n"/>
+      <c r="R17" s="227" t="n"/>
+      <c r="S17" s="227" t="n"/>
+      <c r="T17" s="227" t="n"/>
+      <c r="U17" s="229" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="V17" s="107" t="n"/>
-      <c r="W17" s="107" t="n"/>
-      <c r="X17" s="107" t="n"/>
-      <c r="Y17" s="107" t="n"/>
-      <c r="Z17" s="107" t="n"/>
-      <c r="AA17" s="108" t="n"/>
-      <c r="AB17" s="76" t="n"/>
-      <c r="AC17" s="109" t="n"/>
-      <c r="AD17" s="109" t="n"/>
-      <c r="AE17" s="109" t="n"/>
-      <c r="AF17" s="109" t="n"/>
-      <c r="AG17" s="109" t="n"/>
-      <c r="AH17" s="109" t="n"/>
-      <c r="AI17" s="109" t="n"/>
-      <c r="AJ17" s="109" t="n"/>
-      <c r="AK17" s="109" t="n"/>
-      <c r="AL17" s="109" t="n"/>
-      <c r="AM17" s="109" t="n"/>
-      <c r="AN17" s="110" t="n"/>
+      <c r="V17" s="59" t="n"/>
+      <c r="W17" s="59" t="n"/>
+      <c r="X17" s="59" t="n"/>
+      <c r="Y17" s="59" t="n"/>
+      <c r="Z17" s="59" t="n"/>
+      <c r="AA17" s="230" t="n"/>
+      <c r="AB17" s="137" t="n"/>
+      <c r="AC17" s="227" t="n"/>
+      <c r="AD17" s="227" t="n"/>
+      <c r="AE17" s="227" t="n"/>
+      <c r="AF17" s="227" t="n"/>
+      <c r="AG17" s="227" t="n"/>
+      <c r="AH17" s="227" t="n"/>
+      <c r="AI17" s="227" t="n"/>
+      <c r="AJ17" s="227" t="n"/>
+      <c r="AK17" s="227" t="n"/>
+      <c r="AL17" s="227" t="n"/>
+      <c r="AM17" s="227" t="n"/>
+      <c r="AN17" s="231" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="79" t="inlineStr">
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="232" t="inlineStr">
         <is>
           <t>Prepared By</t>
         </is>
       </c>
-      <c r="B18" s="104" t="n"/>
-      <c r="C18" s="104" t="n"/>
-      <c r="D18" s="104" t="n"/>
-      <c r="E18" s="104" t="n"/>
-      <c r="F18" s="104" t="n"/>
-      <c r="G18" s="104" t="n"/>
-      <c r="H18" s="104" t="n"/>
-      <c r="I18" s="104" t="n"/>
-      <c r="J18" s="104" t="n"/>
-      <c r="K18" s="104" t="n"/>
-      <c r="L18" s="104" t="n"/>
-      <c r="M18" s="105" t="n"/>
-      <c r="N18" s="79" t="inlineStr">
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="59" t="n"/>
+      <c r="G18" s="59" t="n"/>
+      <c r="H18" s="230" t="n"/>
+      <c r="I18" s="59" t="n"/>
+      <c r="J18" s="59" t="n"/>
+      <c r="K18" s="59" t="n"/>
+      <c r="L18" s="59" t="n"/>
+      <c r="M18" s="59" t="n"/>
+      <c r="N18" s="233" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="O18" s="104" t="n"/>
-      <c r="P18" s="104" t="n"/>
-      <c r="Q18" s="104" t="n"/>
-      <c r="R18" s="104" t="n"/>
-      <c r="S18" s="104" t="n"/>
-      <c r="T18" s="104" t="n"/>
-      <c r="U18" s="104" t="n"/>
-      <c r="V18" s="104" t="n"/>
-      <c r="W18" s="104" t="n"/>
-      <c r="X18" s="104" t="n"/>
-      <c r="Y18" s="104" t="n"/>
-      <c r="Z18" s="105" t="n"/>
-      <c r="AA18" s="79" t="inlineStr">
+      <c r="O18" s="59" t="n"/>
+      <c r="P18" s="59" t="n"/>
+      <c r="Q18" s="59" t="n"/>
+      <c r="R18" s="59" t="n"/>
+      <c r="S18" s="59" t="n"/>
+      <c r="T18" s="59" t="n"/>
+      <c r="U18" s="230" t="n"/>
+      <c r="V18" s="59" t="n"/>
+      <c r="W18" s="59" t="n"/>
+      <c r="X18" s="59" t="n"/>
+      <c r="Y18" s="59" t="n"/>
+      <c r="Z18" s="59" t="n"/>
+      <c r="AA18" s="233" t="inlineStr">
         <is>
           <t>Approved By</t>
         </is>
       </c>
-      <c r="AB18" s="104" t="n"/>
-      <c r="AC18" s="104" t="n"/>
-      <c r="AD18" s="104" t="n"/>
-      <c r="AE18" s="104" t="n"/>
-      <c r="AF18" s="104" t="n"/>
-      <c r="AG18" s="104" t="n"/>
-      <c r="AH18" s="104" t="n"/>
-      <c r="AI18" s="104" t="n"/>
-      <c r="AJ18" s="104" t="n"/>
-      <c r="AK18" s="104" t="n"/>
-      <c r="AL18" s="104" t="n"/>
-      <c r="AM18" s="104" t="n"/>
-      <c r="AN18" s="105" t="n"/>
+      <c r="AB18" s="230" t="n"/>
+      <c r="AC18" s="59" t="n"/>
+      <c r="AD18" s="59" t="n"/>
+      <c r="AE18" s="59" t="n"/>
+      <c r="AF18" s="59" t="n"/>
+      <c r="AG18" s="59" t="n"/>
+      <c r="AH18" s="59" t="n"/>
+      <c r="AI18" s="59" t="n"/>
+      <c r="AJ18" s="59" t="n"/>
+      <c r="AK18" s="59" t="n"/>
+      <c r="AL18" s="59" t="n"/>
+      <c r="AM18" s="59" t="n"/>
+      <c r="AN18" s="234" t="n"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="80" t="inlineStr">
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="147" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B19" s="81" t="n"/>
-      <c r="C19" s="81" t="n"/>
-      <c r="D19" s="81" t="n"/>
-      <c r="E19" s="81" t="n"/>
-      <c r="F19" s="81" t="n"/>
-      <c r="G19" s="81" t="n"/>
-      <c r="H19" s="81" t="n"/>
-      <c r="I19" s="81" t="n"/>
-      <c r="J19" s="81" t="n"/>
-      <c r="K19" s="81" t="n"/>
-      <c r="L19" s="81" t="n"/>
-      <c r="M19" s="111" t="n"/>
-      <c r="N19" s="80" t="inlineStr">
+      <c r="B19" s="227" t="n"/>
+      <c r="C19" s="227" t="n"/>
+      <c r="D19" s="227" t="n"/>
+      <c r="E19" s="227" t="n"/>
+      <c r="F19" s="227" t="n"/>
+      <c r="G19" s="227" t="n"/>
+      <c r="H19" s="228" t="n"/>
+      <c r="I19" s="227" t="n"/>
+      <c r="J19" s="227" t="n"/>
+      <c r="K19" s="227" t="n"/>
+      <c r="L19" s="227" t="n"/>
+      <c r="M19" s="227" t="n"/>
+      <c r="N19" s="148" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O19" s="81" t="n"/>
-      <c r="P19" s="81" t="n"/>
-      <c r="Q19" s="81" t="n"/>
-      <c r="R19" s="81" t="n"/>
-      <c r="S19" s="81" t="n"/>
-      <c r="T19" s="81" t="n"/>
-      <c r="U19" s="81" t="n"/>
-      <c r="V19" s="81" t="n"/>
-      <c r="W19" s="81" t="n"/>
-      <c r="X19" s="81" t="n"/>
-      <c r="Y19" s="81" t="n"/>
-      <c r="Z19" s="111" t="n"/>
-      <c r="AA19" s="80" t="inlineStr">
+      <c r="O19" s="227" t="n"/>
+      <c r="P19" s="227" t="n"/>
+      <c r="Q19" s="227" t="n"/>
+      <c r="R19" s="227" t="n"/>
+      <c r="S19" s="227" t="n"/>
+      <c r="T19" s="227" t="n"/>
+      <c r="U19" s="228" t="n"/>
+      <c r="V19" s="227" t="n"/>
+      <c r="W19" s="227" t="n"/>
+      <c r="X19" s="227" t="n"/>
+      <c r="Y19" s="227" t="n"/>
+      <c r="Z19" s="227" t="n"/>
+      <c r="AA19" s="148" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB19" s="81" t="n"/>
-      <c r="AC19" s="81" t="n"/>
-      <c r="AD19" s="81" t="n"/>
-      <c r="AE19" s="81" t="n"/>
-      <c r="AF19" s="81" t="n"/>
-      <c r="AG19" s="81" t="n"/>
-      <c r="AH19" s="81" t="n"/>
-      <c r="AI19" s="81" t="n"/>
-      <c r="AJ19" s="81" t="n"/>
-      <c r="AK19" s="81" t="n"/>
-      <c r="AL19" s="81" t="n"/>
-      <c r="AM19" s="81" t="n"/>
-      <c r="AN19" s="111" t="n"/>
+      <c r="AB19" s="228" t="n"/>
+      <c r="AC19" s="227" t="n"/>
+      <c r="AD19" s="227" t="n"/>
+      <c r="AE19" s="227" t="n"/>
+      <c r="AF19" s="227" t="n"/>
+      <c r="AG19" s="227" t="n"/>
+      <c r="AH19" s="227" t="n"/>
+      <c r="AI19" s="227" t="n"/>
+      <c r="AJ19" s="227" t="n"/>
+      <c r="AK19" s="227" t="n"/>
+      <c r="AL19" s="227" t="n"/>
+      <c r="AM19" s="227" t="n"/>
+      <c r="AN19" s="231" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="112" t="n"/>
-      <c r="B20" s="84" t="n"/>
-      <c r="C20" s="84" t="n"/>
-      <c r="D20" s="84" t="n"/>
-      <c r="E20" s="84" t="n"/>
-      <c r="F20" s="84" t="n"/>
-      <c r="G20" s="84" t="n"/>
-      <c r="H20" s="84" t="n"/>
-      <c r="I20" s="84" t="n"/>
-      <c r="J20" s="84" t="n"/>
-      <c r="K20" s="84" t="n"/>
-      <c r="L20" s="84" t="n"/>
-      <c r="M20" s="113" t="n"/>
-      <c r="N20" s="112" t="n"/>
-      <c r="O20" s="84" t="n"/>
-      <c r="P20" s="84" t="n"/>
-      <c r="Q20" s="84" t="n"/>
-      <c r="R20" s="84" t="n"/>
-      <c r="S20" s="84" t="n"/>
-      <c r="T20" s="84" t="n"/>
-      <c r="U20" s="84" t="n"/>
-      <c r="V20" s="84" t="n"/>
-      <c r="W20" s="84" t="n"/>
-      <c r="X20" s="84" t="n"/>
-      <c r="Y20" s="84" t="n"/>
-      <c r="Z20" s="113" t="n"/>
-      <c r="AA20" s="112" t="n"/>
-      <c r="AB20" s="84" t="n"/>
-      <c r="AC20" s="84" t="n"/>
-      <c r="AD20" s="84" t="n"/>
-      <c r="AE20" s="84" t="n"/>
-      <c r="AF20" s="84" t="n"/>
-      <c r="AG20" s="84" t="n"/>
-      <c r="AH20" s="84" t="n"/>
-      <c r="AI20" s="84" t="n"/>
-      <c r="AJ20" s="84" t="n"/>
-      <c r="AK20" s="84" t="n"/>
-      <c r="AL20" s="84" t="n"/>
-      <c r="AM20" s="84" t="n"/>
-      <c r="AN20" s="113" t="n"/>
+      <c r="A20" s="235" t="n"/>
+      <c r="B20" s="227" t="n"/>
+      <c r="C20" s="227" t="n"/>
+      <c r="D20" s="227" t="n"/>
+      <c r="E20" s="227" t="n"/>
+      <c r="F20" s="227" t="n"/>
+      <c r="G20" s="227" t="n"/>
+      <c r="H20" s="228" t="n"/>
+      <c r="I20" s="227" t="n"/>
+      <c r="J20" s="227" t="n"/>
+      <c r="K20" s="227" t="n"/>
+      <c r="L20" s="227" t="n"/>
+      <c r="M20" s="227" t="n"/>
+      <c r="N20" s="228" t="n"/>
+      <c r="O20" s="227" t="n"/>
+      <c r="P20" s="227" t="n"/>
+      <c r="Q20" s="227" t="n"/>
+      <c r="R20" s="227" t="n"/>
+      <c r="S20" s="227" t="n"/>
+      <c r="T20" s="227" t="n"/>
+      <c r="U20" s="228" t="n"/>
+      <c r="V20" s="227" t="n"/>
+      <c r="W20" s="227" t="n"/>
+      <c r="X20" s="227" t="n"/>
+      <c r="Y20" s="227" t="n"/>
+      <c r="Z20" s="227" t="n"/>
+      <c r="AA20" s="228" t="n"/>
+      <c r="AB20" s="228" t="n"/>
+      <c r="AC20" s="227" t="n"/>
+      <c r="AD20" s="227" t="n"/>
+      <c r="AE20" s="227" t="n"/>
+      <c r="AF20" s="227" t="n"/>
+      <c r="AG20" s="227" t="n"/>
+      <c r="AH20" s="227" t="n"/>
+      <c r="AI20" s="227" t="n"/>
+      <c r="AJ20" s="227" t="n"/>
+      <c r="AK20" s="227" t="n"/>
+      <c r="AL20" s="227" t="n"/>
+      <c r="AM20" s="227" t="n"/>
+      <c r="AN20" s="231" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="114" t="n"/>
-      <c r="B21" s="115" t="n"/>
-      <c r="C21" s="115" t="n"/>
-      <c r="D21" s="115" t="n"/>
-      <c r="E21" s="115" t="n"/>
-      <c r="F21" s="115" t="n"/>
-      <c r="G21" s="115" t="n"/>
-      <c r="H21" s="115" t="n"/>
-      <c r="I21" s="115" t="n"/>
-      <c r="J21" s="115" t="n"/>
-      <c r="K21" s="115" t="n"/>
-      <c r="L21" s="115" t="n"/>
-      <c r="M21" s="116" t="n"/>
-      <c r="N21" s="114" t="n"/>
-      <c r="O21" s="115" t="n"/>
-      <c r="P21" s="115" t="n"/>
-      <c r="Q21" s="115" t="n"/>
-      <c r="R21" s="115" t="n"/>
-      <c r="S21" s="115" t="n"/>
-      <c r="T21" s="115" t="n"/>
-      <c r="U21" s="115" t="n"/>
-      <c r="V21" s="115" t="n"/>
-      <c r="W21" s="115" t="n"/>
-      <c r="X21" s="115" t="n"/>
-      <c r="Y21" s="115" t="n"/>
-      <c r="Z21" s="116" t="n"/>
-      <c r="AA21" s="114" t="n"/>
-      <c r="AB21" s="115" t="n"/>
-      <c r="AC21" s="115" t="n"/>
-      <c r="AD21" s="115" t="n"/>
-      <c r="AE21" s="115" t="n"/>
-      <c r="AF21" s="115" t="n"/>
-      <c r="AG21" s="115" t="n"/>
-      <c r="AH21" s="115" t="n"/>
-      <c r="AI21" s="115" t="n"/>
-      <c r="AJ21" s="115" t="n"/>
-      <c r="AK21" s="115" t="n"/>
-      <c r="AL21" s="115" t="n"/>
-      <c r="AM21" s="115" t="n"/>
-      <c r="AN21" s="116" t="n"/>
+      <c r="A21" s="236" t="n"/>
+      <c r="B21" s="215" t="n"/>
+      <c r="C21" s="215" t="n"/>
+      <c r="D21" s="215" t="n"/>
+      <c r="E21" s="215" t="n"/>
+      <c r="F21" s="215" t="n"/>
+      <c r="G21" s="215" t="n"/>
+      <c r="H21" s="237" t="n"/>
+      <c r="I21" s="215" t="n"/>
+      <c r="J21" s="215" t="n"/>
+      <c r="K21" s="215" t="n"/>
+      <c r="L21" s="215" t="n"/>
+      <c r="M21" s="215" t="n"/>
+      <c r="N21" s="237" t="n"/>
+      <c r="O21" s="215" t="n"/>
+      <c r="P21" s="215" t="n"/>
+      <c r="Q21" s="215" t="n"/>
+      <c r="R21" s="215" t="n"/>
+      <c r="S21" s="215" t="n"/>
+      <c r="T21" s="215" t="n"/>
+      <c r="U21" s="237" t="n"/>
+      <c r="V21" s="215" t="n"/>
+      <c r="W21" s="215" t="n"/>
+      <c r="X21" s="215" t="n"/>
+      <c r="Y21" s="215" t="n"/>
+      <c r="Z21" s="215" t="n"/>
+      <c r="AA21" s="237" t="n"/>
+      <c r="AB21" s="237" t="n"/>
+      <c r="AC21" s="215" t="n"/>
+      <c r="AD21" s="215" t="n"/>
+      <c r="AE21" s="215" t="n"/>
+      <c r="AF21" s="215" t="n"/>
+      <c r="AG21" s="215" t="n"/>
+      <c r="AH21" s="215" t="n"/>
+      <c r="AI21" s="215" t="n"/>
+      <c r="AJ21" s="215" t="n"/>
+      <c r="AK21" s="215" t="n"/>
+      <c r="AL21" s="215" t="n"/>
+      <c r="AM21" s="215" t="n"/>
+      <c r="AN21" s="217" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="72" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLES</t>
         </is>
       </c>
-      <c r="B22" s="107" t="n"/>
-      <c r="C22" s="107" t="n"/>
-      <c r="D22" s="107" t="n"/>
-      <c r="E22" s="107" t="n"/>
-      <c r="F22" s="107" t="n"/>
-      <c r="G22" s="107" t="n"/>
-      <c r="H22" s="107" t="n"/>
-      <c r="I22" s="107" t="n"/>
-      <c r="J22" s="107" t="n"/>
-      <c r="K22" s="107" t="n"/>
-      <c r="L22" s="107" t="n"/>
-      <c r="M22" s="107" t="n"/>
-      <c r="N22" s="107" t="n"/>
-      <c r="O22" s="107" t="n"/>
-      <c r="P22" s="107" t="n"/>
-      <c r="Q22" s="107" t="n"/>
-      <c r="R22" s="107" t="n"/>
-      <c r="S22" s="107" t="n"/>
-      <c r="T22" s="107" t="n"/>
-      <c r="U22" s="107" t="n"/>
-      <c r="V22" s="107" t="n"/>
-      <c r="W22" s="107" t="n"/>
-      <c r="X22" s="107" t="n"/>
-      <c r="Y22" s="107" t="n"/>
-      <c r="Z22" s="107" t="n"/>
-      <c r="AA22" s="107" t="n"/>
-      <c r="AB22" s="107" t="n"/>
-      <c r="AC22" s="107" t="n"/>
-      <c r="AD22" s="107" t="n"/>
-      <c r="AE22" s="107" t="n"/>
-      <c r="AF22" s="107" t="n"/>
-      <c r="AG22" s="107" t="n"/>
-      <c r="AH22" s="107" t="n"/>
-      <c r="AI22" s="107" t="n"/>
-      <c r="AJ22" s="107" t="n"/>
-      <c r="AK22" s="107" t="n"/>
-      <c r="AL22" s="107" t="n"/>
-      <c r="AM22" s="107" t="n"/>
-      <c r="AN22" s="108" t="n"/>
+      <c r="B22" s="205" t="n"/>
+      <c r="C22" s="205" t="n"/>
+      <c r="D22" s="205" t="n"/>
+      <c r="E22" s="205" t="n"/>
+      <c r="F22" s="205" t="n"/>
+      <c r="G22" s="205" t="n"/>
+      <c r="H22" s="205" t="n"/>
+      <c r="I22" s="205" t="n"/>
+      <c r="J22" s="205" t="n"/>
+      <c r="K22" s="205" t="n"/>
+      <c r="L22" s="205" t="n"/>
+      <c r="M22" s="205" t="n"/>
+      <c r="N22" s="205" t="n"/>
+      <c r="O22" s="205" t="n"/>
+      <c r="P22" s="205" t="n"/>
+      <c r="Q22" s="205" t="n"/>
+      <c r="R22" s="205" t="n"/>
+      <c r="S22" s="205" t="n"/>
+      <c r="T22" s="205" t="n"/>
+      <c r="U22" s="205" t="n"/>
+      <c r="V22" s="205" t="n"/>
+      <c r="W22" s="205" t="n"/>
+      <c r="X22" s="205" t="n"/>
+      <c r="Y22" s="205" t="n"/>
+      <c r="Z22" s="205" t="n"/>
+      <c r="AA22" s="205" t="n"/>
+      <c r="AB22" s="205" t="n"/>
+      <c r="AC22" s="205" t="n"/>
+      <c r="AD22" s="205" t="n"/>
+      <c r="AE22" s="205" t="n"/>
+      <c r="AF22" s="205" t="n"/>
+      <c r="AG22" s="205" t="n"/>
+      <c r="AH22" s="205" t="n"/>
+      <c r="AI22" s="205" t="n"/>
+      <c r="AJ22" s="205" t="n"/>
+      <c r="AK22" s="205" t="n"/>
+      <c r="AL22" s="205" t="n"/>
+      <c r="AM22" s="205" t="n"/>
+      <c r="AN22" s="206" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="73" t="inlineStr">
+      <c r="A23" s="207" t="inlineStr">
         <is>
           <t>Support Sheet</t>
         </is>
       </c>
-      <c r="B23" s="107" t="n"/>
-      <c r="C23" s="107" t="n"/>
-      <c r="D23" s="107" t="n"/>
-      <c r="E23" s="107" t="n"/>
-      <c r="F23" s="107" t="n"/>
-      <c r="G23" s="108" t="n"/>
-      <c r="H23" s="76" t="n"/>
-      <c r="I23" s="109" t="n"/>
-      <c r="J23" s="109" t="n"/>
-      <c r="K23" s="109" t="n"/>
-      <c r="L23" s="109" t="n"/>
-      <c r="M23" s="109" t="n"/>
-      <c r="N23" s="109" t="n"/>
-      <c r="O23" s="109" t="n"/>
-      <c r="P23" s="109" t="n"/>
-      <c r="Q23" s="109" t="n"/>
-      <c r="R23" s="109" t="n"/>
-      <c r="S23" s="109" t="n"/>
-      <c r="T23" s="110" t="n"/>
-      <c r="U23" s="73" t="inlineStr">
+      <c r="B23" s="208" t="n"/>
+      <c r="C23" s="208" t="n"/>
+      <c r="D23" s="208" t="n"/>
+      <c r="E23" s="208" t="n"/>
+      <c r="F23" s="208" t="n"/>
+      <c r="G23" s="208" t="n"/>
+      <c r="H23" s="129" t="n"/>
+      <c r="I23" s="209" t="n"/>
+      <c r="J23" s="209" t="n"/>
+      <c r="K23" s="209" t="n"/>
+      <c r="L23" s="209" t="n"/>
+      <c r="M23" s="209" t="n"/>
+      <c r="N23" s="209" t="n"/>
+      <c r="O23" s="209" t="n"/>
+      <c r="P23" s="209" t="n"/>
+      <c r="Q23" s="209" t="n"/>
+      <c r="R23" s="209" t="n"/>
+      <c r="S23" s="209" t="n"/>
+      <c r="T23" s="209" t="n"/>
+      <c r="U23" s="210" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="V23" s="107" t="n"/>
-      <c r="W23" s="107" t="n"/>
-      <c r="X23" s="107" t="n"/>
-      <c r="Y23" s="107" t="n"/>
-      <c r="Z23" s="107" t="n"/>
-      <c r="AA23" s="108" t="n"/>
-      <c r="AB23" s="76" t="n"/>
-      <c r="AC23" s="109" t="n"/>
-      <c r="AD23" s="109" t="n"/>
-      <c r="AE23" s="109" t="n"/>
-      <c r="AF23" s="109" t="n"/>
-      <c r="AG23" s="109" t="n"/>
-      <c r="AH23" s="109" t="n"/>
-      <c r="AI23" s="109" t="n"/>
-      <c r="AJ23" s="109" t="n"/>
-      <c r="AK23" s="109" t="n"/>
-      <c r="AL23" s="109" t="n"/>
-      <c r="AM23" s="109" t="n"/>
-      <c r="AN23" s="110" t="n"/>
+      <c r="V23" s="208" t="n"/>
+      <c r="W23" s="208" t="n"/>
+      <c r="X23" s="208" t="n"/>
+      <c r="Y23" s="208" t="n"/>
+      <c r="Z23" s="208" t="n"/>
+      <c r="AA23" s="208" t="n"/>
+      <c r="AB23" s="129" t="n"/>
+      <c r="AC23" s="209" t="n"/>
+      <c r="AD23" s="209" t="n"/>
+      <c r="AE23" s="209" t="n"/>
+      <c r="AF23" s="209" t="n"/>
+      <c r="AG23" s="209" t="n"/>
+      <c r="AH23" s="209" t="n"/>
+      <c r="AI23" s="209" t="n"/>
+      <c r="AJ23" s="209" t="n"/>
+      <c r="AK23" s="209" t="n"/>
+      <c r="AL23" s="209" t="n"/>
+      <c r="AM23" s="209" t="n"/>
+      <c r="AN23" s="211" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="73" t="inlineStr">
+      <c r="A24" s="212" t="inlineStr">
         <is>
           <t>See workbook secondary sheet</t>
         </is>
       </c>
-      <c r="B24" s="107" t="n"/>
-      <c r="C24" s="107" t="n"/>
-      <c r="D24" s="107" t="n"/>
-      <c r="E24" s="107" t="n"/>
-      <c r="F24" s="107" t="n"/>
-      <c r="G24" s="108" t="n"/>
-      <c r="H24" s="76" t="n"/>
-      <c r="I24" s="109" t="n"/>
-      <c r="J24" s="109" t="n"/>
-      <c r="K24" s="109" t="n"/>
-      <c r="L24" s="109" t="n"/>
-      <c r="M24" s="109" t="n"/>
-      <c r="N24" s="109" t="n"/>
-      <c r="O24" s="109" t="n"/>
-      <c r="P24" s="109" t="n"/>
-      <c r="Q24" s="109" t="n"/>
-      <c r="R24" s="109" t="n"/>
-      <c r="S24" s="109" t="n"/>
-      <c r="T24" s="110" t="n"/>
-      <c r="U24" s="73" t="inlineStr">
+      <c r="B24" s="213" t="n"/>
+      <c r="C24" s="213" t="n"/>
+      <c r="D24" s="213" t="n"/>
+      <c r="E24" s="213" t="n"/>
+      <c r="F24" s="213" t="n"/>
+      <c r="G24" s="213" t="n"/>
+      <c r="H24" s="214" t="n"/>
+      <c r="I24" s="215" t="n"/>
+      <c r="J24" s="215" t="n"/>
+      <c r="K24" s="215" t="n"/>
+      <c r="L24" s="215" t="n"/>
+      <c r="M24" s="215" t="n"/>
+      <c r="N24" s="215" t="n"/>
+      <c r="O24" s="215" t="n"/>
+      <c r="P24" s="215" t="n"/>
+      <c r="Q24" s="215" t="n"/>
+      <c r="R24" s="215" t="n"/>
+      <c r="S24" s="215" t="n"/>
+      <c r="T24" s="215" t="n"/>
+      <c r="U24" s="216" t="inlineStr">
         <is>
           <t>Detailed actions / findings / decisions</t>
         </is>
       </c>
-      <c r="V24" s="107" t="n"/>
-      <c r="W24" s="107" t="n"/>
-      <c r="X24" s="107" t="n"/>
-      <c r="Y24" s="107" t="n"/>
-      <c r="Z24" s="107" t="n"/>
-      <c r="AA24" s="108" t="n"/>
-      <c r="AB24" s="76" t="n"/>
-      <c r="AC24" s="109" t="n"/>
-      <c r="AD24" s="109" t="n"/>
-      <c r="AE24" s="109" t="n"/>
-      <c r="AF24" s="109" t="n"/>
-      <c r="AG24" s="109" t="n"/>
-      <c r="AH24" s="109" t="n"/>
-      <c r="AI24" s="109" t="n"/>
-      <c r="AJ24" s="109" t="n"/>
-      <c r="AK24" s="109" t="n"/>
-      <c r="AL24" s="109" t="n"/>
-      <c r="AM24" s="109" t="n"/>
-      <c r="AN24" s="110" t="n"/>
+      <c r="V24" s="213" t="n"/>
+      <c r="W24" s="213" t="n"/>
+      <c r="X24" s="213" t="n"/>
+      <c r="Y24" s="213" t="n"/>
+      <c r="Z24" s="213" t="n"/>
+      <c r="AA24" s="213" t="n"/>
+      <c r="AB24" s="214" t="n"/>
+      <c r="AC24" s="215" t="n"/>
+      <c r="AD24" s="215" t="n"/>
+      <c r="AE24" s="215" t="n"/>
+      <c r="AF24" s="215" t="n"/>
+      <c r="AG24" s="215" t="n"/>
+      <c r="AH24" s="215" t="n"/>
+      <c r="AI24" s="215" t="n"/>
+      <c r="AJ24" s="215" t="n"/>
+      <c r="AK24" s="215" t="n"/>
+      <c r="AL24" s="215" t="n"/>
+      <c r="AM24" s="215" t="n"/>
+      <c r="AN24" s="217" t="n"/>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="89" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="204" t="inlineStr">
         <is>
           <t>NOTICE: Review access against least-privilege and segregation-of-duty expectations, close dormant or inappropriate access with owner and due date, and keep evidence linked to the reviewed system snapshot.</t>
         </is>
       </c>
-      <c r="B25" s="101" t="n"/>
-      <c r="C25" s="101" t="n"/>
-      <c r="D25" s="101" t="n"/>
-      <c r="E25" s="101" t="n"/>
-      <c r="F25" s="101" t="n"/>
-      <c r="G25" s="101" t="n"/>
-      <c r="H25" s="101" t="n"/>
-      <c r="I25" s="101" t="n"/>
-      <c r="J25" s="101" t="n"/>
-      <c r="K25" s="101" t="n"/>
-      <c r="L25" s="101" t="n"/>
-      <c r="M25" s="101" t="n"/>
-      <c r="N25" s="101" t="n"/>
-      <c r="O25" s="101" t="n"/>
-      <c r="P25" s="101" t="n"/>
-      <c r="Q25" s="101" t="n"/>
-      <c r="R25" s="101" t="n"/>
-      <c r="S25" s="101" t="n"/>
-      <c r="T25" s="101" t="n"/>
-      <c r="U25" s="101" t="n"/>
-      <c r="V25" s="101" t="n"/>
-      <c r="W25" s="101" t="n"/>
-      <c r="X25" s="101" t="n"/>
-      <c r="Y25" s="101" t="n"/>
-      <c r="Z25" s="101" t="n"/>
-      <c r="AA25" s="101" t="n"/>
-      <c r="AB25" s="101" t="n"/>
-      <c r="AC25" s="101" t="n"/>
-      <c r="AD25" s="101" t="n"/>
-      <c r="AE25" s="101" t="n"/>
-      <c r="AF25" s="101" t="n"/>
-      <c r="AG25" s="101" t="n"/>
-      <c r="AH25" s="101" t="n"/>
-      <c r="AI25" s="101" t="n"/>
-      <c r="AJ25" s="101" t="n"/>
-      <c r="AK25" s="101" t="n"/>
-      <c r="AL25" s="101" t="n"/>
-      <c r="AM25" s="101" t="n"/>
-      <c r="AN25" s="102" t="n"/>
+      <c r="B25" s="205" t="n"/>
+      <c r="C25" s="205" t="n"/>
+      <c r="D25" s="205" t="n"/>
+      <c r="E25" s="205" t="n"/>
+      <c r="F25" s="205" t="n"/>
+      <c r="G25" s="205" t="n"/>
+      <c r="H25" s="205" t="n"/>
+      <c r="I25" s="205" t="n"/>
+      <c r="J25" s="205" t="n"/>
+      <c r="K25" s="205" t="n"/>
+      <c r="L25" s="205" t="n"/>
+      <c r="M25" s="205" t="n"/>
+      <c r="N25" s="205" t="n"/>
+      <c r="O25" s="205" t="n"/>
+      <c r="P25" s="205" t="n"/>
+      <c r="Q25" s="205" t="n"/>
+      <c r="R25" s="205" t="n"/>
+      <c r="S25" s="205" t="n"/>
+      <c r="T25" s="205" t="n"/>
+      <c r="U25" s="205" t="n"/>
+      <c r="V25" s="205" t="n"/>
+      <c r="W25" s="205" t="n"/>
+      <c r="X25" s="205" t="n"/>
+      <c r="Y25" s="205" t="n"/>
+      <c r="Z25" s="205" t="n"/>
+      <c r="AA25" s="205" t="n"/>
+      <c r="AB25" s="205" t="n"/>
+      <c r="AC25" s="205" t="n"/>
+      <c r="AD25" s="205" t="n"/>
+      <c r="AE25" s="205" t="n"/>
+      <c r="AF25" s="205" t="n"/>
+      <c r="AG25" s="205" t="n"/>
+      <c r="AH25" s="205" t="n"/>
+      <c r="AI25" s="205" t="n"/>
+      <c r="AJ25" s="205" t="n"/>
+      <c r="AK25" s="205" t="n"/>
+      <c r="AL25" s="205" t="n"/>
+      <c r="AM25" s="205" t="n"/>
+      <c r="AN25" s="206" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="63">
+  <mergeCells count="62">
     <mergeCell ref="U24:AA24"/>
     <mergeCell ref="A12:AN12"/>
     <mergeCell ref="A17:G17"/>
@@ -2667,7 +3930,6 @@
     <mergeCell ref="H16:T16"/>
     <mergeCell ref="AB16:AN16"/>
     <mergeCell ref="U16:AA16"/>
-    <mergeCell ref="A6:AN6"/>
     <mergeCell ref="AA18:AN18"/>
     <mergeCell ref="N18:Z18"/>
     <mergeCell ref="AI1:AN1"/>
@@ -2710,6 +3972,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2781,1144 +4044,1234 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="55" t="n"/>
-      <c r="B1" s="120" t="n"/>
-      <c r="C1" s="120" t="n"/>
-      <c r="D1" s="120" t="n"/>
-      <c r="E1" s="120" t="n"/>
-      <c r="F1" s="120" t="n"/>
-      <c r="G1" s="120" t="n"/>
-      <c r="H1" s="120" t="n"/>
-      <c r="I1" s="120" t="n"/>
-      <c r="J1" s="120" t="n"/>
-      <c r="K1" s="120" t="n"/>
-      <c r="L1" s="57" t="inlineStr">
+      <c r="A1" s="165" t="n"/>
+      <c r="B1" s="166" t="n"/>
+      <c r="C1" s="166" t="n"/>
+      <c r="D1" s="166" t="n"/>
+      <c r="E1" s="166" t="n"/>
+      <c r="F1" s="166" t="n"/>
+      <c r="G1" s="166" t="n"/>
+      <c r="H1" s="166" t="n"/>
+      <c r="I1" s="166" t="n"/>
+      <c r="J1" s="166" t="n"/>
+      <c r="K1" s="167" t="n"/>
+      <c r="L1" s="168" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW — FINDINGS AND ACTIONS</t>
         </is>
       </c>
-      <c r="M1" s="120" t="n"/>
-      <c r="N1" s="120" t="n"/>
-      <c r="O1" s="120" t="n"/>
-      <c r="P1" s="120" t="n"/>
-      <c r="Q1" s="120" t="n"/>
-      <c r="R1" s="120" t="n"/>
-      <c r="S1" s="120" t="n"/>
-      <c r="T1" s="120" t="n"/>
-      <c r="U1" s="120" t="n"/>
-      <c r="V1" s="120" t="n"/>
-      <c r="W1" s="120" t="n"/>
-      <c r="X1" s="120" t="n"/>
-      <c r="Y1" s="120" t="n"/>
-      <c r="Z1" s="120" t="n"/>
-      <c r="AA1" s="120" t="n"/>
-      <c r="AB1" s="120" t="n"/>
-      <c r="AC1" s="120" t="n"/>
-      <c r="AD1" s="120" t="n"/>
-      <c r="AE1" s="120" t="n"/>
-      <c r="AF1" s="120" t="n"/>
-      <c r="AG1" s="120" t="n"/>
-      <c r="AH1" s="120" t="n"/>
-      <c r="AI1" s="120" t="n"/>
-      <c r="AJ1" s="120" t="n"/>
-      <c r="AK1" s="120" t="n"/>
-      <c r="AL1" s="120" t="n"/>
-      <c r="AM1" s="120" t="n"/>
-      <c r="AN1" s="120" t="n"/>
-      <c r="AO1" s="120" t="n"/>
-      <c r="AP1" s="120" t="n"/>
-      <c r="AQ1" s="58" t="inlineStr">
+      <c r="M1" s="169" t="n"/>
+      <c r="N1" s="169" t="n"/>
+      <c r="O1" s="169" t="n"/>
+      <c r="P1" s="169" t="n"/>
+      <c r="Q1" s="169" t="n"/>
+      <c r="R1" s="169" t="n"/>
+      <c r="S1" s="169" t="n"/>
+      <c r="T1" s="169" t="n"/>
+      <c r="U1" s="169" t="n"/>
+      <c r="V1" s="169" t="n"/>
+      <c r="W1" s="169" t="n"/>
+      <c r="X1" s="169" t="n"/>
+      <c r="Y1" s="169" t="n"/>
+      <c r="Z1" s="169" t="n"/>
+      <c r="AA1" s="169" t="n"/>
+      <c r="AB1" s="169" t="n"/>
+      <c r="AC1" s="169" t="n"/>
+      <c r="AD1" s="169" t="n"/>
+      <c r="AE1" s="169" t="n"/>
+      <c r="AF1" s="169" t="n"/>
+      <c r="AG1" s="169" t="n"/>
+      <c r="AH1" s="169" t="n"/>
+      <c r="AI1" s="169" t="n"/>
+      <c r="AJ1" s="169" t="n"/>
+      <c r="AK1" s="169" t="n"/>
+      <c r="AL1" s="169" t="n"/>
+      <c r="AM1" s="169" t="n"/>
+      <c r="AN1" s="169" t="n"/>
+      <c r="AO1" s="169" t="n"/>
+      <c r="AP1" s="170" t="n"/>
+      <c r="AQ1" s="171" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="121" t="n"/>
-      <c r="AS1" s="121" t="n"/>
-      <c r="AT1" s="121" t="n"/>
-      <c r="AU1" s="121" t="n"/>
-      <c r="AV1" s="122" t="n"/>
-      <c r="AW1" s="61" t="inlineStr">
+      <c r="AR1" s="172" t="n"/>
+      <c r="AS1" s="172" t="n"/>
+      <c r="AT1" s="172" t="n"/>
+      <c r="AU1" s="172" t="n"/>
+      <c r="AV1" s="173" t="n"/>
+      <c r="AW1" s="174" t="inlineStr">
         <is>
           <t>FRM-111</t>
         </is>
       </c>
-      <c r="AX1" s="121" t="n"/>
-      <c r="AY1" s="121" t="n"/>
-      <c r="AZ1" s="121" t="n"/>
-      <c r="BA1" s="121" t="n"/>
-      <c r="BB1" s="121" t="n"/>
-      <c r="BC1" s="121" t="n"/>
-      <c r="BD1" s="122" t="n"/>
+      <c r="AX1" s="175" t="n"/>
+      <c r="AY1" s="175" t="n"/>
+      <c r="AZ1" s="175" t="n"/>
+      <c r="BA1" s="175" t="n"/>
+      <c r="BB1" s="175" t="n"/>
+      <c r="BC1" s="175" t="n"/>
+      <c r="BD1" s="176" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="123" t="n"/>
-      <c r="L2" s="123" t="n"/>
-      <c r="AQ2" s="64" t="inlineStr">
+      <c r="A2" s="177" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="54" t="n"/>
+      <c r="J2" s="54" t="n"/>
+      <c r="K2" s="178" t="n"/>
+      <c r="L2" s="179" t="n"/>
+      <c r="M2" s="180" t="n"/>
+      <c r="N2" s="180" t="n"/>
+      <c r="O2" s="180" t="n"/>
+      <c r="P2" s="180" t="n"/>
+      <c r="Q2" s="180" t="n"/>
+      <c r="R2" s="180" t="n"/>
+      <c r="S2" s="180" t="n"/>
+      <c r="T2" s="180" t="n"/>
+      <c r="U2" s="180" t="n"/>
+      <c r="V2" s="180" t="n"/>
+      <c r="W2" s="180" t="n"/>
+      <c r="X2" s="180" t="n"/>
+      <c r="Y2" s="180" t="n"/>
+      <c r="Z2" s="180" t="n"/>
+      <c r="AA2" s="180" t="n"/>
+      <c r="AB2" s="180" t="n"/>
+      <c r="AC2" s="180" t="n"/>
+      <c r="AD2" s="180" t="n"/>
+      <c r="AE2" s="180" t="n"/>
+      <c r="AF2" s="180" t="n"/>
+      <c r="AG2" s="180" t="n"/>
+      <c r="AH2" s="180" t="n"/>
+      <c r="AI2" s="180" t="n"/>
+      <c r="AJ2" s="180" t="n"/>
+      <c r="AK2" s="180" t="n"/>
+      <c r="AL2" s="180" t="n"/>
+      <c r="AM2" s="180" t="n"/>
+      <c r="AN2" s="180" t="n"/>
+      <c r="AO2" s="180" t="n"/>
+      <c r="AP2" s="181" t="n"/>
+      <c r="AQ2" s="182" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="124" t="n"/>
-      <c r="AS2" s="124" t="n"/>
-      <c r="AT2" s="124" t="n"/>
-      <c r="AU2" s="124" t="n"/>
-      <c r="AV2" s="125" t="n"/>
-      <c r="AW2" s="67" t="inlineStr">
+      <c r="AR2" s="183" t="n"/>
+      <c r="AS2" s="183" t="n"/>
+      <c r="AT2" s="183" t="n"/>
+      <c r="AU2" s="183" t="n"/>
+      <c r="AV2" s="184" t="n"/>
+      <c r="AW2" s="185" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="124" t="n"/>
-      <c r="AY2" s="124" t="n"/>
-      <c r="AZ2" s="124" t="n"/>
-      <c r="BA2" s="124" t="n"/>
-      <c r="BB2" s="124" t="n"/>
-      <c r="BC2" s="124" t="n"/>
-      <c r="BD2" s="125" t="n"/>
+      <c r="AX2" s="186" t="n"/>
+      <c r="AY2" s="186" t="n"/>
+      <c r="AZ2" s="186" t="n"/>
+      <c r="BA2" s="186" t="n"/>
+      <c r="BB2" s="186" t="n"/>
+      <c r="BC2" s="186" t="n"/>
+      <c r="BD2" s="187" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="123" t="n"/>
-      <c r="L3" s="126" t="n"/>
-      <c r="M3" s="124" t="n"/>
-      <c r="N3" s="124" t="n"/>
-      <c r="O3" s="124" t="n"/>
-      <c r="P3" s="124" t="n"/>
-      <c r="Q3" s="124" t="n"/>
-      <c r="R3" s="124" t="n"/>
-      <c r="S3" s="124" t="n"/>
-      <c r="T3" s="124" t="n"/>
-      <c r="U3" s="124" t="n"/>
-      <c r="V3" s="124" t="n"/>
-      <c r="W3" s="124" t="n"/>
-      <c r="X3" s="124" t="n"/>
-      <c r="Y3" s="124" t="n"/>
-      <c r="Z3" s="124" t="n"/>
-      <c r="AA3" s="124" t="n"/>
-      <c r="AB3" s="124" t="n"/>
-      <c r="AC3" s="124" t="n"/>
-      <c r="AD3" s="124" t="n"/>
-      <c r="AE3" s="124" t="n"/>
-      <c r="AF3" s="124" t="n"/>
-      <c r="AG3" s="124" t="n"/>
-      <c r="AH3" s="124" t="n"/>
-      <c r="AI3" s="124" t="n"/>
-      <c r="AJ3" s="124" t="n"/>
-      <c r="AK3" s="124" t="n"/>
-      <c r="AL3" s="124" t="n"/>
-      <c r="AM3" s="124" t="n"/>
-      <c r="AN3" s="124" t="n"/>
-      <c r="AO3" s="124" t="n"/>
-      <c r="AP3" s="124" t="n"/>
-      <c r="AQ3" s="64" t="inlineStr">
+      <c r="A3" s="177" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="178" t="n"/>
+      <c r="L3" s="179" t="n"/>
+      <c r="M3" s="180" t="n"/>
+      <c r="N3" s="180" t="n"/>
+      <c r="O3" s="180" t="n"/>
+      <c r="P3" s="180" t="n"/>
+      <c r="Q3" s="180" t="n"/>
+      <c r="R3" s="180" t="n"/>
+      <c r="S3" s="180" t="n"/>
+      <c r="T3" s="180" t="n"/>
+      <c r="U3" s="180" t="n"/>
+      <c r="V3" s="180" t="n"/>
+      <c r="W3" s="180" t="n"/>
+      <c r="X3" s="180" t="n"/>
+      <c r="Y3" s="180" t="n"/>
+      <c r="Z3" s="180" t="n"/>
+      <c r="AA3" s="180" t="n"/>
+      <c r="AB3" s="180" t="n"/>
+      <c r="AC3" s="180" t="n"/>
+      <c r="AD3" s="180" t="n"/>
+      <c r="AE3" s="180" t="n"/>
+      <c r="AF3" s="180" t="n"/>
+      <c r="AG3" s="180" t="n"/>
+      <c r="AH3" s="180" t="n"/>
+      <c r="AI3" s="180" t="n"/>
+      <c r="AJ3" s="180" t="n"/>
+      <c r="AK3" s="180" t="n"/>
+      <c r="AL3" s="180" t="n"/>
+      <c r="AM3" s="180" t="n"/>
+      <c r="AN3" s="180" t="n"/>
+      <c r="AO3" s="180" t="n"/>
+      <c r="AP3" s="181" t="n"/>
+      <c r="AQ3" s="182" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="124" t="n"/>
-      <c r="AS3" s="124" t="n"/>
-      <c r="AT3" s="124" t="n"/>
-      <c r="AU3" s="124" t="n"/>
-      <c r="AV3" s="125" t="n"/>
-      <c r="AW3" s="67" t="inlineStr">
+      <c r="AR3" s="183" t="n"/>
+      <c r="AS3" s="183" t="n"/>
+      <c r="AT3" s="183" t="n"/>
+      <c r="AU3" s="183" t="n"/>
+      <c r="AV3" s="184" t="n"/>
+      <c r="AW3" s="185" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="124" t="n"/>
-      <c r="AY3" s="124" t="n"/>
-      <c r="AZ3" s="124" t="n"/>
-      <c r="BA3" s="124" t="n"/>
-      <c r="BB3" s="124" t="n"/>
-      <c r="BC3" s="124" t="n"/>
-      <c r="BD3" s="125" t="n"/>
+      <c r="AX3" s="186" t="n"/>
+      <c r="AY3" s="186" t="n"/>
+      <c r="AZ3" s="186" t="n"/>
+      <c r="BA3" s="186" t="n"/>
+      <c r="BB3" s="186" t="n"/>
+      <c r="BC3" s="186" t="n"/>
+      <c r="BD3" s="187" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="123" t="n"/>
-      <c r="L4" s="69" t="inlineStr">
+      <c r="A4" s="177" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="178" t="n"/>
+      <c r="L4" s="188" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="64" t="inlineStr">
+      <c r="M4" s="189" t="n"/>
+      <c r="N4" s="189" t="n"/>
+      <c r="O4" s="189" t="n"/>
+      <c r="P4" s="189" t="n"/>
+      <c r="Q4" s="189" t="n"/>
+      <c r="R4" s="189" t="n"/>
+      <c r="S4" s="189" t="n"/>
+      <c r="T4" s="189" t="n"/>
+      <c r="U4" s="189" t="n"/>
+      <c r="V4" s="189" t="n"/>
+      <c r="W4" s="189" t="n"/>
+      <c r="X4" s="189" t="n"/>
+      <c r="Y4" s="189" t="n"/>
+      <c r="Z4" s="189" t="n"/>
+      <c r="AA4" s="189" t="n"/>
+      <c r="AB4" s="189" t="n"/>
+      <c r="AC4" s="189" t="n"/>
+      <c r="AD4" s="189" t="n"/>
+      <c r="AE4" s="189" t="n"/>
+      <c r="AF4" s="189" t="n"/>
+      <c r="AG4" s="189" t="n"/>
+      <c r="AH4" s="189" t="n"/>
+      <c r="AI4" s="189" t="n"/>
+      <c r="AJ4" s="189" t="n"/>
+      <c r="AK4" s="189" t="n"/>
+      <c r="AL4" s="189" t="n"/>
+      <c r="AM4" s="189" t="n"/>
+      <c r="AN4" s="189" t="n"/>
+      <c r="AO4" s="189" t="n"/>
+      <c r="AP4" s="190" t="n"/>
+      <c r="AQ4" s="182" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="124" t="n"/>
-      <c r="AS4" s="124" t="n"/>
-      <c r="AT4" s="124" t="n"/>
-      <c r="AU4" s="124" t="n"/>
-      <c r="AV4" s="125" t="n"/>
-      <c r="AW4" s="67" t="inlineStr">
+      <c r="AR4" s="183" t="n"/>
+      <c r="AS4" s="183" t="n"/>
+      <c r="AT4" s="183" t="n"/>
+      <c r="AU4" s="183" t="n"/>
+      <c r="AV4" s="184" t="n"/>
+      <c r="AW4" s="185" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AX4" s="124" t="n"/>
-      <c r="AY4" s="124" t="n"/>
-      <c r="AZ4" s="124" t="n"/>
-      <c r="BA4" s="124" t="n"/>
-      <c r="BB4" s="124" t="n"/>
-      <c r="BC4" s="124" t="n"/>
-      <c r="BD4" s="125" t="n"/>
+      <c r="AX4" s="186" t="n"/>
+      <c r="AY4" s="186" t="n"/>
+      <c r="AZ4" s="186" t="n"/>
+      <c r="BA4" s="186" t="n"/>
+      <c r="BB4" s="186" t="n"/>
+      <c r="BC4" s="186" t="n"/>
+      <c r="BD4" s="187" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="126" t="n"/>
-      <c r="B5" s="124" t="n"/>
-      <c r="C5" s="124" t="n"/>
-      <c r="D5" s="124" t="n"/>
-      <c r="E5" s="124" t="n"/>
-      <c r="F5" s="124" t="n"/>
-      <c r="G5" s="124" t="n"/>
-      <c r="H5" s="124" t="n"/>
-      <c r="I5" s="124" t="n"/>
-      <c r="J5" s="124" t="n"/>
-      <c r="K5" s="124" t="n"/>
-      <c r="L5" s="70" t="inlineStr">
+      <c r="A5" s="191" t="n"/>
+      <c r="B5" s="192" t="n"/>
+      <c r="C5" s="192" t="n"/>
+      <c r="D5" s="192" t="n"/>
+      <c r="E5" s="192" t="n"/>
+      <c r="F5" s="192" t="n"/>
+      <c r="G5" s="192" t="n"/>
+      <c r="H5" s="192" t="n"/>
+      <c r="I5" s="192" t="n"/>
+      <c r="J5" s="192" t="n"/>
+      <c r="K5" s="193" t="n"/>
+      <c r="L5" s="194" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="124" t="n"/>
-      <c r="N5" s="124" t="n"/>
-      <c r="O5" s="124" t="n"/>
-      <c r="P5" s="124" t="n"/>
-      <c r="Q5" s="124" t="n"/>
-      <c r="R5" s="124" t="n"/>
-      <c r="S5" s="124" t="n"/>
-      <c r="T5" s="124" t="n"/>
-      <c r="U5" s="124" t="n"/>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
-      <c r="X5" s="124" t="n"/>
-      <c r="Y5" s="124" t="n"/>
-      <c r="Z5" s="124" t="n"/>
-      <c r="AA5" s="124" t="n"/>
-      <c r="AB5" s="124" t="n"/>
-      <c r="AC5" s="124" t="n"/>
-      <c r="AD5" s="124" t="n"/>
-      <c r="AE5" s="124" t="n"/>
-      <c r="AF5" s="124" t="n"/>
-      <c r="AG5" s="124" t="n"/>
-      <c r="AH5" s="124" t="n"/>
-      <c r="AI5" s="124" t="n"/>
-      <c r="AJ5" s="124" t="n"/>
-      <c r="AK5" s="124" t="n"/>
-      <c r="AL5" s="124" t="n"/>
-      <c r="AM5" s="124" t="n"/>
-      <c r="AN5" s="124" t="n"/>
-      <c r="AO5" s="124" t="n"/>
-      <c r="AP5" s="124" t="n"/>
-      <c r="AQ5" s="64" t="inlineStr">
+      <c r="M5" s="195" t="n"/>
+      <c r="N5" s="195" t="n"/>
+      <c r="O5" s="195" t="n"/>
+      <c r="P5" s="195" t="n"/>
+      <c r="Q5" s="195" t="n"/>
+      <c r="R5" s="195" t="n"/>
+      <c r="S5" s="195" t="n"/>
+      <c r="T5" s="195" t="n"/>
+      <c r="U5" s="195" t="n"/>
+      <c r="V5" s="195" t="n"/>
+      <c r="W5" s="195" t="n"/>
+      <c r="X5" s="195" t="n"/>
+      <c r="Y5" s="195" t="n"/>
+      <c r="Z5" s="195" t="n"/>
+      <c r="AA5" s="195" t="n"/>
+      <c r="AB5" s="195" t="n"/>
+      <c r="AC5" s="195" t="n"/>
+      <c r="AD5" s="195" t="n"/>
+      <c r="AE5" s="195" t="n"/>
+      <c r="AF5" s="195" t="n"/>
+      <c r="AG5" s="195" t="n"/>
+      <c r="AH5" s="195" t="n"/>
+      <c r="AI5" s="195" t="n"/>
+      <c r="AJ5" s="195" t="n"/>
+      <c r="AK5" s="195" t="n"/>
+      <c r="AL5" s="195" t="n"/>
+      <c r="AM5" s="195" t="n"/>
+      <c r="AN5" s="195" t="n"/>
+      <c r="AO5" s="195" t="n"/>
+      <c r="AP5" s="196" t="n"/>
+      <c r="AQ5" s="197" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="124" t="n"/>
-      <c r="AS5" s="124" t="n"/>
-      <c r="AT5" s="124" t="n"/>
-      <c r="AU5" s="124" t="n"/>
-      <c r="AV5" s="125" t="n"/>
-      <c r="AW5" s="67" t="inlineStr">
+      <c r="AR5" s="198" t="n"/>
+      <c r="AS5" s="198" t="n"/>
+      <c r="AT5" s="198" t="n"/>
+      <c r="AU5" s="198" t="n"/>
+      <c r="AV5" s="199" t="n"/>
+      <c r="AW5" s="200" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="124" t="n"/>
-      <c r="AY5" s="124" t="n"/>
-      <c r="AZ5" s="124" t="n"/>
-      <c r="BA5" s="124" t="n"/>
-      <c r="BB5" s="124" t="n"/>
-      <c r="BC5" s="124" t="n"/>
-      <c r="BD5" s="125" t="n"/>
+      <c r="AX5" s="201" t="n"/>
+      <c r="AY5" s="201" t="n"/>
+      <c r="AZ5" s="201" t="n"/>
+      <c r="BA5" s="201" t="n"/>
+      <c r="BB5" s="201" t="n"/>
+      <c r="BC5" s="201" t="n"/>
+      <c r="BD5" s="202" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="71" t="n"/>
-      <c r="B6" s="119" t="n"/>
-      <c r="C6" s="119" t="n"/>
-      <c r="D6" s="119" t="n"/>
-      <c r="E6" s="119" t="n"/>
-      <c r="F6" s="119" t="n"/>
-      <c r="G6" s="119" t="n"/>
-      <c r="H6" s="119" t="n"/>
-      <c r="I6" s="119" t="n"/>
-      <c r="J6" s="119" t="n"/>
-      <c r="K6" s="119" t="n"/>
-      <c r="L6" s="119" t="n"/>
-      <c r="M6" s="119" t="n"/>
-      <c r="N6" s="119" t="n"/>
-      <c r="O6" s="119" t="n"/>
-      <c r="P6" s="119" t="n"/>
-      <c r="Q6" s="119" t="n"/>
-      <c r="R6" s="119" t="n"/>
-      <c r="S6" s="119" t="n"/>
-      <c r="T6" s="119" t="n"/>
-      <c r="U6" s="119" t="n"/>
-      <c r="V6" s="119" t="n"/>
-      <c r="W6" s="119" t="n"/>
-      <c r="X6" s="119" t="n"/>
-      <c r="Y6" s="119" t="n"/>
-      <c r="Z6" s="119" t="n"/>
-      <c r="AA6" s="119" t="n"/>
-      <c r="AB6" s="119" t="n"/>
-      <c r="AC6" s="119" t="n"/>
-      <c r="AD6" s="119" t="n"/>
-      <c r="AE6" s="119" t="n"/>
-      <c r="AF6" s="119" t="n"/>
-      <c r="AG6" s="119" t="n"/>
-      <c r="AH6" s="119" t="n"/>
-      <c r="AI6" s="119" t="n"/>
-      <c r="AJ6" s="119" t="n"/>
-      <c r="AK6" s="119" t="n"/>
-      <c r="AL6" s="119" t="n"/>
-      <c r="AM6" s="119" t="n"/>
-      <c r="AN6" s="119" t="n"/>
-      <c r="AO6" s="119" t="n"/>
-      <c r="AP6" s="119" t="n"/>
-      <c r="AQ6" s="119" t="n"/>
-      <c r="AR6" s="119" t="n"/>
-      <c r="AS6" s="119" t="n"/>
-      <c r="AT6" s="119" t="n"/>
-      <c r="AU6" s="119" t="n"/>
-      <c r="AV6" s="119" t="n"/>
-      <c r="AW6" s="119" t="n"/>
-      <c r="AX6" s="119" t="n"/>
-      <c r="AY6" s="119" t="n"/>
-      <c r="AZ6" s="119" t="n"/>
-      <c r="BA6" s="119" t="n"/>
-      <c r="BB6" s="119" t="n"/>
-      <c r="BC6" s="119" t="n"/>
-      <c r="BD6" s="119" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="203" t="n"/>
+      <c r="B6" s="203" t="n"/>
+      <c r="C6" s="203" t="n"/>
+      <c r="D6" s="203" t="n"/>
+      <c r="E6" s="203" t="n"/>
+      <c r="F6" s="203" t="n"/>
+      <c r="G6" s="203" t="n"/>
+      <c r="H6" s="203" t="n"/>
+      <c r="I6" s="203" t="n"/>
+      <c r="J6" s="203" t="n"/>
+      <c r="K6" s="203" t="n"/>
+      <c r="L6" s="203" t="n"/>
+      <c r="M6" s="203" t="n"/>
+      <c r="N6" s="203" t="n"/>
+      <c r="O6" s="203" t="n"/>
+      <c r="P6" s="203" t="n"/>
+      <c r="Q6" s="203" t="n"/>
+      <c r="R6" s="203" t="n"/>
+      <c r="S6" s="203" t="n"/>
+      <c r="T6" s="203" t="n"/>
+      <c r="U6" s="203" t="n"/>
+      <c r="V6" s="203" t="n"/>
+      <c r="W6" s="203" t="n"/>
+      <c r="X6" s="203" t="n"/>
+      <c r="Y6" s="203" t="n"/>
+      <c r="Z6" s="203" t="n"/>
+      <c r="AA6" s="203" t="n"/>
+      <c r="AB6" s="203" t="n"/>
+      <c r="AC6" s="203" t="n"/>
+      <c r="AD6" s="203" t="n"/>
+      <c r="AE6" s="203" t="n"/>
+      <c r="AF6" s="203" t="n"/>
+      <c r="AG6" s="203" t="n"/>
+      <c r="AH6" s="203" t="n"/>
+      <c r="AI6" s="203" t="n"/>
+      <c r="AJ6" s="203" t="n"/>
+      <c r="AK6" s="203" t="n"/>
+      <c r="AL6" s="203" t="n"/>
+      <c r="AM6" s="203" t="n"/>
+      <c r="AN6" s="203" t="n"/>
+      <c r="AO6" s="203" t="n"/>
+      <c r="AP6" s="203" t="n"/>
+      <c r="AQ6" s="203" t="n"/>
+      <c r="AR6" s="203" t="n"/>
+      <c r="AS6" s="203" t="n"/>
+      <c r="AT6" s="203" t="n"/>
+      <c r="AU6" s="203" t="n"/>
+      <c r="AV6" s="203" t="n"/>
+      <c r="AW6" s="203" t="n"/>
+      <c r="AX6" s="203" t="n"/>
+      <c r="AY6" s="203" t="n"/>
+      <c r="AZ6" s="203" t="n"/>
+      <c r="BA6" s="203" t="n"/>
+      <c r="BB6" s="203" t="n"/>
+      <c r="BC6" s="203" t="n"/>
+      <c r="BD6" s="203" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="72" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="121" t="n"/>
-      <c r="C7" s="121" t="n"/>
-      <c r="D7" s="121" t="n"/>
-      <c r="E7" s="121" t="n"/>
-      <c r="F7" s="121" t="n"/>
-      <c r="G7" s="121" t="n"/>
-      <c r="H7" s="121" t="n"/>
-      <c r="I7" s="121" t="n"/>
-      <c r="J7" s="121" t="n"/>
-      <c r="K7" s="121" t="n"/>
-      <c r="L7" s="121" t="n"/>
-      <c r="M7" s="121" t="n"/>
-      <c r="N7" s="121" t="n"/>
-      <c r="O7" s="121" t="n"/>
-      <c r="P7" s="121" t="n"/>
-      <c r="Q7" s="121" t="n"/>
-      <c r="R7" s="121" t="n"/>
-      <c r="S7" s="121" t="n"/>
-      <c r="T7" s="121" t="n"/>
-      <c r="U7" s="121" t="n"/>
-      <c r="V7" s="121" t="n"/>
-      <c r="W7" s="121" t="n"/>
-      <c r="X7" s="121" t="n"/>
-      <c r="Y7" s="121" t="n"/>
-      <c r="Z7" s="121" t="n"/>
-      <c r="AA7" s="121" t="n"/>
-      <c r="AB7" s="121" t="n"/>
-      <c r="AC7" s="121" t="n"/>
-      <c r="AD7" s="121" t="n"/>
-      <c r="AE7" s="121" t="n"/>
-      <c r="AF7" s="121" t="n"/>
-      <c r="AG7" s="121" t="n"/>
-      <c r="AH7" s="121" t="n"/>
-      <c r="AI7" s="121" t="n"/>
-      <c r="AJ7" s="121" t="n"/>
-      <c r="AK7" s="121" t="n"/>
-      <c r="AL7" s="121" t="n"/>
-      <c r="AM7" s="121" t="n"/>
-      <c r="AN7" s="121" t="n"/>
-      <c r="AO7" s="121" t="n"/>
-      <c r="AP7" s="121" t="n"/>
-      <c r="AQ7" s="121" t="n"/>
-      <c r="AR7" s="121" t="n"/>
-      <c r="AS7" s="121" t="n"/>
-      <c r="AT7" s="121" t="n"/>
-      <c r="AU7" s="121" t="n"/>
-      <c r="AV7" s="121" t="n"/>
-      <c r="AW7" s="121" t="n"/>
-      <c r="AX7" s="121" t="n"/>
-      <c r="AY7" s="121" t="n"/>
-      <c r="AZ7" s="121" t="n"/>
-      <c r="BA7" s="121" t="n"/>
-      <c r="BB7" s="121" t="n"/>
-      <c r="BC7" s="121" t="n"/>
-      <c r="BD7" s="122" t="n"/>
+      <c r="B7" s="205" t="n"/>
+      <c r="C7" s="205" t="n"/>
+      <c r="D7" s="205" t="n"/>
+      <c r="E7" s="205" t="n"/>
+      <c r="F7" s="205" t="n"/>
+      <c r="G7" s="205" t="n"/>
+      <c r="H7" s="205" t="n"/>
+      <c r="I7" s="205" t="n"/>
+      <c r="J7" s="205" t="n"/>
+      <c r="K7" s="205" t="n"/>
+      <c r="L7" s="205" t="n"/>
+      <c r="M7" s="205" t="n"/>
+      <c r="N7" s="205" t="n"/>
+      <c r="O7" s="205" t="n"/>
+      <c r="P7" s="205" t="n"/>
+      <c r="Q7" s="205" t="n"/>
+      <c r="R7" s="205" t="n"/>
+      <c r="S7" s="205" t="n"/>
+      <c r="T7" s="205" t="n"/>
+      <c r="U7" s="205" t="n"/>
+      <c r="V7" s="205" t="n"/>
+      <c r="W7" s="205" t="n"/>
+      <c r="X7" s="205" t="n"/>
+      <c r="Y7" s="205" t="n"/>
+      <c r="Z7" s="205" t="n"/>
+      <c r="AA7" s="205" t="n"/>
+      <c r="AB7" s="205" t="n"/>
+      <c r="AC7" s="205" t="n"/>
+      <c r="AD7" s="205" t="n"/>
+      <c r="AE7" s="205" t="n"/>
+      <c r="AF7" s="205" t="n"/>
+      <c r="AG7" s="205" t="n"/>
+      <c r="AH7" s="205" t="n"/>
+      <c r="AI7" s="205" t="n"/>
+      <c r="AJ7" s="205" t="n"/>
+      <c r="AK7" s="205" t="n"/>
+      <c r="AL7" s="205" t="n"/>
+      <c r="AM7" s="205" t="n"/>
+      <c r="AN7" s="205" t="n"/>
+      <c r="AO7" s="205" t="n"/>
+      <c r="AP7" s="205" t="n"/>
+      <c r="AQ7" s="205" t="n"/>
+      <c r="AR7" s="205" t="n"/>
+      <c r="AS7" s="205" t="n"/>
+      <c r="AT7" s="205" t="n"/>
+      <c r="AU7" s="205" t="n"/>
+      <c r="AV7" s="205" t="n"/>
+      <c r="AW7" s="205" t="n"/>
+      <c r="AX7" s="205" t="n"/>
+      <c r="AY7" s="205" t="n"/>
+      <c r="AZ7" s="205" t="n"/>
+      <c r="BA7" s="205" t="n"/>
+      <c r="BB7" s="205" t="n"/>
+      <c r="BC7" s="205" t="n"/>
+      <c r="BD7" s="206" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="207" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="107" t="n"/>
-      <c r="C8" s="107" t="n"/>
-      <c r="D8" s="107" t="n"/>
-      <c r="E8" s="107" t="n"/>
-      <c r="F8" s="107" t="n"/>
-      <c r="G8" s="107" t="n"/>
-      <c r="H8" s="107" t="n"/>
-      <c r="I8" s="107" t="n"/>
-      <c r="J8" s="108" t="n"/>
-      <c r="K8" s="90" t="inlineStr">
+      <c r="B8" s="208" t="n"/>
+      <c r="C8" s="208" t="n"/>
+      <c r="D8" s="208" t="n"/>
+      <c r="E8" s="208" t="n"/>
+      <c r="F8" s="208" t="n"/>
+      <c r="G8" s="208" t="n"/>
+      <c r="H8" s="208" t="n"/>
+      <c r="I8" s="208" t="n"/>
+      <c r="J8" s="208" t="n"/>
+      <c r="K8" s="154" t="inlineStr">
         <is>
           <t>SOP: SOP-104 | ANNEX: ANNEX-QMS-005, ANNEX-QMS-006, ANNEX-QMS-012, ANNEX-QMS-019, ANNEX-QMS-021, ANNEX-IT-001, ANNEX-IT-002</t>
         </is>
       </c>
-      <c r="L8" s="107" t="n"/>
-      <c r="M8" s="107" t="n"/>
-      <c r="N8" s="107" t="n"/>
-      <c r="O8" s="107" t="n"/>
-      <c r="P8" s="107" t="n"/>
-      <c r="Q8" s="107" t="n"/>
-      <c r="R8" s="107" t="n"/>
-      <c r="S8" s="107" t="n"/>
-      <c r="T8" s="107" t="n"/>
-      <c r="U8" s="107" t="n"/>
-      <c r="V8" s="107" t="n"/>
-      <c r="W8" s="107" t="n"/>
-      <c r="X8" s="107" t="n"/>
-      <c r="Y8" s="107" t="n"/>
-      <c r="Z8" s="107" t="n"/>
-      <c r="AA8" s="107" t="n"/>
-      <c r="AB8" s="108" t="n"/>
-      <c r="AC8" s="20" t="inlineStr"/>
-      <c r="AD8" s="91" t="n"/>
-      <c r="AE8" s="91" t="n"/>
-      <c r="AF8" s="91" t="n"/>
-      <c r="AG8" s="91" t="n"/>
-      <c r="AH8" s="91" t="n"/>
-      <c r="AI8" s="91" t="n"/>
-      <c r="AJ8" s="91" t="n"/>
-      <c r="AK8" s="91" t="n"/>
-      <c r="AL8" s="91" t="n"/>
-      <c r="AM8" s="20" t="inlineStr"/>
-      <c r="AN8" s="91" t="n"/>
-      <c r="AO8" s="91" t="n"/>
-      <c r="AP8" s="91" t="n"/>
-      <c r="AQ8" s="91" t="n"/>
-      <c r="AR8" s="91" t="n"/>
-      <c r="AS8" s="91" t="n"/>
-      <c r="AT8" s="91" t="n"/>
-      <c r="AU8" s="91" t="n"/>
-      <c r="AV8" s="91" t="n"/>
-      <c r="AW8" s="91" t="n"/>
-      <c r="AX8" s="91" t="n"/>
-      <c r="AY8" s="91" t="n"/>
-      <c r="AZ8" s="91" t="n"/>
-      <c r="BA8" s="91" t="n"/>
-      <c r="BB8" s="91" t="n"/>
-      <c r="BC8" s="91" t="n"/>
-      <c r="BD8" s="91" t="n"/>
+      <c r="L8" s="208" t="n"/>
+      <c r="M8" s="208" t="n"/>
+      <c r="N8" s="208" t="n"/>
+      <c r="O8" s="208" t="n"/>
+      <c r="P8" s="208" t="n"/>
+      <c r="Q8" s="208" t="n"/>
+      <c r="R8" s="208" t="n"/>
+      <c r="S8" s="208" t="n"/>
+      <c r="T8" s="208" t="n"/>
+      <c r="U8" s="208" t="n"/>
+      <c r="V8" s="208" t="n"/>
+      <c r="W8" s="208" t="n"/>
+      <c r="X8" s="208" t="n"/>
+      <c r="Y8" s="208" t="n"/>
+      <c r="Z8" s="208" t="n"/>
+      <c r="AA8" s="208" t="n"/>
+      <c r="AB8" s="208" t="n"/>
+      <c r="AC8" s="155" t="inlineStr"/>
+      <c r="AD8" s="208" t="n"/>
+      <c r="AE8" s="208" t="n"/>
+      <c r="AF8" s="208" t="n"/>
+      <c r="AG8" s="208" t="n"/>
+      <c r="AH8" s="208" t="n"/>
+      <c r="AI8" s="208" t="n"/>
+      <c r="AJ8" s="208" t="n"/>
+      <c r="AK8" s="208" t="n"/>
+      <c r="AL8" s="208" t="n"/>
+      <c r="AM8" s="155" t="inlineStr"/>
+      <c r="AN8" s="208" t="n"/>
+      <c r="AO8" s="208" t="n"/>
+      <c r="AP8" s="208" t="n"/>
+      <c r="AQ8" s="208" t="n"/>
+      <c r="AR8" s="208" t="n"/>
+      <c r="AS8" s="208" t="n"/>
+      <c r="AT8" s="208" t="n"/>
+      <c r="AU8" s="208" t="n"/>
+      <c r="AV8" s="208" t="n"/>
+      <c r="AW8" s="208" t="n"/>
+      <c r="AX8" s="208" t="n"/>
+      <c r="AY8" s="208" t="n"/>
+      <c r="AZ8" s="208" t="n"/>
+      <c r="BA8" s="208" t="n"/>
+      <c r="BB8" s="208" t="n"/>
+      <c r="BC8" s="208" t="n"/>
+      <c r="BD8" s="238" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="226" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="107" t="n"/>
-      <c r="C9" s="107" t="n"/>
-      <c r="D9" s="107" t="n"/>
-      <c r="E9" s="107" t="n"/>
-      <c r="F9" s="107" t="n"/>
-      <c r="G9" s="107" t="n"/>
-      <c r="H9" s="107" t="n"/>
-      <c r="I9" s="107" t="n"/>
-      <c r="J9" s="108" t="n"/>
-      <c r="K9" s="90" t="inlineStr">
+      <c r="B9" s="59" t="n"/>
+      <c r="C9" s="59" t="n"/>
+      <c r="D9" s="59" t="n"/>
+      <c r="E9" s="59" t="n"/>
+      <c r="F9" s="59" t="n"/>
+      <c r="G9" s="59" t="n"/>
+      <c r="H9" s="59" t="n"/>
+      <c r="I9" s="59" t="n"/>
+      <c r="J9" s="59" t="n"/>
+      <c r="K9" s="157" t="inlineStr">
         <is>
           <t>Detailed finding / action sheet linked from the primary gate page.</t>
         </is>
       </c>
-      <c r="L9" s="107" t="n"/>
-      <c r="M9" s="107" t="n"/>
-      <c r="N9" s="107" t="n"/>
-      <c r="O9" s="107" t="n"/>
-      <c r="P9" s="107" t="n"/>
-      <c r="Q9" s="107" t="n"/>
-      <c r="R9" s="107" t="n"/>
-      <c r="S9" s="107" t="n"/>
-      <c r="T9" s="107" t="n"/>
-      <c r="U9" s="107" t="n"/>
-      <c r="V9" s="107" t="n"/>
-      <c r="W9" s="107" t="n"/>
-      <c r="X9" s="107" t="n"/>
-      <c r="Y9" s="107" t="n"/>
-      <c r="Z9" s="107" t="n"/>
-      <c r="AA9" s="107" t="n"/>
-      <c r="AB9" s="108" t="n"/>
-      <c r="AC9" s="20" t="inlineStr"/>
-      <c r="AD9" s="91" t="n"/>
-      <c r="AE9" s="91" t="n"/>
-      <c r="AF9" s="91" t="n"/>
-      <c r="AG9" s="91" t="n"/>
-      <c r="AH9" s="91" t="n"/>
-      <c r="AI9" s="91" t="n"/>
-      <c r="AJ9" s="91" t="n"/>
-      <c r="AK9" s="91" t="n"/>
-      <c r="AL9" s="91" t="n"/>
-      <c r="AM9" s="20" t="inlineStr"/>
-      <c r="AN9" s="91" t="n"/>
-      <c r="AO9" s="91" t="n"/>
-      <c r="AP9" s="91" t="n"/>
-      <c r="AQ9" s="91" t="n"/>
-      <c r="AR9" s="91" t="n"/>
-      <c r="AS9" s="91" t="n"/>
-      <c r="AT9" s="91" t="n"/>
-      <c r="AU9" s="91" t="n"/>
-      <c r="AV9" s="91" t="n"/>
-      <c r="AW9" s="91" t="n"/>
-      <c r="AX9" s="91" t="n"/>
-      <c r="AY9" s="91" t="n"/>
-      <c r="AZ9" s="91" t="n"/>
-      <c r="BA9" s="91" t="n"/>
-      <c r="BB9" s="91" t="n"/>
-      <c r="BC9" s="91" t="n"/>
-      <c r="BD9" s="91" t="n"/>
+      <c r="L9" s="59" t="n"/>
+      <c r="M9" s="59" t="n"/>
+      <c r="N9" s="59" t="n"/>
+      <c r="O9" s="59" t="n"/>
+      <c r="P9" s="59" t="n"/>
+      <c r="Q9" s="59" t="n"/>
+      <c r="R9" s="59" t="n"/>
+      <c r="S9" s="59" t="n"/>
+      <c r="T9" s="59" t="n"/>
+      <c r="U9" s="59" t="n"/>
+      <c r="V9" s="59" t="n"/>
+      <c r="W9" s="59" t="n"/>
+      <c r="X9" s="59" t="n"/>
+      <c r="Y9" s="59" t="n"/>
+      <c r="Z9" s="59" t="n"/>
+      <c r="AA9" s="59" t="n"/>
+      <c r="AB9" s="59" t="n"/>
+      <c r="AC9" s="158" t="inlineStr"/>
+      <c r="AD9" s="59" t="n"/>
+      <c r="AE9" s="59" t="n"/>
+      <c r="AF9" s="59" t="n"/>
+      <c r="AG9" s="59" t="n"/>
+      <c r="AH9" s="59" t="n"/>
+      <c r="AI9" s="59" t="n"/>
+      <c r="AJ9" s="59" t="n"/>
+      <c r="AK9" s="59" t="n"/>
+      <c r="AL9" s="59" t="n"/>
+      <c r="AM9" s="158" t="inlineStr"/>
+      <c r="AN9" s="59" t="n"/>
+      <c r="AO9" s="59" t="n"/>
+      <c r="AP9" s="59" t="n"/>
+      <c r="AQ9" s="59" t="n"/>
+      <c r="AR9" s="59" t="n"/>
+      <c r="AS9" s="59" t="n"/>
+      <c r="AT9" s="59" t="n"/>
+      <c r="AU9" s="59" t="n"/>
+      <c r="AV9" s="59" t="n"/>
+      <c r="AW9" s="59" t="n"/>
+      <c r="AX9" s="59" t="n"/>
+      <c r="AY9" s="59" t="n"/>
+      <c r="AZ9" s="59" t="n"/>
+      <c r="BA9" s="59" t="n"/>
+      <c r="BB9" s="59" t="n"/>
+      <c r="BC9" s="59" t="n"/>
+      <c r="BD9" s="234" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="73" t="inlineStr">
+      <c r="A10" s="212" t="inlineStr">
         <is>
           <t>Boundary / SoR</t>
         </is>
       </c>
-      <c r="B10" s="107" t="n"/>
-      <c r="C10" s="107" t="n"/>
-      <c r="D10" s="107" t="n"/>
-      <c r="E10" s="107" t="n"/>
-      <c r="F10" s="107" t="n"/>
-      <c r="G10" s="107" t="n"/>
-      <c r="H10" s="107" t="n"/>
-      <c r="I10" s="107" t="n"/>
-      <c r="J10" s="108" t="n"/>
-      <c r="K10" s="90" t="inlineStr">
+      <c r="B10" s="213" t="n"/>
+      <c r="C10" s="213" t="n"/>
+      <c r="D10" s="213" t="n"/>
+      <c r="E10" s="213" t="n"/>
+      <c r="F10" s="213" t="n"/>
+      <c r="G10" s="213" t="n"/>
+      <c r="H10" s="213" t="n"/>
+      <c r="I10" s="213" t="n"/>
+      <c r="J10" s="213" t="n"/>
+      <c r="K10" s="239" t="inlineStr">
         <is>
           <t>Periodic access review only; role master stays in system / ANNEX.</t>
         </is>
       </c>
-      <c r="L10" s="107" t="n"/>
-      <c r="M10" s="107" t="n"/>
-      <c r="N10" s="107" t="n"/>
-      <c r="O10" s="107" t="n"/>
-      <c r="P10" s="107" t="n"/>
-      <c r="Q10" s="107" t="n"/>
-      <c r="R10" s="107" t="n"/>
-      <c r="S10" s="107" t="n"/>
-      <c r="T10" s="107" t="n"/>
-      <c r="U10" s="107" t="n"/>
-      <c r="V10" s="107" t="n"/>
-      <c r="W10" s="107" t="n"/>
-      <c r="X10" s="107" t="n"/>
-      <c r="Y10" s="107" t="n"/>
-      <c r="Z10" s="107" t="n"/>
-      <c r="AA10" s="107" t="n"/>
-      <c r="AB10" s="108" t="n"/>
-      <c r="AC10" s="20" t="inlineStr"/>
-      <c r="AD10" s="91" t="n"/>
-      <c r="AE10" s="91" t="n"/>
-      <c r="AF10" s="91" t="n"/>
-      <c r="AG10" s="91" t="n"/>
-      <c r="AH10" s="91" t="n"/>
-      <c r="AI10" s="91" t="n"/>
-      <c r="AJ10" s="91" t="n"/>
-      <c r="AK10" s="91" t="n"/>
-      <c r="AL10" s="91" t="n"/>
-      <c r="AM10" s="20" t="inlineStr"/>
-      <c r="AN10" s="91" t="n"/>
-      <c r="AO10" s="91" t="n"/>
-      <c r="AP10" s="91" t="n"/>
-      <c r="AQ10" s="91" t="n"/>
-      <c r="AR10" s="91" t="n"/>
-      <c r="AS10" s="91" t="n"/>
-      <c r="AT10" s="91" t="n"/>
-      <c r="AU10" s="91" t="n"/>
-      <c r="AV10" s="91" t="n"/>
-      <c r="AW10" s="91" t="n"/>
-      <c r="AX10" s="91" t="n"/>
-      <c r="AY10" s="91" t="n"/>
-      <c r="AZ10" s="91" t="n"/>
-      <c r="BA10" s="91" t="n"/>
-      <c r="BB10" s="91" t="n"/>
-      <c r="BC10" s="91" t="n"/>
-      <c r="BD10" s="91" t="n"/>
+      <c r="L10" s="213" t="n"/>
+      <c r="M10" s="213" t="n"/>
+      <c r="N10" s="213" t="n"/>
+      <c r="O10" s="213" t="n"/>
+      <c r="P10" s="213" t="n"/>
+      <c r="Q10" s="213" t="n"/>
+      <c r="R10" s="213" t="n"/>
+      <c r="S10" s="213" t="n"/>
+      <c r="T10" s="213" t="n"/>
+      <c r="U10" s="213" t="n"/>
+      <c r="V10" s="213" t="n"/>
+      <c r="W10" s="213" t="n"/>
+      <c r="X10" s="213" t="n"/>
+      <c r="Y10" s="213" t="n"/>
+      <c r="Z10" s="213" t="n"/>
+      <c r="AA10" s="213" t="n"/>
+      <c r="AB10" s="213" t="n"/>
+      <c r="AC10" s="240" t="inlineStr"/>
+      <c r="AD10" s="213" t="n"/>
+      <c r="AE10" s="213" t="n"/>
+      <c r="AF10" s="213" t="n"/>
+      <c r="AG10" s="213" t="n"/>
+      <c r="AH10" s="213" t="n"/>
+      <c r="AI10" s="213" t="n"/>
+      <c r="AJ10" s="213" t="n"/>
+      <c r="AK10" s="213" t="n"/>
+      <c r="AL10" s="213" t="n"/>
+      <c r="AM10" s="240" t="inlineStr"/>
+      <c r="AN10" s="213" t="n"/>
+      <c r="AO10" s="213" t="n"/>
+      <c r="AP10" s="213" t="n"/>
+      <c r="AQ10" s="213" t="n"/>
+      <c r="AR10" s="213" t="n"/>
+      <c r="AS10" s="213" t="n"/>
+      <c r="AT10" s="213" t="n"/>
+      <c r="AU10" s="213" t="n"/>
+      <c r="AV10" s="213" t="n"/>
+      <c r="AW10" s="213" t="n"/>
+      <c r="AX10" s="213" t="n"/>
+      <c r="AY10" s="213" t="n"/>
+      <c r="AZ10" s="213" t="n"/>
+      <c r="BA10" s="213" t="n"/>
+      <c r="BB10" s="213" t="n"/>
+      <c r="BC10" s="213" t="n"/>
+      <c r="BD10" s="241" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B11" s="107" t="n"/>
-      <c r="C11" s="107" t="n"/>
-      <c r="D11" s="107" t="n"/>
-      <c r="E11" s="107" t="n"/>
-      <c r="F11" s="107" t="n"/>
-      <c r="G11" s="107" t="n"/>
-      <c r="H11" s="107" t="n"/>
-      <c r="I11" s="107" t="n"/>
-      <c r="J11" s="107" t="n"/>
-      <c r="K11" s="107" t="n"/>
-      <c r="L11" s="107" t="n"/>
-      <c r="M11" s="107" t="n"/>
-      <c r="N11" s="107" t="n"/>
-      <c r="O11" s="107" t="n"/>
-      <c r="P11" s="107" t="n"/>
-      <c r="Q11" s="107" t="n"/>
-      <c r="R11" s="107" t="n"/>
-      <c r="S11" s="107" t="n"/>
-      <c r="T11" s="107" t="n"/>
-      <c r="U11" s="107" t="n"/>
-      <c r="V11" s="107" t="n"/>
-      <c r="W11" s="107" t="n"/>
-      <c r="X11" s="107" t="n"/>
-      <c r="Y11" s="107" t="n"/>
-      <c r="Z11" s="107" t="n"/>
-      <c r="AA11" s="107" t="n"/>
-      <c r="AB11" s="107" t="n"/>
-      <c r="AC11" s="107" t="n"/>
-      <c r="AD11" s="107" t="n"/>
-      <c r="AE11" s="107" t="n"/>
-      <c r="AF11" s="107" t="n"/>
-      <c r="AG11" s="107" t="n"/>
-      <c r="AH11" s="107" t="n"/>
-      <c r="AI11" s="107" t="n"/>
-      <c r="AJ11" s="107" t="n"/>
-      <c r="AK11" s="107" t="n"/>
-      <c r="AL11" s="107" t="n"/>
-      <c r="AM11" s="107" t="n"/>
-      <c r="AN11" s="107" t="n"/>
-      <c r="AO11" s="107" t="n"/>
-      <c r="AP11" s="107" t="n"/>
-      <c r="AQ11" s="107" t="n"/>
-      <c r="AR11" s="107" t="n"/>
-      <c r="AS11" s="107" t="n"/>
-      <c r="AT11" s="107" t="n"/>
-      <c r="AU11" s="107" t="n"/>
-      <c r="AV11" s="107" t="n"/>
-      <c r="AW11" s="107" t="n"/>
-      <c r="AX11" s="107" t="n"/>
-      <c r="AY11" s="107" t="n"/>
-      <c r="AZ11" s="107" t="n"/>
-      <c r="BA11" s="107" t="n"/>
-      <c r="BB11" s="107" t="n"/>
-      <c r="BC11" s="107" t="n"/>
-      <c r="BD11" s="108" t="n"/>
+      <c r="B11" s="205" t="n"/>
+      <c r="C11" s="205" t="n"/>
+      <c r="D11" s="205" t="n"/>
+      <c r="E11" s="205" t="n"/>
+      <c r="F11" s="205" t="n"/>
+      <c r="G11" s="205" t="n"/>
+      <c r="H11" s="205" t="n"/>
+      <c r="I11" s="205" t="n"/>
+      <c r="J11" s="205" t="n"/>
+      <c r="K11" s="205" t="n"/>
+      <c r="L11" s="205" t="n"/>
+      <c r="M11" s="205" t="n"/>
+      <c r="N11" s="205" t="n"/>
+      <c r="O11" s="205" t="n"/>
+      <c r="P11" s="205" t="n"/>
+      <c r="Q11" s="205" t="n"/>
+      <c r="R11" s="205" t="n"/>
+      <c r="S11" s="205" t="n"/>
+      <c r="T11" s="205" t="n"/>
+      <c r="U11" s="205" t="n"/>
+      <c r="V11" s="205" t="n"/>
+      <c r="W11" s="205" t="n"/>
+      <c r="X11" s="205" t="n"/>
+      <c r="Y11" s="205" t="n"/>
+      <c r="Z11" s="205" t="n"/>
+      <c r="AA11" s="205" t="n"/>
+      <c r="AB11" s="205" t="n"/>
+      <c r="AC11" s="205" t="n"/>
+      <c r="AD11" s="205" t="n"/>
+      <c r="AE11" s="205" t="n"/>
+      <c r="AF11" s="205" t="n"/>
+      <c r="AG11" s="205" t="n"/>
+      <c r="AH11" s="205" t="n"/>
+      <c r="AI11" s="205" t="n"/>
+      <c r="AJ11" s="205" t="n"/>
+      <c r="AK11" s="205" t="n"/>
+      <c r="AL11" s="205" t="n"/>
+      <c r="AM11" s="205" t="n"/>
+      <c r="AN11" s="205" t="n"/>
+      <c r="AO11" s="205" t="n"/>
+      <c r="AP11" s="205" t="n"/>
+      <c r="AQ11" s="205" t="n"/>
+      <c r="AR11" s="205" t="n"/>
+      <c r="AS11" s="205" t="n"/>
+      <c r="AT11" s="205" t="n"/>
+      <c r="AU11" s="205" t="n"/>
+      <c r="AV11" s="205" t="n"/>
+      <c r="AW11" s="205" t="n"/>
+      <c r="AX11" s="205" t="n"/>
+      <c r="AY11" s="205" t="n"/>
+      <c r="AZ11" s="205" t="n"/>
+      <c r="BA11" s="205" t="n"/>
+      <c r="BB11" s="205" t="n"/>
+      <c r="BC11" s="205" t="n"/>
+      <c r="BD11" s="206" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="92" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="242" t="inlineStr">
         <is>
           <t>Finding ID</t>
         </is>
       </c>
-      <c r="B12" s="107" t="n"/>
-      <c r="C12" s="107" t="n"/>
-      <c r="D12" s="107" t="n"/>
-      <c r="E12" s="108" t="n"/>
-      <c r="F12" s="92" t="inlineStr">
+      <c r="B12" s="243" t="n"/>
+      <c r="C12" s="243" t="n"/>
+      <c r="D12" s="243" t="n"/>
+      <c r="E12" s="243" t="n"/>
+      <c r="F12" s="244" t="inlineStr">
         <is>
           <t>Account / Group</t>
         </is>
       </c>
-      <c r="G12" s="107" t="n"/>
-      <c r="H12" s="107" t="n"/>
-      <c r="I12" s="107" t="n"/>
-      <c r="J12" s="108" t="n"/>
-      <c r="K12" s="92" t="inlineStr">
+      <c r="G12" s="243" t="n"/>
+      <c r="H12" s="243" t="n"/>
+      <c r="I12" s="243" t="n"/>
+      <c r="J12" s="243" t="n"/>
+      <c r="K12" s="244" t="inlineStr">
         <is>
           <t>Objective Evidence</t>
         </is>
       </c>
-      <c r="L12" s="107" t="n"/>
-      <c r="M12" s="107" t="n"/>
-      <c r="N12" s="107" t="n"/>
-      <c r="O12" s="107" t="n"/>
-      <c r="P12" s="107" t="n"/>
-      <c r="Q12" s="107" t="n"/>
-      <c r="R12" s="108" t="n"/>
-      <c r="S12" s="92" t="inlineStr">
+      <c r="L12" s="243" t="n"/>
+      <c r="M12" s="243" t="n"/>
+      <c r="N12" s="243" t="n"/>
+      <c r="O12" s="243" t="n"/>
+      <c r="P12" s="243" t="n"/>
+      <c r="Q12" s="243" t="n"/>
+      <c r="R12" s="243" t="n"/>
+      <c r="S12" s="244" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="T12" s="107" t="n"/>
-      <c r="U12" s="107" t="n"/>
-      <c r="V12" s="107" t="n"/>
-      <c r="W12" s="107" t="n"/>
-      <c r="X12" s="108" t="n"/>
-      <c r="Y12" s="92" t="inlineStr">
+      <c r="T12" s="243" t="n"/>
+      <c r="U12" s="243" t="n"/>
+      <c r="V12" s="243" t="n"/>
+      <c r="W12" s="243" t="n"/>
+      <c r="X12" s="243" t="n"/>
+      <c r="Y12" s="244" t="inlineStr">
         <is>
           <t>Containment Need</t>
         </is>
       </c>
-      <c r="Z12" s="107" t="n"/>
-      <c r="AA12" s="107" t="n"/>
-      <c r="AB12" s="107" t="n"/>
-      <c r="AC12" s="107" t="n"/>
-      <c r="AD12" s="108" t="n"/>
-      <c r="AE12" s="92" t="inlineStr">
+      <c r="Z12" s="243" t="n"/>
+      <c r="AA12" s="243" t="n"/>
+      <c r="AB12" s="243" t="n"/>
+      <c r="AC12" s="243" t="n"/>
+      <c r="AD12" s="243" t="n"/>
+      <c r="AE12" s="244" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF12" s="107" t="n"/>
-      <c r="AG12" s="107" t="n"/>
-      <c r="AH12" s="107" t="n"/>
-      <c r="AI12" s="107" t="n"/>
-      <c r="AJ12" s="108" t="n"/>
-      <c r="AK12" s="92" t="inlineStr">
+      <c r="AF12" s="243" t="n"/>
+      <c r="AG12" s="243" t="n"/>
+      <c r="AH12" s="243" t="n"/>
+      <c r="AI12" s="243" t="n"/>
+      <c r="AJ12" s="243" t="n"/>
+      <c r="AK12" s="244" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AL12" s="107" t="n"/>
-      <c r="AM12" s="107" t="n"/>
-      <c r="AN12" s="107" t="n"/>
-      <c r="AO12" s="107" t="n"/>
-      <c r="AP12" s="108" t="n"/>
-      <c r="AQ12" s="92" t="inlineStr">
+      <c r="AL12" s="243" t="n"/>
+      <c r="AM12" s="243" t="n"/>
+      <c r="AN12" s="243" t="n"/>
+      <c r="AO12" s="243" t="n"/>
+      <c r="AP12" s="243" t="n"/>
+      <c r="AQ12" s="244" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AR12" s="107" t="n"/>
-      <c r="AS12" s="107" t="n"/>
-      <c r="AT12" s="107" t="n"/>
-      <c r="AU12" s="107" t="n"/>
-      <c r="AV12" s="108" t="n"/>
-      <c r="AW12" s="92" t="inlineStr">
+      <c r="AR12" s="243" t="n"/>
+      <c r="AS12" s="243" t="n"/>
+      <c r="AT12" s="243" t="n"/>
+      <c r="AU12" s="243" t="n"/>
+      <c r="AV12" s="243" t="n"/>
+      <c r="AW12" s="244" t="inlineStr">
         <is>
           <t>Link or Ref</t>
         </is>
       </c>
-      <c r="AX12" s="107" t="n"/>
-      <c r="AY12" s="107" t="n"/>
-      <c r="AZ12" s="107" t="n"/>
-      <c r="BA12" s="107" t="n"/>
-      <c r="BB12" s="107" t="n"/>
-      <c r="BC12" s="107" t="n"/>
-      <c r="BD12" s="108" t="n"/>
+      <c r="AX12" s="243" t="n"/>
+      <c r="AY12" s="243" t="n"/>
+      <c r="AZ12" s="243" t="n"/>
+      <c r="BA12" s="243" t="n"/>
+      <c r="BB12" s="243" t="n"/>
+      <c r="BC12" s="243" t="n"/>
+      <c r="BD12" s="245" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="93" t="n"/>
-      <c r="B13" s="115" t="n"/>
-      <c r="C13" s="115" t="n"/>
-      <c r="D13" s="115" t="n"/>
-      <c r="E13" s="116" t="n"/>
-      <c r="F13" s="94" t="n"/>
-      <c r="G13" s="115" t="n"/>
-      <c r="H13" s="115" t="n"/>
-      <c r="I13" s="115" t="n"/>
-      <c r="J13" s="116" t="n"/>
-      <c r="K13" s="94" t="n"/>
-      <c r="L13" s="115" t="n"/>
-      <c r="M13" s="115" t="n"/>
-      <c r="N13" s="115" t="n"/>
-      <c r="O13" s="115" t="n"/>
-      <c r="P13" s="115" t="n"/>
-      <c r="Q13" s="115" t="n"/>
-      <c r="R13" s="116" t="n"/>
-      <c r="S13" s="95" t="n"/>
-      <c r="T13" s="115" t="n"/>
-      <c r="U13" s="115" t="n"/>
-      <c r="V13" s="115" t="n"/>
-      <c r="W13" s="115" t="n"/>
-      <c r="X13" s="116" t="n"/>
-      <c r="Y13" s="94" t="n"/>
-      <c r="Z13" s="115" t="n"/>
-      <c r="AA13" s="115" t="n"/>
-      <c r="AB13" s="115" t="n"/>
-      <c r="AC13" s="115" t="n"/>
-      <c r="AD13" s="116" t="n"/>
-      <c r="AE13" s="95" t="n"/>
-      <c r="AF13" s="115" t="n"/>
-      <c r="AG13" s="115" t="n"/>
-      <c r="AH13" s="115" t="n"/>
-      <c r="AI13" s="115" t="n"/>
-      <c r="AJ13" s="116" t="n"/>
-      <c r="AK13" s="95" t="n"/>
-      <c r="AL13" s="115" t="n"/>
-      <c r="AM13" s="115" t="n"/>
-      <c r="AN13" s="115" t="n"/>
-      <c r="AO13" s="115" t="n"/>
-      <c r="AP13" s="116" t="n"/>
-      <c r="AQ13" s="95" t="n"/>
-      <c r="AR13" s="115" t="n"/>
-      <c r="AS13" s="115" t="n"/>
-      <c r="AT13" s="115" t="n"/>
-      <c r="AU13" s="115" t="n"/>
-      <c r="AV13" s="116" t="n"/>
-      <c r="AW13" s="94" t="n"/>
-      <c r="AX13" s="115" t="n"/>
-      <c r="AY13" s="115" t="n"/>
-      <c r="AZ13" s="115" t="n"/>
-      <c r="BA13" s="115" t="n"/>
-      <c r="BB13" s="115" t="n"/>
-      <c r="BC13" s="115" t="n"/>
-      <c r="BD13" s="116" t="n"/>
+      <c r="A13" s="246" t="n"/>
+      <c r="B13" s="209" t="n"/>
+      <c r="C13" s="209" t="n"/>
+      <c r="D13" s="209" t="n"/>
+      <c r="E13" s="209" t="n"/>
+      <c r="F13" s="129" t="n"/>
+      <c r="G13" s="209" t="n"/>
+      <c r="H13" s="209" t="n"/>
+      <c r="I13" s="209" t="n"/>
+      <c r="J13" s="209" t="n"/>
+      <c r="K13" s="129" t="n"/>
+      <c r="L13" s="209" t="n"/>
+      <c r="M13" s="209" t="n"/>
+      <c r="N13" s="209" t="n"/>
+      <c r="O13" s="209" t="n"/>
+      <c r="P13" s="209" t="n"/>
+      <c r="Q13" s="209" t="n"/>
+      <c r="R13" s="209" t="n"/>
+      <c r="S13" s="247" t="n"/>
+      <c r="T13" s="209" t="n"/>
+      <c r="U13" s="209" t="n"/>
+      <c r="V13" s="209" t="n"/>
+      <c r="W13" s="209" t="n"/>
+      <c r="X13" s="209" t="n"/>
+      <c r="Y13" s="129" t="n"/>
+      <c r="Z13" s="209" t="n"/>
+      <c r="AA13" s="209" t="n"/>
+      <c r="AB13" s="209" t="n"/>
+      <c r="AC13" s="209" t="n"/>
+      <c r="AD13" s="209" t="n"/>
+      <c r="AE13" s="247" t="n"/>
+      <c r="AF13" s="209" t="n"/>
+      <c r="AG13" s="209" t="n"/>
+      <c r="AH13" s="209" t="n"/>
+      <c r="AI13" s="209" t="n"/>
+      <c r="AJ13" s="209" t="n"/>
+      <c r="AK13" s="247" t="n"/>
+      <c r="AL13" s="209" t="n"/>
+      <c r="AM13" s="209" t="n"/>
+      <c r="AN13" s="209" t="n"/>
+      <c r="AO13" s="209" t="n"/>
+      <c r="AP13" s="209" t="n"/>
+      <c r="AQ13" s="247" t="n"/>
+      <c r="AR13" s="209" t="n"/>
+      <c r="AS13" s="209" t="n"/>
+      <c r="AT13" s="209" t="n"/>
+      <c r="AU13" s="209" t="n"/>
+      <c r="AV13" s="209" t="n"/>
+      <c r="AW13" s="129" t="n"/>
+      <c r="AX13" s="209" t="n"/>
+      <c r="AY13" s="209" t="n"/>
+      <c r="AZ13" s="209" t="n"/>
+      <c r="BA13" s="209" t="n"/>
+      <c r="BB13" s="209" t="n"/>
+      <c r="BC13" s="209" t="n"/>
+      <c r="BD13" s="211" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="93" t="n"/>
-      <c r="B14" s="115" t="n"/>
-      <c r="C14" s="115" t="n"/>
-      <c r="D14" s="115" t="n"/>
-      <c r="E14" s="116" t="n"/>
-      <c r="F14" s="96" t="n"/>
-      <c r="G14" s="115" t="n"/>
-      <c r="H14" s="115" t="n"/>
-      <c r="I14" s="115" t="n"/>
-      <c r="J14" s="116" t="n"/>
-      <c r="K14" s="96" t="n"/>
-      <c r="L14" s="115" t="n"/>
-      <c r="M14" s="115" t="n"/>
-      <c r="N14" s="115" t="n"/>
-      <c r="O14" s="115" t="n"/>
-      <c r="P14" s="115" t="n"/>
-      <c r="Q14" s="115" t="n"/>
-      <c r="R14" s="116" t="n"/>
-      <c r="S14" s="95" t="n"/>
-      <c r="T14" s="115" t="n"/>
-      <c r="U14" s="115" t="n"/>
-      <c r="V14" s="115" t="n"/>
-      <c r="W14" s="115" t="n"/>
-      <c r="X14" s="116" t="n"/>
-      <c r="Y14" s="96" t="n"/>
-      <c r="Z14" s="115" t="n"/>
-      <c r="AA14" s="115" t="n"/>
-      <c r="AB14" s="115" t="n"/>
-      <c r="AC14" s="115" t="n"/>
-      <c r="AD14" s="116" t="n"/>
-      <c r="AE14" s="95" t="n"/>
-      <c r="AF14" s="115" t="n"/>
-      <c r="AG14" s="115" t="n"/>
-      <c r="AH14" s="115" t="n"/>
-      <c r="AI14" s="115" t="n"/>
-      <c r="AJ14" s="116" t="n"/>
-      <c r="AK14" s="95" t="n"/>
-      <c r="AL14" s="115" t="n"/>
-      <c r="AM14" s="115" t="n"/>
-      <c r="AN14" s="115" t="n"/>
-      <c r="AO14" s="115" t="n"/>
-      <c r="AP14" s="116" t="n"/>
-      <c r="AQ14" s="95" t="n"/>
-      <c r="AR14" s="115" t="n"/>
-      <c r="AS14" s="115" t="n"/>
-      <c r="AT14" s="115" t="n"/>
-      <c r="AU14" s="115" t="n"/>
-      <c r="AV14" s="116" t="n"/>
-      <c r="AW14" s="96" t="n"/>
-      <c r="AX14" s="115" t="n"/>
-      <c r="AY14" s="115" t="n"/>
-      <c r="AZ14" s="115" t="n"/>
-      <c r="BA14" s="115" t="n"/>
-      <c r="BB14" s="115" t="n"/>
-      <c r="BC14" s="115" t="n"/>
-      <c r="BD14" s="116" t="n"/>
+      <c r="A14" s="248" t="n"/>
+      <c r="B14" s="227" t="n"/>
+      <c r="C14" s="227" t="n"/>
+      <c r="D14" s="227" t="n"/>
+      <c r="E14" s="227" t="n"/>
+      <c r="F14" s="163" t="n"/>
+      <c r="G14" s="227" t="n"/>
+      <c r="H14" s="227" t="n"/>
+      <c r="I14" s="227" t="n"/>
+      <c r="J14" s="227" t="n"/>
+      <c r="K14" s="163" t="n"/>
+      <c r="L14" s="227" t="n"/>
+      <c r="M14" s="227" t="n"/>
+      <c r="N14" s="227" t="n"/>
+      <c r="O14" s="227" t="n"/>
+      <c r="P14" s="227" t="n"/>
+      <c r="Q14" s="227" t="n"/>
+      <c r="R14" s="227" t="n"/>
+      <c r="S14" s="162" t="n"/>
+      <c r="T14" s="227" t="n"/>
+      <c r="U14" s="227" t="n"/>
+      <c r="V14" s="227" t="n"/>
+      <c r="W14" s="227" t="n"/>
+      <c r="X14" s="227" t="n"/>
+      <c r="Y14" s="163" t="n"/>
+      <c r="Z14" s="227" t="n"/>
+      <c r="AA14" s="227" t="n"/>
+      <c r="AB14" s="227" t="n"/>
+      <c r="AC14" s="227" t="n"/>
+      <c r="AD14" s="227" t="n"/>
+      <c r="AE14" s="162" t="n"/>
+      <c r="AF14" s="227" t="n"/>
+      <c r="AG14" s="227" t="n"/>
+      <c r="AH14" s="227" t="n"/>
+      <c r="AI14" s="227" t="n"/>
+      <c r="AJ14" s="227" t="n"/>
+      <c r="AK14" s="162" t="n"/>
+      <c r="AL14" s="227" t="n"/>
+      <c r="AM14" s="227" t="n"/>
+      <c r="AN14" s="227" t="n"/>
+      <c r="AO14" s="227" t="n"/>
+      <c r="AP14" s="227" t="n"/>
+      <c r="AQ14" s="162" t="n"/>
+      <c r="AR14" s="227" t="n"/>
+      <c r="AS14" s="227" t="n"/>
+      <c r="AT14" s="227" t="n"/>
+      <c r="AU14" s="227" t="n"/>
+      <c r="AV14" s="227" t="n"/>
+      <c r="AW14" s="163" t="n"/>
+      <c r="AX14" s="227" t="n"/>
+      <c r="AY14" s="227" t="n"/>
+      <c r="AZ14" s="227" t="n"/>
+      <c r="BA14" s="227" t="n"/>
+      <c r="BB14" s="227" t="n"/>
+      <c r="BC14" s="227" t="n"/>
+      <c r="BD14" s="231" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="93" t="n"/>
-      <c r="B15" s="115" t="n"/>
-      <c r="C15" s="115" t="n"/>
-      <c r="D15" s="115" t="n"/>
-      <c r="E15" s="116" t="n"/>
-      <c r="F15" s="94" t="n"/>
-      <c r="G15" s="115" t="n"/>
-      <c r="H15" s="115" t="n"/>
-      <c r="I15" s="115" t="n"/>
-      <c r="J15" s="116" t="n"/>
-      <c r="K15" s="94" t="n"/>
-      <c r="L15" s="115" t="n"/>
-      <c r="M15" s="115" t="n"/>
-      <c r="N15" s="115" t="n"/>
-      <c r="O15" s="115" t="n"/>
-      <c r="P15" s="115" t="n"/>
-      <c r="Q15" s="115" t="n"/>
-      <c r="R15" s="116" t="n"/>
-      <c r="S15" s="95" t="n"/>
-      <c r="T15" s="115" t="n"/>
-      <c r="U15" s="115" t="n"/>
-      <c r="V15" s="115" t="n"/>
-      <c r="W15" s="115" t="n"/>
-      <c r="X15" s="116" t="n"/>
-      <c r="Y15" s="94" t="n"/>
-      <c r="Z15" s="115" t="n"/>
-      <c r="AA15" s="115" t="n"/>
-      <c r="AB15" s="115" t="n"/>
-      <c r="AC15" s="115" t="n"/>
-      <c r="AD15" s="116" t="n"/>
-      <c r="AE15" s="95" t="n"/>
-      <c r="AF15" s="115" t="n"/>
-      <c r="AG15" s="115" t="n"/>
-      <c r="AH15" s="115" t="n"/>
-      <c r="AI15" s="115" t="n"/>
-      <c r="AJ15" s="116" t="n"/>
-      <c r="AK15" s="95" t="n"/>
-      <c r="AL15" s="115" t="n"/>
-      <c r="AM15" s="115" t="n"/>
-      <c r="AN15" s="115" t="n"/>
-      <c r="AO15" s="115" t="n"/>
-      <c r="AP15" s="116" t="n"/>
-      <c r="AQ15" s="95" t="n"/>
-      <c r="AR15" s="115" t="n"/>
-      <c r="AS15" s="115" t="n"/>
-      <c r="AT15" s="115" t="n"/>
-      <c r="AU15" s="115" t="n"/>
-      <c r="AV15" s="116" t="n"/>
-      <c r="AW15" s="94" t="n"/>
-      <c r="AX15" s="115" t="n"/>
-      <c r="AY15" s="115" t="n"/>
-      <c r="AZ15" s="115" t="n"/>
-      <c r="BA15" s="115" t="n"/>
-      <c r="BB15" s="115" t="n"/>
-      <c r="BC15" s="115" t="n"/>
-      <c r="BD15" s="116" t="n"/>
+      <c r="A15" s="248" t="n"/>
+      <c r="B15" s="227" t="n"/>
+      <c r="C15" s="227" t="n"/>
+      <c r="D15" s="227" t="n"/>
+      <c r="E15" s="227" t="n"/>
+      <c r="F15" s="137" t="n"/>
+      <c r="G15" s="227" t="n"/>
+      <c r="H15" s="227" t="n"/>
+      <c r="I15" s="227" t="n"/>
+      <c r="J15" s="227" t="n"/>
+      <c r="K15" s="137" t="n"/>
+      <c r="L15" s="227" t="n"/>
+      <c r="M15" s="227" t="n"/>
+      <c r="N15" s="227" t="n"/>
+      <c r="O15" s="227" t="n"/>
+      <c r="P15" s="227" t="n"/>
+      <c r="Q15" s="227" t="n"/>
+      <c r="R15" s="227" t="n"/>
+      <c r="S15" s="162" t="n"/>
+      <c r="T15" s="227" t="n"/>
+      <c r="U15" s="227" t="n"/>
+      <c r="V15" s="227" t="n"/>
+      <c r="W15" s="227" t="n"/>
+      <c r="X15" s="227" t="n"/>
+      <c r="Y15" s="137" t="n"/>
+      <c r="Z15" s="227" t="n"/>
+      <c r="AA15" s="227" t="n"/>
+      <c r="AB15" s="227" t="n"/>
+      <c r="AC15" s="227" t="n"/>
+      <c r="AD15" s="227" t="n"/>
+      <c r="AE15" s="162" t="n"/>
+      <c r="AF15" s="227" t="n"/>
+      <c r="AG15" s="227" t="n"/>
+      <c r="AH15" s="227" t="n"/>
+      <c r="AI15" s="227" t="n"/>
+      <c r="AJ15" s="227" t="n"/>
+      <c r="AK15" s="162" t="n"/>
+      <c r="AL15" s="227" t="n"/>
+      <c r="AM15" s="227" t="n"/>
+      <c r="AN15" s="227" t="n"/>
+      <c r="AO15" s="227" t="n"/>
+      <c r="AP15" s="227" t="n"/>
+      <c r="AQ15" s="162" t="n"/>
+      <c r="AR15" s="227" t="n"/>
+      <c r="AS15" s="227" t="n"/>
+      <c r="AT15" s="227" t="n"/>
+      <c r="AU15" s="227" t="n"/>
+      <c r="AV15" s="227" t="n"/>
+      <c r="AW15" s="137" t="n"/>
+      <c r="AX15" s="227" t="n"/>
+      <c r="AY15" s="227" t="n"/>
+      <c r="AZ15" s="227" t="n"/>
+      <c r="BA15" s="227" t="n"/>
+      <c r="BB15" s="227" t="n"/>
+      <c r="BC15" s="227" t="n"/>
+      <c r="BD15" s="231" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="93" t="n"/>
-      <c r="B16" s="115" t="n"/>
-      <c r="C16" s="115" t="n"/>
-      <c r="D16" s="115" t="n"/>
-      <c r="E16" s="116" t="n"/>
-      <c r="F16" s="96" t="n"/>
-      <c r="G16" s="115" t="n"/>
-      <c r="H16" s="115" t="n"/>
-      <c r="I16" s="115" t="n"/>
-      <c r="J16" s="116" t="n"/>
-      <c r="K16" s="96" t="n"/>
-      <c r="L16" s="115" t="n"/>
-      <c r="M16" s="115" t="n"/>
-      <c r="N16" s="115" t="n"/>
-      <c r="O16" s="115" t="n"/>
-      <c r="P16" s="115" t="n"/>
-      <c r="Q16" s="115" t="n"/>
-      <c r="R16" s="116" t="n"/>
-      <c r="S16" s="95" t="n"/>
-      <c r="T16" s="115" t="n"/>
-      <c r="U16" s="115" t="n"/>
-      <c r="V16" s="115" t="n"/>
-      <c r="W16" s="115" t="n"/>
-      <c r="X16" s="116" t="n"/>
-      <c r="Y16" s="96" t="n"/>
-      <c r="Z16" s="115" t="n"/>
-      <c r="AA16" s="115" t="n"/>
-      <c r="AB16" s="115" t="n"/>
-      <c r="AC16" s="115" t="n"/>
-      <c r="AD16" s="116" t="n"/>
-      <c r="AE16" s="95" t="n"/>
-      <c r="AF16" s="115" t="n"/>
-      <c r="AG16" s="115" t="n"/>
-      <c r="AH16" s="115" t="n"/>
-      <c r="AI16" s="115" t="n"/>
-      <c r="AJ16" s="116" t="n"/>
-      <c r="AK16" s="95" t="n"/>
-      <c r="AL16" s="115" t="n"/>
-      <c r="AM16" s="115" t="n"/>
-      <c r="AN16" s="115" t="n"/>
-      <c r="AO16" s="115" t="n"/>
-      <c r="AP16" s="116" t="n"/>
-      <c r="AQ16" s="95" t="n"/>
-      <c r="AR16" s="115" t="n"/>
-      <c r="AS16" s="115" t="n"/>
-      <c r="AT16" s="115" t="n"/>
-      <c r="AU16" s="115" t="n"/>
-      <c r="AV16" s="116" t="n"/>
-      <c r="AW16" s="96" t="n"/>
-      <c r="AX16" s="115" t="n"/>
-      <c r="AY16" s="115" t="n"/>
-      <c r="AZ16" s="115" t="n"/>
-      <c r="BA16" s="115" t="n"/>
-      <c r="BB16" s="115" t="n"/>
-      <c r="BC16" s="115" t="n"/>
-      <c r="BD16" s="116" t="n"/>
+      <c r="A16" s="248" t="n"/>
+      <c r="B16" s="227" t="n"/>
+      <c r="C16" s="227" t="n"/>
+      <c r="D16" s="227" t="n"/>
+      <c r="E16" s="227" t="n"/>
+      <c r="F16" s="163" t="n"/>
+      <c r="G16" s="227" t="n"/>
+      <c r="H16" s="227" t="n"/>
+      <c r="I16" s="227" t="n"/>
+      <c r="J16" s="227" t="n"/>
+      <c r="K16" s="163" t="n"/>
+      <c r="L16" s="227" t="n"/>
+      <c r="M16" s="227" t="n"/>
+      <c r="N16" s="227" t="n"/>
+      <c r="O16" s="227" t="n"/>
+      <c r="P16" s="227" t="n"/>
+      <c r="Q16" s="227" t="n"/>
+      <c r="R16" s="227" t="n"/>
+      <c r="S16" s="162" t="n"/>
+      <c r="T16" s="227" t="n"/>
+      <c r="U16" s="227" t="n"/>
+      <c r="V16" s="227" t="n"/>
+      <c r="W16" s="227" t="n"/>
+      <c r="X16" s="227" t="n"/>
+      <c r="Y16" s="163" t="n"/>
+      <c r="Z16" s="227" t="n"/>
+      <c r="AA16" s="227" t="n"/>
+      <c r="AB16" s="227" t="n"/>
+      <c r="AC16" s="227" t="n"/>
+      <c r="AD16" s="227" t="n"/>
+      <c r="AE16" s="162" t="n"/>
+      <c r="AF16" s="227" t="n"/>
+      <c r="AG16" s="227" t="n"/>
+      <c r="AH16" s="227" t="n"/>
+      <c r="AI16" s="227" t="n"/>
+      <c r="AJ16" s="227" t="n"/>
+      <c r="AK16" s="162" t="n"/>
+      <c r="AL16" s="227" t="n"/>
+      <c r="AM16" s="227" t="n"/>
+      <c r="AN16" s="227" t="n"/>
+      <c r="AO16" s="227" t="n"/>
+      <c r="AP16" s="227" t="n"/>
+      <c r="AQ16" s="162" t="n"/>
+      <c r="AR16" s="227" t="n"/>
+      <c r="AS16" s="227" t="n"/>
+      <c r="AT16" s="227" t="n"/>
+      <c r="AU16" s="227" t="n"/>
+      <c r="AV16" s="227" t="n"/>
+      <c r="AW16" s="163" t="n"/>
+      <c r="AX16" s="227" t="n"/>
+      <c r="AY16" s="227" t="n"/>
+      <c r="AZ16" s="227" t="n"/>
+      <c r="BA16" s="227" t="n"/>
+      <c r="BB16" s="227" t="n"/>
+      <c r="BC16" s="227" t="n"/>
+      <c r="BD16" s="231" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="93" t="n"/>
-      <c r="B17" s="115" t="n"/>
-      <c r="C17" s="115" t="n"/>
-      <c r="D17" s="115" t="n"/>
-      <c r="E17" s="116" t="n"/>
-      <c r="F17" s="94" t="n"/>
-      <c r="G17" s="115" t="n"/>
-      <c r="H17" s="115" t="n"/>
-      <c r="I17" s="115" t="n"/>
-      <c r="J17" s="116" t="n"/>
-      <c r="K17" s="94" t="n"/>
-      <c r="L17" s="115" t="n"/>
-      <c r="M17" s="115" t="n"/>
-      <c r="N17" s="115" t="n"/>
-      <c r="O17" s="115" t="n"/>
-      <c r="P17" s="115" t="n"/>
-      <c r="Q17" s="115" t="n"/>
-      <c r="R17" s="116" t="n"/>
-      <c r="S17" s="95" t="n"/>
-      <c r="T17" s="115" t="n"/>
-      <c r="U17" s="115" t="n"/>
-      <c r="V17" s="115" t="n"/>
-      <c r="W17" s="115" t="n"/>
-      <c r="X17" s="116" t="n"/>
-      <c r="Y17" s="94" t="n"/>
-      <c r="Z17" s="115" t="n"/>
-      <c r="AA17" s="115" t="n"/>
-      <c r="AB17" s="115" t="n"/>
-      <c r="AC17" s="115" t="n"/>
-      <c r="AD17" s="116" t="n"/>
-      <c r="AE17" s="95" t="n"/>
-      <c r="AF17" s="115" t="n"/>
-      <c r="AG17" s="115" t="n"/>
-      <c r="AH17" s="115" t="n"/>
-      <c r="AI17" s="115" t="n"/>
-      <c r="AJ17" s="116" t="n"/>
-      <c r="AK17" s="95" t="n"/>
-      <c r="AL17" s="115" t="n"/>
-      <c r="AM17" s="115" t="n"/>
-      <c r="AN17" s="115" t="n"/>
-      <c r="AO17" s="115" t="n"/>
-      <c r="AP17" s="116" t="n"/>
-      <c r="AQ17" s="95" t="n"/>
-      <c r="AR17" s="115" t="n"/>
-      <c r="AS17" s="115" t="n"/>
-      <c r="AT17" s="115" t="n"/>
-      <c r="AU17" s="115" t="n"/>
-      <c r="AV17" s="116" t="n"/>
-      <c r="AW17" s="94" t="n"/>
-      <c r="AX17" s="115" t="n"/>
-      <c r="AY17" s="115" t="n"/>
-      <c r="AZ17" s="115" t="n"/>
-      <c r="BA17" s="115" t="n"/>
-      <c r="BB17" s="115" t="n"/>
-      <c r="BC17" s="115" t="n"/>
-      <c r="BD17" s="116" t="n"/>
+      <c r="A17" s="248" t="n"/>
+      <c r="B17" s="227" t="n"/>
+      <c r="C17" s="227" t="n"/>
+      <c r="D17" s="227" t="n"/>
+      <c r="E17" s="227" t="n"/>
+      <c r="F17" s="137" t="n"/>
+      <c r="G17" s="227" t="n"/>
+      <c r="H17" s="227" t="n"/>
+      <c r="I17" s="227" t="n"/>
+      <c r="J17" s="227" t="n"/>
+      <c r="K17" s="137" t="n"/>
+      <c r="L17" s="227" t="n"/>
+      <c r="M17" s="227" t="n"/>
+      <c r="N17" s="227" t="n"/>
+      <c r="O17" s="227" t="n"/>
+      <c r="P17" s="227" t="n"/>
+      <c r="Q17" s="227" t="n"/>
+      <c r="R17" s="227" t="n"/>
+      <c r="S17" s="162" t="n"/>
+      <c r="T17" s="227" t="n"/>
+      <c r="U17" s="227" t="n"/>
+      <c r="V17" s="227" t="n"/>
+      <c r="W17" s="227" t="n"/>
+      <c r="X17" s="227" t="n"/>
+      <c r="Y17" s="137" t="n"/>
+      <c r="Z17" s="227" t="n"/>
+      <c r="AA17" s="227" t="n"/>
+      <c r="AB17" s="227" t="n"/>
+      <c r="AC17" s="227" t="n"/>
+      <c r="AD17" s="227" t="n"/>
+      <c r="AE17" s="162" t="n"/>
+      <c r="AF17" s="227" t="n"/>
+      <c r="AG17" s="227" t="n"/>
+      <c r="AH17" s="227" t="n"/>
+      <c r="AI17" s="227" t="n"/>
+      <c r="AJ17" s="227" t="n"/>
+      <c r="AK17" s="162" t="n"/>
+      <c r="AL17" s="227" t="n"/>
+      <c r="AM17" s="227" t="n"/>
+      <c r="AN17" s="227" t="n"/>
+      <c r="AO17" s="227" t="n"/>
+      <c r="AP17" s="227" t="n"/>
+      <c r="AQ17" s="162" t="n"/>
+      <c r="AR17" s="227" t="n"/>
+      <c r="AS17" s="227" t="n"/>
+      <c r="AT17" s="227" t="n"/>
+      <c r="AU17" s="227" t="n"/>
+      <c r="AV17" s="227" t="n"/>
+      <c r="AW17" s="137" t="n"/>
+      <c r="AX17" s="227" t="n"/>
+      <c r="AY17" s="227" t="n"/>
+      <c r="AZ17" s="227" t="n"/>
+      <c r="BA17" s="227" t="n"/>
+      <c r="BB17" s="227" t="n"/>
+      <c r="BC17" s="227" t="n"/>
+      <c r="BD17" s="231" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="93" t="n"/>
-      <c r="B18" s="115" t="n"/>
-      <c r="C18" s="115" t="n"/>
-      <c r="D18" s="115" t="n"/>
-      <c r="E18" s="116" t="n"/>
-      <c r="F18" s="96" t="n"/>
-      <c r="G18" s="115" t="n"/>
-      <c r="H18" s="115" t="n"/>
-      <c r="I18" s="115" t="n"/>
-      <c r="J18" s="116" t="n"/>
-      <c r="K18" s="96" t="n"/>
-      <c r="L18" s="115" t="n"/>
-      <c r="M18" s="115" t="n"/>
-      <c r="N18" s="115" t="n"/>
-      <c r="O18" s="115" t="n"/>
-      <c r="P18" s="115" t="n"/>
-      <c r="Q18" s="115" t="n"/>
-      <c r="R18" s="116" t="n"/>
-      <c r="S18" s="95" t="n"/>
-      <c r="T18" s="115" t="n"/>
-      <c r="U18" s="115" t="n"/>
-      <c r="V18" s="115" t="n"/>
-      <c r="W18" s="115" t="n"/>
-      <c r="X18" s="116" t="n"/>
-      <c r="Y18" s="96" t="n"/>
-      <c r="Z18" s="115" t="n"/>
-      <c r="AA18" s="115" t="n"/>
-      <c r="AB18" s="115" t="n"/>
-      <c r="AC18" s="115" t="n"/>
-      <c r="AD18" s="116" t="n"/>
-      <c r="AE18" s="95" t="n"/>
-      <c r="AF18" s="115" t="n"/>
-      <c r="AG18" s="115" t="n"/>
-      <c r="AH18" s="115" t="n"/>
-      <c r="AI18" s="115" t="n"/>
-      <c r="AJ18" s="116" t="n"/>
-      <c r="AK18" s="95" t="n"/>
-      <c r="AL18" s="115" t="n"/>
-      <c r="AM18" s="115" t="n"/>
-      <c r="AN18" s="115" t="n"/>
-      <c r="AO18" s="115" t="n"/>
-      <c r="AP18" s="116" t="n"/>
-      <c r="AQ18" s="95" t="n"/>
-      <c r="AR18" s="115" t="n"/>
-      <c r="AS18" s="115" t="n"/>
-      <c r="AT18" s="115" t="n"/>
-      <c r="AU18" s="115" t="n"/>
-      <c r="AV18" s="116" t="n"/>
-      <c r="AW18" s="96" t="n"/>
-      <c r="AX18" s="115" t="n"/>
-      <c r="AY18" s="115" t="n"/>
-      <c r="AZ18" s="115" t="n"/>
-      <c r="BA18" s="115" t="n"/>
-      <c r="BB18" s="115" t="n"/>
-      <c r="BC18" s="115" t="n"/>
-      <c r="BD18" s="116" t="n"/>
+      <c r="A18" s="249" t="n"/>
+      <c r="B18" s="215" t="n"/>
+      <c r="C18" s="215" t="n"/>
+      <c r="D18" s="215" t="n"/>
+      <c r="E18" s="215" t="n"/>
+      <c r="F18" s="250" t="n"/>
+      <c r="G18" s="215" t="n"/>
+      <c r="H18" s="215" t="n"/>
+      <c r="I18" s="215" t="n"/>
+      <c r="J18" s="215" t="n"/>
+      <c r="K18" s="250" t="n"/>
+      <c r="L18" s="215" t="n"/>
+      <c r="M18" s="215" t="n"/>
+      <c r="N18" s="215" t="n"/>
+      <c r="O18" s="215" t="n"/>
+      <c r="P18" s="215" t="n"/>
+      <c r="Q18" s="215" t="n"/>
+      <c r="R18" s="215" t="n"/>
+      <c r="S18" s="251" t="n"/>
+      <c r="T18" s="215" t="n"/>
+      <c r="U18" s="215" t="n"/>
+      <c r="V18" s="215" t="n"/>
+      <c r="W18" s="215" t="n"/>
+      <c r="X18" s="215" t="n"/>
+      <c r="Y18" s="250" t="n"/>
+      <c r="Z18" s="215" t="n"/>
+      <c r="AA18" s="215" t="n"/>
+      <c r="AB18" s="215" t="n"/>
+      <c r="AC18" s="215" t="n"/>
+      <c r="AD18" s="215" t="n"/>
+      <c r="AE18" s="251" t="n"/>
+      <c r="AF18" s="215" t="n"/>
+      <c r="AG18" s="215" t="n"/>
+      <c r="AH18" s="215" t="n"/>
+      <c r="AI18" s="215" t="n"/>
+      <c r="AJ18" s="215" t="n"/>
+      <c r="AK18" s="251" t="n"/>
+      <c r="AL18" s="215" t="n"/>
+      <c r="AM18" s="215" t="n"/>
+      <c r="AN18" s="215" t="n"/>
+      <c r="AO18" s="215" t="n"/>
+      <c r="AP18" s="215" t="n"/>
+      <c r="AQ18" s="251" t="n"/>
+      <c r="AR18" s="215" t="n"/>
+      <c r="AS18" s="215" t="n"/>
+      <c r="AT18" s="215" t="n"/>
+      <c r="AU18" s="215" t="n"/>
+      <c r="AV18" s="215" t="n"/>
+      <c r="AW18" s="250" t="n"/>
+      <c r="AX18" s="215" t="n"/>
+      <c r="AY18" s="215" t="n"/>
+      <c r="AZ18" s="215" t="n"/>
+      <c r="BA18" s="215" t="n"/>
+      <c r="BB18" s="215" t="n"/>
+      <c r="BC18" s="215" t="n"/>
+      <c r="BD18" s="217" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="89" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="204" t="inlineStr">
         <is>
           <t>NOTICE: Use one row per finding. Record objective evidence, severity, owner, due date and verification reference; avoid vague or conclusion-only wording.</t>
         </is>
       </c>
-      <c r="B19" s="101" t="n"/>
-      <c r="C19" s="101" t="n"/>
-      <c r="D19" s="101" t="n"/>
-      <c r="E19" s="101" t="n"/>
-      <c r="F19" s="101" t="n"/>
-      <c r="G19" s="101" t="n"/>
-      <c r="H19" s="101" t="n"/>
-      <c r="I19" s="101" t="n"/>
-      <c r="J19" s="101" t="n"/>
-      <c r="K19" s="101" t="n"/>
-      <c r="L19" s="101" t="n"/>
-      <c r="M19" s="101" t="n"/>
-      <c r="N19" s="101" t="n"/>
-      <c r="O19" s="101" t="n"/>
-      <c r="P19" s="101" t="n"/>
-      <c r="Q19" s="101" t="n"/>
-      <c r="R19" s="101" t="n"/>
-      <c r="S19" s="101" t="n"/>
-      <c r="T19" s="101" t="n"/>
-      <c r="U19" s="101" t="n"/>
-      <c r="V19" s="101" t="n"/>
-      <c r="W19" s="101" t="n"/>
-      <c r="X19" s="101" t="n"/>
-      <c r="Y19" s="101" t="n"/>
-      <c r="Z19" s="101" t="n"/>
-      <c r="AA19" s="101" t="n"/>
-      <c r="AB19" s="101" t="n"/>
-      <c r="AC19" s="101" t="n"/>
-      <c r="AD19" s="101" t="n"/>
-      <c r="AE19" s="101" t="n"/>
-      <c r="AF19" s="101" t="n"/>
-      <c r="AG19" s="101" t="n"/>
-      <c r="AH19" s="101" t="n"/>
-      <c r="AI19" s="101" t="n"/>
-      <c r="AJ19" s="101" t="n"/>
-      <c r="AK19" s="101" t="n"/>
-      <c r="AL19" s="101" t="n"/>
-      <c r="AM19" s="101" t="n"/>
-      <c r="AN19" s="101" t="n"/>
-      <c r="AO19" s="101" t="n"/>
-      <c r="AP19" s="101" t="n"/>
-      <c r="AQ19" s="101" t="n"/>
-      <c r="AR19" s="101" t="n"/>
-      <c r="AS19" s="101" t="n"/>
-      <c r="AT19" s="101" t="n"/>
-      <c r="AU19" s="101" t="n"/>
-      <c r="AV19" s="101" t="n"/>
-      <c r="AW19" s="101" t="n"/>
-      <c r="AX19" s="101" t="n"/>
-      <c r="AY19" s="101" t="n"/>
-      <c r="AZ19" s="101" t="n"/>
-      <c r="BA19" s="101" t="n"/>
-      <c r="BB19" s="101" t="n"/>
-      <c r="BC19" s="101" t="n"/>
-      <c r="BD19" s="102" t="n"/>
+      <c r="B19" s="205" t="n"/>
+      <c r="C19" s="205" t="n"/>
+      <c r="D19" s="205" t="n"/>
+      <c r="E19" s="205" t="n"/>
+      <c r="F19" s="205" t="n"/>
+      <c r="G19" s="205" t="n"/>
+      <c r="H19" s="205" t="n"/>
+      <c r="I19" s="205" t="n"/>
+      <c r="J19" s="205" t="n"/>
+      <c r="K19" s="205" t="n"/>
+      <c r="L19" s="205" t="n"/>
+      <c r="M19" s="205" t="n"/>
+      <c r="N19" s="205" t="n"/>
+      <c r="O19" s="205" t="n"/>
+      <c r="P19" s="205" t="n"/>
+      <c r="Q19" s="205" t="n"/>
+      <c r="R19" s="205" t="n"/>
+      <c r="S19" s="205" t="n"/>
+      <c r="T19" s="205" t="n"/>
+      <c r="U19" s="205" t="n"/>
+      <c r="V19" s="205" t="n"/>
+      <c r="W19" s="205" t="n"/>
+      <c r="X19" s="205" t="n"/>
+      <c r="Y19" s="205" t="n"/>
+      <c r="Z19" s="205" t="n"/>
+      <c r="AA19" s="205" t="n"/>
+      <c r="AB19" s="205" t="n"/>
+      <c r="AC19" s="205" t="n"/>
+      <c r="AD19" s="205" t="n"/>
+      <c r="AE19" s="205" t="n"/>
+      <c r="AF19" s="205" t="n"/>
+      <c r="AG19" s="205" t="n"/>
+      <c r="AH19" s="205" t="n"/>
+      <c r="AI19" s="205" t="n"/>
+      <c r="AJ19" s="205" t="n"/>
+      <c r="AK19" s="205" t="n"/>
+      <c r="AL19" s="205" t="n"/>
+      <c r="AM19" s="205" t="n"/>
+      <c r="AN19" s="205" t="n"/>
+      <c r="AO19" s="205" t="n"/>
+      <c r="AP19" s="205" t="n"/>
+      <c r="AQ19" s="205" t="n"/>
+      <c r="AR19" s="205" t="n"/>
+      <c r="AS19" s="205" t="n"/>
+      <c r="AT19" s="205" t="n"/>
+      <c r="AU19" s="205" t="n"/>
+      <c r="AV19" s="205" t="n"/>
+      <c r="AW19" s="205" t="n"/>
+      <c r="AX19" s="205" t="n"/>
+      <c r="AY19" s="205" t="n"/>
+      <c r="AZ19" s="205" t="n"/>
+      <c r="BA19" s="205" t="n"/>
+      <c r="BB19" s="205" t="n"/>
+      <c r="BC19" s="205" t="n"/>
+      <c r="BD19" s="206" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="93">
+  <mergeCells count="92">
     <mergeCell ref="K16:R16"/>
     <mergeCell ref="Y14:AD14"/>
     <mergeCell ref="AW2:BD2"/>
@@ -3932,7 +5285,6 @@
     <mergeCell ref="Y12:AD12"/>
     <mergeCell ref="AQ4:AV4"/>
     <mergeCell ref="F17:J17"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AE15:AJ15"/>
     <mergeCell ref="K12:R12"/>
@@ -4038,6 +5390,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4109,1074 +5462,1164 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="55" t="n"/>
-      <c r="B1" s="120" t="n"/>
-      <c r="C1" s="120" t="n"/>
-      <c r="D1" s="120" t="n"/>
-      <c r="E1" s="120" t="n"/>
-      <c r="F1" s="120" t="n"/>
-      <c r="G1" s="120" t="n"/>
-      <c r="H1" s="120" t="n"/>
-      <c r="I1" s="120" t="n"/>
-      <c r="J1" s="120" t="n"/>
-      <c r="K1" s="120" t="n"/>
-      <c r="L1" s="57" t="inlineStr">
+      <c r="A1" s="165" t="n"/>
+      <c r="B1" s="166" t="n"/>
+      <c r="C1" s="166" t="n"/>
+      <c r="D1" s="166" t="n"/>
+      <c r="E1" s="166" t="n"/>
+      <c r="F1" s="166" t="n"/>
+      <c r="G1" s="166" t="n"/>
+      <c r="H1" s="166" t="n"/>
+      <c r="I1" s="166" t="n"/>
+      <c r="J1" s="166" t="n"/>
+      <c r="K1" s="167" t="n"/>
+      <c r="L1" s="168" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW — EVIDENCE REFERENCE REGISTER</t>
         </is>
       </c>
-      <c r="M1" s="120" t="n"/>
-      <c r="N1" s="120" t="n"/>
-      <c r="O1" s="120" t="n"/>
-      <c r="P1" s="120" t="n"/>
-      <c r="Q1" s="120" t="n"/>
-      <c r="R1" s="120" t="n"/>
-      <c r="S1" s="120" t="n"/>
-      <c r="T1" s="120" t="n"/>
-      <c r="U1" s="120" t="n"/>
-      <c r="V1" s="120" t="n"/>
-      <c r="W1" s="120" t="n"/>
-      <c r="X1" s="120" t="n"/>
-      <c r="Y1" s="120" t="n"/>
-      <c r="Z1" s="120" t="n"/>
-      <c r="AA1" s="120" t="n"/>
-      <c r="AB1" s="120" t="n"/>
-      <c r="AC1" s="120" t="n"/>
-      <c r="AD1" s="120" t="n"/>
-      <c r="AE1" s="120" t="n"/>
-      <c r="AF1" s="120" t="n"/>
-      <c r="AG1" s="120" t="n"/>
-      <c r="AH1" s="120" t="n"/>
-      <c r="AI1" s="120" t="n"/>
-      <c r="AJ1" s="120" t="n"/>
-      <c r="AK1" s="120" t="n"/>
-      <c r="AL1" s="120" t="n"/>
-      <c r="AM1" s="120" t="n"/>
-      <c r="AN1" s="120" t="n"/>
-      <c r="AO1" s="120" t="n"/>
-      <c r="AP1" s="120" t="n"/>
-      <c r="AQ1" s="58" t="inlineStr">
+      <c r="M1" s="169" t="n"/>
+      <c r="N1" s="169" t="n"/>
+      <c r="O1" s="169" t="n"/>
+      <c r="P1" s="169" t="n"/>
+      <c r="Q1" s="169" t="n"/>
+      <c r="R1" s="169" t="n"/>
+      <c r="S1" s="169" t="n"/>
+      <c r="T1" s="169" t="n"/>
+      <c r="U1" s="169" t="n"/>
+      <c r="V1" s="169" t="n"/>
+      <c r="W1" s="169" t="n"/>
+      <c r="X1" s="169" t="n"/>
+      <c r="Y1" s="169" t="n"/>
+      <c r="Z1" s="169" t="n"/>
+      <c r="AA1" s="169" t="n"/>
+      <c r="AB1" s="169" t="n"/>
+      <c r="AC1" s="169" t="n"/>
+      <c r="AD1" s="169" t="n"/>
+      <c r="AE1" s="169" t="n"/>
+      <c r="AF1" s="169" t="n"/>
+      <c r="AG1" s="169" t="n"/>
+      <c r="AH1" s="169" t="n"/>
+      <c r="AI1" s="169" t="n"/>
+      <c r="AJ1" s="169" t="n"/>
+      <c r="AK1" s="169" t="n"/>
+      <c r="AL1" s="169" t="n"/>
+      <c r="AM1" s="169" t="n"/>
+      <c r="AN1" s="169" t="n"/>
+      <c r="AO1" s="169" t="n"/>
+      <c r="AP1" s="170" t="n"/>
+      <c r="AQ1" s="171" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="121" t="n"/>
-      <c r="AS1" s="121" t="n"/>
-      <c r="AT1" s="121" t="n"/>
-      <c r="AU1" s="121" t="n"/>
-      <c r="AV1" s="122" t="n"/>
-      <c r="AW1" s="61" t="inlineStr">
+      <c r="AR1" s="172" t="n"/>
+      <c r="AS1" s="172" t="n"/>
+      <c r="AT1" s="172" t="n"/>
+      <c r="AU1" s="172" t="n"/>
+      <c r="AV1" s="173" t="n"/>
+      <c r="AW1" s="174" t="inlineStr">
         <is>
           <t>FRM-111</t>
         </is>
       </c>
-      <c r="AX1" s="121" t="n"/>
-      <c r="AY1" s="121" t="n"/>
-      <c r="AZ1" s="121" t="n"/>
-      <c r="BA1" s="121" t="n"/>
-      <c r="BB1" s="121" t="n"/>
-      <c r="BC1" s="121" t="n"/>
-      <c r="BD1" s="122" t="n"/>
+      <c r="AX1" s="175" t="n"/>
+      <c r="AY1" s="175" t="n"/>
+      <c r="AZ1" s="175" t="n"/>
+      <c r="BA1" s="175" t="n"/>
+      <c r="BB1" s="175" t="n"/>
+      <c r="BC1" s="175" t="n"/>
+      <c r="BD1" s="176" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="123" t="n"/>
-      <c r="L2" s="123" t="n"/>
-      <c r="AQ2" s="64" t="inlineStr">
+      <c r="A2" s="177" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="54" t="n"/>
+      <c r="J2" s="54" t="n"/>
+      <c r="K2" s="178" t="n"/>
+      <c r="L2" s="179" t="n"/>
+      <c r="M2" s="180" t="n"/>
+      <c r="N2" s="180" t="n"/>
+      <c r="O2" s="180" t="n"/>
+      <c r="P2" s="180" t="n"/>
+      <c r="Q2" s="180" t="n"/>
+      <c r="R2" s="180" t="n"/>
+      <c r="S2" s="180" t="n"/>
+      <c r="T2" s="180" t="n"/>
+      <c r="U2" s="180" t="n"/>
+      <c r="V2" s="180" t="n"/>
+      <c r="W2" s="180" t="n"/>
+      <c r="X2" s="180" t="n"/>
+      <c r="Y2" s="180" t="n"/>
+      <c r="Z2" s="180" t="n"/>
+      <c r="AA2" s="180" t="n"/>
+      <c r="AB2" s="180" t="n"/>
+      <c r="AC2" s="180" t="n"/>
+      <c r="AD2" s="180" t="n"/>
+      <c r="AE2" s="180" t="n"/>
+      <c r="AF2" s="180" t="n"/>
+      <c r="AG2" s="180" t="n"/>
+      <c r="AH2" s="180" t="n"/>
+      <c r="AI2" s="180" t="n"/>
+      <c r="AJ2" s="180" t="n"/>
+      <c r="AK2" s="180" t="n"/>
+      <c r="AL2" s="180" t="n"/>
+      <c r="AM2" s="180" t="n"/>
+      <c r="AN2" s="180" t="n"/>
+      <c r="AO2" s="180" t="n"/>
+      <c r="AP2" s="181" t="n"/>
+      <c r="AQ2" s="182" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="124" t="n"/>
-      <c r="AS2" s="124" t="n"/>
-      <c r="AT2" s="124" t="n"/>
-      <c r="AU2" s="124" t="n"/>
-      <c r="AV2" s="125" t="n"/>
-      <c r="AW2" s="67" t="inlineStr">
+      <c r="AR2" s="183" t="n"/>
+      <c r="AS2" s="183" t="n"/>
+      <c r="AT2" s="183" t="n"/>
+      <c r="AU2" s="183" t="n"/>
+      <c r="AV2" s="184" t="n"/>
+      <c r="AW2" s="185" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="124" t="n"/>
-      <c r="AY2" s="124" t="n"/>
-      <c r="AZ2" s="124" t="n"/>
-      <c r="BA2" s="124" t="n"/>
-      <c r="BB2" s="124" t="n"/>
-      <c r="BC2" s="124" t="n"/>
-      <c r="BD2" s="125" t="n"/>
+      <c r="AX2" s="186" t="n"/>
+      <c r="AY2" s="186" t="n"/>
+      <c r="AZ2" s="186" t="n"/>
+      <c r="BA2" s="186" t="n"/>
+      <c r="BB2" s="186" t="n"/>
+      <c r="BC2" s="186" t="n"/>
+      <c r="BD2" s="187" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="123" t="n"/>
-      <c r="L3" s="126" t="n"/>
-      <c r="M3" s="124" t="n"/>
-      <c r="N3" s="124" t="n"/>
-      <c r="O3" s="124" t="n"/>
-      <c r="P3" s="124" t="n"/>
-      <c r="Q3" s="124" t="n"/>
-      <c r="R3" s="124" t="n"/>
-      <c r="S3" s="124" t="n"/>
-      <c r="T3" s="124" t="n"/>
-      <c r="U3" s="124" t="n"/>
-      <c r="V3" s="124" t="n"/>
-      <c r="W3" s="124" t="n"/>
-      <c r="X3" s="124" t="n"/>
-      <c r="Y3" s="124" t="n"/>
-      <c r="Z3" s="124" t="n"/>
-      <c r="AA3" s="124" t="n"/>
-      <c r="AB3" s="124" t="n"/>
-      <c r="AC3" s="124" t="n"/>
-      <c r="AD3" s="124" t="n"/>
-      <c r="AE3" s="124" t="n"/>
-      <c r="AF3" s="124" t="n"/>
-      <c r="AG3" s="124" t="n"/>
-      <c r="AH3" s="124" t="n"/>
-      <c r="AI3" s="124" t="n"/>
-      <c r="AJ3" s="124" t="n"/>
-      <c r="AK3" s="124" t="n"/>
-      <c r="AL3" s="124" t="n"/>
-      <c r="AM3" s="124" t="n"/>
-      <c r="AN3" s="124" t="n"/>
-      <c r="AO3" s="124" t="n"/>
-      <c r="AP3" s="124" t="n"/>
-      <c r="AQ3" s="64" t="inlineStr">
+      <c r="A3" s="177" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="178" t="n"/>
+      <c r="L3" s="179" t="n"/>
+      <c r="M3" s="180" t="n"/>
+      <c r="N3" s="180" t="n"/>
+      <c r="O3" s="180" t="n"/>
+      <c r="P3" s="180" t="n"/>
+      <c r="Q3" s="180" t="n"/>
+      <c r="R3" s="180" t="n"/>
+      <c r="S3" s="180" t="n"/>
+      <c r="T3" s="180" t="n"/>
+      <c r="U3" s="180" t="n"/>
+      <c r="V3" s="180" t="n"/>
+      <c r="W3" s="180" t="n"/>
+      <c r="X3" s="180" t="n"/>
+      <c r="Y3" s="180" t="n"/>
+      <c r="Z3" s="180" t="n"/>
+      <c r="AA3" s="180" t="n"/>
+      <c r="AB3" s="180" t="n"/>
+      <c r="AC3" s="180" t="n"/>
+      <c r="AD3" s="180" t="n"/>
+      <c r="AE3" s="180" t="n"/>
+      <c r="AF3" s="180" t="n"/>
+      <c r="AG3" s="180" t="n"/>
+      <c r="AH3" s="180" t="n"/>
+      <c r="AI3" s="180" t="n"/>
+      <c r="AJ3" s="180" t="n"/>
+      <c r="AK3" s="180" t="n"/>
+      <c r="AL3" s="180" t="n"/>
+      <c r="AM3" s="180" t="n"/>
+      <c r="AN3" s="180" t="n"/>
+      <c r="AO3" s="180" t="n"/>
+      <c r="AP3" s="181" t="n"/>
+      <c r="AQ3" s="182" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="124" t="n"/>
-      <c r="AS3" s="124" t="n"/>
-      <c r="AT3" s="124" t="n"/>
-      <c r="AU3" s="124" t="n"/>
-      <c r="AV3" s="125" t="n"/>
-      <c r="AW3" s="67" t="inlineStr">
+      <c r="AR3" s="183" t="n"/>
+      <c r="AS3" s="183" t="n"/>
+      <c r="AT3" s="183" t="n"/>
+      <c r="AU3" s="183" t="n"/>
+      <c r="AV3" s="184" t="n"/>
+      <c r="AW3" s="185" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="124" t="n"/>
-      <c r="AY3" s="124" t="n"/>
-      <c r="AZ3" s="124" t="n"/>
-      <c r="BA3" s="124" t="n"/>
-      <c r="BB3" s="124" t="n"/>
-      <c r="BC3" s="124" t="n"/>
-      <c r="BD3" s="125" t="n"/>
+      <c r="AX3" s="186" t="n"/>
+      <c r="AY3" s="186" t="n"/>
+      <c r="AZ3" s="186" t="n"/>
+      <c r="BA3" s="186" t="n"/>
+      <c r="BB3" s="186" t="n"/>
+      <c r="BC3" s="186" t="n"/>
+      <c r="BD3" s="187" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="123" t="n"/>
-      <c r="L4" s="69" t="inlineStr">
+      <c r="A4" s="177" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="178" t="n"/>
+      <c r="L4" s="188" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="64" t="inlineStr">
+      <c r="M4" s="189" t="n"/>
+      <c r="N4" s="189" t="n"/>
+      <c r="O4" s="189" t="n"/>
+      <c r="P4" s="189" t="n"/>
+      <c r="Q4" s="189" t="n"/>
+      <c r="R4" s="189" t="n"/>
+      <c r="S4" s="189" t="n"/>
+      <c r="T4" s="189" t="n"/>
+      <c r="U4" s="189" t="n"/>
+      <c r="V4" s="189" t="n"/>
+      <c r="W4" s="189" t="n"/>
+      <c r="X4" s="189" t="n"/>
+      <c r="Y4" s="189" t="n"/>
+      <c r="Z4" s="189" t="n"/>
+      <c r="AA4" s="189" t="n"/>
+      <c r="AB4" s="189" t="n"/>
+      <c r="AC4" s="189" t="n"/>
+      <c r="AD4" s="189" t="n"/>
+      <c r="AE4" s="189" t="n"/>
+      <c r="AF4" s="189" t="n"/>
+      <c r="AG4" s="189" t="n"/>
+      <c r="AH4" s="189" t="n"/>
+      <c r="AI4" s="189" t="n"/>
+      <c r="AJ4" s="189" t="n"/>
+      <c r="AK4" s="189" t="n"/>
+      <c r="AL4" s="189" t="n"/>
+      <c r="AM4" s="189" t="n"/>
+      <c r="AN4" s="189" t="n"/>
+      <c r="AO4" s="189" t="n"/>
+      <c r="AP4" s="190" t="n"/>
+      <c r="AQ4" s="182" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="124" t="n"/>
-      <c r="AS4" s="124" t="n"/>
-      <c r="AT4" s="124" t="n"/>
-      <c r="AU4" s="124" t="n"/>
-      <c r="AV4" s="125" t="n"/>
-      <c r="AW4" s="67" t="inlineStr">
+      <c r="AR4" s="183" t="n"/>
+      <c r="AS4" s="183" t="n"/>
+      <c r="AT4" s="183" t="n"/>
+      <c r="AU4" s="183" t="n"/>
+      <c r="AV4" s="184" t="n"/>
+      <c r="AW4" s="185" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AX4" s="124" t="n"/>
-      <c r="AY4" s="124" t="n"/>
-      <c r="AZ4" s="124" t="n"/>
-      <c r="BA4" s="124" t="n"/>
-      <c r="BB4" s="124" t="n"/>
-      <c r="BC4" s="124" t="n"/>
-      <c r="BD4" s="125" t="n"/>
+      <c r="AX4" s="186" t="n"/>
+      <c r="AY4" s="186" t="n"/>
+      <c r="AZ4" s="186" t="n"/>
+      <c r="BA4" s="186" t="n"/>
+      <c r="BB4" s="186" t="n"/>
+      <c r="BC4" s="186" t="n"/>
+      <c r="BD4" s="187" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="126" t="n"/>
-      <c r="B5" s="124" t="n"/>
-      <c r="C5" s="124" t="n"/>
-      <c r="D5" s="124" t="n"/>
-      <c r="E5" s="124" t="n"/>
-      <c r="F5" s="124" t="n"/>
-      <c r="G5" s="124" t="n"/>
-      <c r="H5" s="124" t="n"/>
-      <c r="I5" s="124" t="n"/>
-      <c r="J5" s="124" t="n"/>
-      <c r="K5" s="124" t="n"/>
-      <c r="L5" s="70" t="inlineStr">
+      <c r="A5" s="191" t="n"/>
+      <c r="B5" s="192" t="n"/>
+      <c r="C5" s="192" t="n"/>
+      <c r="D5" s="192" t="n"/>
+      <c r="E5" s="192" t="n"/>
+      <c r="F5" s="192" t="n"/>
+      <c r="G5" s="192" t="n"/>
+      <c r="H5" s="192" t="n"/>
+      <c r="I5" s="192" t="n"/>
+      <c r="J5" s="192" t="n"/>
+      <c r="K5" s="193" t="n"/>
+      <c r="L5" s="194" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="124" t="n"/>
-      <c r="N5" s="124" t="n"/>
-      <c r="O5" s="124" t="n"/>
-      <c r="P5" s="124" t="n"/>
-      <c r="Q5" s="124" t="n"/>
-      <c r="R5" s="124" t="n"/>
-      <c r="S5" s="124" t="n"/>
-      <c r="T5" s="124" t="n"/>
-      <c r="U5" s="124" t="n"/>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
-      <c r="X5" s="124" t="n"/>
-      <c r="Y5" s="124" t="n"/>
-      <c r="Z5" s="124" t="n"/>
-      <c r="AA5" s="124" t="n"/>
-      <c r="AB5" s="124" t="n"/>
-      <c r="AC5" s="124" t="n"/>
-      <c r="AD5" s="124" t="n"/>
-      <c r="AE5" s="124" t="n"/>
-      <c r="AF5" s="124" t="n"/>
-      <c r="AG5" s="124" t="n"/>
-      <c r="AH5" s="124" t="n"/>
-      <c r="AI5" s="124" t="n"/>
-      <c r="AJ5" s="124" t="n"/>
-      <c r="AK5" s="124" t="n"/>
-      <c r="AL5" s="124" t="n"/>
-      <c r="AM5" s="124" t="n"/>
-      <c r="AN5" s="124" t="n"/>
-      <c r="AO5" s="124" t="n"/>
-      <c r="AP5" s="124" t="n"/>
-      <c r="AQ5" s="64" t="inlineStr">
+      <c r="M5" s="195" t="n"/>
+      <c r="N5" s="195" t="n"/>
+      <c r="O5" s="195" t="n"/>
+      <c r="P5" s="195" t="n"/>
+      <c r="Q5" s="195" t="n"/>
+      <c r="R5" s="195" t="n"/>
+      <c r="S5" s="195" t="n"/>
+      <c r="T5" s="195" t="n"/>
+      <c r="U5" s="195" t="n"/>
+      <c r="V5" s="195" t="n"/>
+      <c r="W5" s="195" t="n"/>
+      <c r="X5" s="195" t="n"/>
+      <c r="Y5" s="195" t="n"/>
+      <c r="Z5" s="195" t="n"/>
+      <c r="AA5" s="195" t="n"/>
+      <c r="AB5" s="195" t="n"/>
+      <c r="AC5" s="195" t="n"/>
+      <c r="AD5" s="195" t="n"/>
+      <c r="AE5" s="195" t="n"/>
+      <c r="AF5" s="195" t="n"/>
+      <c r="AG5" s="195" t="n"/>
+      <c r="AH5" s="195" t="n"/>
+      <c r="AI5" s="195" t="n"/>
+      <c r="AJ5" s="195" t="n"/>
+      <c r="AK5" s="195" t="n"/>
+      <c r="AL5" s="195" t="n"/>
+      <c r="AM5" s="195" t="n"/>
+      <c r="AN5" s="195" t="n"/>
+      <c r="AO5" s="195" t="n"/>
+      <c r="AP5" s="196" t="n"/>
+      <c r="AQ5" s="197" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="124" t="n"/>
-      <c r="AS5" s="124" t="n"/>
-      <c r="AT5" s="124" t="n"/>
-      <c r="AU5" s="124" t="n"/>
-      <c r="AV5" s="125" t="n"/>
-      <c r="AW5" s="67" t="inlineStr">
+      <c r="AR5" s="198" t="n"/>
+      <c r="AS5" s="198" t="n"/>
+      <c r="AT5" s="198" t="n"/>
+      <c r="AU5" s="198" t="n"/>
+      <c r="AV5" s="199" t="n"/>
+      <c r="AW5" s="200" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="124" t="n"/>
-      <c r="AY5" s="124" t="n"/>
-      <c r="AZ5" s="124" t="n"/>
-      <c r="BA5" s="124" t="n"/>
-      <c r="BB5" s="124" t="n"/>
-      <c r="BC5" s="124" t="n"/>
-      <c r="BD5" s="125" t="n"/>
+      <c r="AX5" s="201" t="n"/>
+      <c r="AY5" s="201" t="n"/>
+      <c r="AZ5" s="201" t="n"/>
+      <c r="BA5" s="201" t="n"/>
+      <c r="BB5" s="201" t="n"/>
+      <c r="BC5" s="201" t="n"/>
+      <c r="BD5" s="202" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="71" t="n"/>
-      <c r="B6" s="119" t="n"/>
-      <c r="C6" s="119" t="n"/>
-      <c r="D6" s="119" t="n"/>
-      <c r="E6" s="119" t="n"/>
-      <c r="F6" s="119" t="n"/>
-      <c r="G6" s="119" t="n"/>
-      <c r="H6" s="119" t="n"/>
-      <c r="I6" s="119" t="n"/>
-      <c r="J6" s="119" t="n"/>
-      <c r="K6" s="119" t="n"/>
-      <c r="L6" s="119" t="n"/>
-      <c r="M6" s="119" t="n"/>
-      <c r="N6" s="119" t="n"/>
-      <c r="O6" s="119" t="n"/>
-      <c r="P6" s="119" t="n"/>
-      <c r="Q6" s="119" t="n"/>
-      <c r="R6" s="119" t="n"/>
-      <c r="S6" s="119" t="n"/>
-      <c r="T6" s="119" t="n"/>
-      <c r="U6" s="119" t="n"/>
-      <c r="V6" s="119" t="n"/>
-      <c r="W6" s="119" t="n"/>
-      <c r="X6" s="119" t="n"/>
-      <c r="Y6" s="119" t="n"/>
-      <c r="Z6" s="119" t="n"/>
-      <c r="AA6" s="119" t="n"/>
-      <c r="AB6" s="119" t="n"/>
-      <c r="AC6" s="119" t="n"/>
-      <c r="AD6" s="119" t="n"/>
-      <c r="AE6" s="119" t="n"/>
-      <c r="AF6" s="119" t="n"/>
-      <c r="AG6" s="119" t="n"/>
-      <c r="AH6" s="119" t="n"/>
-      <c r="AI6" s="119" t="n"/>
-      <c r="AJ6" s="119" t="n"/>
-      <c r="AK6" s="119" t="n"/>
-      <c r="AL6" s="119" t="n"/>
-      <c r="AM6" s="119" t="n"/>
-      <c r="AN6" s="119" t="n"/>
-      <c r="AO6" s="119" t="n"/>
-      <c r="AP6" s="119" t="n"/>
-      <c r="AQ6" s="119" t="n"/>
-      <c r="AR6" s="119" t="n"/>
-      <c r="AS6" s="119" t="n"/>
-      <c r="AT6" s="119" t="n"/>
-      <c r="AU6" s="119" t="n"/>
-      <c r="AV6" s="119" t="n"/>
-      <c r="AW6" s="119" t="n"/>
-      <c r="AX6" s="119" t="n"/>
-      <c r="AY6" s="119" t="n"/>
-      <c r="AZ6" s="119" t="n"/>
-      <c r="BA6" s="119" t="n"/>
-      <c r="BB6" s="119" t="n"/>
-      <c r="BC6" s="119" t="n"/>
-      <c r="BD6" s="119" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="203" t="n"/>
+      <c r="B6" s="203" t="n"/>
+      <c r="C6" s="203" t="n"/>
+      <c r="D6" s="203" t="n"/>
+      <c r="E6" s="203" t="n"/>
+      <c r="F6" s="203" t="n"/>
+      <c r="G6" s="203" t="n"/>
+      <c r="H6" s="203" t="n"/>
+      <c r="I6" s="203" t="n"/>
+      <c r="J6" s="203" t="n"/>
+      <c r="K6" s="203" t="n"/>
+      <c r="L6" s="203" t="n"/>
+      <c r="M6" s="203" t="n"/>
+      <c r="N6" s="203" t="n"/>
+      <c r="O6" s="203" t="n"/>
+      <c r="P6" s="203" t="n"/>
+      <c r="Q6" s="203" t="n"/>
+      <c r="R6" s="203" t="n"/>
+      <c r="S6" s="203" t="n"/>
+      <c r="T6" s="203" t="n"/>
+      <c r="U6" s="203" t="n"/>
+      <c r="V6" s="203" t="n"/>
+      <c r="W6" s="203" t="n"/>
+      <c r="X6" s="203" t="n"/>
+      <c r="Y6" s="203" t="n"/>
+      <c r="Z6" s="203" t="n"/>
+      <c r="AA6" s="203" t="n"/>
+      <c r="AB6" s="203" t="n"/>
+      <c r="AC6" s="203" t="n"/>
+      <c r="AD6" s="203" t="n"/>
+      <c r="AE6" s="203" t="n"/>
+      <c r="AF6" s="203" t="n"/>
+      <c r="AG6" s="203" t="n"/>
+      <c r="AH6" s="203" t="n"/>
+      <c r="AI6" s="203" t="n"/>
+      <c r="AJ6" s="203" t="n"/>
+      <c r="AK6" s="203" t="n"/>
+      <c r="AL6" s="203" t="n"/>
+      <c r="AM6" s="203" t="n"/>
+      <c r="AN6" s="203" t="n"/>
+      <c r="AO6" s="203" t="n"/>
+      <c r="AP6" s="203" t="n"/>
+      <c r="AQ6" s="203" t="n"/>
+      <c r="AR6" s="203" t="n"/>
+      <c r="AS6" s="203" t="n"/>
+      <c r="AT6" s="203" t="n"/>
+      <c r="AU6" s="203" t="n"/>
+      <c r="AV6" s="203" t="n"/>
+      <c r="AW6" s="203" t="n"/>
+      <c r="AX6" s="203" t="n"/>
+      <c r="AY6" s="203" t="n"/>
+      <c r="AZ6" s="203" t="n"/>
+      <c r="BA6" s="203" t="n"/>
+      <c r="BB6" s="203" t="n"/>
+      <c r="BC6" s="203" t="n"/>
+      <c r="BD6" s="203" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="72" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="121" t="n"/>
-      <c r="C7" s="121" t="n"/>
-      <c r="D7" s="121" t="n"/>
-      <c r="E7" s="121" t="n"/>
-      <c r="F7" s="121" t="n"/>
-      <c r="G7" s="121" t="n"/>
-      <c r="H7" s="121" t="n"/>
-      <c r="I7" s="121" t="n"/>
-      <c r="J7" s="121" t="n"/>
-      <c r="K7" s="121" t="n"/>
-      <c r="L7" s="121" t="n"/>
-      <c r="M7" s="121" t="n"/>
-      <c r="N7" s="121" t="n"/>
-      <c r="O7" s="121" t="n"/>
-      <c r="P7" s="121" t="n"/>
-      <c r="Q7" s="121" t="n"/>
-      <c r="R7" s="121" t="n"/>
-      <c r="S7" s="121" t="n"/>
-      <c r="T7" s="121" t="n"/>
-      <c r="U7" s="121" t="n"/>
-      <c r="V7" s="121" t="n"/>
-      <c r="W7" s="121" t="n"/>
-      <c r="X7" s="121" t="n"/>
-      <c r="Y7" s="121" t="n"/>
-      <c r="Z7" s="121" t="n"/>
-      <c r="AA7" s="121" t="n"/>
-      <c r="AB7" s="121" t="n"/>
-      <c r="AC7" s="121" t="n"/>
-      <c r="AD7" s="121" t="n"/>
-      <c r="AE7" s="121" t="n"/>
-      <c r="AF7" s="121" t="n"/>
-      <c r="AG7" s="121" t="n"/>
-      <c r="AH7" s="121" t="n"/>
-      <c r="AI7" s="121" t="n"/>
-      <c r="AJ7" s="121" t="n"/>
-      <c r="AK7" s="121" t="n"/>
-      <c r="AL7" s="121" t="n"/>
-      <c r="AM7" s="121" t="n"/>
-      <c r="AN7" s="121" t="n"/>
-      <c r="AO7" s="121" t="n"/>
-      <c r="AP7" s="121" t="n"/>
-      <c r="AQ7" s="121" t="n"/>
-      <c r="AR7" s="121" t="n"/>
-      <c r="AS7" s="121" t="n"/>
-      <c r="AT7" s="121" t="n"/>
-      <c r="AU7" s="121" t="n"/>
-      <c r="AV7" s="121" t="n"/>
-      <c r="AW7" s="121" t="n"/>
-      <c r="AX7" s="121" t="n"/>
-      <c r="AY7" s="121" t="n"/>
-      <c r="AZ7" s="121" t="n"/>
-      <c r="BA7" s="121" t="n"/>
-      <c r="BB7" s="121" t="n"/>
-      <c r="BC7" s="121" t="n"/>
-      <c r="BD7" s="122" t="n"/>
+      <c r="B7" s="205" t="n"/>
+      <c r="C7" s="205" t="n"/>
+      <c r="D7" s="205" t="n"/>
+      <c r="E7" s="205" t="n"/>
+      <c r="F7" s="205" t="n"/>
+      <c r="G7" s="205" t="n"/>
+      <c r="H7" s="205" t="n"/>
+      <c r="I7" s="205" t="n"/>
+      <c r="J7" s="205" t="n"/>
+      <c r="K7" s="205" t="n"/>
+      <c r="L7" s="205" t="n"/>
+      <c r="M7" s="205" t="n"/>
+      <c r="N7" s="205" t="n"/>
+      <c r="O7" s="205" t="n"/>
+      <c r="P7" s="205" t="n"/>
+      <c r="Q7" s="205" t="n"/>
+      <c r="R7" s="205" t="n"/>
+      <c r="S7" s="205" t="n"/>
+      <c r="T7" s="205" t="n"/>
+      <c r="U7" s="205" t="n"/>
+      <c r="V7" s="205" t="n"/>
+      <c r="W7" s="205" t="n"/>
+      <c r="X7" s="205" t="n"/>
+      <c r="Y7" s="205" t="n"/>
+      <c r="Z7" s="205" t="n"/>
+      <c r="AA7" s="205" t="n"/>
+      <c r="AB7" s="205" t="n"/>
+      <c r="AC7" s="205" t="n"/>
+      <c r="AD7" s="205" t="n"/>
+      <c r="AE7" s="205" t="n"/>
+      <c r="AF7" s="205" t="n"/>
+      <c r="AG7" s="205" t="n"/>
+      <c r="AH7" s="205" t="n"/>
+      <c r="AI7" s="205" t="n"/>
+      <c r="AJ7" s="205" t="n"/>
+      <c r="AK7" s="205" t="n"/>
+      <c r="AL7" s="205" t="n"/>
+      <c r="AM7" s="205" t="n"/>
+      <c r="AN7" s="205" t="n"/>
+      <c r="AO7" s="205" t="n"/>
+      <c r="AP7" s="205" t="n"/>
+      <c r="AQ7" s="205" t="n"/>
+      <c r="AR7" s="205" t="n"/>
+      <c r="AS7" s="205" t="n"/>
+      <c r="AT7" s="205" t="n"/>
+      <c r="AU7" s="205" t="n"/>
+      <c r="AV7" s="205" t="n"/>
+      <c r="AW7" s="205" t="n"/>
+      <c r="AX7" s="205" t="n"/>
+      <c r="AY7" s="205" t="n"/>
+      <c r="AZ7" s="205" t="n"/>
+      <c r="BA7" s="205" t="n"/>
+      <c r="BB7" s="205" t="n"/>
+      <c r="BC7" s="205" t="n"/>
+      <c r="BD7" s="206" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="207" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="107" t="n"/>
-      <c r="C8" s="107" t="n"/>
-      <c r="D8" s="107" t="n"/>
-      <c r="E8" s="107" t="n"/>
-      <c r="F8" s="107" t="n"/>
-      <c r="G8" s="107" t="n"/>
-      <c r="H8" s="107" t="n"/>
-      <c r="I8" s="107" t="n"/>
-      <c r="J8" s="108" t="n"/>
-      <c r="K8" s="90" t="inlineStr">
+      <c r="B8" s="208" t="n"/>
+      <c r="C8" s="208" t="n"/>
+      <c r="D8" s="208" t="n"/>
+      <c r="E8" s="208" t="n"/>
+      <c r="F8" s="208" t="n"/>
+      <c r="G8" s="208" t="n"/>
+      <c r="H8" s="208" t="n"/>
+      <c r="I8" s="208" t="n"/>
+      <c r="J8" s="208" t="n"/>
+      <c r="K8" s="154" t="inlineStr">
         <is>
           <t>Access-role master and effective rights remain in the live system + ANNEX-IT-001 / 025 control set; workbook captures request / review evidence only, not the source permission model.</t>
         </is>
       </c>
-      <c r="L8" s="107" t="n"/>
-      <c r="M8" s="107" t="n"/>
-      <c r="N8" s="107" t="n"/>
-      <c r="O8" s="107" t="n"/>
-      <c r="P8" s="107" t="n"/>
-      <c r="Q8" s="107" t="n"/>
-      <c r="R8" s="107" t="n"/>
-      <c r="S8" s="107" t="n"/>
-      <c r="T8" s="107" t="n"/>
-      <c r="U8" s="107" t="n"/>
-      <c r="V8" s="107" t="n"/>
-      <c r="W8" s="107" t="n"/>
-      <c r="X8" s="107" t="n"/>
-      <c r="Y8" s="107" t="n"/>
-      <c r="Z8" s="107" t="n"/>
-      <c r="AA8" s="107" t="n"/>
-      <c r="AB8" s="108" t="n"/>
-      <c r="AC8" s="20" t="inlineStr"/>
-      <c r="AD8" s="91" t="n"/>
-      <c r="AE8" s="91" t="n"/>
-      <c r="AF8" s="91" t="n"/>
-      <c r="AG8" s="91" t="n"/>
-      <c r="AH8" s="91" t="n"/>
-      <c r="AI8" s="91" t="n"/>
-      <c r="AJ8" s="91" t="n"/>
-      <c r="AK8" s="91" t="n"/>
-      <c r="AL8" s="91" t="n"/>
-      <c r="AM8" s="20" t="inlineStr"/>
-      <c r="AN8" s="91" t="n"/>
-      <c r="AO8" s="91" t="n"/>
-      <c r="AP8" s="91" t="n"/>
-      <c r="AQ8" s="91" t="n"/>
-      <c r="AR8" s="91" t="n"/>
-      <c r="AS8" s="91" t="n"/>
-      <c r="AT8" s="91" t="n"/>
-      <c r="AU8" s="91" t="n"/>
-      <c r="AV8" s="91" t="n"/>
-      <c r="AW8" s="91" t="n"/>
-      <c r="AX8" s="91" t="n"/>
-      <c r="AY8" s="91" t="n"/>
-      <c r="AZ8" s="91" t="n"/>
-      <c r="BA8" s="91" t="n"/>
-      <c r="BB8" s="91" t="n"/>
-      <c r="BC8" s="91" t="n"/>
-      <c r="BD8" s="91" t="n"/>
+      <c r="L8" s="208" t="n"/>
+      <c r="M8" s="208" t="n"/>
+      <c r="N8" s="208" t="n"/>
+      <c r="O8" s="208" t="n"/>
+      <c r="P8" s="208" t="n"/>
+      <c r="Q8" s="208" t="n"/>
+      <c r="R8" s="208" t="n"/>
+      <c r="S8" s="208" t="n"/>
+      <c r="T8" s="208" t="n"/>
+      <c r="U8" s="208" t="n"/>
+      <c r="V8" s="208" t="n"/>
+      <c r="W8" s="208" t="n"/>
+      <c r="X8" s="208" t="n"/>
+      <c r="Y8" s="208" t="n"/>
+      <c r="Z8" s="208" t="n"/>
+      <c r="AA8" s="208" t="n"/>
+      <c r="AB8" s="208" t="n"/>
+      <c r="AC8" s="155" t="inlineStr"/>
+      <c r="AD8" s="208" t="n"/>
+      <c r="AE8" s="208" t="n"/>
+      <c r="AF8" s="208" t="n"/>
+      <c r="AG8" s="208" t="n"/>
+      <c r="AH8" s="208" t="n"/>
+      <c r="AI8" s="208" t="n"/>
+      <c r="AJ8" s="208" t="n"/>
+      <c r="AK8" s="208" t="n"/>
+      <c r="AL8" s="208" t="n"/>
+      <c r="AM8" s="155" t="inlineStr"/>
+      <c r="AN8" s="208" t="n"/>
+      <c r="AO8" s="208" t="n"/>
+      <c r="AP8" s="208" t="n"/>
+      <c r="AQ8" s="208" t="n"/>
+      <c r="AR8" s="208" t="n"/>
+      <c r="AS8" s="208" t="n"/>
+      <c r="AT8" s="208" t="n"/>
+      <c r="AU8" s="208" t="n"/>
+      <c r="AV8" s="208" t="n"/>
+      <c r="AW8" s="208" t="n"/>
+      <c r="AX8" s="208" t="n"/>
+      <c r="AY8" s="208" t="n"/>
+      <c r="AZ8" s="208" t="n"/>
+      <c r="BA8" s="208" t="n"/>
+      <c r="BB8" s="208" t="n"/>
+      <c r="BC8" s="208" t="n"/>
+      <c r="BD8" s="238" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="212" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="107" t="n"/>
-      <c r="C9" s="107" t="n"/>
-      <c r="D9" s="107" t="n"/>
-      <c r="E9" s="107" t="n"/>
-      <c r="F9" s="107" t="n"/>
-      <c r="G9" s="107" t="n"/>
-      <c r="H9" s="107" t="n"/>
-      <c r="I9" s="107" t="n"/>
-      <c r="J9" s="108" t="n"/>
-      <c r="K9" s="90" t="inlineStr">
+      <c r="B9" s="213" t="n"/>
+      <c r="C9" s="213" t="n"/>
+      <c r="D9" s="213" t="n"/>
+      <c r="E9" s="213" t="n"/>
+      <c r="F9" s="213" t="n"/>
+      <c r="G9" s="213" t="n"/>
+      <c r="H9" s="213" t="n"/>
+      <c r="I9" s="213" t="n"/>
+      <c r="J9" s="213" t="n"/>
+      <c r="K9" s="239" t="inlineStr">
         <is>
           <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
         </is>
       </c>
-      <c r="L9" s="107" t="n"/>
-      <c r="M9" s="107" t="n"/>
-      <c r="N9" s="107" t="n"/>
-      <c r="O9" s="107" t="n"/>
-      <c r="P9" s="107" t="n"/>
-      <c r="Q9" s="107" t="n"/>
-      <c r="R9" s="107" t="n"/>
-      <c r="S9" s="107" t="n"/>
-      <c r="T9" s="107" t="n"/>
-      <c r="U9" s="107" t="n"/>
-      <c r="V9" s="107" t="n"/>
-      <c r="W9" s="107" t="n"/>
-      <c r="X9" s="107" t="n"/>
-      <c r="Y9" s="107" t="n"/>
-      <c r="Z9" s="107" t="n"/>
-      <c r="AA9" s="107" t="n"/>
-      <c r="AB9" s="108" t="n"/>
-      <c r="AC9" s="20" t="inlineStr"/>
-      <c r="AD9" s="91" t="n"/>
-      <c r="AE9" s="91" t="n"/>
-      <c r="AF9" s="91" t="n"/>
-      <c r="AG9" s="91" t="n"/>
-      <c r="AH9" s="91" t="n"/>
-      <c r="AI9" s="91" t="n"/>
-      <c r="AJ9" s="91" t="n"/>
-      <c r="AK9" s="91" t="n"/>
-      <c r="AL9" s="91" t="n"/>
-      <c r="AM9" s="20" t="inlineStr"/>
-      <c r="AN9" s="91" t="n"/>
-      <c r="AO9" s="91" t="n"/>
-      <c r="AP9" s="91" t="n"/>
-      <c r="AQ9" s="91" t="n"/>
-      <c r="AR9" s="91" t="n"/>
-      <c r="AS9" s="91" t="n"/>
-      <c r="AT9" s="91" t="n"/>
-      <c r="AU9" s="91" t="n"/>
-      <c r="AV9" s="91" t="n"/>
-      <c r="AW9" s="91" t="n"/>
-      <c r="AX9" s="91" t="n"/>
-      <c r="AY9" s="91" t="n"/>
-      <c r="AZ9" s="91" t="n"/>
-      <c r="BA9" s="91" t="n"/>
-      <c r="BB9" s="91" t="n"/>
-      <c r="BC9" s="91" t="n"/>
-      <c r="BD9" s="91" t="n"/>
+      <c r="L9" s="213" t="n"/>
+      <c r="M9" s="213" t="n"/>
+      <c r="N9" s="213" t="n"/>
+      <c r="O9" s="213" t="n"/>
+      <c r="P9" s="213" t="n"/>
+      <c r="Q9" s="213" t="n"/>
+      <c r="R9" s="213" t="n"/>
+      <c r="S9" s="213" t="n"/>
+      <c r="T9" s="213" t="n"/>
+      <c r="U9" s="213" t="n"/>
+      <c r="V9" s="213" t="n"/>
+      <c r="W9" s="213" t="n"/>
+      <c r="X9" s="213" t="n"/>
+      <c r="Y9" s="213" t="n"/>
+      <c r="Z9" s="213" t="n"/>
+      <c r="AA9" s="213" t="n"/>
+      <c r="AB9" s="213" t="n"/>
+      <c r="AC9" s="240" t="inlineStr"/>
+      <c r="AD9" s="213" t="n"/>
+      <c r="AE9" s="213" t="n"/>
+      <c r="AF9" s="213" t="n"/>
+      <c r="AG9" s="213" t="n"/>
+      <c r="AH9" s="213" t="n"/>
+      <c r="AI9" s="213" t="n"/>
+      <c r="AJ9" s="213" t="n"/>
+      <c r="AK9" s="213" t="n"/>
+      <c r="AL9" s="213" t="n"/>
+      <c r="AM9" s="240" t="inlineStr"/>
+      <c r="AN9" s="213" t="n"/>
+      <c r="AO9" s="213" t="n"/>
+      <c r="AP9" s="213" t="n"/>
+      <c r="AQ9" s="213" t="n"/>
+      <c r="AR9" s="213" t="n"/>
+      <c r="AS9" s="213" t="n"/>
+      <c r="AT9" s="213" t="n"/>
+      <c r="AU9" s="213" t="n"/>
+      <c r="AV9" s="213" t="n"/>
+      <c r="AW9" s="213" t="n"/>
+      <c r="AX9" s="213" t="n"/>
+      <c r="AY9" s="213" t="n"/>
+      <c r="AZ9" s="213" t="n"/>
+      <c r="BA9" s="213" t="n"/>
+      <c r="BB9" s="213" t="n"/>
+      <c r="BC9" s="213" t="n"/>
+      <c r="BD9" s="241" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="204" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B10" s="107" t="n"/>
-      <c r="C10" s="107" t="n"/>
-      <c r="D10" s="107" t="n"/>
-      <c r="E10" s="107" t="n"/>
-      <c r="F10" s="107" t="n"/>
-      <c r="G10" s="107" t="n"/>
-      <c r="H10" s="107" t="n"/>
-      <c r="I10" s="107" t="n"/>
-      <c r="J10" s="107" t="n"/>
-      <c r="K10" s="107" t="n"/>
-      <c r="L10" s="107" t="n"/>
-      <c r="M10" s="107" t="n"/>
-      <c r="N10" s="107" t="n"/>
-      <c r="O10" s="107" t="n"/>
-      <c r="P10" s="107" t="n"/>
-      <c r="Q10" s="107" t="n"/>
-      <c r="R10" s="107" t="n"/>
-      <c r="S10" s="107" t="n"/>
-      <c r="T10" s="107" t="n"/>
-      <c r="U10" s="107" t="n"/>
-      <c r="V10" s="107" t="n"/>
-      <c r="W10" s="107" t="n"/>
-      <c r="X10" s="107" t="n"/>
-      <c r="Y10" s="107" t="n"/>
-      <c r="Z10" s="107" t="n"/>
-      <c r="AA10" s="107" t="n"/>
-      <c r="AB10" s="107" t="n"/>
-      <c r="AC10" s="107" t="n"/>
-      <c r="AD10" s="107" t="n"/>
-      <c r="AE10" s="107" t="n"/>
-      <c r="AF10" s="107" t="n"/>
-      <c r="AG10" s="107" t="n"/>
-      <c r="AH10" s="107" t="n"/>
-      <c r="AI10" s="107" t="n"/>
-      <c r="AJ10" s="107" t="n"/>
-      <c r="AK10" s="107" t="n"/>
-      <c r="AL10" s="107" t="n"/>
-      <c r="AM10" s="107" t="n"/>
-      <c r="AN10" s="107" t="n"/>
-      <c r="AO10" s="107" t="n"/>
-      <c r="AP10" s="107" t="n"/>
-      <c r="AQ10" s="107" t="n"/>
-      <c r="AR10" s="107" t="n"/>
-      <c r="AS10" s="107" t="n"/>
-      <c r="AT10" s="107" t="n"/>
-      <c r="AU10" s="107" t="n"/>
-      <c r="AV10" s="107" t="n"/>
-      <c r="AW10" s="107" t="n"/>
-      <c r="AX10" s="107" t="n"/>
-      <c r="AY10" s="107" t="n"/>
-      <c r="AZ10" s="107" t="n"/>
-      <c r="BA10" s="107" t="n"/>
-      <c r="BB10" s="107" t="n"/>
-      <c r="BC10" s="107" t="n"/>
-      <c r="BD10" s="108" t="n"/>
+      <c r="B10" s="205" t="n"/>
+      <c r="C10" s="205" t="n"/>
+      <c r="D10" s="205" t="n"/>
+      <c r="E10" s="205" t="n"/>
+      <c r="F10" s="205" t="n"/>
+      <c r="G10" s="205" t="n"/>
+      <c r="H10" s="205" t="n"/>
+      <c r="I10" s="205" t="n"/>
+      <c r="J10" s="205" t="n"/>
+      <c r="K10" s="205" t="n"/>
+      <c r="L10" s="205" t="n"/>
+      <c r="M10" s="205" t="n"/>
+      <c r="N10" s="205" t="n"/>
+      <c r="O10" s="205" t="n"/>
+      <c r="P10" s="205" t="n"/>
+      <c r="Q10" s="205" t="n"/>
+      <c r="R10" s="205" t="n"/>
+      <c r="S10" s="205" t="n"/>
+      <c r="T10" s="205" t="n"/>
+      <c r="U10" s="205" t="n"/>
+      <c r="V10" s="205" t="n"/>
+      <c r="W10" s="205" t="n"/>
+      <c r="X10" s="205" t="n"/>
+      <c r="Y10" s="205" t="n"/>
+      <c r="Z10" s="205" t="n"/>
+      <c r="AA10" s="205" t="n"/>
+      <c r="AB10" s="205" t="n"/>
+      <c r="AC10" s="205" t="n"/>
+      <c r="AD10" s="205" t="n"/>
+      <c r="AE10" s="205" t="n"/>
+      <c r="AF10" s="205" t="n"/>
+      <c r="AG10" s="205" t="n"/>
+      <c r="AH10" s="205" t="n"/>
+      <c r="AI10" s="205" t="n"/>
+      <c r="AJ10" s="205" t="n"/>
+      <c r="AK10" s="205" t="n"/>
+      <c r="AL10" s="205" t="n"/>
+      <c r="AM10" s="205" t="n"/>
+      <c r="AN10" s="205" t="n"/>
+      <c r="AO10" s="205" t="n"/>
+      <c r="AP10" s="205" t="n"/>
+      <c r="AQ10" s="205" t="n"/>
+      <c r="AR10" s="205" t="n"/>
+      <c r="AS10" s="205" t="n"/>
+      <c r="AT10" s="205" t="n"/>
+      <c r="AU10" s="205" t="n"/>
+      <c r="AV10" s="205" t="n"/>
+      <c r="AW10" s="205" t="n"/>
+      <c r="AX10" s="205" t="n"/>
+      <c r="AY10" s="205" t="n"/>
+      <c r="AZ10" s="205" t="n"/>
+      <c r="BA10" s="205" t="n"/>
+      <c r="BB10" s="205" t="n"/>
+      <c r="BC10" s="205" t="n"/>
+      <c r="BD10" s="206" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="92" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="242" t="inlineStr">
         <is>
           <t>Evidence ID</t>
         </is>
       </c>
-      <c r="B11" s="107" t="n"/>
-      <c r="C11" s="107" t="n"/>
-      <c r="D11" s="107" t="n"/>
-      <c r="E11" s="107" t="n"/>
-      <c r="F11" s="107" t="n"/>
-      <c r="G11" s="107" t="n"/>
-      <c r="H11" s="108" t="n"/>
-      <c r="I11" s="92" t="inlineStr">
+      <c r="B11" s="243" t="n"/>
+      <c r="C11" s="243" t="n"/>
+      <c r="D11" s="243" t="n"/>
+      <c r="E11" s="243" t="n"/>
+      <c r="F11" s="243" t="n"/>
+      <c r="G11" s="243" t="n"/>
+      <c r="H11" s="243" t="n"/>
+      <c r="I11" s="244" t="inlineStr">
         <is>
           <t>Related Record</t>
         </is>
       </c>
-      <c r="J11" s="107" t="n"/>
-      <c r="K11" s="107" t="n"/>
-      <c r="L11" s="107" t="n"/>
-      <c r="M11" s="108" t="n"/>
-      <c r="N11" s="92" t="inlineStr">
+      <c r="J11" s="243" t="n"/>
+      <c r="K11" s="243" t="n"/>
+      <c r="L11" s="243" t="n"/>
+      <c r="M11" s="243" t="n"/>
+      <c r="N11" s="244" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O11" s="107" t="n"/>
-      <c r="P11" s="107" t="n"/>
-      <c r="Q11" s="107" t="n"/>
-      <c r="R11" s="107" t="n"/>
-      <c r="S11" s="107" t="n"/>
-      <c r="T11" s="107" t="n"/>
-      <c r="U11" s="107" t="n"/>
-      <c r="V11" s="107" t="n"/>
-      <c r="W11" s="107" t="n"/>
-      <c r="X11" s="108" t="n"/>
-      <c r="Y11" s="92" t="inlineStr">
+      <c r="O11" s="243" t="n"/>
+      <c r="P11" s="243" t="n"/>
+      <c r="Q11" s="243" t="n"/>
+      <c r="R11" s="243" t="n"/>
+      <c r="S11" s="243" t="n"/>
+      <c r="T11" s="243" t="n"/>
+      <c r="U11" s="243" t="n"/>
+      <c r="V11" s="243" t="n"/>
+      <c r="W11" s="243" t="n"/>
+      <c r="X11" s="243" t="n"/>
+      <c r="Y11" s="244" t="inlineStr">
         <is>
           <t>Source System</t>
         </is>
       </c>
-      <c r="Z11" s="107" t="n"/>
-      <c r="AA11" s="107" t="n"/>
-      <c r="AB11" s="107" t="n"/>
-      <c r="AC11" s="108" t="n"/>
-      <c r="AD11" s="92" t="inlineStr">
+      <c r="Z11" s="243" t="n"/>
+      <c r="AA11" s="243" t="n"/>
+      <c r="AB11" s="243" t="n"/>
+      <c r="AC11" s="243" t="n"/>
+      <c r="AD11" s="244" t="inlineStr">
         <is>
           <t>Reference Path or Link</t>
         </is>
       </c>
-      <c r="AE11" s="107" t="n"/>
-      <c r="AF11" s="107" t="n"/>
-      <c r="AG11" s="107" t="n"/>
-      <c r="AH11" s="107" t="n"/>
-      <c r="AI11" s="107" t="n"/>
-      <c r="AJ11" s="108" t="n"/>
-      <c r="AK11" s="92" t="inlineStr">
+      <c r="AE11" s="243" t="n"/>
+      <c r="AF11" s="243" t="n"/>
+      <c r="AG11" s="243" t="n"/>
+      <c r="AH11" s="243" t="n"/>
+      <c r="AI11" s="243" t="n"/>
+      <c r="AJ11" s="243" t="n"/>
+      <c r="AK11" s="244" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AL11" s="107" t="n"/>
-      <c r="AM11" s="107" t="n"/>
-      <c r="AN11" s="107" t="n"/>
-      <c r="AO11" s="107" t="n"/>
-      <c r="AP11" s="108" t="n"/>
-      <c r="AQ11" s="92" t="inlineStr">
+      <c r="AL11" s="243" t="n"/>
+      <c r="AM11" s="243" t="n"/>
+      <c r="AN11" s="243" t="n"/>
+      <c r="AO11" s="243" t="n"/>
+      <c r="AP11" s="243" t="n"/>
+      <c r="AQ11" s="244" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="AR11" s="107" t="n"/>
-      <c r="AS11" s="107" t="n"/>
-      <c r="AT11" s="107" t="n"/>
-      <c r="AU11" s="108" t="n"/>
-      <c r="AV11" s="92" t="inlineStr">
+      <c r="AR11" s="243" t="n"/>
+      <c r="AS11" s="243" t="n"/>
+      <c r="AT11" s="243" t="n"/>
+      <c r="AU11" s="243" t="n"/>
+      <c r="AV11" s="244" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AW11" s="107" t="n"/>
-      <c r="AX11" s="107" t="n"/>
-      <c r="AY11" s="107" t="n"/>
-      <c r="AZ11" s="107" t="n"/>
-      <c r="BA11" s="107" t="n"/>
-      <c r="BB11" s="107" t="n"/>
-      <c r="BC11" s="107" t="n"/>
-      <c r="BD11" s="108" t="n"/>
+      <c r="AW11" s="243" t="n"/>
+      <c r="AX11" s="243" t="n"/>
+      <c r="AY11" s="243" t="n"/>
+      <c r="AZ11" s="243" t="n"/>
+      <c r="BA11" s="243" t="n"/>
+      <c r="BB11" s="243" t="n"/>
+      <c r="BC11" s="243" t="n"/>
+      <c r="BD11" s="245" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="97" t="n"/>
-      <c r="B12" s="117" t="n"/>
-      <c r="C12" s="117" t="n"/>
-      <c r="D12" s="117" t="n"/>
-      <c r="E12" s="117" t="n"/>
-      <c r="F12" s="117" t="n"/>
-      <c r="G12" s="117" t="n"/>
-      <c r="H12" s="118" t="n"/>
-      <c r="I12" s="94" t="n"/>
-      <c r="J12" s="115" t="n"/>
-      <c r="K12" s="115" t="n"/>
-      <c r="L12" s="115" t="n"/>
-      <c r="M12" s="116" t="n"/>
-      <c r="N12" s="94" t="n"/>
-      <c r="O12" s="115" t="n"/>
-      <c r="P12" s="115" t="n"/>
-      <c r="Q12" s="115" t="n"/>
-      <c r="R12" s="115" t="n"/>
-      <c r="S12" s="115" t="n"/>
-      <c r="T12" s="115" t="n"/>
-      <c r="U12" s="115" t="n"/>
-      <c r="V12" s="115" t="n"/>
-      <c r="W12" s="115" t="n"/>
-      <c r="X12" s="116" t="n"/>
-      <c r="Y12" s="94" t="n"/>
-      <c r="Z12" s="115" t="n"/>
-      <c r="AA12" s="115" t="n"/>
-      <c r="AB12" s="115" t="n"/>
-      <c r="AC12" s="116" t="n"/>
-      <c r="AD12" s="94" t="n"/>
-      <c r="AE12" s="115" t="n"/>
-      <c r="AF12" s="115" t="n"/>
-      <c r="AG12" s="115" t="n"/>
-      <c r="AH12" s="115" t="n"/>
-      <c r="AI12" s="115" t="n"/>
-      <c r="AJ12" s="116" t="n"/>
-      <c r="AK12" s="95" t="n"/>
-      <c r="AL12" s="115" t="n"/>
-      <c r="AM12" s="115" t="n"/>
-      <c r="AN12" s="115" t="n"/>
-      <c r="AO12" s="115" t="n"/>
-      <c r="AP12" s="116" t="n"/>
-      <c r="AQ12" s="94" t="n"/>
-      <c r="AR12" s="115" t="n"/>
-      <c r="AS12" s="115" t="n"/>
-      <c r="AT12" s="115" t="n"/>
-      <c r="AU12" s="116" t="n"/>
-      <c r="AV12" s="94" t="n"/>
-      <c r="AW12" s="115" t="n"/>
-      <c r="AX12" s="115" t="n"/>
-      <c r="AY12" s="115" t="n"/>
-      <c r="AZ12" s="115" t="n"/>
-      <c r="BA12" s="115" t="n"/>
-      <c r="BB12" s="115" t="n"/>
-      <c r="BC12" s="115" t="n"/>
-      <c r="BD12" s="116" t="n"/>
+      <c r="A12" s="252" t="n"/>
+      <c r="B12" s="208" t="n"/>
+      <c r="C12" s="208" t="n"/>
+      <c r="D12" s="208" t="n"/>
+      <c r="E12" s="208" t="n"/>
+      <c r="F12" s="208" t="n"/>
+      <c r="G12" s="208" t="n"/>
+      <c r="H12" s="208" t="n"/>
+      <c r="I12" s="129" t="n"/>
+      <c r="J12" s="209" t="n"/>
+      <c r="K12" s="209" t="n"/>
+      <c r="L12" s="209" t="n"/>
+      <c r="M12" s="209" t="n"/>
+      <c r="N12" s="129" t="n"/>
+      <c r="O12" s="209" t="n"/>
+      <c r="P12" s="209" t="n"/>
+      <c r="Q12" s="209" t="n"/>
+      <c r="R12" s="209" t="n"/>
+      <c r="S12" s="209" t="n"/>
+      <c r="T12" s="209" t="n"/>
+      <c r="U12" s="209" t="n"/>
+      <c r="V12" s="209" t="n"/>
+      <c r="W12" s="209" t="n"/>
+      <c r="X12" s="209" t="n"/>
+      <c r="Y12" s="129" t="n"/>
+      <c r="Z12" s="209" t="n"/>
+      <c r="AA12" s="209" t="n"/>
+      <c r="AB12" s="209" t="n"/>
+      <c r="AC12" s="209" t="n"/>
+      <c r="AD12" s="129" t="n"/>
+      <c r="AE12" s="209" t="n"/>
+      <c r="AF12" s="209" t="n"/>
+      <c r="AG12" s="209" t="n"/>
+      <c r="AH12" s="209" t="n"/>
+      <c r="AI12" s="209" t="n"/>
+      <c r="AJ12" s="209" t="n"/>
+      <c r="AK12" s="247" t="n"/>
+      <c r="AL12" s="209" t="n"/>
+      <c r="AM12" s="209" t="n"/>
+      <c r="AN12" s="209" t="n"/>
+      <c r="AO12" s="209" t="n"/>
+      <c r="AP12" s="209" t="n"/>
+      <c r="AQ12" s="129" t="n"/>
+      <c r="AR12" s="209" t="n"/>
+      <c r="AS12" s="209" t="n"/>
+      <c r="AT12" s="209" t="n"/>
+      <c r="AU12" s="209" t="n"/>
+      <c r="AV12" s="129" t="n"/>
+      <c r="AW12" s="209" t="n"/>
+      <c r="AX12" s="209" t="n"/>
+      <c r="AY12" s="209" t="n"/>
+      <c r="AZ12" s="209" t="n"/>
+      <c r="BA12" s="209" t="n"/>
+      <c r="BB12" s="209" t="n"/>
+      <c r="BC12" s="209" t="n"/>
+      <c r="BD12" s="211" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="97" t="n"/>
-      <c r="B13" s="117" t="n"/>
-      <c r="C13" s="117" t="n"/>
-      <c r="D13" s="117" t="n"/>
-      <c r="E13" s="117" t="n"/>
-      <c r="F13" s="117" t="n"/>
-      <c r="G13" s="117" t="n"/>
-      <c r="H13" s="118" t="n"/>
-      <c r="I13" s="96" t="n"/>
-      <c r="J13" s="115" t="n"/>
-      <c r="K13" s="115" t="n"/>
-      <c r="L13" s="115" t="n"/>
-      <c r="M13" s="116" t="n"/>
-      <c r="N13" s="96" t="n"/>
-      <c r="O13" s="115" t="n"/>
-      <c r="P13" s="115" t="n"/>
-      <c r="Q13" s="115" t="n"/>
-      <c r="R13" s="115" t="n"/>
-      <c r="S13" s="115" t="n"/>
-      <c r="T13" s="115" t="n"/>
-      <c r="U13" s="115" t="n"/>
-      <c r="V13" s="115" t="n"/>
-      <c r="W13" s="115" t="n"/>
-      <c r="X13" s="116" t="n"/>
-      <c r="Y13" s="96" t="n"/>
-      <c r="Z13" s="115" t="n"/>
-      <c r="AA13" s="115" t="n"/>
-      <c r="AB13" s="115" t="n"/>
-      <c r="AC13" s="116" t="n"/>
-      <c r="AD13" s="96" t="n"/>
-      <c r="AE13" s="115" t="n"/>
-      <c r="AF13" s="115" t="n"/>
-      <c r="AG13" s="115" t="n"/>
-      <c r="AH13" s="115" t="n"/>
-      <c r="AI13" s="115" t="n"/>
-      <c r="AJ13" s="116" t="n"/>
-      <c r="AK13" s="95" t="n"/>
-      <c r="AL13" s="115" t="n"/>
-      <c r="AM13" s="115" t="n"/>
-      <c r="AN13" s="115" t="n"/>
-      <c r="AO13" s="115" t="n"/>
-      <c r="AP13" s="116" t="n"/>
-      <c r="AQ13" s="96" t="n"/>
-      <c r="AR13" s="115" t="n"/>
-      <c r="AS13" s="115" t="n"/>
-      <c r="AT13" s="115" t="n"/>
-      <c r="AU13" s="116" t="n"/>
-      <c r="AV13" s="96" t="n"/>
-      <c r="AW13" s="115" t="n"/>
-      <c r="AX13" s="115" t="n"/>
-      <c r="AY13" s="115" t="n"/>
-      <c r="AZ13" s="115" t="n"/>
-      <c r="BA13" s="115" t="n"/>
-      <c r="BB13" s="115" t="n"/>
-      <c r="BC13" s="115" t="n"/>
-      <c r="BD13" s="116" t="n"/>
+      <c r="A13" s="253" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="59" t="n"/>
+      <c r="G13" s="59" t="n"/>
+      <c r="H13" s="59" t="n"/>
+      <c r="I13" s="163" t="n"/>
+      <c r="J13" s="227" t="n"/>
+      <c r="K13" s="227" t="n"/>
+      <c r="L13" s="227" t="n"/>
+      <c r="M13" s="227" t="n"/>
+      <c r="N13" s="163" t="n"/>
+      <c r="O13" s="227" t="n"/>
+      <c r="P13" s="227" t="n"/>
+      <c r="Q13" s="227" t="n"/>
+      <c r="R13" s="227" t="n"/>
+      <c r="S13" s="227" t="n"/>
+      <c r="T13" s="227" t="n"/>
+      <c r="U13" s="227" t="n"/>
+      <c r="V13" s="227" t="n"/>
+      <c r="W13" s="227" t="n"/>
+      <c r="X13" s="227" t="n"/>
+      <c r="Y13" s="163" t="n"/>
+      <c r="Z13" s="227" t="n"/>
+      <c r="AA13" s="227" t="n"/>
+      <c r="AB13" s="227" t="n"/>
+      <c r="AC13" s="227" t="n"/>
+      <c r="AD13" s="163" t="n"/>
+      <c r="AE13" s="227" t="n"/>
+      <c r="AF13" s="227" t="n"/>
+      <c r="AG13" s="227" t="n"/>
+      <c r="AH13" s="227" t="n"/>
+      <c r="AI13" s="227" t="n"/>
+      <c r="AJ13" s="227" t="n"/>
+      <c r="AK13" s="162" t="n"/>
+      <c r="AL13" s="227" t="n"/>
+      <c r="AM13" s="227" t="n"/>
+      <c r="AN13" s="227" t="n"/>
+      <c r="AO13" s="227" t="n"/>
+      <c r="AP13" s="227" t="n"/>
+      <c r="AQ13" s="163" t="n"/>
+      <c r="AR13" s="227" t="n"/>
+      <c r="AS13" s="227" t="n"/>
+      <c r="AT13" s="227" t="n"/>
+      <c r="AU13" s="227" t="n"/>
+      <c r="AV13" s="163" t="n"/>
+      <c r="AW13" s="227" t="n"/>
+      <c r="AX13" s="227" t="n"/>
+      <c r="AY13" s="227" t="n"/>
+      <c r="AZ13" s="227" t="n"/>
+      <c r="BA13" s="227" t="n"/>
+      <c r="BB13" s="227" t="n"/>
+      <c r="BC13" s="227" t="n"/>
+      <c r="BD13" s="231" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="97" t="n"/>
-      <c r="B14" s="117" t="n"/>
-      <c r="C14" s="117" t="n"/>
-      <c r="D14" s="117" t="n"/>
-      <c r="E14" s="117" t="n"/>
-      <c r="F14" s="117" t="n"/>
-      <c r="G14" s="117" t="n"/>
-      <c r="H14" s="118" t="n"/>
-      <c r="I14" s="94" t="n"/>
-      <c r="J14" s="115" t="n"/>
-      <c r="K14" s="115" t="n"/>
-      <c r="L14" s="115" t="n"/>
-      <c r="M14" s="116" t="n"/>
-      <c r="N14" s="94" t="n"/>
-      <c r="O14" s="115" t="n"/>
-      <c r="P14" s="115" t="n"/>
-      <c r="Q14" s="115" t="n"/>
-      <c r="R14" s="115" t="n"/>
-      <c r="S14" s="115" t="n"/>
-      <c r="T14" s="115" t="n"/>
-      <c r="U14" s="115" t="n"/>
-      <c r="V14" s="115" t="n"/>
-      <c r="W14" s="115" t="n"/>
-      <c r="X14" s="116" t="n"/>
-      <c r="Y14" s="94" t="n"/>
-      <c r="Z14" s="115" t="n"/>
-      <c r="AA14" s="115" t="n"/>
-      <c r="AB14" s="115" t="n"/>
-      <c r="AC14" s="116" t="n"/>
-      <c r="AD14" s="94" t="n"/>
-      <c r="AE14" s="115" t="n"/>
-      <c r="AF14" s="115" t="n"/>
-      <c r="AG14" s="115" t="n"/>
-      <c r="AH14" s="115" t="n"/>
-      <c r="AI14" s="115" t="n"/>
-      <c r="AJ14" s="116" t="n"/>
-      <c r="AK14" s="95" t="n"/>
-      <c r="AL14" s="115" t="n"/>
-      <c r="AM14" s="115" t="n"/>
-      <c r="AN14" s="115" t="n"/>
-      <c r="AO14" s="115" t="n"/>
-      <c r="AP14" s="116" t="n"/>
-      <c r="AQ14" s="94" t="n"/>
-      <c r="AR14" s="115" t="n"/>
-      <c r="AS14" s="115" t="n"/>
-      <c r="AT14" s="115" t="n"/>
-      <c r="AU14" s="116" t="n"/>
-      <c r="AV14" s="94" t="n"/>
-      <c r="AW14" s="115" t="n"/>
-      <c r="AX14" s="115" t="n"/>
-      <c r="AY14" s="115" t="n"/>
-      <c r="AZ14" s="115" t="n"/>
-      <c r="BA14" s="115" t="n"/>
-      <c r="BB14" s="115" t="n"/>
-      <c r="BC14" s="115" t="n"/>
-      <c r="BD14" s="116" t="n"/>
+      <c r="A14" s="253" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="59" t="n"/>
+      <c r="G14" s="59" t="n"/>
+      <c r="H14" s="59" t="n"/>
+      <c r="I14" s="137" t="n"/>
+      <c r="J14" s="227" t="n"/>
+      <c r="K14" s="227" t="n"/>
+      <c r="L14" s="227" t="n"/>
+      <c r="M14" s="227" t="n"/>
+      <c r="N14" s="137" t="n"/>
+      <c r="O14" s="227" t="n"/>
+      <c r="P14" s="227" t="n"/>
+      <c r="Q14" s="227" t="n"/>
+      <c r="R14" s="227" t="n"/>
+      <c r="S14" s="227" t="n"/>
+      <c r="T14" s="227" t="n"/>
+      <c r="U14" s="227" t="n"/>
+      <c r="V14" s="227" t="n"/>
+      <c r="W14" s="227" t="n"/>
+      <c r="X14" s="227" t="n"/>
+      <c r="Y14" s="137" t="n"/>
+      <c r="Z14" s="227" t="n"/>
+      <c r="AA14" s="227" t="n"/>
+      <c r="AB14" s="227" t="n"/>
+      <c r="AC14" s="227" t="n"/>
+      <c r="AD14" s="137" t="n"/>
+      <c r="AE14" s="227" t="n"/>
+      <c r="AF14" s="227" t="n"/>
+      <c r="AG14" s="227" t="n"/>
+      <c r="AH14" s="227" t="n"/>
+      <c r="AI14" s="227" t="n"/>
+      <c r="AJ14" s="227" t="n"/>
+      <c r="AK14" s="162" t="n"/>
+      <c r="AL14" s="227" t="n"/>
+      <c r="AM14" s="227" t="n"/>
+      <c r="AN14" s="227" t="n"/>
+      <c r="AO14" s="227" t="n"/>
+      <c r="AP14" s="227" t="n"/>
+      <c r="AQ14" s="137" t="n"/>
+      <c r="AR14" s="227" t="n"/>
+      <c r="AS14" s="227" t="n"/>
+      <c r="AT14" s="227" t="n"/>
+      <c r="AU14" s="227" t="n"/>
+      <c r="AV14" s="137" t="n"/>
+      <c r="AW14" s="227" t="n"/>
+      <c r="AX14" s="227" t="n"/>
+      <c r="AY14" s="227" t="n"/>
+      <c r="AZ14" s="227" t="n"/>
+      <c r="BA14" s="227" t="n"/>
+      <c r="BB14" s="227" t="n"/>
+      <c r="BC14" s="227" t="n"/>
+      <c r="BD14" s="231" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="97" t="n"/>
-      <c r="B15" s="117" t="n"/>
-      <c r="C15" s="117" t="n"/>
-      <c r="D15" s="117" t="n"/>
-      <c r="E15" s="117" t="n"/>
-      <c r="F15" s="117" t="n"/>
-      <c r="G15" s="117" t="n"/>
-      <c r="H15" s="118" t="n"/>
-      <c r="I15" s="96" t="n"/>
-      <c r="J15" s="115" t="n"/>
-      <c r="K15" s="115" t="n"/>
-      <c r="L15" s="115" t="n"/>
-      <c r="M15" s="116" t="n"/>
-      <c r="N15" s="96" t="n"/>
-      <c r="O15" s="115" t="n"/>
-      <c r="P15" s="115" t="n"/>
-      <c r="Q15" s="115" t="n"/>
-      <c r="R15" s="115" t="n"/>
-      <c r="S15" s="115" t="n"/>
-      <c r="T15" s="115" t="n"/>
-      <c r="U15" s="115" t="n"/>
-      <c r="V15" s="115" t="n"/>
-      <c r="W15" s="115" t="n"/>
-      <c r="X15" s="116" t="n"/>
-      <c r="Y15" s="96" t="n"/>
-      <c r="Z15" s="115" t="n"/>
-      <c r="AA15" s="115" t="n"/>
-      <c r="AB15" s="115" t="n"/>
-      <c r="AC15" s="116" t="n"/>
-      <c r="AD15" s="96" t="n"/>
-      <c r="AE15" s="115" t="n"/>
-      <c r="AF15" s="115" t="n"/>
-      <c r="AG15" s="115" t="n"/>
-      <c r="AH15" s="115" t="n"/>
-      <c r="AI15" s="115" t="n"/>
-      <c r="AJ15" s="116" t="n"/>
-      <c r="AK15" s="95" t="n"/>
-      <c r="AL15" s="115" t="n"/>
-      <c r="AM15" s="115" t="n"/>
-      <c r="AN15" s="115" t="n"/>
-      <c r="AO15" s="115" t="n"/>
-      <c r="AP15" s="116" t="n"/>
-      <c r="AQ15" s="96" t="n"/>
-      <c r="AR15" s="115" t="n"/>
-      <c r="AS15" s="115" t="n"/>
-      <c r="AT15" s="115" t="n"/>
-      <c r="AU15" s="116" t="n"/>
-      <c r="AV15" s="96" t="n"/>
-      <c r="AW15" s="115" t="n"/>
-      <c r="AX15" s="115" t="n"/>
-      <c r="AY15" s="115" t="n"/>
-      <c r="AZ15" s="115" t="n"/>
-      <c r="BA15" s="115" t="n"/>
-      <c r="BB15" s="115" t="n"/>
-      <c r="BC15" s="115" t="n"/>
-      <c r="BD15" s="116" t="n"/>
+      <c r="A15" s="253" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="59" t="n"/>
+      <c r="G15" s="59" t="n"/>
+      <c r="H15" s="59" t="n"/>
+      <c r="I15" s="163" t="n"/>
+      <c r="J15" s="227" t="n"/>
+      <c r="K15" s="227" t="n"/>
+      <c r="L15" s="227" t="n"/>
+      <c r="M15" s="227" t="n"/>
+      <c r="N15" s="163" t="n"/>
+      <c r="O15" s="227" t="n"/>
+      <c r="P15" s="227" t="n"/>
+      <c r="Q15" s="227" t="n"/>
+      <c r="R15" s="227" t="n"/>
+      <c r="S15" s="227" t="n"/>
+      <c r="T15" s="227" t="n"/>
+      <c r="U15" s="227" t="n"/>
+      <c r="V15" s="227" t="n"/>
+      <c r="W15" s="227" t="n"/>
+      <c r="X15" s="227" t="n"/>
+      <c r="Y15" s="163" t="n"/>
+      <c r="Z15" s="227" t="n"/>
+      <c r="AA15" s="227" t="n"/>
+      <c r="AB15" s="227" t="n"/>
+      <c r="AC15" s="227" t="n"/>
+      <c r="AD15" s="163" t="n"/>
+      <c r="AE15" s="227" t="n"/>
+      <c r="AF15" s="227" t="n"/>
+      <c r="AG15" s="227" t="n"/>
+      <c r="AH15" s="227" t="n"/>
+      <c r="AI15" s="227" t="n"/>
+      <c r="AJ15" s="227" t="n"/>
+      <c r="AK15" s="162" t="n"/>
+      <c r="AL15" s="227" t="n"/>
+      <c r="AM15" s="227" t="n"/>
+      <c r="AN15" s="227" t="n"/>
+      <c r="AO15" s="227" t="n"/>
+      <c r="AP15" s="227" t="n"/>
+      <c r="AQ15" s="163" t="n"/>
+      <c r="AR15" s="227" t="n"/>
+      <c r="AS15" s="227" t="n"/>
+      <c r="AT15" s="227" t="n"/>
+      <c r="AU15" s="227" t="n"/>
+      <c r="AV15" s="163" t="n"/>
+      <c r="AW15" s="227" t="n"/>
+      <c r="AX15" s="227" t="n"/>
+      <c r="AY15" s="227" t="n"/>
+      <c r="AZ15" s="227" t="n"/>
+      <c r="BA15" s="227" t="n"/>
+      <c r="BB15" s="227" t="n"/>
+      <c r="BC15" s="227" t="n"/>
+      <c r="BD15" s="231" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="97" t="n"/>
-      <c r="B16" s="117" t="n"/>
-      <c r="C16" s="117" t="n"/>
-      <c r="D16" s="117" t="n"/>
-      <c r="E16" s="117" t="n"/>
-      <c r="F16" s="117" t="n"/>
-      <c r="G16" s="117" t="n"/>
-      <c r="H16" s="118" t="n"/>
-      <c r="I16" s="94" t="n"/>
-      <c r="J16" s="115" t="n"/>
-      <c r="K16" s="115" t="n"/>
-      <c r="L16" s="115" t="n"/>
-      <c r="M16" s="116" t="n"/>
-      <c r="N16" s="94" t="n"/>
-      <c r="O16" s="115" t="n"/>
-      <c r="P16" s="115" t="n"/>
-      <c r="Q16" s="115" t="n"/>
-      <c r="R16" s="115" t="n"/>
-      <c r="S16" s="115" t="n"/>
-      <c r="T16" s="115" t="n"/>
-      <c r="U16" s="115" t="n"/>
-      <c r="V16" s="115" t="n"/>
-      <c r="W16" s="115" t="n"/>
-      <c r="X16" s="116" t="n"/>
-      <c r="Y16" s="94" t="n"/>
-      <c r="Z16" s="115" t="n"/>
-      <c r="AA16" s="115" t="n"/>
-      <c r="AB16" s="115" t="n"/>
-      <c r="AC16" s="116" t="n"/>
-      <c r="AD16" s="94" t="n"/>
-      <c r="AE16" s="115" t="n"/>
-      <c r="AF16" s="115" t="n"/>
-      <c r="AG16" s="115" t="n"/>
-      <c r="AH16" s="115" t="n"/>
-      <c r="AI16" s="115" t="n"/>
-      <c r="AJ16" s="116" t="n"/>
-      <c r="AK16" s="95" t="n"/>
-      <c r="AL16" s="115" t="n"/>
-      <c r="AM16" s="115" t="n"/>
-      <c r="AN16" s="115" t="n"/>
-      <c r="AO16" s="115" t="n"/>
-      <c r="AP16" s="116" t="n"/>
-      <c r="AQ16" s="94" t="n"/>
-      <c r="AR16" s="115" t="n"/>
-      <c r="AS16" s="115" t="n"/>
-      <c r="AT16" s="115" t="n"/>
-      <c r="AU16" s="116" t="n"/>
-      <c r="AV16" s="94" t="n"/>
-      <c r="AW16" s="115" t="n"/>
-      <c r="AX16" s="115" t="n"/>
-      <c r="AY16" s="115" t="n"/>
-      <c r="AZ16" s="115" t="n"/>
-      <c r="BA16" s="115" t="n"/>
-      <c r="BB16" s="115" t="n"/>
-      <c r="BC16" s="115" t="n"/>
-      <c r="BD16" s="116" t="n"/>
+      <c r="A16" s="253" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="59" t="n"/>
+      <c r="G16" s="59" t="n"/>
+      <c r="H16" s="59" t="n"/>
+      <c r="I16" s="137" t="n"/>
+      <c r="J16" s="227" t="n"/>
+      <c r="K16" s="227" t="n"/>
+      <c r="L16" s="227" t="n"/>
+      <c r="M16" s="227" t="n"/>
+      <c r="N16" s="137" t="n"/>
+      <c r="O16" s="227" t="n"/>
+      <c r="P16" s="227" t="n"/>
+      <c r="Q16" s="227" t="n"/>
+      <c r="R16" s="227" t="n"/>
+      <c r="S16" s="227" t="n"/>
+      <c r="T16" s="227" t="n"/>
+      <c r="U16" s="227" t="n"/>
+      <c r="V16" s="227" t="n"/>
+      <c r="W16" s="227" t="n"/>
+      <c r="X16" s="227" t="n"/>
+      <c r="Y16" s="137" t="n"/>
+      <c r="Z16" s="227" t="n"/>
+      <c r="AA16" s="227" t="n"/>
+      <c r="AB16" s="227" t="n"/>
+      <c r="AC16" s="227" t="n"/>
+      <c r="AD16" s="137" t="n"/>
+      <c r="AE16" s="227" t="n"/>
+      <c r="AF16" s="227" t="n"/>
+      <c r="AG16" s="227" t="n"/>
+      <c r="AH16" s="227" t="n"/>
+      <c r="AI16" s="227" t="n"/>
+      <c r="AJ16" s="227" t="n"/>
+      <c r="AK16" s="162" t="n"/>
+      <c r="AL16" s="227" t="n"/>
+      <c r="AM16" s="227" t="n"/>
+      <c r="AN16" s="227" t="n"/>
+      <c r="AO16" s="227" t="n"/>
+      <c r="AP16" s="227" t="n"/>
+      <c r="AQ16" s="137" t="n"/>
+      <c r="AR16" s="227" t="n"/>
+      <c r="AS16" s="227" t="n"/>
+      <c r="AT16" s="227" t="n"/>
+      <c r="AU16" s="227" t="n"/>
+      <c r="AV16" s="137" t="n"/>
+      <c r="AW16" s="227" t="n"/>
+      <c r="AX16" s="227" t="n"/>
+      <c r="AY16" s="227" t="n"/>
+      <c r="AZ16" s="227" t="n"/>
+      <c r="BA16" s="227" t="n"/>
+      <c r="BB16" s="227" t="n"/>
+      <c r="BC16" s="227" t="n"/>
+      <c r="BD16" s="231" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="97" t="n"/>
-      <c r="B17" s="117" t="n"/>
-      <c r="C17" s="117" t="n"/>
-      <c r="D17" s="117" t="n"/>
-      <c r="E17" s="117" t="n"/>
-      <c r="F17" s="117" t="n"/>
-      <c r="G17" s="117" t="n"/>
-      <c r="H17" s="118" t="n"/>
-      <c r="I17" s="96" t="n"/>
-      <c r="J17" s="115" t="n"/>
-      <c r="K17" s="115" t="n"/>
-      <c r="L17" s="115" t="n"/>
-      <c r="M17" s="116" t="n"/>
-      <c r="N17" s="96" t="n"/>
-      <c r="O17" s="115" t="n"/>
-      <c r="P17" s="115" t="n"/>
-      <c r="Q17" s="115" t="n"/>
-      <c r="R17" s="115" t="n"/>
-      <c r="S17" s="115" t="n"/>
-      <c r="T17" s="115" t="n"/>
-      <c r="U17" s="115" t="n"/>
-      <c r="V17" s="115" t="n"/>
-      <c r="W17" s="115" t="n"/>
-      <c r="X17" s="116" t="n"/>
-      <c r="Y17" s="96" t="n"/>
-      <c r="Z17" s="115" t="n"/>
-      <c r="AA17" s="115" t="n"/>
-      <c r="AB17" s="115" t="n"/>
-      <c r="AC17" s="116" t="n"/>
-      <c r="AD17" s="96" t="n"/>
-      <c r="AE17" s="115" t="n"/>
-      <c r="AF17" s="115" t="n"/>
-      <c r="AG17" s="115" t="n"/>
-      <c r="AH17" s="115" t="n"/>
-      <c r="AI17" s="115" t="n"/>
-      <c r="AJ17" s="116" t="n"/>
-      <c r="AK17" s="95" t="n"/>
-      <c r="AL17" s="115" t="n"/>
-      <c r="AM17" s="115" t="n"/>
-      <c r="AN17" s="115" t="n"/>
-      <c r="AO17" s="115" t="n"/>
-      <c r="AP17" s="116" t="n"/>
-      <c r="AQ17" s="96" t="n"/>
-      <c r="AR17" s="115" t="n"/>
-      <c r="AS17" s="115" t="n"/>
-      <c r="AT17" s="115" t="n"/>
-      <c r="AU17" s="116" t="n"/>
-      <c r="AV17" s="96" t="n"/>
-      <c r="AW17" s="115" t="n"/>
-      <c r="AX17" s="115" t="n"/>
-      <c r="AY17" s="115" t="n"/>
-      <c r="AZ17" s="115" t="n"/>
-      <c r="BA17" s="115" t="n"/>
-      <c r="BB17" s="115" t="n"/>
-      <c r="BC17" s="115" t="n"/>
-      <c r="BD17" s="116" t="n"/>
+      <c r="A17" s="254" t="n"/>
+      <c r="B17" s="213" t="n"/>
+      <c r="C17" s="213" t="n"/>
+      <c r="D17" s="213" t="n"/>
+      <c r="E17" s="213" t="n"/>
+      <c r="F17" s="213" t="n"/>
+      <c r="G17" s="213" t="n"/>
+      <c r="H17" s="213" t="n"/>
+      <c r="I17" s="250" t="n"/>
+      <c r="J17" s="215" t="n"/>
+      <c r="K17" s="215" t="n"/>
+      <c r="L17" s="215" t="n"/>
+      <c r="M17" s="215" t="n"/>
+      <c r="N17" s="250" t="n"/>
+      <c r="O17" s="215" t="n"/>
+      <c r="P17" s="215" t="n"/>
+      <c r="Q17" s="215" t="n"/>
+      <c r="R17" s="215" t="n"/>
+      <c r="S17" s="215" t="n"/>
+      <c r="T17" s="215" t="n"/>
+      <c r="U17" s="215" t="n"/>
+      <c r="V17" s="215" t="n"/>
+      <c r="W17" s="215" t="n"/>
+      <c r="X17" s="215" t="n"/>
+      <c r="Y17" s="250" t="n"/>
+      <c r="Z17" s="215" t="n"/>
+      <c r="AA17" s="215" t="n"/>
+      <c r="AB17" s="215" t="n"/>
+      <c r="AC17" s="215" t="n"/>
+      <c r="AD17" s="250" t="n"/>
+      <c r="AE17" s="215" t="n"/>
+      <c r="AF17" s="215" t="n"/>
+      <c r="AG17" s="215" t="n"/>
+      <c r="AH17" s="215" t="n"/>
+      <c r="AI17" s="215" t="n"/>
+      <c r="AJ17" s="215" t="n"/>
+      <c r="AK17" s="251" t="n"/>
+      <c r="AL17" s="215" t="n"/>
+      <c r="AM17" s="215" t="n"/>
+      <c r="AN17" s="215" t="n"/>
+      <c r="AO17" s="215" t="n"/>
+      <c r="AP17" s="215" t="n"/>
+      <c r="AQ17" s="250" t="n"/>
+      <c r="AR17" s="215" t="n"/>
+      <c r="AS17" s="215" t="n"/>
+      <c r="AT17" s="215" t="n"/>
+      <c r="AU17" s="215" t="n"/>
+      <c r="AV17" s="250" t="n"/>
+      <c r="AW17" s="215" t="n"/>
+      <c r="AX17" s="215" t="n"/>
+      <c r="AY17" s="215" t="n"/>
+      <c r="AZ17" s="215" t="n"/>
+      <c r="BA17" s="215" t="n"/>
+      <c r="BB17" s="215" t="n"/>
+      <c r="BC17" s="215" t="n"/>
+      <c r="BD17" s="217" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="89" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="204" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B18" s="101" t="n"/>
-      <c r="C18" s="101" t="n"/>
-      <c r="D18" s="101" t="n"/>
-      <c r="E18" s="101" t="n"/>
-      <c r="F18" s="101" t="n"/>
-      <c r="G18" s="101" t="n"/>
-      <c r="H18" s="101" t="n"/>
-      <c r="I18" s="101" t="n"/>
-      <c r="J18" s="101" t="n"/>
-      <c r="K18" s="101" t="n"/>
-      <c r="L18" s="101" t="n"/>
-      <c r="M18" s="101" t="n"/>
-      <c r="N18" s="101" t="n"/>
-      <c r="O18" s="101" t="n"/>
-      <c r="P18" s="101" t="n"/>
-      <c r="Q18" s="101" t="n"/>
-      <c r="R18" s="101" t="n"/>
-      <c r="S18" s="101" t="n"/>
-      <c r="T18" s="101" t="n"/>
-      <c r="U18" s="101" t="n"/>
-      <c r="V18" s="101" t="n"/>
-      <c r="W18" s="101" t="n"/>
-      <c r="X18" s="101" t="n"/>
-      <c r="Y18" s="101" t="n"/>
-      <c r="Z18" s="101" t="n"/>
-      <c r="AA18" s="101" t="n"/>
-      <c r="AB18" s="101" t="n"/>
-      <c r="AC18" s="101" t="n"/>
-      <c r="AD18" s="101" t="n"/>
-      <c r="AE18" s="101" t="n"/>
-      <c r="AF18" s="101" t="n"/>
-      <c r="AG18" s="101" t="n"/>
-      <c r="AH18" s="101" t="n"/>
-      <c r="AI18" s="101" t="n"/>
-      <c r="AJ18" s="101" t="n"/>
-      <c r="AK18" s="101" t="n"/>
-      <c r="AL18" s="101" t="n"/>
-      <c r="AM18" s="101" t="n"/>
-      <c r="AN18" s="101" t="n"/>
-      <c r="AO18" s="101" t="n"/>
-      <c r="AP18" s="101" t="n"/>
-      <c r="AQ18" s="101" t="n"/>
-      <c r="AR18" s="101" t="n"/>
-      <c r="AS18" s="101" t="n"/>
-      <c r="AT18" s="101" t="n"/>
-      <c r="AU18" s="101" t="n"/>
-      <c r="AV18" s="101" t="n"/>
-      <c r="AW18" s="101" t="n"/>
-      <c r="AX18" s="101" t="n"/>
-      <c r="AY18" s="101" t="n"/>
-      <c r="AZ18" s="101" t="n"/>
-      <c r="BA18" s="101" t="n"/>
-      <c r="BB18" s="101" t="n"/>
-      <c r="BC18" s="101" t="n"/>
-      <c r="BD18" s="102" t="n"/>
+      <c r="B18" s="205" t="n"/>
+      <c r="C18" s="205" t="n"/>
+      <c r="D18" s="205" t="n"/>
+      <c r="E18" s="205" t="n"/>
+      <c r="F18" s="205" t="n"/>
+      <c r="G18" s="205" t="n"/>
+      <c r="H18" s="205" t="n"/>
+      <c r="I18" s="205" t="n"/>
+      <c r="J18" s="205" t="n"/>
+      <c r="K18" s="205" t="n"/>
+      <c r="L18" s="205" t="n"/>
+      <c r="M18" s="205" t="n"/>
+      <c r="N18" s="205" t="n"/>
+      <c r="O18" s="205" t="n"/>
+      <c r="P18" s="205" t="n"/>
+      <c r="Q18" s="205" t="n"/>
+      <c r="R18" s="205" t="n"/>
+      <c r="S18" s="205" t="n"/>
+      <c r="T18" s="205" t="n"/>
+      <c r="U18" s="205" t="n"/>
+      <c r="V18" s="205" t="n"/>
+      <c r="W18" s="205" t="n"/>
+      <c r="X18" s="205" t="n"/>
+      <c r="Y18" s="205" t="n"/>
+      <c r="Z18" s="205" t="n"/>
+      <c r="AA18" s="205" t="n"/>
+      <c r="AB18" s="205" t="n"/>
+      <c r="AC18" s="205" t="n"/>
+      <c r="AD18" s="205" t="n"/>
+      <c r="AE18" s="205" t="n"/>
+      <c r="AF18" s="205" t="n"/>
+      <c r="AG18" s="205" t="n"/>
+      <c r="AH18" s="205" t="n"/>
+      <c r="AI18" s="205" t="n"/>
+      <c r="AJ18" s="205" t="n"/>
+      <c r="AK18" s="205" t="n"/>
+      <c r="AL18" s="205" t="n"/>
+      <c r="AM18" s="205" t="n"/>
+      <c r="AN18" s="205" t="n"/>
+      <c r="AO18" s="205" t="n"/>
+      <c r="AP18" s="205" t="n"/>
+      <c r="AQ18" s="205" t="n"/>
+      <c r="AR18" s="205" t="n"/>
+      <c r="AS18" s="205" t="n"/>
+      <c r="AT18" s="205" t="n"/>
+      <c r="AU18" s="205" t="n"/>
+      <c r="AV18" s="205" t="n"/>
+      <c r="AW18" s="205" t="n"/>
+      <c r="AX18" s="205" t="n"/>
+      <c r="AY18" s="205" t="n"/>
+      <c r="AZ18" s="205" t="n"/>
+      <c r="BA18" s="205" t="n"/>
+      <c r="BB18" s="205" t="n"/>
+      <c r="BC18" s="205" t="n"/>
+      <c r="BD18" s="206" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="82">
+  <mergeCells count="81">
     <mergeCell ref="AV17:BD17"/>
     <mergeCell ref="AV11:BD11"/>
     <mergeCell ref="N11:X11"/>
@@ -5191,7 +6634,6 @@
     <mergeCell ref="AQ12:AU12"/>
     <mergeCell ref="AQ4:AV4"/>
     <mergeCell ref="N14:X14"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="AV15:BD15"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="Y13:AC13"/>
@@ -5270,6 +6712,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5594,61 +7037,6 @@
     </row>
     <row r="6" ht="4" customHeight="1">
       <c r="A6" s="71" t="n"/>
-      <c r="B6" s="119" t="n"/>
-      <c r="C6" s="119" t="n"/>
-      <c r="D6" s="119" t="n"/>
-      <c r="E6" s="119" t="n"/>
-      <c r="F6" s="119" t="n"/>
-      <c r="G6" s="119" t="n"/>
-      <c r="H6" s="119" t="n"/>
-      <c r="I6" s="119" t="n"/>
-      <c r="J6" s="119" t="n"/>
-      <c r="K6" s="119" t="n"/>
-      <c r="L6" s="119" t="n"/>
-      <c r="M6" s="119" t="n"/>
-      <c r="N6" s="119" t="n"/>
-      <c r="O6" s="119" t="n"/>
-      <c r="P6" s="119" t="n"/>
-      <c r="Q6" s="119" t="n"/>
-      <c r="R6" s="119" t="n"/>
-      <c r="S6" s="119" t="n"/>
-      <c r="T6" s="119" t="n"/>
-      <c r="U6" s="119" t="n"/>
-      <c r="V6" s="119" t="n"/>
-      <c r="W6" s="119" t="n"/>
-      <c r="X6" s="119" t="n"/>
-      <c r="Y6" s="119" t="n"/>
-      <c r="Z6" s="119" t="n"/>
-      <c r="AA6" s="119" t="n"/>
-      <c r="AB6" s="119" t="n"/>
-      <c r="AC6" s="119" t="n"/>
-      <c r="AD6" s="119" t="n"/>
-      <c r="AE6" s="119" t="n"/>
-      <c r="AF6" s="119" t="n"/>
-      <c r="AG6" s="119" t="n"/>
-      <c r="AH6" s="119" t="n"/>
-      <c r="AI6" s="119" t="n"/>
-      <c r="AJ6" s="119" t="n"/>
-      <c r="AK6" s="119" t="n"/>
-      <c r="AL6" s="119" t="n"/>
-      <c r="AM6" s="119" t="n"/>
-      <c r="AN6" s="119" t="n"/>
-      <c r="AO6" s="119" t="n"/>
-      <c r="AP6" s="119" t="n"/>
-      <c r="AQ6" s="119" t="n"/>
-      <c r="AR6" s="119" t="n"/>
-      <c r="AS6" s="119" t="n"/>
-      <c r="AT6" s="119" t="n"/>
-      <c r="AU6" s="119" t="n"/>
-      <c r="AV6" s="119" t="n"/>
-      <c r="AW6" s="119" t="n"/>
-      <c r="AX6" s="119" t="n"/>
-      <c r="AY6" s="119" t="n"/>
-      <c r="AZ6" s="119" t="n"/>
-      <c r="BA6" s="119" t="n"/>
-      <c r="BB6" s="119" t="n"/>
-      <c r="BC6" s="119" t="n"/>
-      <c r="BD6" s="119" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="72" t="inlineStr">
@@ -5718,61 +7106,61 @@
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="107" t="n"/>
-      <c r="C8" s="107" t="n"/>
-      <c r="D8" s="107" t="n"/>
-      <c r="E8" s="107" t="n"/>
-      <c r="F8" s="107" t="n"/>
-      <c r="G8" s="107" t="n"/>
-      <c r="H8" s="107" t="n"/>
-      <c r="I8" s="107" t="n"/>
-      <c r="J8" s="107" t="n"/>
-      <c r="K8" s="107" t="n"/>
-      <c r="L8" s="107" t="n"/>
-      <c r="M8" s="107" t="n"/>
-      <c r="N8" s="107" t="n"/>
-      <c r="O8" s="107" t="n"/>
-      <c r="P8" s="107" t="n"/>
-      <c r="Q8" s="107" t="n"/>
-      <c r="R8" s="107" t="n"/>
-      <c r="S8" s="107" t="n"/>
-      <c r="T8" s="107" t="n"/>
-      <c r="U8" s="107" t="n"/>
-      <c r="V8" s="107" t="n"/>
-      <c r="W8" s="107" t="n"/>
-      <c r="X8" s="107" t="n"/>
-      <c r="Y8" s="107" t="n"/>
-      <c r="Z8" s="107" t="n"/>
-      <c r="AA8" s="107" t="n"/>
-      <c r="AB8" s="107" t="n"/>
-      <c r="AC8" s="107" t="n"/>
-      <c r="AD8" s="107" t="n"/>
-      <c r="AE8" s="107" t="n"/>
-      <c r="AF8" s="107" t="n"/>
-      <c r="AG8" s="107" t="n"/>
-      <c r="AH8" s="107" t="n"/>
-      <c r="AI8" s="107" t="n"/>
-      <c r="AJ8" s="107" t="n"/>
-      <c r="AK8" s="107" t="n"/>
-      <c r="AL8" s="107" t="n"/>
-      <c r="AM8" s="107" t="n"/>
-      <c r="AN8" s="107" t="n"/>
-      <c r="AO8" s="107" t="n"/>
-      <c r="AP8" s="107" t="n"/>
-      <c r="AQ8" s="107" t="n"/>
-      <c r="AR8" s="107" t="n"/>
-      <c r="AS8" s="107" t="n"/>
-      <c r="AT8" s="107" t="n"/>
-      <c r="AU8" s="107" t="n"/>
-      <c r="AV8" s="107" t="n"/>
-      <c r="AW8" s="107" t="n"/>
-      <c r="AX8" s="107" t="n"/>
-      <c r="AY8" s="107" t="n"/>
-      <c r="AZ8" s="107" t="n"/>
-      <c r="BA8" s="107" t="n"/>
-      <c r="BB8" s="107" t="n"/>
-      <c r="BC8" s="107" t="n"/>
-      <c r="BD8" s="108" t="n"/>
+      <c r="B8" s="121" t="n"/>
+      <c r="C8" s="121" t="n"/>
+      <c r="D8" s="121" t="n"/>
+      <c r="E8" s="121" t="n"/>
+      <c r="F8" s="121" t="n"/>
+      <c r="G8" s="121" t="n"/>
+      <c r="H8" s="121" t="n"/>
+      <c r="I8" s="121" t="n"/>
+      <c r="J8" s="121" t="n"/>
+      <c r="K8" s="121" t="n"/>
+      <c r="L8" s="121" t="n"/>
+      <c r="M8" s="121" t="n"/>
+      <c r="N8" s="121" t="n"/>
+      <c r="O8" s="121" t="n"/>
+      <c r="P8" s="121" t="n"/>
+      <c r="Q8" s="121" t="n"/>
+      <c r="R8" s="121" t="n"/>
+      <c r="S8" s="121" t="n"/>
+      <c r="T8" s="121" t="n"/>
+      <c r="U8" s="121" t="n"/>
+      <c r="V8" s="121" t="n"/>
+      <c r="W8" s="121" t="n"/>
+      <c r="X8" s="121" t="n"/>
+      <c r="Y8" s="121" t="n"/>
+      <c r="Z8" s="121" t="n"/>
+      <c r="AA8" s="121" t="n"/>
+      <c r="AB8" s="121" t="n"/>
+      <c r="AC8" s="121" t="n"/>
+      <c r="AD8" s="121" t="n"/>
+      <c r="AE8" s="121" t="n"/>
+      <c r="AF8" s="121" t="n"/>
+      <c r="AG8" s="121" t="n"/>
+      <c r="AH8" s="121" t="n"/>
+      <c r="AI8" s="121" t="n"/>
+      <c r="AJ8" s="121" t="n"/>
+      <c r="AK8" s="121" t="n"/>
+      <c r="AL8" s="121" t="n"/>
+      <c r="AM8" s="121" t="n"/>
+      <c r="AN8" s="121" t="n"/>
+      <c r="AO8" s="121" t="n"/>
+      <c r="AP8" s="121" t="n"/>
+      <c r="AQ8" s="121" t="n"/>
+      <c r="AR8" s="121" t="n"/>
+      <c r="AS8" s="121" t="n"/>
+      <c r="AT8" s="121" t="n"/>
+      <c r="AU8" s="121" t="n"/>
+      <c r="AV8" s="121" t="n"/>
+      <c r="AW8" s="121" t="n"/>
+      <c r="AX8" s="121" t="n"/>
+      <c r="AY8" s="121" t="n"/>
+      <c r="AZ8" s="121" t="n"/>
+      <c r="BA8" s="121" t="n"/>
+      <c r="BB8" s="121" t="n"/>
+      <c r="BC8" s="121" t="n"/>
+      <c r="BD8" s="122" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="92" t="inlineStr">
@@ -7226,61 +8614,61 @@
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="107" t="n"/>
-      <c r="C20" s="107" t="n"/>
-      <c r="D20" s="107" t="n"/>
-      <c r="E20" s="107" t="n"/>
-      <c r="F20" s="107" t="n"/>
-      <c r="G20" s="107" t="n"/>
-      <c r="H20" s="107" t="n"/>
-      <c r="I20" s="107" t="n"/>
-      <c r="J20" s="107" t="n"/>
-      <c r="K20" s="107" t="n"/>
-      <c r="L20" s="107" t="n"/>
-      <c r="M20" s="107" t="n"/>
-      <c r="N20" s="107" t="n"/>
-      <c r="O20" s="107" t="n"/>
-      <c r="P20" s="107" t="n"/>
-      <c r="Q20" s="107" t="n"/>
-      <c r="R20" s="107" t="n"/>
-      <c r="S20" s="107" t="n"/>
-      <c r="T20" s="107" t="n"/>
-      <c r="U20" s="107" t="n"/>
-      <c r="V20" s="107" t="n"/>
-      <c r="W20" s="107" t="n"/>
-      <c r="X20" s="107" t="n"/>
-      <c r="Y20" s="107" t="n"/>
-      <c r="Z20" s="107" t="n"/>
-      <c r="AA20" s="107" t="n"/>
-      <c r="AB20" s="107" t="n"/>
-      <c r="AC20" s="107" t="n"/>
-      <c r="AD20" s="107" t="n"/>
-      <c r="AE20" s="107" t="n"/>
-      <c r="AF20" s="107" t="n"/>
-      <c r="AG20" s="107" t="n"/>
-      <c r="AH20" s="107" t="n"/>
-      <c r="AI20" s="107" t="n"/>
-      <c r="AJ20" s="107" t="n"/>
-      <c r="AK20" s="107" t="n"/>
-      <c r="AL20" s="107" t="n"/>
-      <c r="AM20" s="107" t="n"/>
-      <c r="AN20" s="107" t="n"/>
-      <c r="AO20" s="107" t="n"/>
-      <c r="AP20" s="107" t="n"/>
-      <c r="AQ20" s="107" t="n"/>
-      <c r="AR20" s="107" t="n"/>
-      <c r="AS20" s="107" t="n"/>
-      <c r="AT20" s="107" t="n"/>
-      <c r="AU20" s="107" t="n"/>
-      <c r="AV20" s="107" t="n"/>
-      <c r="AW20" s="107" t="n"/>
-      <c r="AX20" s="107" t="n"/>
-      <c r="AY20" s="107" t="n"/>
-      <c r="AZ20" s="107" t="n"/>
-      <c r="BA20" s="107" t="n"/>
-      <c r="BB20" s="107" t="n"/>
-      <c r="BC20" s="107" t="n"/>
-      <c r="BD20" s="108" t="n"/>
+      <c r="B20" s="121" t="n"/>
+      <c r="C20" s="121" t="n"/>
+      <c r="D20" s="121" t="n"/>
+      <c r="E20" s="121" t="n"/>
+      <c r="F20" s="121" t="n"/>
+      <c r="G20" s="121" t="n"/>
+      <c r="H20" s="121" t="n"/>
+      <c r="I20" s="121" t="n"/>
+      <c r="J20" s="121" t="n"/>
+      <c r="K20" s="121" t="n"/>
+      <c r="L20" s="121" t="n"/>
+      <c r="M20" s="121" t="n"/>
+      <c r="N20" s="121" t="n"/>
+      <c r="O20" s="121" t="n"/>
+      <c r="P20" s="121" t="n"/>
+      <c r="Q20" s="121" t="n"/>
+      <c r="R20" s="121" t="n"/>
+      <c r="S20" s="121" t="n"/>
+      <c r="T20" s="121" t="n"/>
+      <c r="U20" s="121" t="n"/>
+      <c r="V20" s="121" t="n"/>
+      <c r="W20" s="121" t="n"/>
+      <c r="X20" s="121" t="n"/>
+      <c r="Y20" s="121" t="n"/>
+      <c r="Z20" s="121" t="n"/>
+      <c r="AA20" s="121" t="n"/>
+      <c r="AB20" s="121" t="n"/>
+      <c r="AC20" s="121" t="n"/>
+      <c r="AD20" s="121" t="n"/>
+      <c r="AE20" s="121" t="n"/>
+      <c r="AF20" s="121" t="n"/>
+      <c r="AG20" s="121" t="n"/>
+      <c r="AH20" s="121" t="n"/>
+      <c r="AI20" s="121" t="n"/>
+      <c r="AJ20" s="121" t="n"/>
+      <c r="AK20" s="121" t="n"/>
+      <c r="AL20" s="121" t="n"/>
+      <c r="AM20" s="121" t="n"/>
+      <c r="AN20" s="121" t="n"/>
+      <c r="AO20" s="121" t="n"/>
+      <c r="AP20" s="121" t="n"/>
+      <c r="AQ20" s="121" t="n"/>
+      <c r="AR20" s="121" t="n"/>
+      <c r="AS20" s="121" t="n"/>
+      <c r="AT20" s="121" t="n"/>
+      <c r="AU20" s="121" t="n"/>
+      <c r="AV20" s="121" t="n"/>
+      <c r="AW20" s="121" t="n"/>
+      <c r="AX20" s="121" t="n"/>
+      <c r="AY20" s="121" t="n"/>
+      <c r="AZ20" s="121" t="n"/>
+      <c r="BA20" s="121" t="n"/>
+      <c r="BB20" s="121" t="n"/>
+      <c r="BC20" s="121" t="n"/>
+      <c r="BD20" s="122" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -199,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="139">
+  <borders count="150">
     <border>
       <left/>
       <right/>
@@ -1691,11 +1691,144 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="359">
+  <cellXfs count="430">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2630,6 +2763,217 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="136" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="137" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="134" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="136" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="136" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="34" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2730,6 +3074,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2760,6 +3107,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2790,6 +3140,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2820,6 +3173,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3162,266 +3518,185 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="255" t="n"/>
-      <c r="B1" s="256" t="n"/>
-      <c r="C1" s="256" t="n"/>
-      <c r="D1" s="256" t="n"/>
-      <c r="E1" s="256" t="n"/>
-      <c r="F1" s="256" t="n"/>
-      <c r="G1" s="256" t="n"/>
-      <c r="H1" s="257" t="n"/>
+      <c r="A1" s="359" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="3" t="n"/>
       <c r="I1" s="258" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW</t>
         </is>
       </c>
-      <c r="J1" s="256" t="n"/>
-      <c r="K1" s="256" t="n"/>
-      <c r="L1" s="256" t="n"/>
-      <c r="M1" s="256" t="n"/>
-      <c r="N1" s="256" t="n"/>
-      <c r="O1" s="256" t="n"/>
-      <c r="P1" s="256" t="n"/>
-      <c r="Q1" s="256" t="n"/>
-      <c r="R1" s="256" t="n"/>
-      <c r="S1" s="256" t="n"/>
-      <c r="T1" s="256" t="n"/>
-      <c r="U1" s="256" t="n"/>
-      <c r="V1" s="256" t="n"/>
-      <c r="W1" s="256" t="n"/>
-      <c r="X1" s="256" t="n"/>
-      <c r="Y1" s="256" t="n"/>
-      <c r="Z1" s="256" t="n"/>
-      <c r="AA1" s="256" t="n"/>
-      <c r="AB1" s="256" t="n"/>
-      <c r="AC1" s="256" t="n"/>
-      <c r="AD1" s="256" t="n"/>
-      <c r="AE1" s="259" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="360" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="256" t="n"/>
-      <c r="AG1" s="256" t="n"/>
-      <c r="AH1" s="260" t="n"/>
-      <c r="AI1" s="261" t="inlineStr">
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="361" t="n"/>
+      <c r="AI1" s="362" t="inlineStr">
         <is>
           <t>FRM-111</t>
         </is>
       </c>
-      <c r="AJ1" s="256" t="n"/>
-      <c r="AK1" s="256" t="n"/>
-      <c r="AL1" s="256" t="n"/>
-      <c r="AM1" s="256" t="n"/>
-      <c r="AN1" s="257" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="262" t="n"/>
-      <c r="B2" s="263" t="n"/>
-      <c r="C2" s="263" t="n"/>
-      <c r="D2" s="263" t="n"/>
-      <c r="E2" s="263" t="n"/>
-      <c r="F2" s="263" t="n"/>
-      <c r="G2" s="263" t="n"/>
-      <c r="H2" s="264" t="n"/>
-      <c r="I2" s="262" t="n"/>
-      <c r="J2" s="263" t="n"/>
-      <c r="K2" s="263" t="n"/>
-      <c r="L2" s="263" t="n"/>
-      <c r="M2" s="263" t="n"/>
-      <c r="N2" s="263" t="n"/>
-      <c r="O2" s="263" t="n"/>
-      <c r="P2" s="263" t="n"/>
-      <c r="Q2" s="263" t="n"/>
-      <c r="R2" s="263" t="n"/>
-      <c r="S2" s="263" t="n"/>
-      <c r="T2" s="263" t="n"/>
-      <c r="U2" s="263" t="n"/>
-      <c r="V2" s="263" t="n"/>
-      <c r="W2" s="263" t="n"/>
-      <c r="X2" s="263" t="n"/>
-      <c r="Y2" s="263" t="n"/>
-      <c r="Z2" s="263" t="n"/>
-      <c r="AA2" s="263" t="n"/>
-      <c r="AB2" s="263" t="n"/>
-      <c r="AC2" s="263" t="n"/>
-      <c r="AD2" s="263" t="n"/>
-      <c r="AE2" s="265" t="inlineStr">
+      <c r="A2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="AE2" s="363" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="266" t="n"/>
-      <c r="AG2" s="266" t="n"/>
-      <c r="AH2" s="267" t="n"/>
-      <c r="AI2" s="268" t="inlineStr">
+      <c r="AF2" s="364" t="n"/>
+      <c r="AG2" s="364" t="n"/>
+      <c r="AH2" s="365" t="n"/>
+      <c r="AI2" s="366" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="266" t="n"/>
-      <c r="AK2" s="266" t="n"/>
-      <c r="AL2" s="266" t="n"/>
-      <c r="AM2" s="266" t="n"/>
-      <c r="AN2" s="269" t="n"/>
+      <c r="AJ2" s="364" t="n"/>
+      <c r="AK2" s="364" t="n"/>
+      <c r="AL2" s="364" t="n"/>
+      <c r="AM2" s="364" t="n"/>
+      <c r="AN2" s="367" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="262" t="n"/>
-      <c r="B3" s="263" t="n"/>
-      <c r="C3" s="263" t="n"/>
-      <c r="D3" s="263" t="n"/>
-      <c r="E3" s="263" t="n"/>
-      <c r="F3" s="263" t="n"/>
-      <c r="G3" s="263" t="n"/>
-      <c r="H3" s="264" t="n"/>
-      <c r="I3" s="262" t="n"/>
-      <c r="J3" s="263" t="n"/>
-      <c r="K3" s="263" t="n"/>
-      <c r="L3" s="263" t="n"/>
-      <c r="M3" s="263" t="n"/>
-      <c r="N3" s="263" t="n"/>
-      <c r="O3" s="263" t="n"/>
-      <c r="P3" s="263" t="n"/>
-      <c r="Q3" s="263" t="n"/>
-      <c r="R3" s="263" t="n"/>
-      <c r="S3" s="263" t="n"/>
-      <c r="T3" s="263" t="n"/>
-      <c r="U3" s="263" t="n"/>
-      <c r="V3" s="263" t="n"/>
-      <c r="W3" s="263" t="n"/>
-      <c r="X3" s="263" t="n"/>
-      <c r="Y3" s="263" t="n"/>
-      <c r="Z3" s="263" t="n"/>
-      <c r="AA3" s="263" t="n"/>
-      <c r="AB3" s="263" t="n"/>
-      <c r="AC3" s="263" t="n"/>
-      <c r="AD3" s="263" t="n"/>
-      <c r="AE3" s="265" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="AE3" s="363" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="266" t="n"/>
-      <c r="AG3" s="266" t="n"/>
-      <c r="AH3" s="267" t="n"/>
-      <c r="AI3" s="268" t="inlineStr">
+      <c r="AF3" s="364" t="n"/>
+      <c r="AG3" s="364" t="n"/>
+      <c r="AH3" s="365" t="n"/>
+      <c r="AI3" s="366" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="266" t="n"/>
-      <c r="AK3" s="266" t="n"/>
-      <c r="AL3" s="266" t="n"/>
-      <c r="AM3" s="266" t="n"/>
-      <c r="AN3" s="269" t="n"/>
+      <c r="AJ3" s="364" t="n"/>
+      <c r="AK3" s="364" t="n"/>
+      <c r="AL3" s="364" t="n"/>
+      <c r="AM3" s="364" t="n"/>
+      <c r="AN3" s="367" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="262" t="n"/>
-      <c r="B4" s="263" t="n"/>
-      <c r="C4" s="263" t="n"/>
-      <c r="D4" s="263" t="n"/>
-      <c r="E4" s="263" t="n"/>
-      <c r="F4" s="263" t="n"/>
-      <c r="G4" s="263" t="n"/>
-      <c r="H4" s="264" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
       <c r="I4" s="270" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="263" t="n"/>
-      <c r="K4" s="263" t="n"/>
-      <c r="L4" s="263" t="n"/>
-      <c r="M4" s="263" t="n"/>
-      <c r="N4" s="263" t="n"/>
-      <c r="O4" s="263" t="n"/>
-      <c r="P4" s="263" t="n"/>
-      <c r="Q4" s="263" t="n"/>
-      <c r="R4" s="263" t="n"/>
-      <c r="S4" s="263" t="n"/>
-      <c r="T4" s="263" t="n"/>
-      <c r="U4" s="263" t="n"/>
-      <c r="V4" s="263" t="n"/>
-      <c r="W4" s="263" t="n"/>
-      <c r="X4" s="263" t="n"/>
-      <c r="Y4" s="263" t="n"/>
-      <c r="Z4" s="263" t="n"/>
-      <c r="AA4" s="263" t="n"/>
-      <c r="AB4" s="263" t="n"/>
-      <c r="AC4" s="263" t="n"/>
-      <c r="AD4" s="263" t="n"/>
-      <c r="AE4" s="265" t="inlineStr">
+      <c r="AE4" s="363" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="266" t="n"/>
-      <c r="AG4" s="266" t="n"/>
-      <c r="AH4" s="267" t="n"/>
-      <c r="AI4" s="268" t="inlineStr">
+      <c r="AF4" s="364" t="n"/>
+      <c r="AG4" s="364" t="n"/>
+      <c r="AH4" s="365" t="n"/>
+      <c r="AI4" s="366" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AJ4" s="266" t="n"/>
-      <c r="AK4" s="266" t="n"/>
-      <c r="AL4" s="266" t="n"/>
-      <c r="AM4" s="266" t="n"/>
-      <c r="AN4" s="269" t="n"/>
+      <c r="AJ4" s="364" t="n"/>
+      <c r="AK4" s="364" t="n"/>
+      <c r="AL4" s="364" t="n"/>
+      <c r="AM4" s="364" t="n"/>
+      <c r="AN4" s="367" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="271" t="n"/>
-      <c r="B5" s="272" t="n"/>
-      <c r="C5" s="272" t="n"/>
-      <c r="D5" s="272" t="n"/>
-      <c r="E5" s="272" t="n"/>
-      <c r="F5" s="272" t="n"/>
-      <c r="G5" s="272" t="n"/>
-      <c r="H5" s="273" t="n"/>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="18" t="n"/>
       <c r="I5" s="50" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="272" t="n"/>
-      <c r="K5" s="272" t="n"/>
-      <c r="L5" s="272" t="n"/>
-      <c r="M5" s="272" t="n"/>
-      <c r="N5" s="272" t="n"/>
-      <c r="O5" s="272" t="n"/>
-      <c r="P5" s="272" t="n"/>
-      <c r="Q5" s="272" t="n"/>
-      <c r="R5" s="272" t="n"/>
-      <c r="S5" s="272" t="n"/>
-      <c r="T5" s="272" t="n"/>
-      <c r="U5" s="272" t="n"/>
-      <c r="V5" s="272" t="n"/>
-      <c r="W5" s="272" t="n"/>
-      <c r="X5" s="272" t="n"/>
-      <c r="Y5" s="272" t="n"/>
-      <c r="Z5" s="272" t="n"/>
-      <c r="AA5" s="272" t="n"/>
-      <c r="AB5" s="272" t="n"/>
-      <c r="AC5" s="272" t="n"/>
-      <c r="AD5" s="272" t="n"/>
-      <c r="AE5" s="274" t="inlineStr">
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="17" t="n"/>
+      <c r="P5" s="17" t="n"/>
+      <c r="Q5" s="17" t="n"/>
+      <c r="R5" s="17" t="n"/>
+      <c r="S5" s="17" t="n"/>
+      <c r="T5" s="17" t="n"/>
+      <c r="U5" s="17" t="n"/>
+      <c r="V5" s="17" t="n"/>
+      <c r="W5" s="17" t="n"/>
+      <c r="X5" s="17" t="n"/>
+      <c r="Y5" s="17" t="n"/>
+      <c r="Z5" s="17" t="n"/>
+      <c r="AA5" s="17" t="n"/>
+      <c r="AB5" s="17" t="n"/>
+      <c r="AC5" s="17" t="n"/>
+      <c r="AD5" s="17" t="n"/>
+      <c r="AE5" s="368" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="275" t="n"/>
-      <c r="AG5" s="275" t="n"/>
-      <c r="AH5" s="276" t="n"/>
-      <c r="AI5" s="277" t="inlineStr">
+      <c r="AF5" s="369" t="n"/>
+      <c r="AG5" s="369" t="n"/>
+      <c r="AH5" s="370" t="n"/>
+      <c r="AI5" s="371" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AJ5" s="275" t="n"/>
-      <c r="AK5" s="275" t="n"/>
-      <c r="AL5" s="275" t="n"/>
-      <c r="AM5" s="275" t="n"/>
-      <c r="AN5" s="278" t="n"/>
+      <c r="AJ5" s="369" t="n"/>
+      <c r="AK5" s="369" t="n"/>
+      <c r="AL5" s="369" t="n"/>
+      <c r="AM5" s="369" t="n"/>
+      <c r="AN5" s="372" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="279" t="n"/>
@@ -3466,922 +3741,922 @@
       <c r="AN6" s="279" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="280" t="inlineStr">
+      <c r="A7" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REVIEW HEADER</t>
         </is>
       </c>
-      <c r="B7" s="281" t="n"/>
-      <c r="C7" s="281" t="n"/>
-      <c r="D7" s="281" t="n"/>
-      <c r="E7" s="281" t="n"/>
-      <c r="F7" s="281" t="n"/>
-      <c r="G7" s="281" t="n"/>
-      <c r="H7" s="281" t="n"/>
-      <c r="I7" s="281" t="n"/>
-      <c r="J7" s="281" t="n"/>
-      <c r="K7" s="281" t="n"/>
-      <c r="L7" s="281" t="n"/>
-      <c r="M7" s="281" t="n"/>
-      <c r="N7" s="281" t="n"/>
-      <c r="O7" s="281" t="n"/>
-      <c r="P7" s="281" t="n"/>
-      <c r="Q7" s="281" t="n"/>
-      <c r="R7" s="281" t="n"/>
-      <c r="S7" s="281" t="n"/>
-      <c r="T7" s="281" t="n"/>
-      <c r="U7" s="281" t="n"/>
-      <c r="V7" s="281" t="n"/>
-      <c r="W7" s="281" t="n"/>
-      <c r="X7" s="281" t="n"/>
-      <c r="Y7" s="281" t="n"/>
-      <c r="Z7" s="281" t="n"/>
-      <c r="AA7" s="281" t="n"/>
-      <c r="AB7" s="281" t="n"/>
-      <c r="AC7" s="281" t="n"/>
-      <c r="AD7" s="281" t="n"/>
-      <c r="AE7" s="281" t="n"/>
-      <c r="AF7" s="281" t="n"/>
-      <c r="AG7" s="281" t="n"/>
-      <c r="AH7" s="281" t="n"/>
-      <c r="AI7" s="281" t="n"/>
-      <c r="AJ7" s="281" t="n"/>
-      <c r="AK7" s="281" t="n"/>
-      <c r="AL7" s="281" t="n"/>
-      <c r="AM7" s="281" t="n"/>
-      <c r="AN7" s="282" t="n"/>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="22" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="22" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="22" t="n"/>
+      <c r="AF7" s="22" t="n"/>
+      <c r="AG7" s="22" t="n"/>
+      <c r="AH7" s="22" t="n"/>
+      <c r="AI7" s="22" t="n"/>
+      <c r="AJ7" s="22" t="n"/>
+      <c r="AK7" s="22" t="n"/>
+      <c r="AL7" s="22" t="n"/>
+      <c r="AM7" s="22" t="n"/>
+      <c r="AN7" s="23" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="283" t="inlineStr">
+      <c r="A8" s="374" t="inlineStr">
         <is>
           <t>Access Review ID</t>
         </is>
       </c>
-      <c r="B8" s="284" t="n"/>
-      <c r="C8" s="284" t="n"/>
-      <c r="D8" s="284" t="n"/>
-      <c r="E8" s="284" t="n"/>
-      <c r="F8" s="284" t="n"/>
-      <c r="G8" s="285" t="n"/>
-      <c r="H8" s="286" t="n"/>
-      <c r="I8" s="287" t="n"/>
-      <c r="J8" s="287" t="n"/>
-      <c r="K8" s="287" t="n"/>
-      <c r="L8" s="287" t="n"/>
-      <c r="M8" s="287" t="n"/>
-      <c r="N8" s="287" t="n"/>
-      <c r="O8" s="287" t="n"/>
-      <c r="P8" s="287" t="n"/>
-      <c r="Q8" s="287" t="n"/>
-      <c r="R8" s="287" t="n"/>
-      <c r="S8" s="287" t="n"/>
-      <c r="T8" s="288" t="n"/>
-      <c r="U8" s="289" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="26" t="n"/>
+      <c r="M8" s="26" t="n"/>
+      <c r="N8" s="26" t="n"/>
+      <c r="O8" s="26" t="n"/>
+      <c r="P8" s="26" t="n"/>
+      <c r="Q8" s="26" t="n"/>
+      <c r="R8" s="26" t="n"/>
+      <c r="S8" s="26" t="n"/>
+      <c r="T8" s="27" t="n"/>
+      <c r="U8" s="375" t="inlineStr">
         <is>
           <t>System / Area</t>
         </is>
       </c>
-      <c r="V8" s="284" t="n"/>
-      <c r="W8" s="284" t="n"/>
-      <c r="X8" s="284" t="n"/>
-      <c r="Y8" s="284" t="n"/>
-      <c r="Z8" s="284" t="n"/>
-      <c r="AA8" s="285" t="n"/>
-      <c r="AB8" s="286" t="n"/>
-      <c r="AC8" s="287" t="n"/>
-      <c r="AD8" s="287" t="n"/>
-      <c r="AE8" s="287" t="n"/>
-      <c r="AF8" s="287" t="n"/>
-      <c r="AG8" s="287" t="n"/>
-      <c r="AH8" s="287" t="n"/>
-      <c r="AI8" s="287" t="n"/>
-      <c r="AJ8" s="287" t="n"/>
-      <c r="AK8" s="287" t="n"/>
-      <c r="AL8" s="287" t="n"/>
-      <c r="AM8" s="287" t="n"/>
-      <c r="AN8" s="290" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="7" t="n"/>
+      <c r="AB8" s="376" t="n"/>
+      <c r="AC8" s="26" t="n"/>
+      <c r="AD8" s="26" t="n"/>
+      <c r="AE8" s="26" t="n"/>
+      <c r="AF8" s="26" t="n"/>
+      <c r="AG8" s="26" t="n"/>
+      <c r="AH8" s="26" t="n"/>
+      <c r="AI8" s="26" t="n"/>
+      <c r="AJ8" s="26" t="n"/>
+      <c r="AK8" s="26" t="n"/>
+      <c r="AL8" s="26" t="n"/>
+      <c r="AM8" s="26" t="n"/>
+      <c r="AN8" s="377" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="291" t="inlineStr">
+      <c r="A9" s="378" t="inlineStr">
         <is>
           <t>Reviewer / Process Owner</t>
         </is>
       </c>
-      <c r="B9" s="272" t="n"/>
-      <c r="C9" s="272" t="n"/>
-      <c r="D9" s="272" t="n"/>
-      <c r="E9" s="272" t="n"/>
-      <c r="F9" s="272" t="n"/>
-      <c r="G9" s="292" t="n"/>
-      <c r="H9" s="293" t="n"/>
-      <c r="I9" s="294" t="n"/>
-      <c r="J9" s="294" t="n"/>
-      <c r="K9" s="294" t="n"/>
-      <c r="L9" s="294" t="n"/>
-      <c r="M9" s="294" t="n"/>
-      <c r="N9" s="294" t="n"/>
-      <c r="O9" s="294" t="n"/>
-      <c r="P9" s="294" t="n"/>
-      <c r="Q9" s="294" t="n"/>
-      <c r="R9" s="294" t="n"/>
-      <c r="S9" s="294" t="n"/>
-      <c r="T9" s="295" t="n"/>
-      <c r="U9" s="296" t="inlineStr">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="379" t="n"/>
+      <c r="I9" s="380" t="n"/>
+      <c r="J9" s="380" t="n"/>
+      <c r="K9" s="380" t="n"/>
+      <c r="L9" s="380" t="n"/>
+      <c r="M9" s="380" t="n"/>
+      <c r="N9" s="380" t="n"/>
+      <c r="O9" s="380" t="n"/>
+      <c r="P9" s="380" t="n"/>
+      <c r="Q9" s="380" t="n"/>
+      <c r="R9" s="380" t="n"/>
+      <c r="S9" s="380" t="n"/>
+      <c r="T9" s="381" t="n"/>
+      <c r="U9" s="382" t="inlineStr">
         <is>
           <t>Review Period</t>
         </is>
       </c>
-      <c r="V9" s="272" t="n"/>
-      <c r="W9" s="272" t="n"/>
-      <c r="X9" s="272" t="n"/>
-      <c r="Y9" s="272" t="n"/>
-      <c r="Z9" s="272" t="n"/>
-      <c r="AA9" s="292" t="n"/>
-      <c r="AB9" s="293" t="n"/>
-      <c r="AC9" s="294" t="n"/>
-      <c r="AD9" s="294" t="n"/>
-      <c r="AE9" s="294" t="n"/>
-      <c r="AF9" s="294" t="n"/>
-      <c r="AG9" s="294" t="n"/>
-      <c r="AH9" s="294" t="n"/>
-      <c r="AI9" s="294" t="n"/>
-      <c r="AJ9" s="294" t="n"/>
-      <c r="AK9" s="294" t="n"/>
-      <c r="AL9" s="294" t="n"/>
-      <c r="AM9" s="294" t="n"/>
-      <c r="AN9" s="297" t="n"/>
+      <c r="V9" s="17" t="n"/>
+      <c r="W9" s="17" t="n"/>
+      <c r="X9" s="17" t="n"/>
+      <c r="Y9" s="17" t="n"/>
+      <c r="Z9" s="17" t="n"/>
+      <c r="AA9" s="52" t="n"/>
+      <c r="AB9" s="383" t="n"/>
+      <c r="AC9" s="380" t="n"/>
+      <c r="AD9" s="380" t="n"/>
+      <c r="AE9" s="380" t="n"/>
+      <c r="AF9" s="380" t="n"/>
+      <c r="AG9" s="380" t="n"/>
+      <c r="AH9" s="380" t="n"/>
+      <c r="AI9" s="380" t="n"/>
+      <c r="AJ9" s="380" t="n"/>
+      <c r="AK9" s="380" t="n"/>
+      <c r="AL9" s="380" t="n"/>
+      <c r="AM9" s="380" t="n"/>
+      <c r="AN9" s="384" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="280" t="inlineStr">
+      <c r="A10" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. REVIEW SCOPE AND BASIS</t>
         </is>
       </c>
-      <c r="B10" s="281" t="n"/>
-      <c r="C10" s="281" t="n"/>
-      <c r="D10" s="281" t="n"/>
-      <c r="E10" s="281" t="n"/>
-      <c r="F10" s="281" t="n"/>
-      <c r="G10" s="281" t="n"/>
-      <c r="H10" s="281" t="n"/>
-      <c r="I10" s="281" t="n"/>
-      <c r="J10" s="281" t="n"/>
-      <c r="K10" s="281" t="n"/>
-      <c r="L10" s="281" t="n"/>
-      <c r="M10" s="281" t="n"/>
-      <c r="N10" s="281" t="n"/>
-      <c r="O10" s="281" t="n"/>
-      <c r="P10" s="281" t="n"/>
-      <c r="Q10" s="281" t="n"/>
-      <c r="R10" s="281" t="n"/>
-      <c r="S10" s="281" t="n"/>
-      <c r="T10" s="281" t="n"/>
-      <c r="U10" s="281" t="n"/>
-      <c r="V10" s="281" t="n"/>
-      <c r="W10" s="281" t="n"/>
-      <c r="X10" s="281" t="n"/>
-      <c r="Y10" s="281" t="n"/>
-      <c r="Z10" s="281" t="n"/>
-      <c r="AA10" s="281" t="n"/>
-      <c r="AB10" s="281" t="n"/>
-      <c r="AC10" s="281" t="n"/>
-      <c r="AD10" s="281" t="n"/>
-      <c r="AE10" s="281" t="n"/>
-      <c r="AF10" s="281" t="n"/>
-      <c r="AG10" s="281" t="n"/>
-      <c r="AH10" s="281" t="n"/>
-      <c r="AI10" s="281" t="n"/>
-      <c r="AJ10" s="281" t="n"/>
-      <c r="AK10" s="281" t="n"/>
-      <c r="AL10" s="281" t="n"/>
-      <c r="AM10" s="281" t="n"/>
-      <c r="AN10" s="282" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="22" t="n"/>
+      <c r="U10" s="22" t="n"/>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="22" t="n"/>
+      <c r="Y10" s="22" t="n"/>
+      <c r="Z10" s="22" t="n"/>
+      <c r="AA10" s="22" t="n"/>
+      <c r="AB10" s="22" t="n"/>
+      <c r="AC10" s="22" t="n"/>
+      <c r="AD10" s="22" t="n"/>
+      <c r="AE10" s="22" t="n"/>
+      <c r="AF10" s="22" t="n"/>
+      <c r="AG10" s="22" t="n"/>
+      <c r="AH10" s="22" t="n"/>
+      <c r="AI10" s="22" t="n"/>
+      <c r="AJ10" s="22" t="n"/>
+      <c r="AK10" s="22" t="n"/>
+      <c r="AL10" s="22" t="n"/>
+      <c r="AM10" s="22" t="n"/>
+      <c r="AN10" s="23" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="298" t="inlineStr">
+      <c r="A11" s="385" t="inlineStr">
         <is>
           <t>Account Population / Role Scope</t>
         </is>
       </c>
-      <c r="B11" s="281" t="n"/>
-      <c r="C11" s="281" t="n"/>
-      <c r="D11" s="281" t="n"/>
-      <c r="E11" s="281" t="n"/>
-      <c r="F11" s="281" t="n"/>
-      <c r="G11" s="299" t="n"/>
-      <c r="H11" s="300" t="n"/>
-      <c r="I11" s="301" t="n"/>
-      <c r="J11" s="301" t="n"/>
-      <c r="K11" s="301" t="n"/>
-      <c r="L11" s="301" t="n"/>
-      <c r="M11" s="301" t="n"/>
-      <c r="N11" s="301" t="n"/>
-      <c r="O11" s="301" t="n"/>
-      <c r="P11" s="301" t="n"/>
-      <c r="Q11" s="301" t="n"/>
-      <c r="R11" s="301" t="n"/>
-      <c r="S11" s="301" t="n"/>
-      <c r="T11" s="302" t="n"/>
-      <c r="U11" s="303" t="inlineStr">
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="386" t="n"/>
+      <c r="H11" s="387" t="n"/>
+      <c r="I11" s="388" t="n"/>
+      <c r="J11" s="388" t="n"/>
+      <c r="K11" s="388" t="n"/>
+      <c r="L11" s="388" t="n"/>
+      <c r="M11" s="388" t="n"/>
+      <c r="N11" s="388" t="n"/>
+      <c r="O11" s="388" t="n"/>
+      <c r="P11" s="388" t="n"/>
+      <c r="Q11" s="388" t="n"/>
+      <c r="R11" s="388" t="n"/>
+      <c r="S11" s="388" t="n"/>
+      <c r="T11" s="389" t="n"/>
+      <c r="U11" s="390" t="inlineStr">
         <is>
           <t>Source-of-Truth Date</t>
         </is>
       </c>
-      <c r="V11" s="281" t="n"/>
-      <c r="W11" s="281" t="n"/>
-      <c r="X11" s="281" t="n"/>
-      <c r="Y11" s="281" t="n"/>
-      <c r="Z11" s="281" t="n"/>
-      <c r="AA11" s="299" t="n"/>
-      <c r="AB11" s="300" t="n"/>
-      <c r="AC11" s="301" t="n"/>
-      <c r="AD11" s="301" t="n"/>
-      <c r="AE11" s="301" t="n"/>
-      <c r="AF11" s="301" t="n"/>
-      <c r="AG11" s="301" t="n"/>
-      <c r="AH11" s="301" t="n"/>
-      <c r="AI11" s="301" t="n"/>
-      <c r="AJ11" s="301" t="n"/>
-      <c r="AK11" s="301" t="n"/>
-      <c r="AL11" s="301" t="n"/>
-      <c r="AM11" s="301" t="n"/>
-      <c r="AN11" s="304" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="22" t="n"/>
+      <c r="Y11" s="22" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="386" t="n"/>
+      <c r="AB11" s="391" t="n"/>
+      <c r="AC11" s="388" t="n"/>
+      <c r="AD11" s="388" t="n"/>
+      <c r="AE11" s="388" t="n"/>
+      <c r="AF11" s="388" t="n"/>
+      <c r="AG11" s="388" t="n"/>
+      <c r="AH11" s="388" t="n"/>
+      <c r="AI11" s="388" t="n"/>
+      <c r="AJ11" s="388" t="n"/>
+      <c r="AK11" s="388" t="n"/>
+      <c r="AL11" s="388" t="n"/>
+      <c r="AM11" s="388" t="n"/>
+      <c r="AN11" s="392" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="280" t="inlineStr">
+      <c r="A12" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. FINDINGS, ACTION AND ESCALATION</t>
         </is>
       </c>
-      <c r="B12" s="281" t="n"/>
-      <c r="C12" s="281" t="n"/>
-      <c r="D12" s="281" t="n"/>
-      <c r="E12" s="281" t="n"/>
-      <c r="F12" s="281" t="n"/>
-      <c r="G12" s="281" t="n"/>
-      <c r="H12" s="281" t="n"/>
-      <c r="I12" s="281" t="n"/>
-      <c r="J12" s="281" t="n"/>
-      <c r="K12" s="281" t="n"/>
-      <c r="L12" s="281" t="n"/>
-      <c r="M12" s="281" t="n"/>
-      <c r="N12" s="281" t="n"/>
-      <c r="O12" s="281" t="n"/>
-      <c r="P12" s="281" t="n"/>
-      <c r="Q12" s="281" t="n"/>
-      <c r="R12" s="281" t="n"/>
-      <c r="S12" s="281" t="n"/>
-      <c r="T12" s="281" t="n"/>
-      <c r="U12" s="281" t="n"/>
-      <c r="V12" s="281" t="n"/>
-      <c r="W12" s="281" t="n"/>
-      <c r="X12" s="281" t="n"/>
-      <c r="Y12" s="281" t="n"/>
-      <c r="Z12" s="281" t="n"/>
-      <c r="AA12" s="281" t="n"/>
-      <c r="AB12" s="281" t="n"/>
-      <c r="AC12" s="281" t="n"/>
-      <c r="AD12" s="281" t="n"/>
-      <c r="AE12" s="281" t="n"/>
-      <c r="AF12" s="281" t="n"/>
-      <c r="AG12" s="281" t="n"/>
-      <c r="AH12" s="281" t="n"/>
-      <c r="AI12" s="281" t="n"/>
-      <c r="AJ12" s="281" t="n"/>
-      <c r="AK12" s="281" t="n"/>
-      <c r="AL12" s="281" t="n"/>
-      <c r="AM12" s="281" t="n"/>
-      <c r="AN12" s="282" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="22" t="n"/>
+      <c r="U12" s="22" t="n"/>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="22" t="n"/>
+      <c r="X12" s="22" t="n"/>
+      <c r="Y12" s="22" t="n"/>
+      <c r="Z12" s="22" t="n"/>
+      <c r="AA12" s="22" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+      <c r="AE12" s="22" t="n"/>
+      <c r="AF12" s="22" t="n"/>
+      <c r="AG12" s="22" t="n"/>
+      <c r="AH12" s="22" t="n"/>
+      <c r="AI12" s="22" t="n"/>
+      <c r="AJ12" s="22" t="n"/>
+      <c r="AK12" s="22" t="n"/>
+      <c r="AL12" s="22" t="n"/>
+      <c r="AM12" s="22" t="n"/>
+      <c r="AN12" s="23" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="298" t="inlineStr">
+      <c r="A13" s="385" t="inlineStr">
         <is>
           <t>Privilege / SoD Exceptions</t>
         </is>
       </c>
-      <c r="B13" s="281" t="n"/>
-      <c r="C13" s="281" t="n"/>
-      <c r="D13" s="281" t="n"/>
-      <c r="E13" s="281" t="n"/>
-      <c r="F13" s="281" t="n"/>
-      <c r="G13" s="299" t="n"/>
-      <c r="H13" s="300" t="n"/>
-      <c r="I13" s="301" t="n"/>
-      <c r="J13" s="301" t="n"/>
-      <c r="K13" s="301" t="n"/>
-      <c r="L13" s="301" t="n"/>
-      <c r="M13" s="301" t="n"/>
-      <c r="N13" s="301" t="n"/>
-      <c r="O13" s="301" t="n"/>
-      <c r="P13" s="301" t="n"/>
-      <c r="Q13" s="301" t="n"/>
-      <c r="R13" s="301" t="n"/>
-      <c r="S13" s="301" t="n"/>
-      <c r="T13" s="302" t="n"/>
-      <c r="U13" s="303" t="inlineStr">
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="386" t="n"/>
+      <c r="H13" s="387" t="n"/>
+      <c r="I13" s="388" t="n"/>
+      <c r="J13" s="388" t="n"/>
+      <c r="K13" s="388" t="n"/>
+      <c r="L13" s="388" t="n"/>
+      <c r="M13" s="388" t="n"/>
+      <c r="N13" s="388" t="n"/>
+      <c r="O13" s="388" t="n"/>
+      <c r="P13" s="388" t="n"/>
+      <c r="Q13" s="388" t="n"/>
+      <c r="R13" s="388" t="n"/>
+      <c r="S13" s="388" t="n"/>
+      <c r="T13" s="389" t="n"/>
+      <c r="U13" s="390" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="V13" s="281" t="n"/>
-      <c r="W13" s="281" t="n"/>
-      <c r="X13" s="281" t="n"/>
-      <c r="Y13" s="281" t="n"/>
-      <c r="Z13" s="281" t="n"/>
-      <c r="AA13" s="299" t="n"/>
-      <c r="AB13" s="300" t="n"/>
-      <c r="AC13" s="301" t="n"/>
-      <c r="AD13" s="301" t="n"/>
-      <c r="AE13" s="301" t="n"/>
-      <c r="AF13" s="301" t="n"/>
-      <c r="AG13" s="301" t="n"/>
-      <c r="AH13" s="301" t="n"/>
-      <c r="AI13" s="301" t="n"/>
-      <c r="AJ13" s="301" t="n"/>
-      <c r="AK13" s="301" t="n"/>
-      <c r="AL13" s="301" t="n"/>
-      <c r="AM13" s="301" t="n"/>
-      <c r="AN13" s="304" t="n"/>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="22" t="n"/>
+      <c r="Y13" s="22" t="n"/>
+      <c r="Z13" s="22" t="n"/>
+      <c r="AA13" s="386" t="n"/>
+      <c r="AB13" s="391" t="n"/>
+      <c r="AC13" s="388" t="n"/>
+      <c r="AD13" s="388" t="n"/>
+      <c r="AE13" s="388" t="n"/>
+      <c r="AF13" s="388" t="n"/>
+      <c r="AG13" s="388" t="n"/>
+      <c r="AH13" s="388" t="n"/>
+      <c r="AI13" s="388" t="n"/>
+      <c r="AJ13" s="388" t="n"/>
+      <c r="AK13" s="388" t="n"/>
+      <c r="AL13" s="388" t="n"/>
+      <c r="AM13" s="388" t="n"/>
+      <c r="AN13" s="392" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="280" t="inlineStr">
+      <c r="A14" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DECISION AND CLOSEOUT</t>
         </is>
       </c>
-      <c r="B14" s="281" t="n"/>
-      <c r="C14" s="281" t="n"/>
-      <c r="D14" s="281" t="n"/>
-      <c r="E14" s="281" t="n"/>
-      <c r="F14" s="281" t="n"/>
-      <c r="G14" s="281" t="n"/>
-      <c r="H14" s="281" t="n"/>
-      <c r="I14" s="281" t="n"/>
-      <c r="J14" s="281" t="n"/>
-      <c r="K14" s="281" t="n"/>
-      <c r="L14" s="281" t="n"/>
-      <c r="M14" s="281" t="n"/>
-      <c r="N14" s="281" t="n"/>
-      <c r="O14" s="281" t="n"/>
-      <c r="P14" s="281" t="n"/>
-      <c r="Q14" s="281" t="n"/>
-      <c r="R14" s="281" t="n"/>
-      <c r="S14" s="281" t="n"/>
-      <c r="T14" s="281" t="n"/>
-      <c r="U14" s="281" t="n"/>
-      <c r="V14" s="281" t="n"/>
-      <c r="W14" s="281" t="n"/>
-      <c r="X14" s="281" t="n"/>
-      <c r="Y14" s="281" t="n"/>
-      <c r="Z14" s="281" t="n"/>
-      <c r="AA14" s="281" t="n"/>
-      <c r="AB14" s="281" t="n"/>
-      <c r="AC14" s="281" t="n"/>
-      <c r="AD14" s="281" t="n"/>
-      <c r="AE14" s="281" t="n"/>
-      <c r="AF14" s="281" t="n"/>
-      <c r="AG14" s="281" t="n"/>
-      <c r="AH14" s="281" t="n"/>
-      <c r="AI14" s="281" t="n"/>
-      <c r="AJ14" s="281" t="n"/>
-      <c r="AK14" s="281" t="n"/>
-      <c r="AL14" s="281" t="n"/>
-      <c r="AM14" s="281" t="n"/>
-      <c r="AN14" s="282" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="22" t="n"/>
+      <c r="R14" s="22" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="22" t="n"/>
+      <c r="U14" s="22" t="n"/>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="22" t="n"/>
+      <c r="Y14" s="22" t="n"/>
+      <c r="Z14" s="22" t="n"/>
+      <c r="AA14" s="22" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="22" t="n"/>
+      <c r="AF14" s="22" t="n"/>
+      <c r="AG14" s="22" t="n"/>
+      <c r="AH14" s="22" t="n"/>
+      <c r="AI14" s="22" t="n"/>
+      <c r="AJ14" s="22" t="n"/>
+      <c r="AK14" s="22" t="n"/>
+      <c r="AL14" s="22" t="n"/>
+      <c r="AM14" s="22" t="n"/>
+      <c r="AN14" s="23" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="283" t="inlineStr">
+      <c r="A15" s="374" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B15" s="284" t="n"/>
-      <c r="C15" s="284" t="n"/>
-      <c r="D15" s="284" t="n"/>
-      <c r="E15" s="284" t="n"/>
-      <c r="F15" s="284" t="n"/>
-      <c r="G15" s="285" t="n"/>
-      <c r="H15" s="286" t="n"/>
-      <c r="I15" s="287" t="n"/>
-      <c r="J15" s="287" t="n"/>
-      <c r="K15" s="287" t="n"/>
-      <c r="L15" s="287" t="n"/>
-      <c r="M15" s="287" t="n"/>
-      <c r="N15" s="287" t="n"/>
-      <c r="O15" s="287" t="n"/>
-      <c r="P15" s="287" t="n"/>
-      <c r="Q15" s="287" t="n"/>
-      <c r="R15" s="287" t="n"/>
-      <c r="S15" s="287" t="n"/>
-      <c r="T15" s="288" t="n"/>
-      <c r="U15" s="289" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="26" t="n"/>
+      <c r="J15" s="26" t="n"/>
+      <c r="K15" s="26" t="n"/>
+      <c r="L15" s="26" t="n"/>
+      <c r="M15" s="26" t="n"/>
+      <c r="N15" s="26" t="n"/>
+      <c r="O15" s="26" t="n"/>
+      <c r="P15" s="26" t="n"/>
+      <c r="Q15" s="26" t="n"/>
+      <c r="R15" s="26" t="n"/>
+      <c r="S15" s="26" t="n"/>
+      <c r="T15" s="27" t="n"/>
+      <c r="U15" s="375" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="V15" s="284" t="n"/>
-      <c r="W15" s="284" t="n"/>
-      <c r="X15" s="284" t="n"/>
-      <c r="Y15" s="284" t="n"/>
-      <c r="Z15" s="284" t="n"/>
-      <c r="AA15" s="285" t="n"/>
-      <c r="AB15" s="286" t="n"/>
-      <c r="AC15" s="287" t="n"/>
-      <c r="AD15" s="287" t="n"/>
-      <c r="AE15" s="287" t="n"/>
-      <c r="AF15" s="287" t="n"/>
-      <c r="AG15" s="287" t="n"/>
-      <c r="AH15" s="287" t="n"/>
-      <c r="AI15" s="287" t="n"/>
-      <c r="AJ15" s="287" t="n"/>
-      <c r="AK15" s="287" t="n"/>
-      <c r="AL15" s="287" t="n"/>
-      <c r="AM15" s="287" t="n"/>
-      <c r="AN15" s="290" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="7" t="n"/>
+      <c r="AB15" s="376" t="n"/>
+      <c r="AC15" s="26" t="n"/>
+      <c r="AD15" s="26" t="n"/>
+      <c r="AE15" s="26" t="n"/>
+      <c r="AF15" s="26" t="n"/>
+      <c r="AG15" s="26" t="n"/>
+      <c r="AH15" s="26" t="n"/>
+      <c r="AI15" s="26" t="n"/>
+      <c r="AJ15" s="26" t="n"/>
+      <c r="AK15" s="26" t="n"/>
+      <c r="AL15" s="26" t="n"/>
+      <c r="AM15" s="26" t="n"/>
+      <c r="AN15" s="377" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="305" t="inlineStr">
+      <c r="A16" s="393" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B16" s="306" t="n"/>
-      <c r="C16" s="306" t="n"/>
-      <c r="D16" s="306" t="n"/>
-      <c r="E16" s="306" t="n"/>
-      <c r="F16" s="306" t="n"/>
-      <c r="G16" s="307" t="n"/>
-      <c r="H16" s="308" t="n"/>
-      <c r="I16" s="309" t="n"/>
-      <c r="J16" s="309" t="n"/>
-      <c r="K16" s="309" t="n"/>
-      <c r="L16" s="309" t="n"/>
-      <c r="M16" s="309" t="n"/>
-      <c r="N16" s="309" t="n"/>
-      <c r="O16" s="309" t="n"/>
-      <c r="P16" s="309" t="n"/>
-      <c r="Q16" s="309" t="n"/>
-      <c r="R16" s="309" t="n"/>
-      <c r="S16" s="309" t="n"/>
-      <c r="T16" s="310" t="n"/>
-      <c r="U16" s="311" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="41" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="35" t="n"/>
+      <c r="N16" s="35" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+      <c r="R16" s="35" t="n"/>
+      <c r="S16" s="35" t="n"/>
+      <c r="T16" s="36" t="n"/>
+      <c r="U16" s="394" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="V16" s="306" t="n"/>
-      <c r="W16" s="306" t="n"/>
-      <c r="X16" s="306" t="n"/>
-      <c r="Y16" s="306" t="n"/>
-      <c r="Z16" s="306" t="n"/>
-      <c r="AA16" s="307" t="n"/>
-      <c r="AB16" s="308" t="n"/>
-      <c r="AC16" s="309" t="n"/>
-      <c r="AD16" s="309" t="n"/>
-      <c r="AE16" s="309" t="n"/>
-      <c r="AF16" s="309" t="n"/>
-      <c r="AG16" s="309" t="n"/>
-      <c r="AH16" s="309" t="n"/>
-      <c r="AI16" s="309" t="n"/>
-      <c r="AJ16" s="309" t="n"/>
-      <c r="AK16" s="309" t="n"/>
-      <c r="AL16" s="309" t="n"/>
-      <c r="AM16" s="309" t="n"/>
-      <c r="AN16" s="312" t="n"/>
+      <c r="V16" s="14" t="n"/>
+      <c r="W16" s="14" t="n"/>
+      <c r="X16" s="14" t="n"/>
+      <c r="Y16" s="14" t="n"/>
+      <c r="Z16" s="14" t="n"/>
+      <c r="AA16" s="29" t="n"/>
+      <c r="AB16" s="395" t="n"/>
+      <c r="AC16" s="35" t="n"/>
+      <c r="AD16" s="35" t="n"/>
+      <c r="AE16" s="35" t="n"/>
+      <c r="AF16" s="35" t="n"/>
+      <c r="AG16" s="35" t="n"/>
+      <c r="AH16" s="35" t="n"/>
+      <c r="AI16" s="35" t="n"/>
+      <c r="AJ16" s="35" t="n"/>
+      <c r="AK16" s="35" t="n"/>
+      <c r="AL16" s="35" t="n"/>
+      <c r="AM16" s="35" t="n"/>
+      <c r="AN16" s="396" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="305" t="inlineStr">
+      <c r="A17" s="393" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="B17" s="306" t="n"/>
-      <c r="C17" s="306" t="n"/>
-      <c r="D17" s="306" t="n"/>
-      <c r="E17" s="306" t="n"/>
-      <c r="F17" s="306" t="n"/>
-      <c r="G17" s="307" t="n"/>
-      <c r="H17" s="308" t="n"/>
-      <c r="I17" s="309" t="n"/>
-      <c r="J17" s="309" t="n"/>
-      <c r="K17" s="309" t="n"/>
-      <c r="L17" s="309" t="n"/>
-      <c r="M17" s="309" t="n"/>
-      <c r="N17" s="309" t="n"/>
-      <c r="O17" s="309" t="n"/>
-      <c r="P17" s="309" t="n"/>
-      <c r="Q17" s="309" t="n"/>
-      <c r="R17" s="309" t="n"/>
-      <c r="S17" s="309" t="n"/>
-      <c r="T17" s="310" t="n"/>
-      <c r="U17" s="311" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="41" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="35" t="n"/>
+      <c r="K17" s="35" t="n"/>
+      <c r="L17" s="35" t="n"/>
+      <c r="M17" s="35" t="n"/>
+      <c r="N17" s="35" t="n"/>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="35" t="n"/>
+      <c r="R17" s="35" t="n"/>
+      <c r="S17" s="35" t="n"/>
+      <c r="T17" s="36" t="n"/>
+      <c r="U17" s="394" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="V17" s="306" t="n"/>
-      <c r="W17" s="306" t="n"/>
-      <c r="X17" s="306" t="n"/>
-      <c r="Y17" s="306" t="n"/>
-      <c r="Z17" s="306" t="n"/>
-      <c r="AA17" s="307" t="n"/>
-      <c r="AB17" s="308" t="n"/>
-      <c r="AC17" s="309" t="n"/>
-      <c r="AD17" s="309" t="n"/>
-      <c r="AE17" s="309" t="n"/>
-      <c r="AF17" s="309" t="n"/>
-      <c r="AG17" s="309" t="n"/>
-      <c r="AH17" s="309" t="n"/>
-      <c r="AI17" s="309" t="n"/>
-      <c r="AJ17" s="309" t="n"/>
-      <c r="AK17" s="309" t="n"/>
-      <c r="AL17" s="309" t="n"/>
-      <c r="AM17" s="309" t="n"/>
-      <c r="AN17" s="312" t="n"/>
+      <c r="V17" s="14" t="n"/>
+      <c r="W17" s="14" t="n"/>
+      <c r="X17" s="14" t="n"/>
+      <c r="Y17" s="14" t="n"/>
+      <c r="Z17" s="14" t="n"/>
+      <c r="AA17" s="29" t="n"/>
+      <c r="AB17" s="395" t="n"/>
+      <c r="AC17" s="35" t="n"/>
+      <c r="AD17" s="35" t="n"/>
+      <c r="AE17" s="35" t="n"/>
+      <c r="AF17" s="35" t="n"/>
+      <c r="AG17" s="35" t="n"/>
+      <c r="AH17" s="35" t="n"/>
+      <c r="AI17" s="35" t="n"/>
+      <c r="AJ17" s="35" t="n"/>
+      <c r="AK17" s="35" t="n"/>
+      <c r="AL17" s="35" t="n"/>
+      <c r="AM17" s="35" t="n"/>
+      <c r="AN17" s="396" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="313" t="inlineStr">
+      <c r="A18" s="397" t="inlineStr">
         <is>
           <t>Prepared By</t>
         </is>
       </c>
-      <c r="B18" s="306" t="n"/>
-      <c r="C18" s="306" t="n"/>
-      <c r="D18" s="306" t="n"/>
-      <c r="E18" s="306" t="n"/>
-      <c r="F18" s="306" t="n"/>
-      <c r="G18" s="306" t="n"/>
-      <c r="H18" s="306" t="n"/>
-      <c r="I18" s="306" t="n"/>
-      <c r="J18" s="306" t="n"/>
-      <c r="K18" s="306" t="n"/>
-      <c r="L18" s="306" t="n"/>
-      <c r="M18" s="307" t="n"/>
-      <c r="N18" s="314" t="inlineStr">
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="29" t="n"/>
+      <c r="N18" s="398" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="O18" s="306" t="n"/>
-      <c r="P18" s="306" t="n"/>
-      <c r="Q18" s="306" t="n"/>
-      <c r="R18" s="306" t="n"/>
-      <c r="S18" s="306" t="n"/>
-      <c r="T18" s="306" t="n"/>
-      <c r="U18" s="306" t="n"/>
-      <c r="V18" s="306" t="n"/>
-      <c r="W18" s="306" t="n"/>
-      <c r="X18" s="306" t="n"/>
-      <c r="Y18" s="306" t="n"/>
-      <c r="Z18" s="307" t="n"/>
-      <c r="AA18" s="314" t="inlineStr">
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
+      <c r="T18" s="14" t="n"/>
+      <c r="U18" s="14" t="n"/>
+      <c r="V18" s="14" t="n"/>
+      <c r="W18" s="14" t="n"/>
+      <c r="X18" s="14" t="n"/>
+      <c r="Y18" s="14" t="n"/>
+      <c r="Z18" s="29" t="n"/>
+      <c r="AA18" s="399" t="inlineStr">
         <is>
           <t>Approved By</t>
         </is>
       </c>
-      <c r="AB18" s="306" t="n"/>
-      <c r="AC18" s="306" t="n"/>
-      <c r="AD18" s="306" t="n"/>
-      <c r="AE18" s="306" t="n"/>
-      <c r="AF18" s="306" t="n"/>
-      <c r="AG18" s="306" t="n"/>
-      <c r="AH18" s="306" t="n"/>
-      <c r="AI18" s="306" t="n"/>
-      <c r="AJ18" s="306" t="n"/>
-      <c r="AK18" s="306" t="n"/>
-      <c r="AL18" s="306" t="n"/>
-      <c r="AM18" s="306" t="n"/>
-      <c r="AN18" s="315" t="n"/>
+      <c r="AB18" s="14" t="n"/>
+      <c r="AC18" s="14" t="n"/>
+      <c r="AD18" s="14" t="n"/>
+      <c r="AE18" s="14" t="n"/>
+      <c r="AF18" s="14" t="n"/>
+      <c r="AG18" s="14" t="n"/>
+      <c r="AH18" s="14" t="n"/>
+      <c r="AI18" s="14" t="n"/>
+      <c r="AJ18" s="14" t="n"/>
+      <c r="AK18" s="14" t="n"/>
+      <c r="AL18" s="14" t="n"/>
+      <c r="AM18" s="14" t="n"/>
+      <c r="AN18" s="48" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="316" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B19" s="309" t="n"/>
-      <c r="C19" s="309" t="n"/>
-      <c r="D19" s="309" t="n"/>
-      <c r="E19" s="309" t="n"/>
-      <c r="F19" s="309" t="n"/>
-      <c r="G19" s="309" t="n"/>
-      <c r="H19" s="309" t="n"/>
-      <c r="I19" s="309" t="n"/>
-      <c r="J19" s="309" t="n"/>
-      <c r="K19" s="309" t="n"/>
-      <c r="L19" s="309" t="n"/>
-      <c r="M19" s="310" t="n"/>
-      <c r="N19" s="317" t="inlineStr">
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="31" t="n"/>
+      <c r="H19" s="31" t="n"/>
+      <c r="I19" s="31" t="n"/>
+      <c r="J19" s="31" t="n"/>
+      <c r="K19" s="31" t="n"/>
+      <c r="L19" s="31" t="n"/>
+      <c r="M19" s="32" t="n"/>
+      <c r="N19" s="400" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O19" s="309" t="n"/>
-      <c r="P19" s="309" t="n"/>
-      <c r="Q19" s="309" t="n"/>
-      <c r="R19" s="309" t="n"/>
-      <c r="S19" s="309" t="n"/>
-      <c r="T19" s="309" t="n"/>
-      <c r="U19" s="309" t="n"/>
-      <c r="V19" s="309" t="n"/>
-      <c r="W19" s="309" t="n"/>
-      <c r="X19" s="309" t="n"/>
-      <c r="Y19" s="309" t="n"/>
-      <c r="Z19" s="310" t="n"/>
-      <c r="AA19" s="317" t="inlineStr">
+      <c r="O19" s="31" t="n"/>
+      <c r="P19" s="31" t="n"/>
+      <c r="Q19" s="31" t="n"/>
+      <c r="R19" s="31" t="n"/>
+      <c r="S19" s="31" t="n"/>
+      <c r="T19" s="31" t="n"/>
+      <c r="U19" s="31" t="n"/>
+      <c r="V19" s="31" t="n"/>
+      <c r="W19" s="31" t="n"/>
+      <c r="X19" s="31" t="n"/>
+      <c r="Y19" s="31" t="n"/>
+      <c r="Z19" s="32" t="n"/>
+      <c r="AA19" s="401" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB19" s="309" t="n"/>
-      <c r="AC19" s="309" t="n"/>
-      <c r="AD19" s="309" t="n"/>
-      <c r="AE19" s="309" t="n"/>
-      <c r="AF19" s="309" t="n"/>
-      <c r="AG19" s="309" t="n"/>
-      <c r="AH19" s="309" t="n"/>
-      <c r="AI19" s="309" t="n"/>
-      <c r="AJ19" s="309" t="n"/>
-      <c r="AK19" s="309" t="n"/>
-      <c r="AL19" s="309" t="n"/>
-      <c r="AM19" s="309" t="n"/>
-      <c r="AN19" s="312" t="n"/>
+      <c r="AB19" s="31" t="n"/>
+      <c r="AC19" s="31" t="n"/>
+      <c r="AD19" s="31" t="n"/>
+      <c r="AE19" s="31" t="n"/>
+      <c r="AF19" s="31" t="n"/>
+      <c r="AG19" s="31" t="n"/>
+      <c r="AH19" s="31" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="31" t="n"/>
+      <c r="AL19" s="31" t="n"/>
+      <c r="AM19" s="31" t="n"/>
+      <c r="AN19" s="402" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="318" t="n"/>
-      <c r="B20" s="309" t="n"/>
-      <c r="C20" s="309" t="n"/>
-      <c r="D20" s="309" t="n"/>
-      <c r="E20" s="309" t="n"/>
-      <c r="F20" s="309" t="n"/>
-      <c r="G20" s="309" t="n"/>
-      <c r="H20" s="309" t="n"/>
-      <c r="I20" s="309" t="n"/>
-      <c r="J20" s="309" t="n"/>
-      <c r="K20" s="309" t="n"/>
-      <c r="L20" s="309" t="n"/>
-      <c r="M20" s="310" t="n"/>
-      <c r="N20" s="309" t="n"/>
-      <c r="O20" s="309" t="n"/>
-      <c r="P20" s="309" t="n"/>
-      <c r="Q20" s="309" t="n"/>
-      <c r="R20" s="309" t="n"/>
-      <c r="S20" s="309" t="n"/>
-      <c r="T20" s="309" t="n"/>
-      <c r="U20" s="309" t="n"/>
-      <c r="V20" s="309" t="n"/>
-      <c r="W20" s="309" t="n"/>
-      <c r="X20" s="309" t="n"/>
-      <c r="Y20" s="309" t="n"/>
-      <c r="Z20" s="310" t="n"/>
-      <c r="AA20" s="309" t="n"/>
-      <c r="AB20" s="309" t="n"/>
-      <c r="AC20" s="309" t="n"/>
-      <c r="AD20" s="309" t="n"/>
-      <c r="AE20" s="309" t="n"/>
-      <c r="AF20" s="309" t="n"/>
-      <c r="AG20" s="309" t="n"/>
-      <c r="AH20" s="309" t="n"/>
-      <c r="AI20" s="309" t="n"/>
-      <c r="AJ20" s="309" t="n"/>
-      <c r="AK20" s="309" t="n"/>
-      <c r="AL20" s="309" t="n"/>
-      <c r="AM20" s="309" t="n"/>
-      <c r="AN20" s="312" t="n"/>
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+      <c r="J20" s="31" t="n"/>
+      <c r="K20" s="31" t="n"/>
+      <c r="L20" s="31" t="n"/>
+      <c r="M20" s="32" t="n"/>
+      <c r="N20" s="31" t="n"/>
+      <c r="O20" s="31" t="n"/>
+      <c r="P20" s="31" t="n"/>
+      <c r="Q20" s="31" t="n"/>
+      <c r="R20" s="31" t="n"/>
+      <c r="S20" s="31" t="n"/>
+      <c r="T20" s="31" t="n"/>
+      <c r="U20" s="31" t="n"/>
+      <c r="V20" s="31" t="n"/>
+      <c r="W20" s="31" t="n"/>
+      <c r="X20" s="31" t="n"/>
+      <c r="Y20" s="31" t="n"/>
+      <c r="Z20" s="32" t="n"/>
+      <c r="AA20" s="31" t="n"/>
+      <c r="AB20" s="31" t="n"/>
+      <c r="AC20" s="31" t="n"/>
+      <c r="AD20" s="31" t="n"/>
+      <c r="AE20" s="31" t="n"/>
+      <c r="AF20" s="31" t="n"/>
+      <c r="AG20" s="31" t="n"/>
+      <c r="AH20" s="31" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="31" t="n"/>
+      <c r="AL20" s="31" t="n"/>
+      <c r="AM20" s="31" t="n"/>
+      <c r="AN20" s="402" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="319" t="n"/>
-      <c r="B21" s="294" t="n"/>
-      <c r="C21" s="294" t="n"/>
-      <c r="D21" s="294" t="n"/>
-      <c r="E21" s="294" t="n"/>
-      <c r="F21" s="294" t="n"/>
-      <c r="G21" s="294" t="n"/>
-      <c r="H21" s="294" t="n"/>
-      <c r="I21" s="294" t="n"/>
-      <c r="J21" s="294" t="n"/>
-      <c r="K21" s="294" t="n"/>
-      <c r="L21" s="294" t="n"/>
-      <c r="M21" s="295" t="n"/>
-      <c r="N21" s="294" t="n"/>
-      <c r="O21" s="294" t="n"/>
-      <c r="P21" s="294" t="n"/>
-      <c r="Q21" s="294" t="n"/>
-      <c r="R21" s="294" t="n"/>
-      <c r="S21" s="294" t="n"/>
-      <c r="T21" s="294" t="n"/>
-      <c r="U21" s="294" t="n"/>
-      <c r="V21" s="294" t="n"/>
-      <c r="W21" s="294" t="n"/>
-      <c r="X21" s="294" t="n"/>
-      <c r="Y21" s="294" t="n"/>
-      <c r="Z21" s="295" t="n"/>
-      <c r="AA21" s="294" t="n"/>
-      <c r="AB21" s="294" t="n"/>
-      <c r="AC21" s="294" t="n"/>
-      <c r="AD21" s="294" t="n"/>
-      <c r="AE21" s="294" t="n"/>
-      <c r="AF21" s="294" t="n"/>
-      <c r="AG21" s="294" t="n"/>
-      <c r="AH21" s="294" t="n"/>
-      <c r="AI21" s="294" t="n"/>
-      <c r="AJ21" s="294" t="n"/>
-      <c r="AK21" s="294" t="n"/>
-      <c r="AL21" s="294" t="n"/>
-      <c r="AM21" s="294" t="n"/>
-      <c r="AN21" s="297" t="n"/>
+      <c r="A21" s="34" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="35" t="n"/>
+      <c r="K21" s="35" t="n"/>
+      <c r="L21" s="35" t="n"/>
+      <c r="M21" s="36" t="n"/>
+      <c r="N21" s="35" t="n"/>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+      <c r="R21" s="35" t="n"/>
+      <c r="S21" s="35" t="n"/>
+      <c r="T21" s="35" t="n"/>
+      <c r="U21" s="35" t="n"/>
+      <c r="V21" s="35" t="n"/>
+      <c r="W21" s="35" t="n"/>
+      <c r="X21" s="35" t="n"/>
+      <c r="Y21" s="35" t="n"/>
+      <c r="Z21" s="36" t="n"/>
+      <c r="AA21" s="35" t="n"/>
+      <c r="AB21" s="35" t="n"/>
+      <c r="AC21" s="35" t="n"/>
+      <c r="AD21" s="35" t="n"/>
+      <c r="AE21" s="35" t="n"/>
+      <c r="AF21" s="35" t="n"/>
+      <c r="AG21" s="35" t="n"/>
+      <c r="AH21" s="35" t="n"/>
+      <c r="AI21" s="35" t="n"/>
+      <c r="AJ21" s="35" t="n"/>
+      <c r="AK21" s="35" t="n"/>
+      <c r="AL21" s="35" t="n"/>
+      <c r="AM21" s="35" t="n"/>
+      <c r="AN21" s="396" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="280" t="inlineStr">
+      <c r="A22" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLES</t>
         </is>
       </c>
-      <c r="B22" s="281" t="n"/>
-      <c r="C22" s="281" t="n"/>
-      <c r="D22" s="281" t="n"/>
-      <c r="E22" s="281" t="n"/>
-      <c r="F22" s="281" t="n"/>
-      <c r="G22" s="281" t="n"/>
-      <c r="H22" s="281" t="n"/>
-      <c r="I22" s="281" t="n"/>
-      <c r="J22" s="281" t="n"/>
-      <c r="K22" s="281" t="n"/>
-      <c r="L22" s="281" t="n"/>
-      <c r="M22" s="281" t="n"/>
-      <c r="N22" s="281" t="n"/>
-      <c r="O22" s="281" t="n"/>
-      <c r="P22" s="281" t="n"/>
-      <c r="Q22" s="281" t="n"/>
-      <c r="R22" s="281" t="n"/>
-      <c r="S22" s="281" t="n"/>
-      <c r="T22" s="281" t="n"/>
-      <c r="U22" s="281" t="n"/>
-      <c r="V22" s="281" t="n"/>
-      <c r="W22" s="281" t="n"/>
-      <c r="X22" s="281" t="n"/>
-      <c r="Y22" s="281" t="n"/>
-      <c r="Z22" s="281" t="n"/>
-      <c r="AA22" s="281" t="n"/>
-      <c r="AB22" s="281" t="n"/>
-      <c r="AC22" s="281" t="n"/>
-      <c r="AD22" s="281" t="n"/>
-      <c r="AE22" s="281" t="n"/>
-      <c r="AF22" s="281" t="n"/>
-      <c r="AG22" s="281" t="n"/>
-      <c r="AH22" s="281" t="n"/>
-      <c r="AI22" s="281" t="n"/>
-      <c r="AJ22" s="281" t="n"/>
-      <c r="AK22" s="281" t="n"/>
-      <c r="AL22" s="281" t="n"/>
-      <c r="AM22" s="281" t="n"/>
-      <c r="AN22" s="282" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="22" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
+      <c r="Q22" s="22" t="n"/>
+      <c r="R22" s="22" t="n"/>
+      <c r="S22" s="22" t="n"/>
+      <c r="T22" s="22" t="n"/>
+      <c r="U22" s="22" t="n"/>
+      <c r="V22" s="22" t="n"/>
+      <c r="W22" s="22" t="n"/>
+      <c r="X22" s="22" t="n"/>
+      <c r="Y22" s="22" t="n"/>
+      <c r="Z22" s="22" t="n"/>
+      <c r="AA22" s="22" t="n"/>
+      <c r="AB22" s="22" t="n"/>
+      <c r="AC22" s="22" t="n"/>
+      <c r="AD22" s="22" t="n"/>
+      <c r="AE22" s="22" t="n"/>
+      <c r="AF22" s="22" t="n"/>
+      <c r="AG22" s="22" t="n"/>
+      <c r="AH22" s="22" t="n"/>
+      <c r="AI22" s="22" t="n"/>
+      <c r="AJ22" s="22" t="n"/>
+      <c r="AK22" s="22" t="n"/>
+      <c r="AL22" s="22" t="n"/>
+      <c r="AM22" s="22" t="n"/>
+      <c r="AN22" s="23" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="283" t="inlineStr">
+      <c r="A23" s="374" t="inlineStr">
         <is>
           <t>Support Sheet</t>
         </is>
       </c>
-      <c r="B23" s="284" t="n"/>
-      <c r="C23" s="284" t="n"/>
-      <c r="D23" s="284" t="n"/>
-      <c r="E23" s="284" t="n"/>
-      <c r="F23" s="284" t="n"/>
-      <c r="G23" s="285" t="n"/>
-      <c r="H23" s="286" t="n"/>
-      <c r="I23" s="287" t="n"/>
-      <c r="J23" s="287" t="n"/>
-      <c r="K23" s="287" t="n"/>
-      <c r="L23" s="287" t="n"/>
-      <c r="M23" s="287" t="n"/>
-      <c r="N23" s="287" t="n"/>
-      <c r="O23" s="287" t="n"/>
-      <c r="P23" s="287" t="n"/>
-      <c r="Q23" s="287" t="n"/>
-      <c r="R23" s="287" t="n"/>
-      <c r="S23" s="287" t="n"/>
-      <c r="T23" s="288" t="n"/>
-      <c r="U23" s="289" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="26" t="n"/>
+      <c r="J23" s="26" t="n"/>
+      <c r="K23" s="26" t="n"/>
+      <c r="L23" s="26" t="n"/>
+      <c r="M23" s="26" t="n"/>
+      <c r="N23" s="26" t="n"/>
+      <c r="O23" s="26" t="n"/>
+      <c r="P23" s="26" t="n"/>
+      <c r="Q23" s="26" t="n"/>
+      <c r="R23" s="26" t="n"/>
+      <c r="S23" s="26" t="n"/>
+      <c r="T23" s="27" t="n"/>
+      <c r="U23" s="375" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="V23" s="284" t="n"/>
-      <c r="W23" s="284" t="n"/>
-      <c r="X23" s="284" t="n"/>
-      <c r="Y23" s="284" t="n"/>
-      <c r="Z23" s="284" t="n"/>
-      <c r="AA23" s="285" t="n"/>
-      <c r="AB23" s="286" t="n"/>
-      <c r="AC23" s="287" t="n"/>
-      <c r="AD23" s="287" t="n"/>
-      <c r="AE23" s="287" t="n"/>
-      <c r="AF23" s="287" t="n"/>
-      <c r="AG23" s="287" t="n"/>
-      <c r="AH23" s="287" t="n"/>
-      <c r="AI23" s="287" t="n"/>
-      <c r="AJ23" s="287" t="n"/>
-      <c r="AK23" s="287" t="n"/>
-      <c r="AL23" s="287" t="n"/>
-      <c r="AM23" s="287" t="n"/>
-      <c r="AN23" s="290" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
+      <c r="Z23" s="6" t="n"/>
+      <c r="AA23" s="7" t="n"/>
+      <c r="AB23" s="376" t="n"/>
+      <c r="AC23" s="26" t="n"/>
+      <c r="AD23" s="26" t="n"/>
+      <c r="AE23" s="26" t="n"/>
+      <c r="AF23" s="26" t="n"/>
+      <c r="AG23" s="26" t="n"/>
+      <c r="AH23" s="26" t="n"/>
+      <c r="AI23" s="26" t="n"/>
+      <c r="AJ23" s="26" t="n"/>
+      <c r="AK23" s="26" t="n"/>
+      <c r="AL23" s="26" t="n"/>
+      <c r="AM23" s="26" t="n"/>
+      <c r="AN23" s="377" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="291" t="inlineStr">
+      <c r="A24" s="378" t="inlineStr">
         <is>
           <t>See workbook secondary sheet</t>
         </is>
       </c>
-      <c r="B24" s="272" t="n"/>
-      <c r="C24" s="272" t="n"/>
-      <c r="D24" s="272" t="n"/>
-      <c r="E24" s="272" t="n"/>
-      <c r="F24" s="272" t="n"/>
-      <c r="G24" s="292" t="n"/>
-      <c r="H24" s="293" t="n"/>
-      <c r="I24" s="294" t="n"/>
-      <c r="J24" s="294" t="n"/>
-      <c r="K24" s="294" t="n"/>
-      <c r="L24" s="294" t="n"/>
-      <c r="M24" s="294" t="n"/>
-      <c r="N24" s="294" t="n"/>
-      <c r="O24" s="294" t="n"/>
-      <c r="P24" s="294" t="n"/>
-      <c r="Q24" s="294" t="n"/>
-      <c r="R24" s="294" t="n"/>
-      <c r="S24" s="294" t="n"/>
-      <c r="T24" s="295" t="n"/>
-      <c r="U24" s="296" t="inlineStr">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="379" t="n"/>
+      <c r="I24" s="380" t="n"/>
+      <c r="J24" s="380" t="n"/>
+      <c r="K24" s="380" t="n"/>
+      <c r="L24" s="380" t="n"/>
+      <c r="M24" s="380" t="n"/>
+      <c r="N24" s="380" t="n"/>
+      <c r="O24" s="380" t="n"/>
+      <c r="P24" s="380" t="n"/>
+      <c r="Q24" s="380" t="n"/>
+      <c r="R24" s="380" t="n"/>
+      <c r="S24" s="380" t="n"/>
+      <c r="T24" s="381" t="n"/>
+      <c r="U24" s="382" t="inlineStr">
         <is>
           <t>Detailed actions / findings / decisions</t>
         </is>
       </c>
-      <c r="V24" s="272" t="n"/>
-      <c r="W24" s="272" t="n"/>
-      <c r="X24" s="272" t="n"/>
-      <c r="Y24" s="272" t="n"/>
-      <c r="Z24" s="272" t="n"/>
-      <c r="AA24" s="292" t="n"/>
-      <c r="AB24" s="293" t="n"/>
-      <c r="AC24" s="294" t="n"/>
-      <c r="AD24" s="294" t="n"/>
-      <c r="AE24" s="294" t="n"/>
-      <c r="AF24" s="294" t="n"/>
-      <c r="AG24" s="294" t="n"/>
-      <c r="AH24" s="294" t="n"/>
-      <c r="AI24" s="294" t="n"/>
-      <c r="AJ24" s="294" t="n"/>
-      <c r="AK24" s="294" t="n"/>
-      <c r="AL24" s="294" t="n"/>
-      <c r="AM24" s="294" t="n"/>
-      <c r="AN24" s="297" t="n"/>
+      <c r="V24" s="17" t="n"/>
+      <c r="W24" s="17" t="n"/>
+      <c r="X24" s="17" t="n"/>
+      <c r="Y24" s="17" t="n"/>
+      <c r="Z24" s="17" t="n"/>
+      <c r="AA24" s="52" t="n"/>
+      <c r="AB24" s="383" t="n"/>
+      <c r="AC24" s="380" t="n"/>
+      <c r="AD24" s="380" t="n"/>
+      <c r="AE24" s="380" t="n"/>
+      <c r="AF24" s="380" t="n"/>
+      <c r="AG24" s="380" t="n"/>
+      <c r="AH24" s="380" t="n"/>
+      <c r="AI24" s="380" t="n"/>
+      <c r="AJ24" s="380" t="n"/>
+      <c r="AK24" s="380" t="n"/>
+      <c r="AL24" s="380" t="n"/>
+      <c r="AM24" s="380" t="n"/>
+      <c r="AN24" s="384" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="280" t="inlineStr">
+      <c r="A25" s="373" t="inlineStr">
         <is>
           <t>NOTICE: Review access against least-privilege and segregation-of-duty expectations, close dormant or inappropriate access with owner and due date, and keep evidence linked to the reviewed system snapshot.</t>
         </is>
       </c>
-      <c r="B25" s="281" t="n"/>
-      <c r="C25" s="281" t="n"/>
-      <c r="D25" s="281" t="n"/>
-      <c r="E25" s="281" t="n"/>
-      <c r="F25" s="281" t="n"/>
-      <c r="G25" s="281" t="n"/>
-      <c r="H25" s="281" t="n"/>
-      <c r="I25" s="281" t="n"/>
-      <c r="J25" s="281" t="n"/>
-      <c r="K25" s="281" t="n"/>
-      <c r="L25" s="281" t="n"/>
-      <c r="M25" s="281" t="n"/>
-      <c r="N25" s="281" t="n"/>
-      <c r="O25" s="281" t="n"/>
-      <c r="P25" s="281" t="n"/>
-      <c r="Q25" s="281" t="n"/>
-      <c r="R25" s="281" t="n"/>
-      <c r="S25" s="281" t="n"/>
-      <c r="T25" s="281" t="n"/>
-      <c r="U25" s="281" t="n"/>
-      <c r="V25" s="281" t="n"/>
-      <c r="W25" s="281" t="n"/>
-      <c r="X25" s="281" t="n"/>
-      <c r="Y25" s="281" t="n"/>
-      <c r="Z25" s="281" t="n"/>
-      <c r="AA25" s="281" t="n"/>
-      <c r="AB25" s="281" t="n"/>
-      <c r="AC25" s="281" t="n"/>
-      <c r="AD25" s="281" t="n"/>
-      <c r="AE25" s="281" t="n"/>
-      <c r="AF25" s="281" t="n"/>
-      <c r="AG25" s="281" t="n"/>
-      <c r="AH25" s="281" t="n"/>
-      <c r="AI25" s="281" t="n"/>
-      <c r="AJ25" s="281" t="n"/>
-      <c r="AK25" s="281" t="n"/>
-      <c r="AL25" s="281" t="n"/>
-      <c r="AM25" s="281" t="n"/>
-      <c r="AN25" s="282" t="n"/>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="22" t="n"/>
+      <c r="R25" s="22" t="n"/>
+      <c r="S25" s="22" t="n"/>
+      <c r="T25" s="22" t="n"/>
+      <c r="U25" s="22" t="n"/>
+      <c r="V25" s="22" t="n"/>
+      <c r="W25" s="22" t="n"/>
+      <c r="X25" s="22" t="n"/>
+      <c r="Y25" s="22" t="n"/>
+      <c r="Z25" s="22" t="n"/>
+      <c r="AA25" s="22" t="n"/>
+      <c r="AB25" s="22" t="n"/>
+      <c r="AC25" s="22" t="n"/>
+      <c r="AD25" s="22" t="n"/>
+      <c r="AE25" s="22" t="n"/>
+      <c r="AF25" s="22" t="n"/>
+      <c r="AG25" s="22" t="n"/>
+      <c r="AH25" s="22" t="n"/>
+      <c r="AI25" s="22" t="n"/>
+      <c r="AJ25" s="22" t="n"/>
+      <c r="AK25" s="22" t="n"/>
+      <c r="AL25" s="22" t="n"/>
+      <c r="AM25" s="22" t="n"/>
+      <c r="AN25" s="23" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -4550,346 +4825,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="255" t="n"/>
-      <c r="B1" s="256" t="n"/>
-      <c r="C1" s="256" t="n"/>
-      <c r="D1" s="256" t="n"/>
-      <c r="E1" s="256" t="n"/>
-      <c r="F1" s="256" t="n"/>
-      <c r="G1" s="256" t="n"/>
-      <c r="H1" s="256" t="n"/>
-      <c r="I1" s="256" t="n"/>
-      <c r="J1" s="256" t="n"/>
-      <c r="K1" s="257" t="n"/>
+      <c r="A1" s="359" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="n"/>
       <c r="L1" s="258" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW — FINDINGS AND ACTIONS</t>
         </is>
       </c>
-      <c r="M1" s="256" t="n"/>
-      <c r="N1" s="256" t="n"/>
-      <c r="O1" s="256" t="n"/>
-      <c r="P1" s="256" t="n"/>
-      <c r="Q1" s="256" t="n"/>
-      <c r="R1" s="256" t="n"/>
-      <c r="S1" s="256" t="n"/>
-      <c r="T1" s="256" t="n"/>
-      <c r="U1" s="256" t="n"/>
-      <c r="V1" s="256" t="n"/>
-      <c r="W1" s="256" t="n"/>
-      <c r="X1" s="256" t="n"/>
-      <c r="Y1" s="256" t="n"/>
-      <c r="Z1" s="256" t="n"/>
-      <c r="AA1" s="256" t="n"/>
-      <c r="AB1" s="256" t="n"/>
-      <c r="AC1" s="256" t="n"/>
-      <c r="AD1" s="256" t="n"/>
-      <c r="AE1" s="256" t="n"/>
-      <c r="AF1" s="256" t="n"/>
-      <c r="AG1" s="256" t="n"/>
-      <c r="AH1" s="256" t="n"/>
-      <c r="AI1" s="256" t="n"/>
-      <c r="AJ1" s="256" t="n"/>
-      <c r="AK1" s="256" t="n"/>
-      <c r="AL1" s="256" t="n"/>
-      <c r="AM1" s="256" t="n"/>
-      <c r="AN1" s="256" t="n"/>
-      <c r="AO1" s="256" t="n"/>
-      <c r="AP1" s="256" t="n"/>
-      <c r="AQ1" s="259" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="360" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="256" t="n"/>
-      <c r="AS1" s="256" t="n"/>
-      <c r="AT1" s="256" t="n"/>
-      <c r="AU1" s="256" t="n"/>
-      <c r="AV1" s="260" t="n"/>
-      <c r="AW1" s="261" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="361" t="n"/>
+      <c r="AW1" s="362" t="inlineStr">
         <is>
           <t>FRM-111</t>
         </is>
       </c>
-      <c r="AX1" s="256" t="n"/>
-      <c r="AY1" s="256" t="n"/>
-      <c r="AZ1" s="256" t="n"/>
-      <c r="BA1" s="256" t="n"/>
-      <c r="BB1" s="256" t="n"/>
-      <c r="BC1" s="256" t="n"/>
-      <c r="BD1" s="257" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="262" t="n"/>
-      <c r="B2" s="263" t="n"/>
-      <c r="C2" s="263" t="n"/>
-      <c r="D2" s="263" t="n"/>
-      <c r="E2" s="263" t="n"/>
-      <c r="F2" s="263" t="n"/>
-      <c r="G2" s="263" t="n"/>
-      <c r="H2" s="263" t="n"/>
-      <c r="I2" s="263" t="n"/>
-      <c r="J2" s="263" t="n"/>
-      <c r="K2" s="264" t="n"/>
-      <c r="L2" s="262" t="n"/>
-      <c r="M2" s="263" t="n"/>
-      <c r="N2" s="263" t="n"/>
-      <c r="O2" s="263" t="n"/>
-      <c r="P2" s="263" t="n"/>
-      <c r="Q2" s="263" t="n"/>
-      <c r="R2" s="263" t="n"/>
-      <c r="S2" s="263" t="n"/>
-      <c r="T2" s="263" t="n"/>
-      <c r="U2" s="263" t="n"/>
-      <c r="V2" s="263" t="n"/>
-      <c r="W2" s="263" t="n"/>
-      <c r="X2" s="263" t="n"/>
-      <c r="Y2" s="263" t="n"/>
-      <c r="Z2" s="263" t="n"/>
-      <c r="AA2" s="263" t="n"/>
-      <c r="AB2" s="263" t="n"/>
-      <c r="AC2" s="263" t="n"/>
-      <c r="AD2" s="263" t="n"/>
-      <c r="AE2" s="263" t="n"/>
-      <c r="AF2" s="263" t="n"/>
-      <c r="AG2" s="263" t="n"/>
-      <c r="AH2" s="263" t="n"/>
-      <c r="AI2" s="263" t="n"/>
-      <c r="AJ2" s="263" t="n"/>
-      <c r="AK2" s="263" t="n"/>
-      <c r="AL2" s="263" t="n"/>
-      <c r="AM2" s="263" t="n"/>
-      <c r="AN2" s="263" t="n"/>
-      <c r="AO2" s="263" t="n"/>
-      <c r="AP2" s="263" t="n"/>
-      <c r="AQ2" s="265" t="inlineStr">
+      <c r="A2" s="10" t="n"/>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="AQ2" s="363" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="266" t="n"/>
-      <c r="AS2" s="266" t="n"/>
-      <c r="AT2" s="266" t="n"/>
-      <c r="AU2" s="266" t="n"/>
-      <c r="AV2" s="267" t="n"/>
-      <c r="AW2" s="268" t="inlineStr">
+      <c r="AR2" s="364" t="n"/>
+      <c r="AS2" s="364" t="n"/>
+      <c r="AT2" s="364" t="n"/>
+      <c r="AU2" s="364" t="n"/>
+      <c r="AV2" s="365" t="n"/>
+      <c r="AW2" s="366" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="266" t="n"/>
-      <c r="AY2" s="266" t="n"/>
-      <c r="AZ2" s="266" t="n"/>
-      <c r="BA2" s="266" t="n"/>
-      <c r="BB2" s="266" t="n"/>
-      <c r="BC2" s="266" t="n"/>
-      <c r="BD2" s="269" t="n"/>
+      <c r="AX2" s="364" t="n"/>
+      <c r="AY2" s="364" t="n"/>
+      <c r="AZ2" s="364" t="n"/>
+      <c r="BA2" s="364" t="n"/>
+      <c r="BB2" s="364" t="n"/>
+      <c r="BC2" s="364" t="n"/>
+      <c r="BD2" s="367" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="262" t="n"/>
-      <c r="B3" s="263" t="n"/>
-      <c r="C3" s="263" t="n"/>
-      <c r="D3" s="263" t="n"/>
-      <c r="E3" s="263" t="n"/>
-      <c r="F3" s="263" t="n"/>
-      <c r="G3" s="263" t="n"/>
-      <c r="H3" s="263" t="n"/>
-      <c r="I3" s="263" t="n"/>
-      <c r="J3" s="263" t="n"/>
-      <c r="K3" s="264" t="n"/>
-      <c r="L3" s="262" t="n"/>
-      <c r="M3" s="263" t="n"/>
-      <c r="N3" s="263" t="n"/>
-      <c r="O3" s="263" t="n"/>
-      <c r="P3" s="263" t="n"/>
-      <c r="Q3" s="263" t="n"/>
-      <c r="R3" s="263" t="n"/>
-      <c r="S3" s="263" t="n"/>
-      <c r="T3" s="263" t="n"/>
-      <c r="U3" s="263" t="n"/>
-      <c r="V3" s="263" t="n"/>
-      <c r="W3" s="263" t="n"/>
-      <c r="X3" s="263" t="n"/>
-      <c r="Y3" s="263" t="n"/>
-      <c r="Z3" s="263" t="n"/>
-      <c r="AA3" s="263" t="n"/>
-      <c r="AB3" s="263" t="n"/>
-      <c r="AC3" s="263" t="n"/>
-      <c r="AD3" s="263" t="n"/>
-      <c r="AE3" s="263" t="n"/>
-      <c r="AF3" s="263" t="n"/>
-      <c r="AG3" s="263" t="n"/>
-      <c r="AH3" s="263" t="n"/>
-      <c r="AI3" s="263" t="n"/>
-      <c r="AJ3" s="263" t="n"/>
-      <c r="AK3" s="263" t="n"/>
-      <c r="AL3" s="263" t="n"/>
-      <c r="AM3" s="263" t="n"/>
-      <c r="AN3" s="263" t="n"/>
-      <c r="AO3" s="263" t="n"/>
-      <c r="AP3" s="263" t="n"/>
-      <c r="AQ3" s="265" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="AQ3" s="363" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="266" t="n"/>
-      <c r="AS3" s="266" t="n"/>
-      <c r="AT3" s="266" t="n"/>
-      <c r="AU3" s="266" t="n"/>
-      <c r="AV3" s="267" t="n"/>
-      <c r="AW3" s="268" t="inlineStr">
+      <c r="AR3" s="364" t="n"/>
+      <c r="AS3" s="364" t="n"/>
+      <c r="AT3" s="364" t="n"/>
+      <c r="AU3" s="364" t="n"/>
+      <c r="AV3" s="365" t="n"/>
+      <c r="AW3" s="366" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="266" t="n"/>
-      <c r="AY3" s="266" t="n"/>
-      <c r="AZ3" s="266" t="n"/>
-      <c r="BA3" s="266" t="n"/>
-      <c r="BB3" s="266" t="n"/>
-      <c r="BC3" s="266" t="n"/>
-      <c r="BD3" s="269" t="n"/>
+      <c r="AX3" s="364" t="n"/>
+      <c r="AY3" s="364" t="n"/>
+      <c r="AZ3" s="364" t="n"/>
+      <c r="BA3" s="364" t="n"/>
+      <c r="BB3" s="364" t="n"/>
+      <c r="BC3" s="364" t="n"/>
+      <c r="BD3" s="367" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="262" t="n"/>
-      <c r="B4" s="263" t="n"/>
-      <c r="C4" s="263" t="n"/>
-      <c r="D4" s="263" t="n"/>
-      <c r="E4" s="263" t="n"/>
-      <c r="F4" s="263" t="n"/>
-      <c r="G4" s="263" t="n"/>
-      <c r="H4" s="263" t="n"/>
-      <c r="I4" s="263" t="n"/>
-      <c r="J4" s="263" t="n"/>
-      <c r="K4" s="264" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="K4" s="11" t="n"/>
       <c r="L4" s="270" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="263" t="n"/>
-      <c r="N4" s="263" t="n"/>
-      <c r="O4" s="263" t="n"/>
-      <c r="P4" s="263" t="n"/>
-      <c r="Q4" s="263" t="n"/>
-      <c r="R4" s="263" t="n"/>
-      <c r="S4" s="263" t="n"/>
-      <c r="T4" s="263" t="n"/>
-      <c r="U4" s="263" t="n"/>
-      <c r="V4" s="263" t="n"/>
-      <c r="W4" s="263" t="n"/>
-      <c r="X4" s="263" t="n"/>
-      <c r="Y4" s="263" t="n"/>
-      <c r="Z4" s="263" t="n"/>
-      <c r="AA4" s="263" t="n"/>
-      <c r="AB4" s="263" t="n"/>
-      <c r="AC4" s="263" t="n"/>
-      <c r="AD4" s="263" t="n"/>
-      <c r="AE4" s="263" t="n"/>
-      <c r="AF4" s="263" t="n"/>
-      <c r="AG4" s="263" t="n"/>
-      <c r="AH4" s="263" t="n"/>
-      <c r="AI4" s="263" t="n"/>
-      <c r="AJ4" s="263" t="n"/>
-      <c r="AK4" s="263" t="n"/>
-      <c r="AL4" s="263" t="n"/>
-      <c r="AM4" s="263" t="n"/>
-      <c r="AN4" s="263" t="n"/>
-      <c r="AO4" s="263" t="n"/>
-      <c r="AP4" s="263" t="n"/>
-      <c r="AQ4" s="265" t="inlineStr">
+      <c r="AQ4" s="363" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="266" t="n"/>
-      <c r="AS4" s="266" t="n"/>
-      <c r="AT4" s="266" t="n"/>
-      <c r="AU4" s="266" t="n"/>
-      <c r="AV4" s="267" t="n"/>
-      <c r="AW4" s="268" t="inlineStr">
+      <c r="AR4" s="364" t="n"/>
+      <c r="AS4" s="364" t="n"/>
+      <c r="AT4" s="364" t="n"/>
+      <c r="AU4" s="364" t="n"/>
+      <c r="AV4" s="365" t="n"/>
+      <c r="AW4" s="366" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AX4" s="266" t="n"/>
-      <c r="AY4" s="266" t="n"/>
-      <c r="AZ4" s="266" t="n"/>
-      <c r="BA4" s="266" t="n"/>
-      <c r="BB4" s="266" t="n"/>
-      <c r="BC4" s="266" t="n"/>
-      <c r="BD4" s="269" t="n"/>
+      <c r="AX4" s="364" t="n"/>
+      <c r="AY4" s="364" t="n"/>
+      <c r="AZ4" s="364" t="n"/>
+      <c r="BA4" s="364" t="n"/>
+      <c r="BB4" s="364" t="n"/>
+      <c r="BC4" s="364" t="n"/>
+      <c r="BD4" s="367" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="271" t="n"/>
-      <c r="B5" s="272" t="n"/>
-      <c r="C5" s="272" t="n"/>
-      <c r="D5" s="272" t="n"/>
-      <c r="E5" s="272" t="n"/>
-      <c r="F5" s="272" t="n"/>
-      <c r="G5" s="272" t="n"/>
-      <c r="H5" s="272" t="n"/>
-      <c r="I5" s="272" t="n"/>
-      <c r="J5" s="272" t="n"/>
-      <c r="K5" s="273" t="n"/>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="18" t="n"/>
       <c r="L5" s="50" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="272" t="n"/>
-      <c r="N5" s="272" t="n"/>
-      <c r="O5" s="272" t="n"/>
-      <c r="P5" s="272" t="n"/>
-      <c r="Q5" s="272" t="n"/>
-      <c r="R5" s="272" t="n"/>
-      <c r="S5" s="272" t="n"/>
-      <c r="T5" s="272" t="n"/>
-      <c r="U5" s="272" t="n"/>
-      <c r="V5" s="272" t="n"/>
-      <c r="W5" s="272" t="n"/>
-      <c r="X5" s="272" t="n"/>
-      <c r="Y5" s="272" t="n"/>
-      <c r="Z5" s="272" t="n"/>
-      <c r="AA5" s="272" t="n"/>
-      <c r="AB5" s="272" t="n"/>
-      <c r="AC5" s="272" t="n"/>
-      <c r="AD5" s="272" t="n"/>
-      <c r="AE5" s="272" t="n"/>
-      <c r="AF5" s="272" t="n"/>
-      <c r="AG5" s="272" t="n"/>
-      <c r="AH5" s="272" t="n"/>
-      <c r="AI5" s="272" t="n"/>
-      <c r="AJ5" s="272" t="n"/>
-      <c r="AK5" s="272" t="n"/>
-      <c r="AL5" s="272" t="n"/>
-      <c r="AM5" s="272" t="n"/>
-      <c r="AN5" s="272" t="n"/>
-      <c r="AO5" s="272" t="n"/>
-      <c r="AP5" s="272" t="n"/>
-      <c r="AQ5" s="274" t="inlineStr">
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="17" t="n"/>
+      <c r="P5" s="17" t="n"/>
+      <c r="Q5" s="17" t="n"/>
+      <c r="R5" s="17" t="n"/>
+      <c r="S5" s="17" t="n"/>
+      <c r="T5" s="17" t="n"/>
+      <c r="U5" s="17" t="n"/>
+      <c r="V5" s="17" t="n"/>
+      <c r="W5" s="17" t="n"/>
+      <c r="X5" s="17" t="n"/>
+      <c r="Y5" s="17" t="n"/>
+      <c r="Z5" s="17" t="n"/>
+      <c r="AA5" s="17" t="n"/>
+      <c r="AB5" s="17" t="n"/>
+      <c r="AC5" s="17" t="n"/>
+      <c r="AD5" s="17" t="n"/>
+      <c r="AE5" s="17" t="n"/>
+      <c r="AF5" s="17" t="n"/>
+      <c r="AG5" s="17" t="n"/>
+      <c r="AH5" s="17" t="n"/>
+      <c r="AI5" s="17" t="n"/>
+      <c r="AJ5" s="17" t="n"/>
+      <c r="AK5" s="17" t="n"/>
+      <c r="AL5" s="17" t="n"/>
+      <c r="AM5" s="17" t="n"/>
+      <c r="AN5" s="17" t="n"/>
+      <c r="AO5" s="17" t="n"/>
+      <c r="AP5" s="17" t="n"/>
+      <c r="AQ5" s="368" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="275" t="n"/>
-      <c r="AS5" s="275" t="n"/>
-      <c r="AT5" s="275" t="n"/>
-      <c r="AU5" s="275" t="n"/>
-      <c r="AV5" s="276" t="n"/>
-      <c r="AW5" s="277" t="inlineStr">
+      <c r="AR5" s="369" t="n"/>
+      <c r="AS5" s="369" t="n"/>
+      <c r="AT5" s="369" t="n"/>
+      <c r="AU5" s="369" t="n"/>
+      <c r="AV5" s="370" t="n"/>
+      <c r="AW5" s="371" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="275" t="n"/>
-      <c r="AY5" s="275" t="n"/>
-      <c r="AZ5" s="275" t="n"/>
-      <c r="BA5" s="275" t="n"/>
-      <c r="BB5" s="275" t="n"/>
-      <c r="BC5" s="275" t="n"/>
-      <c r="BD5" s="278" t="n"/>
+      <c r="AX5" s="369" t="n"/>
+      <c r="AY5" s="369" t="n"/>
+      <c r="AZ5" s="369" t="n"/>
+      <c r="BA5" s="369" t="n"/>
+      <c r="BB5" s="369" t="n"/>
+      <c r="BC5" s="369" t="n"/>
+      <c r="BD5" s="372" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="279" t="n"/>
@@ -4950,830 +5108,830 @@
       <c r="BD6" s="279" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="280" t="inlineStr">
+      <c r="A7" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="281" t="n"/>
-      <c r="C7" s="281" t="n"/>
-      <c r="D7" s="281" t="n"/>
-      <c r="E7" s="281" t="n"/>
-      <c r="F7" s="281" t="n"/>
-      <c r="G7" s="281" t="n"/>
-      <c r="H7" s="281" t="n"/>
-      <c r="I7" s="281" t="n"/>
-      <c r="J7" s="281" t="n"/>
-      <c r="K7" s="281" t="n"/>
-      <c r="L7" s="281" t="n"/>
-      <c r="M7" s="281" t="n"/>
-      <c r="N7" s="281" t="n"/>
-      <c r="O7" s="281" t="n"/>
-      <c r="P7" s="281" t="n"/>
-      <c r="Q7" s="281" t="n"/>
-      <c r="R7" s="281" t="n"/>
-      <c r="S7" s="281" t="n"/>
-      <c r="T7" s="281" t="n"/>
-      <c r="U7" s="281" t="n"/>
-      <c r="V7" s="281" t="n"/>
-      <c r="W7" s="281" t="n"/>
-      <c r="X7" s="281" t="n"/>
-      <c r="Y7" s="281" t="n"/>
-      <c r="Z7" s="281" t="n"/>
-      <c r="AA7" s="281" t="n"/>
-      <c r="AB7" s="281" t="n"/>
-      <c r="AC7" s="281" t="n"/>
-      <c r="AD7" s="281" t="n"/>
-      <c r="AE7" s="281" t="n"/>
-      <c r="AF7" s="281" t="n"/>
-      <c r="AG7" s="281" t="n"/>
-      <c r="AH7" s="281" t="n"/>
-      <c r="AI7" s="281" t="n"/>
-      <c r="AJ7" s="281" t="n"/>
-      <c r="AK7" s="281" t="n"/>
-      <c r="AL7" s="281" t="n"/>
-      <c r="AM7" s="281" t="n"/>
-      <c r="AN7" s="281" t="n"/>
-      <c r="AO7" s="281" t="n"/>
-      <c r="AP7" s="281" t="n"/>
-      <c r="AQ7" s="281" t="n"/>
-      <c r="AR7" s="281" t="n"/>
-      <c r="AS7" s="281" t="n"/>
-      <c r="AT7" s="281" t="n"/>
-      <c r="AU7" s="281" t="n"/>
-      <c r="AV7" s="281" t="n"/>
-      <c r="AW7" s="281" t="n"/>
-      <c r="AX7" s="281" t="n"/>
-      <c r="AY7" s="281" t="n"/>
-      <c r="AZ7" s="281" t="n"/>
-      <c r="BA7" s="281" t="n"/>
-      <c r="BB7" s="281" t="n"/>
-      <c r="BC7" s="281" t="n"/>
-      <c r="BD7" s="282" t="n"/>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="22" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="22" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="22" t="n"/>
+      <c r="AF7" s="22" t="n"/>
+      <c r="AG7" s="22" t="n"/>
+      <c r="AH7" s="22" t="n"/>
+      <c r="AI7" s="22" t="n"/>
+      <c r="AJ7" s="22" t="n"/>
+      <c r="AK7" s="22" t="n"/>
+      <c r="AL7" s="22" t="n"/>
+      <c r="AM7" s="22" t="n"/>
+      <c r="AN7" s="22" t="n"/>
+      <c r="AO7" s="22" t="n"/>
+      <c r="AP7" s="22" t="n"/>
+      <c r="AQ7" s="22" t="n"/>
+      <c r="AR7" s="22" t="n"/>
+      <c r="AS7" s="22" t="n"/>
+      <c r="AT7" s="22" t="n"/>
+      <c r="AU7" s="22" t="n"/>
+      <c r="AV7" s="22" t="n"/>
+      <c r="AW7" s="22" t="n"/>
+      <c r="AX7" s="22" t="n"/>
+      <c r="AY7" s="22" t="n"/>
+      <c r="AZ7" s="22" t="n"/>
+      <c r="BA7" s="22" t="n"/>
+      <c r="BB7" s="22" t="n"/>
+      <c r="BC7" s="22" t="n"/>
+      <c r="BD7" s="23" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="283" t="inlineStr">
+      <c r="A8" s="374" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="284" t="n"/>
-      <c r="C8" s="284" t="n"/>
-      <c r="D8" s="284" t="n"/>
-      <c r="E8" s="284" t="n"/>
-      <c r="F8" s="284" t="n"/>
-      <c r="G8" s="284" t="n"/>
-      <c r="H8" s="284" t="n"/>
-      <c r="I8" s="284" t="n"/>
-      <c r="J8" s="285" t="n"/>
-      <c r="K8" s="320" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="38" t="inlineStr">
         <is>
           <t>SOP: SOP-104 | ANNEX: ANNEX-QMS-005, ANNEX-QMS-006, ANNEX-QMS-012, ANNEX-QMS-019, ANNEX-QMS-021, ANNEX-IT-001, ANNEX-IT-002</t>
         </is>
       </c>
-      <c r="L8" s="284" t="n"/>
-      <c r="M8" s="284" t="n"/>
-      <c r="N8" s="284" t="n"/>
-      <c r="O8" s="284" t="n"/>
-      <c r="P8" s="284" t="n"/>
-      <c r="Q8" s="284" t="n"/>
-      <c r="R8" s="284" t="n"/>
-      <c r="S8" s="284" t="n"/>
-      <c r="T8" s="284" t="n"/>
-      <c r="U8" s="284" t="n"/>
-      <c r="V8" s="284" t="n"/>
-      <c r="W8" s="284" t="n"/>
-      <c r="X8" s="284" t="n"/>
-      <c r="Y8" s="284" t="n"/>
-      <c r="Z8" s="284" t="n"/>
-      <c r="AA8" s="284" t="n"/>
-      <c r="AB8" s="285" t="n"/>
-      <c r="AC8" s="321" t="inlineStr"/>
-      <c r="AD8" s="284" t="n"/>
-      <c r="AE8" s="284" t="n"/>
-      <c r="AF8" s="284" t="n"/>
-      <c r="AG8" s="284" t="n"/>
-      <c r="AH8" s="284" t="n"/>
-      <c r="AI8" s="284" t="n"/>
-      <c r="AJ8" s="284" t="n"/>
-      <c r="AK8" s="284" t="n"/>
-      <c r="AL8" s="285" t="n"/>
-      <c r="AM8" s="321" t="inlineStr"/>
-      <c r="AN8" s="284" t="n"/>
-      <c r="AO8" s="284" t="n"/>
-      <c r="AP8" s="284" t="n"/>
-      <c r="AQ8" s="284" t="n"/>
-      <c r="AR8" s="284" t="n"/>
-      <c r="AS8" s="284" t="n"/>
-      <c r="AT8" s="284" t="n"/>
-      <c r="AU8" s="284" t="n"/>
-      <c r="AV8" s="284" t="n"/>
-      <c r="AW8" s="284" t="n"/>
-      <c r="AX8" s="284" t="n"/>
-      <c r="AY8" s="284" t="n"/>
-      <c r="AZ8" s="284" t="n"/>
-      <c r="BA8" s="284" t="n"/>
-      <c r="BB8" s="284" t="n"/>
-      <c r="BC8" s="284" t="n"/>
-      <c r="BD8" s="322" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="403" t="inlineStr"/>
+      <c r="AD8" s="6" t="n"/>
+      <c r="AE8" s="6" t="n"/>
+      <c r="AF8" s="6" t="n"/>
+      <c r="AG8" s="6" t="n"/>
+      <c r="AH8" s="6" t="n"/>
+      <c r="AI8" s="6" t="n"/>
+      <c r="AJ8" s="6" t="n"/>
+      <c r="AK8" s="6" t="n"/>
+      <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="404" t="inlineStr"/>
+      <c r="AN8" s="6" t="n"/>
+      <c r="AO8" s="6" t="n"/>
+      <c r="AP8" s="6" t="n"/>
+      <c r="AQ8" s="6" t="n"/>
+      <c r="AR8" s="6" t="n"/>
+      <c r="AS8" s="6" t="n"/>
+      <c r="AT8" s="6" t="n"/>
+      <c r="AU8" s="6" t="n"/>
+      <c r="AV8" s="6" t="n"/>
+      <c r="AW8" s="6" t="n"/>
+      <c r="AX8" s="6" t="n"/>
+      <c r="AY8" s="6" t="n"/>
+      <c r="AZ8" s="6" t="n"/>
+      <c r="BA8" s="6" t="n"/>
+      <c r="BB8" s="6" t="n"/>
+      <c r="BC8" s="6" t="n"/>
+      <c r="BD8" s="9" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="305" t="inlineStr">
+      <c r="A9" s="393" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="306" t="n"/>
-      <c r="C9" s="306" t="n"/>
-      <c r="D9" s="306" t="n"/>
-      <c r="E9" s="306" t="n"/>
-      <c r="F9" s="306" t="n"/>
-      <c r="G9" s="306" t="n"/>
-      <c r="H9" s="306" t="n"/>
-      <c r="I9" s="306" t="n"/>
-      <c r="J9" s="307" t="n"/>
-      <c r="K9" s="323" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="405" t="inlineStr">
         <is>
           <t>Detailed finding / action sheet linked from the primary gate page.</t>
         </is>
       </c>
-      <c r="L9" s="306" t="n"/>
-      <c r="M9" s="306" t="n"/>
-      <c r="N9" s="306" t="n"/>
-      <c r="O9" s="306" t="n"/>
-      <c r="P9" s="306" t="n"/>
-      <c r="Q9" s="306" t="n"/>
-      <c r="R9" s="306" t="n"/>
-      <c r="S9" s="306" t="n"/>
-      <c r="T9" s="306" t="n"/>
-      <c r="U9" s="306" t="n"/>
-      <c r="V9" s="306" t="n"/>
-      <c r="W9" s="306" t="n"/>
-      <c r="X9" s="306" t="n"/>
-      <c r="Y9" s="306" t="n"/>
-      <c r="Z9" s="306" t="n"/>
-      <c r="AA9" s="306" t="n"/>
-      <c r="AB9" s="307" t="n"/>
-      <c r="AC9" s="324" t="inlineStr"/>
-      <c r="AD9" s="306" t="n"/>
-      <c r="AE9" s="306" t="n"/>
-      <c r="AF9" s="306" t="n"/>
-      <c r="AG9" s="306" t="n"/>
-      <c r="AH9" s="306" t="n"/>
-      <c r="AI9" s="306" t="n"/>
-      <c r="AJ9" s="306" t="n"/>
-      <c r="AK9" s="306" t="n"/>
-      <c r="AL9" s="307" t="n"/>
-      <c r="AM9" s="324" t="inlineStr"/>
-      <c r="AN9" s="306" t="n"/>
-      <c r="AO9" s="306" t="n"/>
-      <c r="AP9" s="306" t="n"/>
-      <c r="AQ9" s="306" t="n"/>
-      <c r="AR9" s="306" t="n"/>
-      <c r="AS9" s="306" t="n"/>
-      <c r="AT9" s="306" t="n"/>
-      <c r="AU9" s="306" t="n"/>
-      <c r="AV9" s="306" t="n"/>
-      <c r="AW9" s="306" t="n"/>
-      <c r="AX9" s="306" t="n"/>
-      <c r="AY9" s="306" t="n"/>
-      <c r="AZ9" s="306" t="n"/>
-      <c r="BA9" s="306" t="n"/>
-      <c r="BB9" s="306" t="n"/>
-      <c r="BC9" s="306" t="n"/>
-      <c r="BD9" s="315" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
+      <c r="P9" s="14" t="n"/>
+      <c r="Q9" s="14" t="n"/>
+      <c r="R9" s="14" t="n"/>
+      <c r="S9" s="14" t="n"/>
+      <c r="T9" s="14" t="n"/>
+      <c r="U9" s="14" t="n"/>
+      <c r="V9" s="14" t="n"/>
+      <c r="W9" s="14" t="n"/>
+      <c r="X9" s="14" t="n"/>
+      <c r="Y9" s="14" t="n"/>
+      <c r="Z9" s="14" t="n"/>
+      <c r="AA9" s="14" t="n"/>
+      <c r="AB9" s="29" t="n"/>
+      <c r="AC9" s="406" t="inlineStr"/>
+      <c r="AD9" s="14" t="n"/>
+      <c r="AE9" s="14" t="n"/>
+      <c r="AF9" s="14" t="n"/>
+      <c r="AG9" s="14" t="n"/>
+      <c r="AH9" s="14" t="n"/>
+      <c r="AI9" s="14" t="n"/>
+      <c r="AJ9" s="14" t="n"/>
+      <c r="AK9" s="14" t="n"/>
+      <c r="AL9" s="29" t="n"/>
+      <c r="AM9" s="407" t="inlineStr"/>
+      <c r="AN9" s="14" t="n"/>
+      <c r="AO9" s="14" t="n"/>
+      <c r="AP9" s="14" t="n"/>
+      <c r="AQ9" s="14" t="n"/>
+      <c r="AR9" s="14" t="n"/>
+      <c r="AS9" s="14" t="n"/>
+      <c r="AT9" s="14" t="n"/>
+      <c r="AU9" s="14" t="n"/>
+      <c r="AV9" s="14" t="n"/>
+      <c r="AW9" s="14" t="n"/>
+      <c r="AX9" s="14" t="n"/>
+      <c r="AY9" s="14" t="n"/>
+      <c r="AZ9" s="14" t="n"/>
+      <c r="BA9" s="14" t="n"/>
+      <c r="BB9" s="14" t="n"/>
+      <c r="BC9" s="14" t="n"/>
+      <c r="BD9" s="48" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="291" t="inlineStr">
+      <c r="A10" s="378" t="inlineStr">
         <is>
           <t>Boundary / SoR</t>
         </is>
       </c>
-      <c r="B10" s="272" t="n"/>
-      <c r="C10" s="272" t="n"/>
-      <c r="D10" s="272" t="n"/>
-      <c r="E10" s="272" t="n"/>
-      <c r="F10" s="272" t="n"/>
-      <c r="G10" s="272" t="n"/>
-      <c r="H10" s="272" t="n"/>
-      <c r="I10" s="272" t="n"/>
-      <c r="J10" s="292" t="n"/>
-      <c r="K10" s="325" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="52" t="n"/>
+      <c r="K10" s="408" t="inlineStr">
         <is>
           <t>Periodic access review only; role master stays in system / ANNEX.</t>
         </is>
       </c>
-      <c r="L10" s="272" t="n"/>
-      <c r="M10" s="272" t="n"/>
-      <c r="N10" s="272" t="n"/>
-      <c r="O10" s="272" t="n"/>
-      <c r="P10" s="272" t="n"/>
-      <c r="Q10" s="272" t="n"/>
-      <c r="R10" s="272" t="n"/>
-      <c r="S10" s="272" t="n"/>
-      <c r="T10" s="272" t="n"/>
-      <c r="U10" s="272" t="n"/>
-      <c r="V10" s="272" t="n"/>
-      <c r="W10" s="272" t="n"/>
-      <c r="X10" s="272" t="n"/>
-      <c r="Y10" s="272" t="n"/>
-      <c r="Z10" s="272" t="n"/>
-      <c r="AA10" s="272" t="n"/>
-      <c r="AB10" s="292" t="n"/>
-      <c r="AC10" s="326" t="inlineStr"/>
-      <c r="AD10" s="272" t="n"/>
-      <c r="AE10" s="272" t="n"/>
-      <c r="AF10" s="272" t="n"/>
-      <c r="AG10" s="272" t="n"/>
-      <c r="AH10" s="272" t="n"/>
-      <c r="AI10" s="272" t="n"/>
-      <c r="AJ10" s="272" t="n"/>
-      <c r="AK10" s="272" t="n"/>
-      <c r="AL10" s="292" t="n"/>
-      <c r="AM10" s="326" t="inlineStr"/>
-      <c r="AN10" s="272" t="n"/>
-      <c r="AO10" s="272" t="n"/>
-      <c r="AP10" s="272" t="n"/>
-      <c r="AQ10" s="272" t="n"/>
-      <c r="AR10" s="272" t="n"/>
-      <c r="AS10" s="272" t="n"/>
-      <c r="AT10" s="272" t="n"/>
-      <c r="AU10" s="272" t="n"/>
-      <c r="AV10" s="272" t="n"/>
-      <c r="AW10" s="272" t="n"/>
-      <c r="AX10" s="272" t="n"/>
-      <c r="AY10" s="272" t="n"/>
-      <c r="AZ10" s="272" t="n"/>
-      <c r="BA10" s="272" t="n"/>
-      <c r="BB10" s="272" t="n"/>
-      <c r="BC10" s="272" t="n"/>
-      <c r="BD10" s="273" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="17" t="n"/>
+      <c r="P10" s="17" t="n"/>
+      <c r="Q10" s="17" t="n"/>
+      <c r="R10" s="17" t="n"/>
+      <c r="S10" s="17" t="n"/>
+      <c r="T10" s="17" t="n"/>
+      <c r="U10" s="17" t="n"/>
+      <c r="V10" s="17" t="n"/>
+      <c r="W10" s="17" t="n"/>
+      <c r="X10" s="17" t="n"/>
+      <c r="Y10" s="17" t="n"/>
+      <c r="Z10" s="17" t="n"/>
+      <c r="AA10" s="17" t="n"/>
+      <c r="AB10" s="52" t="n"/>
+      <c r="AC10" s="409" t="inlineStr"/>
+      <c r="AD10" s="17" t="n"/>
+      <c r="AE10" s="17" t="n"/>
+      <c r="AF10" s="17" t="n"/>
+      <c r="AG10" s="17" t="n"/>
+      <c r="AH10" s="17" t="n"/>
+      <c r="AI10" s="17" t="n"/>
+      <c r="AJ10" s="17" t="n"/>
+      <c r="AK10" s="17" t="n"/>
+      <c r="AL10" s="52" t="n"/>
+      <c r="AM10" s="410" t="inlineStr"/>
+      <c r="AN10" s="17" t="n"/>
+      <c r="AO10" s="17" t="n"/>
+      <c r="AP10" s="17" t="n"/>
+      <c r="AQ10" s="17" t="n"/>
+      <c r="AR10" s="17" t="n"/>
+      <c r="AS10" s="17" t="n"/>
+      <c r="AT10" s="17" t="n"/>
+      <c r="AU10" s="17" t="n"/>
+      <c r="AV10" s="17" t="n"/>
+      <c r="AW10" s="17" t="n"/>
+      <c r="AX10" s="17" t="n"/>
+      <c r="AY10" s="17" t="n"/>
+      <c r="AZ10" s="17" t="n"/>
+      <c r="BA10" s="17" t="n"/>
+      <c r="BB10" s="17" t="n"/>
+      <c r="BC10" s="17" t="n"/>
+      <c r="BD10" s="18" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="280" t="inlineStr">
+      <c r="A11" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B11" s="281" t="n"/>
-      <c r="C11" s="281" t="n"/>
-      <c r="D11" s="281" t="n"/>
-      <c r="E11" s="281" t="n"/>
-      <c r="F11" s="281" t="n"/>
-      <c r="G11" s="281" t="n"/>
-      <c r="H11" s="281" t="n"/>
-      <c r="I11" s="281" t="n"/>
-      <c r="J11" s="281" t="n"/>
-      <c r="K11" s="281" t="n"/>
-      <c r="L11" s="281" t="n"/>
-      <c r="M11" s="281" t="n"/>
-      <c r="N11" s="281" t="n"/>
-      <c r="O11" s="281" t="n"/>
-      <c r="P11" s="281" t="n"/>
-      <c r="Q11" s="281" t="n"/>
-      <c r="R11" s="281" t="n"/>
-      <c r="S11" s="281" t="n"/>
-      <c r="T11" s="281" t="n"/>
-      <c r="U11" s="281" t="n"/>
-      <c r="V11" s="281" t="n"/>
-      <c r="W11" s="281" t="n"/>
-      <c r="X11" s="281" t="n"/>
-      <c r="Y11" s="281" t="n"/>
-      <c r="Z11" s="281" t="n"/>
-      <c r="AA11" s="281" t="n"/>
-      <c r="AB11" s="281" t="n"/>
-      <c r="AC11" s="281" t="n"/>
-      <c r="AD11" s="281" t="n"/>
-      <c r="AE11" s="281" t="n"/>
-      <c r="AF11" s="281" t="n"/>
-      <c r="AG11" s="281" t="n"/>
-      <c r="AH11" s="281" t="n"/>
-      <c r="AI11" s="281" t="n"/>
-      <c r="AJ11" s="281" t="n"/>
-      <c r="AK11" s="281" t="n"/>
-      <c r="AL11" s="281" t="n"/>
-      <c r="AM11" s="281" t="n"/>
-      <c r="AN11" s="281" t="n"/>
-      <c r="AO11" s="281" t="n"/>
-      <c r="AP11" s="281" t="n"/>
-      <c r="AQ11" s="281" t="n"/>
-      <c r="AR11" s="281" t="n"/>
-      <c r="AS11" s="281" t="n"/>
-      <c r="AT11" s="281" t="n"/>
-      <c r="AU11" s="281" t="n"/>
-      <c r="AV11" s="281" t="n"/>
-      <c r="AW11" s="281" t="n"/>
-      <c r="AX11" s="281" t="n"/>
-      <c r="AY11" s="281" t="n"/>
-      <c r="AZ11" s="281" t="n"/>
-      <c r="BA11" s="281" t="n"/>
-      <c r="BB11" s="281" t="n"/>
-      <c r="BC11" s="281" t="n"/>
-      <c r="BD11" s="282" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="22" t="n"/>
+      <c r="U11" s="22" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="22" t="n"/>
+      <c r="Y11" s="22" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="22" t="n"/>
+      <c r="AB11" s="22" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AD11" s="22" t="n"/>
+      <c r="AE11" s="22" t="n"/>
+      <c r="AF11" s="22" t="n"/>
+      <c r="AG11" s="22" t="n"/>
+      <c r="AH11" s="22" t="n"/>
+      <c r="AI11" s="22" t="n"/>
+      <c r="AJ11" s="22" t="n"/>
+      <c r="AK11" s="22" t="n"/>
+      <c r="AL11" s="22" t="n"/>
+      <c r="AM11" s="22" t="n"/>
+      <c r="AN11" s="22" t="n"/>
+      <c r="AO11" s="22" t="n"/>
+      <c r="AP11" s="22" t="n"/>
+      <c r="AQ11" s="22" t="n"/>
+      <c r="AR11" s="22" t="n"/>
+      <c r="AS11" s="22" t="n"/>
+      <c r="AT11" s="22" t="n"/>
+      <c r="AU11" s="22" t="n"/>
+      <c r="AV11" s="22" t="n"/>
+      <c r="AW11" s="22" t="n"/>
+      <c r="AX11" s="22" t="n"/>
+      <c r="AY11" s="22" t="n"/>
+      <c r="AZ11" s="22" t="n"/>
+      <c r="BA11" s="22" t="n"/>
+      <c r="BB11" s="22" t="n"/>
+      <c r="BC11" s="22" t="n"/>
+      <c r="BD11" s="23" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="327" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Finding ID</t>
         </is>
       </c>
-      <c r="B12" s="284" t="n"/>
-      <c r="C12" s="284" t="n"/>
-      <c r="D12" s="284" t="n"/>
-      <c r="E12" s="285" t="n"/>
-      <c r="F12" s="328" t="inlineStr">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="411" t="inlineStr">
         <is>
           <t>Account / Group</t>
         </is>
       </c>
-      <c r="G12" s="284" t="n"/>
-      <c r="H12" s="284" t="n"/>
-      <c r="I12" s="284" t="n"/>
-      <c r="J12" s="285" t="n"/>
-      <c r="K12" s="328" t="inlineStr">
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="411" t="inlineStr">
         <is>
           <t>Objective Evidence</t>
         </is>
       </c>
-      <c r="L12" s="284" t="n"/>
-      <c r="M12" s="284" t="n"/>
-      <c r="N12" s="284" t="n"/>
-      <c r="O12" s="284" t="n"/>
-      <c r="P12" s="284" t="n"/>
-      <c r="Q12" s="284" t="n"/>
-      <c r="R12" s="285" t="n"/>
-      <c r="S12" s="328" t="inlineStr">
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="411" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="T12" s="284" t="n"/>
-      <c r="U12" s="284" t="n"/>
-      <c r="V12" s="284" t="n"/>
-      <c r="W12" s="284" t="n"/>
-      <c r="X12" s="285" t="n"/>
-      <c r="Y12" s="328" t="inlineStr">
+      <c r="T12" s="6" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="411" t="inlineStr">
         <is>
           <t>Containment Need</t>
         </is>
       </c>
-      <c r="Z12" s="284" t="n"/>
-      <c r="AA12" s="284" t="n"/>
-      <c r="AB12" s="284" t="n"/>
-      <c r="AC12" s="284" t="n"/>
-      <c r="AD12" s="285" t="n"/>
-      <c r="AE12" s="328" t="inlineStr">
+      <c r="Z12" s="6" t="n"/>
+      <c r="AA12" s="6" t="n"/>
+      <c r="AB12" s="6" t="n"/>
+      <c r="AC12" s="6" t="n"/>
+      <c r="AD12" s="7" t="n"/>
+      <c r="AE12" s="411" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF12" s="284" t="n"/>
-      <c r="AG12" s="284" t="n"/>
-      <c r="AH12" s="284" t="n"/>
-      <c r="AI12" s="284" t="n"/>
-      <c r="AJ12" s="285" t="n"/>
-      <c r="AK12" s="328" t="inlineStr">
+      <c r="AF12" s="6" t="n"/>
+      <c r="AG12" s="6" t="n"/>
+      <c r="AH12" s="6" t="n"/>
+      <c r="AI12" s="6" t="n"/>
+      <c r="AJ12" s="7" t="n"/>
+      <c r="AK12" s="411" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AL12" s="284" t="n"/>
-      <c r="AM12" s="284" t="n"/>
-      <c r="AN12" s="284" t="n"/>
-      <c r="AO12" s="284" t="n"/>
-      <c r="AP12" s="285" t="n"/>
-      <c r="AQ12" s="328" t="inlineStr">
+      <c r="AL12" s="6" t="n"/>
+      <c r="AM12" s="6" t="n"/>
+      <c r="AN12" s="6" t="n"/>
+      <c r="AO12" s="6" t="n"/>
+      <c r="AP12" s="7" t="n"/>
+      <c r="AQ12" s="411" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AR12" s="284" t="n"/>
-      <c r="AS12" s="284" t="n"/>
-      <c r="AT12" s="284" t="n"/>
-      <c r="AU12" s="284" t="n"/>
-      <c r="AV12" s="285" t="n"/>
-      <c r="AW12" s="328" t="inlineStr">
+      <c r="AR12" s="6" t="n"/>
+      <c r="AS12" s="6" t="n"/>
+      <c r="AT12" s="6" t="n"/>
+      <c r="AU12" s="6" t="n"/>
+      <c r="AV12" s="7" t="n"/>
+      <c r="AW12" s="412" t="inlineStr">
         <is>
           <t>Link or Ref</t>
         </is>
       </c>
-      <c r="AX12" s="284" t="n"/>
-      <c r="AY12" s="284" t="n"/>
-      <c r="AZ12" s="284" t="n"/>
-      <c r="BA12" s="284" t="n"/>
-      <c r="BB12" s="284" t="n"/>
-      <c r="BC12" s="284" t="n"/>
-      <c r="BD12" s="322" t="n"/>
+      <c r="AX12" s="6" t="n"/>
+      <c r="AY12" s="6" t="n"/>
+      <c r="AZ12" s="6" t="n"/>
+      <c r="BA12" s="6" t="n"/>
+      <c r="BB12" s="6" t="n"/>
+      <c r="BC12" s="6" t="n"/>
+      <c r="BD12" s="9" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="329" t="n"/>
-      <c r="B13" s="287" t="n"/>
-      <c r="C13" s="287" t="n"/>
-      <c r="D13" s="287" t="n"/>
-      <c r="E13" s="288" t="n"/>
-      <c r="F13" s="286" t="n"/>
-      <c r="G13" s="287" t="n"/>
-      <c r="H13" s="287" t="n"/>
-      <c r="I13" s="287" t="n"/>
-      <c r="J13" s="288" t="n"/>
-      <c r="K13" s="286" t="n"/>
-      <c r="L13" s="287" t="n"/>
-      <c r="M13" s="287" t="n"/>
-      <c r="N13" s="287" t="n"/>
-      <c r="O13" s="287" t="n"/>
-      <c r="P13" s="287" t="n"/>
-      <c r="Q13" s="287" t="n"/>
-      <c r="R13" s="288" t="n"/>
-      <c r="S13" s="330" t="n"/>
-      <c r="T13" s="287" t="n"/>
-      <c r="U13" s="287" t="n"/>
-      <c r="V13" s="287" t="n"/>
-      <c r="W13" s="287" t="n"/>
-      <c r="X13" s="288" t="n"/>
-      <c r="Y13" s="286" t="n"/>
-      <c r="Z13" s="287" t="n"/>
-      <c r="AA13" s="287" t="n"/>
-      <c r="AB13" s="287" t="n"/>
-      <c r="AC13" s="287" t="n"/>
-      <c r="AD13" s="288" t="n"/>
-      <c r="AE13" s="330" t="n"/>
-      <c r="AF13" s="287" t="n"/>
-      <c r="AG13" s="287" t="n"/>
-      <c r="AH13" s="287" t="n"/>
-      <c r="AI13" s="287" t="n"/>
-      <c r="AJ13" s="288" t="n"/>
-      <c r="AK13" s="330" t="n"/>
-      <c r="AL13" s="287" t="n"/>
-      <c r="AM13" s="287" t="n"/>
-      <c r="AN13" s="287" t="n"/>
-      <c r="AO13" s="287" t="n"/>
-      <c r="AP13" s="288" t="n"/>
-      <c r="AQ13" s="330" t="n"/>
-      <c r="AR13" s="287" t="n"/>
-      <c r="AS13" s="287" t="n"/>
-      <c r="AT13" s="287" t="n"/>
-      <c r="AU13" s="287" t="n"/>
-      <c r="AV13" s="288" t="n"/>
-      <c r="AW13" s="286" t="n"/>
-      <c r="AX13" s="287" t="n"/>
-      <c r="AY13" s="287" t="n"/>
-      <c r="AZ13" s="287" t="n"/>
-      <c r="BA13" s="287" t="n"/>
-      <c r="BB13" s="287" t="n"/>
-      <c r="BC13" s="287" t="n"/>
-      <c r="BD13" s="290" t="n"/>
+      <c r="A13" s="413" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="27" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="26" t="n"/>
+      <c r="O13" s="26" t="n"/>
+      <c r="P13" s="26" t="n"/>
+      <c r="Q13" s="26" t="n"/>
+      <c r="R13" s="27" t="n"/>
+      <c r="S13" s="414" t="n"/>
+      <c r="T13" s="26" t="n"/>
+      <c r="U13" s="26" t="n"/>
+      <c r="V13" s="26" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="27" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="26" t="n"/>
+      <c r="AB13" s="26" t="n"/>
+      <c r="AC13" s="26" t="n"/>
+      <c r="AD13" s="27" t="n"/>
+      <c r="AE13" s="414" t="n"/>
+      <c r="AF13" s="26" t="n"/>
+      <c r="AG13" s="26" t="n"/>
+      <c r="AH13" s="26" t="n"/>
+      <c r="AI13" s="26" t="n"/>
+      <c r="AJ13" s="27" t="n"/>
+      <c r="AK13" s="414" t="n"/>
+      <c r="AL13" s="26" t="n"/>
+      <c r="AM13" s="26" t="n"/>
+      <c r="AN13" s="26" t="n"/>
+      <c r="AO13" s="26" t="n"/>
+      <c r="AP13" s="27" t="n"/>
+      <c r="AQ13" s="414" t="n"/>
+      <c r="AR13" s="26" t="n"/>
+      <c r="AS13" s="26" t="n"/>
+      <c r="AT13" s="26" t="n"/>
+      <c r="AU13" s="26" t="n"/>
+      <c r="AV13" s="27" t="n"/>
+      <c r="AW13" s="376" t="n"/>
+      <c r="AX13" s="26" t="n"/>
+      <c r="AY13" s="26" t="n"/>
+      <c r="AZ13" s="26" t="n"/>
+      <c r="BA13" s="26" t="n"/>
+      <c r="BB13" s="26" t="n"/>
+      <c r="BC13" s="26" t="n"/>
+      <c r="BD13" s="377" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="331" t="n"/>
-      <c r="B14" s="309" t="n"/>
-      <c r="C14" s="309" t="n"/>
-      <c r="D14" s="309" t="n"/>
-      <c r="E14" s="310" t="n"/>
-      <c r="F14" s="332" t="n"/>
-      <c r="G14" s="309" t="n"/>
-      <c r="H14" s="309" t="n"/>
-      <c r="I14" s="309" t="n"/>
-      <c r="J14" s="310" t="n"/>
-      <c r="K14" s="332" t="n"/>
-      <c r="L14" s="309" t="n"/>
-      <c r="M14" s="309" t="n"/>
-      <c r="N14" s="309" t="n"/>
-      <c r="O14" s="309" t="n"/>
-      <c r="P14" s="309" t="n"/>
-      <c r="Q14" s="309" t="n"/>
-      <c r="R14" s="310" t="n"/>
-      <c r="S14" s="333" t="n"/>
-      <c r="T14" s="309" t="n"/>
-      <c r="U14" s="309" t="n"/>
-      <c r="V14" s="309" t="n"/>
-      <c r="W14" s="309" t="n"/>
-      <c r="X14" s="310" t="n"/>
-      <c r="Y14" s="332" t="n"/>
-      <c r="Z14" s="309" t="n"/>
-      <c r="AA14" s="309" t="n"/>
-      <c r="AB14" s="309" t="n"/>
-      <c r="AC14" s="309" t="n"/>
-      <c r="AD14" s="310" t="n"/>
-      <c r="AE14" s="333" t="n"/>
-      <c r="AF14" s="309" t="n"/>
-      <c r="AG14" s="309" t="n"/>
-      <c r="AH14" s="309" t="n"/>
-      <c r="AI14" s="309" t="n"/>
-      <c r="AJ14" s="310" t="n"/>
-      <c r="AK14" s="333" t="n"/>
-      <c r="AL14" s="309" t="n"/>
-      <c r="AM14" s="309" t="n"/>
-      <c r="AN14" s="309" t="n"/>
-      <c r="AO14" s="309" t="n"/>
-      <c r="AP14" s="310" t="n"/>
-      <c r="AQ14" s="333" t="n"/>
-      <c r="AR14" s="309" t="n"/>
-      <c r="AS14" s="309" t="n"/>
-      <c r="AT14" s="309" t="n"/>
-      <c r="AU14" s="309" t="n"/>
-      <c r="AV14" s="310" t="n"/>
-      <c r="AW14" s="332" t="n"/>
-      <c r="AX14" s="309" t="n"/>
-      <c r="AY14" s="309" t="n"/>
-      <c r="AZ14" s="309" t="n"/>
-      <c r="BA14" s="309" t="n"/>
-      <c r="BB14" s="309" t="n"/>
-      <c r="BC14" s="309" t="n"/>
-      <c r="BD14" s="312" t="n"/>
+      <c r="A14" s="415" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="43" t="n"/>
+      <c r="L14" s="35" t="n"/>
+      <c r="M14" s="35" t="n"/>
+      <c r="N14" s="35" t="n"/>
+      <c r="O14" s="35" t="n"/>
+      <c r="P14" s="35" t="n"/>
+      <c r="Q14" s="35" t="n"/>
+      <c r="R14" s="36" t="n"/>
+      <c r="S14" s="42" t="n"/>
+      <c r="T14" s="35" t="n"/>
+      <c r="U14" s="35" t="n"/>
+      <c r="V14" s="35" t="n"/>
+      <c r="W14" s="35" t="n"/>
+      <c r="X14" s="36" t="n"/>
+      <c r="Y14" s="43" t="n"/>
+      <c r="Z14" s="35" t="n"/>
+      <c r="AA14" s="35" t="n"/>
+      <c r="AB14" s="35" t="n"/>
+      <c r="AC14" s="35" t="n"/>
+      <c r="AD14" s="36" t="n"/>
+      <c r="AE14" s="42" t="n"/>
+      <c r="AF14" s="35" t="n"/>
+      <c r="AG14" s="35" t="n"/>
+      <c r="AH14" s="35" t="n"/>
+      <c r="AI14" s="35" t="n"/>
+      <c r="AJ14" s="36" t="n"/>
+      <c r="AK14" s="42" t="n"/>
+      <c r="AL14" s="35" t="n"/>
+      <c r="AM14" s="35" t="n"/>
+      <c r="AN14" s="35" t="n"/>
+      <c r="AO14" s="35" t="n"/>
+      <c r="AP14" s="36" t="n"/>
+      <c r="AQ14" s="42" t="n"/>
+      <c r="AR14" s="35" t="n"/>
+      <c r="AS14" s="35" t="n"/>
+      <c r="AT14" s="35" t="n"/>
+      <c r="AU14" s="35" t="n"/>
+      <c r="AV14" s="36" t="n"/>
+      <c r="AW14" s="416" t="n"/>
+      <c r="AX14" s="35" t="n"/>
+      <c r="AY14" s="35" t="n"/>
+      <c r="AZ14" s="35" t="n"/>
+      <c r="BA14" s="35" t="n"/>
+      <c r="BB14" s="35" t="n"/>
+      <c r="BC14" s="35" t="n"/>
+      <c r="BD14" s="396" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="331" t="n"/>
-      <c r="B15" s="309" t="n"/>
-      <c r="C15" s="309" t="n"/>
-      <c r="D15" s="309" t="n"/>
-      <c r="E15" s="310" t="n"/>
-      <c r="F15" s="308" t="n"/>
-      <c r="G15" s="309" t="n"/>
-      <c r="H15" s="309" t="n"/>
-      <c r="I15" s="309" t="n"/>
-      <c r="J15" s="310" t="n"/>
-      <c r="K15" s="308" t="n"/>
-      <c r="L15" s="309" t="n"/>
-      <c r="M15" s="309" t="n"/>
-      <c r="N15" s="309" t="n"/>
-      <c r="O15" s="309" t="n"/>
-      <c r="P15" s="309" t="n"/>
-      <c r="Q15" s="309" t="n"/>
-      <c r="R15" s="310" t="n"/>
-      <c r="S15" s="333" t="n"/>
-      <c r="T15" s="309" t="n"/>
-      <c r="U15" s="309" t="n"/>
-      <c r="V15" s="309" t="n"/>
-      <c r="W15" s="309" t="n"/>
-      <c r="X15" s="310" t="n"/>
-      <c r="Y15" s="308" t="n"/>
-      <c r="Z15" s="309" t="n"/>
-      <c r="AA15" s="309" t="n"/>
-      <c r="AB15" s="309" t="n"/>
-      <c r="AC15" s="309" t="n"/>
-      <c r="AD15" s="310" t="n"/>
-      <c r="AE15" s="333" t="n"/>
-      <c r="AF15" s="309" t="n"/>
-      <c r="AG15" s="309" t="n"/>
-      <c r="AH15" s="309" t="n"/>
-      <c r="AI15" s="309" t="n"/>
-      <c r="AJ15" s="310" t="n"/>
-      <c r="AK15" s="333" t="n"/>
-      <c r="AL15" s="309" t="n"/>
-      <c r="AM15" s="309" t="n"/>
-      <c r="AN15" s="309" t="n"/>
-      <c r="AO15" s="309" t="n"/>
-      <c r="AP15" s="310" t="n"/>
-      <c r="AQ15" s="333" t="n"/>
-      <c r="AR15" s="309" t="n"/>
-      <c r="AS15" s="309" t="n"/>
-      <c r="AT15" s="309" t="n"/>
-      <c r="AU15" s="309" t="n"/>
-      <c r="AV15" s="310" t="n"/>
-      <c r="AW15" s="308" t="n"/>
-      <c r="AX15" s="309" t="n"/>
-      <c r="AY15" s="309" t="n"/>
-      <c r="AZ15" s="309" t="n"/>
-      <c r="BA15" s="309" t="n"/>
-      <c r="BB15" s="309" t="n"/>
-      <c r="BC15" s="309" t="n"/>
-      <c r="BD15" s="312" t="n"/>
+      <c r="A15" s="415" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="41" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="35" t="n"/>
+      <c r="M15" s="35" t="n"/>
+      <c r="N15" s="35" t="n"/>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+      <c r="R15" s="36" t="n"/>
+      <c r="S15" s="42" t="n"/>
+      <c r="T15" s="35" t="n"/>
+      <c r="U15" s="35" t="n"/>
+      <c r="V15" s="35" t="n"/>
+      <c r="W15" s="35" t="n"/>
+      <c r="X15" s="36" t="n"/>
+      <c r="Y15" s="41" t="n"/>
+      <c r="Z15" s="35" t="n"/>
+      <c r="AA15" s="35" t="n"/>
+      <c r="AB15" s="35" t="n"/>
+      <c r="AC15" s="35" t="n"/>
+      <c r="AD15" s="36" t="n"/>
+      <c r="AE15" s="42" t="n"/>
+      <c r="AF15" s="35" t="n"/>
+      <c r="AG15" s="35" t="n"/>
+      <c r="AH15" s="35" t="n"/>
+      <c r="AI15" s="35" t="n"/>
+      <c r="AJ15" s="36" t="n"/>
+      <c r="AK15" s="42" t="n"/>
+      <c r="AL15" s="35" t="n"/>
+      <c r="AM15" s="35" t="n"/>
+      <c r="AN15" s="35" t="n"/>
+      <c r="AO15" s="35" t="n"/>
+      <c r="AP15" s="36" t="n"/>
+      <c r="AQ15" s="42" t="n"/>
+      <c r="AR15" s="35" t="n"/>
+      <c r="AS15" s="35" t="n"/>
+      <c r="AT15" s="35" t="n"/>
+      <c r="AU15" s="35" t="n"/>
+      <c r="AV15" s="36" t="n"/>
+      <c r="AW15" s="395" t="n"/>
+      <c r="AX15" s="35" t="n"/>
+      <c r="AY15" s="35" t="n"/>
+      <c r="AZ15" s="35" t="n"/>
+      <c r="BA15" s="35" t="n"/>
+      <c r="BB15" s="35" t="n"/>
+      <c r="BC15" s="35" t="n"/>
+      <c r="BD15" s="396" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="331" t="n"/>
-      <c r="B16" s="309" t="n"/>
-      <c r="C16" s="309" t="n"/>
-      <c r="D16" s="309" t="n"/>
-      <c r="E16" s="310" t="n"/>
-      <c r="F16" s="332" t="n"/>
-      <c r="G16" s="309" t="n"/>
-      <c r="H16" s="309" t="n"/>
-      <c r="I16" s="309" t="n"/>
-      <c r="J16" s="310" t="n"/>
-      <c r="K16" s="332" t="n"/>
-      <c r="L16" s="309" t="n"/>
-      <c r="M16" s="309" t="n"/>
-      <c r="N16" s="309" t="n"/>
-      <c r="O16" s="309" t="n"/>
-      <c r="P16" s="309" t="n"/>
-      <c r="Q16" s="309" t="n"/>
-      <c r="R16" s="310" t="n"/>
-      <c r="S16" s="333" t="n"/>
-      <c r="T16" s="309" t="n"/>
-      <c r="U16" s="309" t="n"/>
-      <c r="V16" s="309" t="n"/>
-      <c r="W16" s="309" t="n"/>
-      <c r="X16" s="310" t="n"/>
-      <c r="Y16" s="332" t="n"/>
-      <c r="Z16" s="309" t="n"/>
-      <c r="AA16" s="309" t="n"/>
-      <c r="AB16" s="309" t="n"/>
-      <c r="AC16" s="309" t="n"/>
-      <c r="AD16" s="310" t="n"/>
-      <c r="AE16" s="333" t="n"/>
-      <c r="AF16" s="309" t="n"/>
-      <c r="AG16" s="309" t="n"/>
-      <c r="AH16" s="309" t="n"/>
-      <c r="AI16" s="309" t="n"/>
-      <c r="AJ16" s="310" t="n"/>
-      <c r="AK16" s="333" t="n"/>
-      <c r="AL16" s="309" t="n"/>
-      <c r="AM16" s="309" t="n"/>
-      <c r="AN16" s="309" t="n"/>
-      <c r="AO16" s="309" t="n"/>
-      <c r="AP16" s="310" t="n"/>
-      <c r="AQ16" s="333" t="n"/>
-      <c r="AR16" s="309" t="n"/>
-      <c r="AS16" s="309" t="n"/>
-      <c r="AT16" s="309" t="n"/>
-      <c r="AU16" s="309" t="n"/>
-      <c r="AV16" s="310" t="n"/>
-      <c r="AW16" s="332" t="n"/>
-      <c r="AX16" s="309" t="n"/>
-      <c r="AY16" s="309" t="n"/>
-      <c r="AZ16" s="309" t="n"/>
-      <c r="BA16" s="309" t="n"/>
-      <c r="BB16" s="309" t="n"/>
-      <c r="BC16" s="309" t="n"/>
-      <c r="BD16" s="312" t="n"/>
+      <c r="A16" s="415" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="43" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="35" t="n"/>
+      <c r="N16" s="35" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+      <c r="R16" s="36" t="n"/>
+      <c r="S16" s="42" t="n"/>
+      <c r="T16" s="35" t="n"/>
+      <c r="U16" s="35" t="n"/>
+      <c r="V16" s="35" t="n"/>
+      <c r="W16" s="35" t="n"/>
+      <c r="X16" s="36" t="n"/>
+      <c r="Y16" s="43" t="n"/>
+      <c r="Z16" s="35" t="n"/>
+      <c r="AA16" s="35" t="n"/>
+      <c r="AB16" s="35" t="n"/>
+      <c r="AC16" s="35" t="n"/>
+      <c r="AD16" s="36" t="n"/>
+      <c r="AE16" s="42" t="n"/>
+      <c r="AF16" s="35" t="n"/>
+      <c r="AG16" s="35" t="n"/>
+      <c r="AH16" s="35" t="n"/>
+      <c r="AI16" s="35" t="n"/>
+      <c r="AJ16" s="36" t="n"/>
+      <c r="AK16" s="42" t="n"/>
+      <c r="AL16" s="35" t="n"/>
+      <c r="AM16" s="35" t="n"/>
+      <c r="AN16" s="35" t="n"/>
+      <c r="AO16" s="35" t="n"/>
+      <c r="AP16" s="36" t="n"/>
+      <c r="AQ16" s="42" t="n"/>
+      <c r="AR16" s="35" t="n"/>
+      <c r="AS16" s="35" t="n"/>
+      <c r="AT16" s="35" t="n"/>
+      <c r="AU16" s="35" t="n"/>
+      <c r="AV16" s="36" t="n"/>
+      <c r="AW16" s="416" t="n"/>
+      <c r="AX16" s="35" t="n"/>
+      <c r="AY16" s="35" t="n"/>
+      <c r="AZ16" s="35" t="n"/>
+      <c r="BA16" s="35" t="n"/>
+      <c r="BB16" s="35" t="n"/>
+      <c r="BC16" s="35" t="n"/>
+      <c r="BD16" s="396" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="331" t="n"/>
-      <c r="B17" s="309" t="n"/>
-      <c r="C17" s="309" t="n"/>
-      <c r="D17" s="309" t="n"/>
-      <c r="E17" s="310" t="n"/>
-      <c r="F17" s="308" t="n"/>
-      <c r="G17" s="309" t="n"/>
-      <c r="H17" s="309" t="n"/>
-      <c r="I17" s="309" t="n"/>
-      <c r="J17" s="310" t="n"/>
-      <c r="K17" s="308" t="n"/>
-      <c r="L17" s="309" t="n"/>
-      <c r="M17" s="309" t="n"/>
-      <c r="N17" s="309" t="n"/>
-      <c r="O17" s="309" t="n"/>
-      <c r="P17" s="309" t="n"/>
-      <c r="Q17" s="309" t="n"/>
-      <c r="R17" s="310" t="n"/>
-      <c r="S17" s="333" t="n"/>
-      <c r="T17" s="309" t="n"/>
-      <c r="U17" s="309" t="n"/>
-      <c r="V17" s="309" t="n"/>
-      <c r="W17" s="309" t="n"/>
-      <c r="X17" s="310" t="n"/>
-      <c r="Y17" s="308" t="n"/>
-      <c r="Z17" s="309" t="n"/>
-      <c r="AA17" s="309" t="n"/>
-      <c r="AB17" s="309" t="n"/>
-      <c r="AC17" s="309" t="n"/>
-      <c r="AD17" s="310" t="n"/>
-      <c r="AE17" s="333" t="n"/>
-      <c r="AF17" s="309" t="n"/>
-      <c r="AG17" s="309" t="n"/>
-      <c r="AH17" s="309" t="n"/>
-      <c r="AI17" s="309" t="n"/>
-      <c r="AJ17" s="310" t="n"/>
-      <c r="AK17" s="333" t="n"/>
-      <c r="AL17" s="309" t="n"/>
-      <c r="AM17" s="309" t="n"/>
-      <c r="AN17" s="309" t="n"/>
-      <c r="AO17" s="309" t="n"/>
-      <c r="AP17" s="310" t="n"/>
-      <c r="AQ17" s="333" t="n"/>
-      <c r="AR17" s="309" t="n"/>
-      <c r="AS17" s="309" t="n"/>
-      <c r="AT17" s="309" t="n"/>
-      <c r="AU17" s="309" t="n"/>
-      <c r="AV17" s="310" t="n"/>
-      <c r="AW17" s="308" t="n"/>
-      <c r="AX17" s="309" t="n"/>
-      <c r="AY17" s="309" t="n"/>
-      <c r="AZ17" s="309" t="n"/>
-      <c r="BA17" s="309" t="n"/>
-      <c r="BB17" s="309" t="n"/>
-      <c r="BC17" s="309" t="n"/>
-      <c r="BD17" s="312" t="n"/>
+      <c r="A17" s="415" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="41" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="35" t="n"/>
+      <c r="M17" s="35" t="n"/>
+      <c r="N17" s="35" t="n"/>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="35" t="n"/>
+      <c r="R17" s="36" t="n"/>
+      <c r="S17" s="42" t="n"/>
+      <c r="T17" s="35" t="n"/>
+      <c r="U17" s="35" t="n"/>
+      <c r="V17" s="35" t="n"/>
+      <c r="W17" s="35" t="n"/>
+      <c r="X17" s="36" t="n"/>
+      <c r="Y17" s="41" t="n"/>
+      <c r="Z17" s="35" t="n"/>
+      <c r="AA17" s="35" t="n"/>
+      <c r="AB17" s="35" t="n"/>
+      <c r="AC17" s="35" t="n"/>
+      <c r="AD17" s="36" t="n"/>
+      <c r="AE17" s="42" t="n"/>
+      <c r="AF17" s="35" t="n"/>
+      <c r="AG17" s="35" t="n"/>
+      <c r="AH17" s="35" t="n"/>
+      <c r="AI17" s="35" t="n"/>
+      <c r="AJ17" s="36" t="n"/>
+      <c r="AK17" s="42" t="n"/>
+      <c r="AL17" s="35" t="n"/>
+      <c r="AM17" s="35" t="n"/>
+      <c r="AN17" s="35" t="n"/>
+      <c r="AO17" s="35" t="n"/>
+      <c r="AP17" s="36" t="n"/>
+      <c r="AQ17" s="42" t="n"/>
+      <c r="AR17" s="35" t="n"/>
+      <c r="AS17" s="35" t="n"/>
+      <c r="AT17" s="35" t="n"/>
+      <c r="AU17" s="35" t="n"/>
+      <c r="AV17" s="36" t="n"/>
+      <c r="AW17" s="395" t="n"/>
+      <c r="AX17" s="35" t="n"/>
+      <c r="AY17" s="35" t="n"/>
+      <c r="AZ17" s="35" t="n"/>
+      <c r="BA17" s="35" t="n"/>
+      <c r="BB17" s="35" t="n"/>
+      <c r="BC17" s="35" t="n"/>
+      <c r="BD17" s="396" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="334" t="n"/>
-      <c r="B18" s="294" t="n"/>
-      <c r="C18" s="294" t="n"/>
-      <c r="D18" s="294" t="n"/>
-      <c r="E18" s="295" t="n"/>
-      <c r="F18" s="335" t="n"/>
-      <c r="G18" s="294" t="n"/>
-      <c r="H18" s="294" t="n"/>
-      <c r="I18" s="294" t="n"/>
-      <c r="J18" s="295" t="n"/>
-      <c r="K18" s="335" t="n"/>
-      <c r="L18" s="294" t="n"/>
-      <c r="M18" s="294" t="n"/>
-      <c r="N18" s="294" t="n"/>
-      <c r="O18" s="294" t="n"/>
-      <c r="P18" s="294" t="n"/>
-      <c r="Q18" s="294" t="n"/>
-      <c r="R18" s="295" t="n"/>
-      <c r="S18" s="336" t="n"/>
-      <c r="T18" s="294" t="n"/>
-      <c r="U18" s="294" t="n"/>
-      <c r="V18" s="294" t="n"/>
-      <c r="W18" s="294" t="n"/>
-      <c r="X18" s="295" t="n"/>
-      <c r="Y18" s="335" t="n"/>
-      <c r="Z18" s="294" t="n"/>
-      <c r="AA18" s="294" t="n"/>
-      <c r="AB18" s="294" t="n"/>
-      <c r="AC18" s="294" t="n"/>
-      <c r="AD18" s="295" t="n"/>
-      <c r="AE18" s="336" t="n"/>
-      <c r="AF18" s="294" t="n"/>
-      <c r="AG18" s="294" t="n"/>
-      <c r="AH18" s="294" t="n"/>
-      <c r="AI18" s="294" t="n"/>
-      <c r="AJ18" s="295" t="n"/>
-      <c r="AK18" s="336" t="n"/>
-      <c r="AL18" s="294" t="n"/>
-      <c r="AM18" s="294" t="n"/>
-      <c r="AN18" s="294" t="n"/>
-      <c r="AO18" s="294" t="n"/>
-      <c r="AP18" s="295" t="n"/>
-      <c r="AQ18" s="336" t="n"/>
-      <c r="AR18" s="294" t="n"/>
-      <c r="AS18" s="294" t="n"/>
-      <c r="AT18" s="294" t="n"/>
-      <c r="AU18" s="294" t="n"/>
-      <c r="AV18" s="295" t="n"/>
-      <c r="AW18" s="335" t="n"/>
-      <c r="AX18" s="294" t="n"/>
-      <c r="AY18" s="294" t="n"/>
-      <c r="AZ18" s="294" t="n"/>
-      <c r="BA18" s="294" t="n"/>
-      <c r="BB18" s="294" t="n"/>
-      <c r="BC18" s="294" t="n"/>
-      <c r="BD18" s="297" t="n"/>
+      <c r="A18" s="417" t="n"/>
+      <c r="B18" s="380" t="n"/>
+      <c r="C18" s="380" t="n"/>
+      <c r="D18" s="380" t="n"/>
+      <c r="E18" s="381" t="n"/>
+      <c r="F18" s="418" t="n"/>
+      <c r="G18" s="380" t="n"/>
+      <c r="H18" s="380" t="n"/>
+      <c r="I18" s="380" t="n"/>
+      <c r="J18" s="381" t="n"/>
+      <c r="K18" s="418" t="n"/>
+      <c r="L18" s="380" t="n"/>
+      <c r="M18" s="380" t="n"/>
+      <c r="N18" s="380" t="n"/>
+      <c r="O18" s="380" t="n"/>
+      <c r="P18" s="380" t="n"/>
+      <c r="Q18" s="380" t="n"/>
+      <c r="R18" s="381" t="n"/>
+      <c r="S18" s="419" t="n"/>
+      <c r="T18" s="380" t="n"/>
+      <c r="U18" s="380" t="n"/>
+      <c r="V18" s="380" t="n"/>
+      <c r="W18" s="380" t="n"/>
+      <c r="X18" s="381" t="n"/>
+      <c r="Y18" s="418" t="n"/>
+      <c r="Z18" s="380" t="n"/>
+      <c r="AA18" s="380" t="n"/>
+      <c r="AB18" s="380" t="n"/>
+      <c r="AC18" s="380" t="n"/>
+      <c r="AD18" s="381" t="n"/>
+      <c r="AE18" s="419" t="n"/>
+      <c r="AF18" s="380" t="n"/>
+      <c r="AG18" s="380" t="n"/>
+      <c r="AH18" s="380" t="n"/>
+      <c r="AI18" s="380" t="n"/>
+      <c r="AJ18" s="381" t="n"/>
+      <c r="AK18" s="419" t="n"/>
+      <c r="AL18" s="380" t="n"/>
+      <c r="AM18" s="380" t="n"/>
+      <c r="AN18" s="380" t="n"/>
+      <c r="AO18" s="380" t="n"/>
+      <c r="AP18" s="381" t="n"/>
+      <c r="AQ18" s="419" t="n"/>
+      <c r="AR18" s="380" t="n"/>
+      <c r="AS18" s="380" t="n"/>
+      <c r="AT18" s="380" t="n"/>
+      <c r="AU18" s="380" t="n"/>
+      <c r="AV18" s="381" t="n"/>
+      <c r="AW18" s="420" t="n"/>
+      <c r="AX18" s="380" t="n"/>
+      <c r="AY18" s="380" t="n"/>
+      <c r="AZ18" s="380" t="n"/>
+      <c r="BA18" s="380" t="n"/>
+      <c r="BB18" s="380" t="n"/>
+      <c r="BC18" s="380" t="n"/>
+      <c r="BD18" s="384" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="280" t="inlineStr">
+      <c r="A19" s="373" t="inlineStr">
         <is>
           <t>NOTICE: Use one row per finding. Record objective evidence, severity, owner, due date and verification reference; avoid vague or conclusion-only wording.</t>
         </is>
       </c>
-      <c r="B19" s="281" t="n"/>
-      <c r="C19" s="281" t="n"/>
-      <c r="D19" s="281" t="n"/>
-      <c r="E19" s="281" t="n"/>
-      <c r="F19" s="281" t="n"/>
-      <c r="G19" s="281" t="n"/>
-      <c r="H19" s="281" t="n"/>
-      <c r="I19" s="281" t="n"/>
-      <c r="J19" s="281" t="n"/>
-      <c r="K19" s="281" t="n"/>
-      <c r="L19" s="281" t="n"/>
-      <c r="M19" s="281" t="n"/>
-      <c r="N19" s="281" t="n"/>
-      <c r="O19" s="281" t="n"/>
-      <c r="P19" s="281" t="n"/>
-      <c r="Q19" s="281" t="n"/>
-      <c r="R19" s="281" t="n"/>
-      <c r="S19" s="281" t="n"/>
-      <c r="T19" s="281" t="n"/>
-      <c r="U19" s="281" t="n"/>
-      <c r="V19" s="281" t="n"/>
-      <c r="W19" s="281" t="n"/>
-      <c r="X19" s="281" t="n"/>
-      <c r="Y19" s="281" t="n"/>
-      <c r="Z19" s="281" t="n"/>
-      <c r="AA19" s="281" t="n"/>
-      <c r="AB19" s="281" t="n"/>
-      <c r="AC19" s="281" t="n"/>
-      <c r="AD19" s="281" t="n"/>
-      <c r="AE19" s="281" t="n"/>
-      <c r="AF19" s="281" t="n"/>
-      <c r="AG19" s="281" t="n"/>
-      <c r="AH19" s="281" t="n"/>
-      <c r="AI19" s="281" t="n"/>
-      <c r="AJ19" s="281" t="n"/>
-      <c r="AK19" s="281" t="n"/>
-      <c r="AL19" s="281" t="n"/>
-      <c r="AM19" s="281" t="n"/>
-      <c r="AN19" s="281" t="n"/>
-      <c r="AO19" s="281" t="n"/>
-      <c r="AP19" s="281" t="n"/>
-      <c r="AQ19" s="281" t="n"/>
-      <c r="AR19" s="281" t="n"/>
-      <c r="AS19" s="281" t="n"/>
-      <c r="AT19" s="281" t="n"/>
-      <c r="AU19" s="281" t="n"/>
-      <c r="AV19" s="281" t="n"/>
-      <c r="AW19" s="281" t="n"/>
-      <c r="AX19" s="281" t="n"/>
-      <c r="AY19" s="281" t="n"/>
-      <c r="AZ19" s="281" t="n"/>
-      <c r="BA19" s="281" t="n"/>
-      <c r="BB19" s="281" t="n"/>
-      <c r="BC19" s="281" t="n"/>
-      <c r="BD19" s="282" t="n"/>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+      <c r="U19" s="22" t="n"/>
+      <c r="V19" s="22" t="n"/>
+      <c r="W19" s="22" t="n"/>
+      <c r="X19" s="22" t="n"/>
+      <c r="Y19" s="22" t="n"/>
+      <c r="Z19" s="22" t="n"/>
+      <c r="AA19" s="22" t="n"/>
+      <c r="AB19" s="22" t="n"/>
+      <c r="AC19" s="22" t="n"/>
+      <c r="AD19" s="22" t="n"/>
+      <c r="AE19" s="22" t="n"/>
+      <c r="AF19" s="22" t="n"/>
+      <c r="AG19" s="22" t="n"/>
+      <c r="AH19" s="22" t="n"/>
+      <c r="AI19" s="22" t="n"/>
+      <c r="AJ19" s="22" t="n"/>
+      <c r="AK19" s="22" t="n"/>
+      <c r="AL19" s="22" t="n"/>
+      <c r="AM19" s="22" t="n"/>
+      <c r="AN19" s="22" t="n"/>
+      <c r="AO19" s="22" t="n"/>
+      <c r="AP19" s="22" t="n"/>
+      <c r="AQ19" s="22" t="n"/>
+      <c r="AR19" s="22" t="n"/>
+      <c r="AS19" s="22" t="n"/>
+      <c r="AT19" s="22" t="n"/>
+      <c r="AU19" s="22" t="n"/>
+      <c r="AV19" s="22" t="n"/>
+      <c r="AW19" s="22" t="n"/>
+      <c r="AX19" s="22" t="n"/>
+      <c r="AY19" s="22" t="n"/>
+      <c r="AZ19" s="22" t="n"/>
+      <c r="BA19" s="22" t="n"/>
+      <c r="BB19" s="22" t="n"/>
+      <c r="BC19" s="22" t="n"/>
+      <c r="BD19" s="23" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -5968,346 +6126,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="255" t="n"/>
-      <c r="B1" s="256" t="n"/>
-      <c r="C1" s="256" t="n"/>
-      <c r="D1" s="256" t="n"/>
-      <c r="E1" s="256" t="n"/>
-      <c r="F1" s="256" t="n"/>
-      <c r="G1" s="256" t="n"/>
-      <c r="H1" s="256" t="n"/>
-      <c r="I1" s="256" t="n"/>
-      <c r="J1" s="256" t="n"/>
-      <c r="K1" s="257" t="n"/>
+      <c r="A1" s="359" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="n"/>
       <c r="L1" s="258" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW — EVIDENCE REFERENCE REGISTER</t>
         </is>
       </c>
-      <c r="M1" s="256" t="n"/>
-      <c r="N1" s="256" t="n"/>
-      <c r="O1" s="256" t="n"/>
-      <c r="P1" s="256" t="n"/>
-      <c r="Q1" s="256" t="n"/>
-      <c r="R1" s="256" t="n"/>
-      <c r="S1" s="256" t="n"/>
-      <c r="T1" s="256" t="n"/>
-      <c r="U1" s="256" t="n"/>
-      <c r="V1" s="256" t="n"/>
-      <c r="W1" s="256" t="n"/>
-      <c r="X1" s="256" t="n"/>
-      <c r="Y1" s="256" t="n"/>
-      <c r="Z1" s="256" t="n"/>
-      <c r="AA1" s="256" t="n"/>
-      <c r="AB1" s="256" t="n"/>
-      <c r="AC1" s="256" t="n"/>
-      <c r="AD1" s="256" t="n"/>
-      <c r="AE1" s="256" t="n"/>
-      <c r="AF1" s="256" t="n"/>
-      <c r="AG1" s="256" t="n"/>
-      <c r="AH1" s="256" t="n"/>
-      <c r="AI1" s="256" t="n"/>
-      <c r="AJ1" s="256" t="n"/>
-      <c r="AK1" s="256" t="n"/>
-      <c r="AL1" s="256" t="n"/>
-      <c r="AM1" s="256" t="n"/>
-      <c r="AN1" s="256" t="n"/>
-      <c r="AO1" s="256" t="n"/>
-      <c r="AP1" s="256" t="n"/>
-      <c r="AQ1" s="259" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="360" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="256" t="n"/>
-      <c r="AS1" s="256" t="n"/>
-      <c r="AT1" s="256" t="n"/>
-      <c r="AU1" s="256" t="n"/>
-      <c r="AV1" s="260" t="n"/>
-      <c r="AW1" s="261" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="361" t="n"/>
+      <c r="AW1" s="362" t="inlineStr">
         <is>
           <t>FRM-111</t>
         </is>
       </c>
-      <c r="AX1" s="256" t="n"/>
-      <c r="AY1" s="256" t="n"/>
-      <c r="AZ1" s="256" t="n"/>
-      <c r="BA1" s="256" t="n"/>
-      <c r="BB1" s="256" t="n"/>
-      <c r="BC1" s="256" t="n"/>
-      <c r="BD1" s="257" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="262" t="n"/>
-      <c r="B2" s="263" t="n"/>
-      <c r="C2" s="263" t="n"/>
-      <c r="D2" s="263" t="n"/>
-      <c r="E2" s="263" t="n"/>
-      <c r="F2" s="263" t="n"/>
-      <c r="G2" s="263" t="n"/>
-      <c r="H2" s="263" t="n"/>
-      <c r="I2" s="263" t="n"/>
-      <c r="J2" s="263" t="n"/>
-      <c r="K2" s="264" t="n"/>
-      <c r="L2" s="262" t="n"/>
-      <c r="M2" s="263" t="n"/>
-      <c r="N2" s="263" t="n"/>
-      <c r="O2" s="263" t="n"/>
-      <c r="P2" s="263" t="n"/>
-      <c r="Q2" s="263" t="n"/>
-      <c r="R2" s="263" t="n"/>
-      <c r="S2" s="263" t="n"/>
-      <c r="T2" s="263" t="n"/>
-      <c r="U2" s="263" t="n"/>
-      <c r="V2" s="263" t="n"/>
-      <c r="W2" s="263" t="n"/>
-      <c r="X2" s="263" t="n"/>
-      <c r="Y2" s="263" t="n"/>
-      <c r="Z2" s="263" t="n"/>
-      <c r="AA2" s="263" t="n"/>
-      <c r="AB2" s="263" t="n"/>
-      <c r="AC2" s="263" t="n"/>
-      <c r="AD2" s="263" t="n"/>
-      <c r="AE2" s="263" t="n"/>
-      <c r="AF2" s="263" t="n"/>
-      <c r="AG2" s="263" t="n"/>
-      <c r="AH2" s="263" t="n"/>
-      <c r="AI2" s="263" t="n"/>
-      <c r="AJ2" s="263" t="n"/>
-      <c r="AK2" s="263" t="n"/>
-      <c r="AL2" s="263" t="n"/>
-      <c r="AM2" s="263" t="n"/>
-      <c r="AN2" s="263" t="n"/>
-      <c r="AO2" s="263" t="n"/>
-      <c r="AP2" s="263" t="n"/>
-      <c r="AQ2" s="265" t="inlineStr">
+      <c r="A2" s="10" t="n"/>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="AQ2" s="363" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="266" t="n"/>
-      <c r="AS2" s="266" t="n"/>
-      <c r="AT2" s="266" t="n"/>
-      <c r="AU2" s="266" t="n"/>
-      <c r="AV2" s="267" t="n"/>
-      <c r="AW2" s="268" t="inlineStr">
+      <c r="AR2" s="364" t="n"/>
+      <c r="AS2" s="364" t="n"/>
+      <c r="AT2" s="364" t="n"/>
+      <c r="AU2" s="364" t="n"/>
+      <c r="AV2" s="365" t="n"/>
+      <c r="AW2" s="366" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="266" t="n"/>
-      <c r="AY2" s="266" t="n"/>
-      <c r="AZ2" s="266" t="n"/>
-      <c r="BA2" s="266" t="n"/>
-      <c r="BB2" s="266" t="n"/>
-      <c r="BC2" s="266" t="n"/>
-      <c r="BD2" s="269" t="n"/>
+      <c r="AX2" s="364" t="n"/>
+      <c r="AY2" s="364" t="n"/>
+      <c r="AZ2" s="364" t="n"/>
+      <c r="BA2" s="364" t="n"/>
+      <c r="BB2" s="364" t="n"/>
+      <c r="BC2" s="364" t="n"/>
+      <c r="BD2" s="367" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="262" t="n"/>
-      <c r="B3" s="263" t="n"/>
-      <c r="C3" s="263" t="n"/>
-      <c r="D3" s="263" t="n"/>
-      <c r="E3" s="263" t="n"/>
-      <c r="F3" s="263" t="n"/>
-      <c r="G3" s="263" t="n"/>
-      <c r="H3" s="263" t="n"/>
-      <c r="I3" s="263" t="n"/>
-      <c r="J3" s="263" t="n"/>
-      <c r="K3" s="264" t="n"/>
-      <c r="L3" s="262" t="n"/>
-      <c r="M3" s="263" t="n"/>
-      <c r="N3" s="263" t="n"/>
-      <c r="O3" s="263" t="n"/>
-      <c r="P3" s="263" t="n"/>
-      <c r="Q3" s="263" t="n"/>
-      <c r="R3" s="263" t="n"/>
-      <c r="S3" s="263" t="n"/>
-      <c r="T3" s="263" t="n"/>
-      <c r="U3" s="263" t="n"/>
-      <c r="V3" s="263" t="n"/>
-      <c r="W3" s="263" t="n"/>
-      <c r="X3" s="263" t="n"/>
-      <c r="Y3" s="263" t="n"/>
-      <c r="Z3" s="263" t="n"/>
-      <c r="AA3" s="263" t="n"/>
-      <c r="AB3" s="263" t="n"/>
-      <c r="AC3" s="263" t="n"/>
-      <c r="AD3" s="263" t="n"/>
-      <c r="AE3" s="263" t="n"/>
-      <c r="AF3" s="263" t="n"/>
-      <c r="AG3" s="263" t="n"/>
-      <c r="AH3" s="263" t="n"/>
-      <c r="AI3" s="263" t="n"/>
-      <c r="AJ3" s="263" t="n"/>
-      <c r="AK3" s="263" t="n"/>
-      <c r="AL3" s="263" t="n"/>
-      <c r="AM3" s="263" t="n"/>
-      <c r="AN3" s="263" t="n"/>
-      <c r="AO3" s="263" t="n"/>
-      <c r="AP3" s="263" t="n"/>
-      <c r="AQ3" s="265" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="AQ3" s="363" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="266" t="n"/>
-      <c r="AS3" s="266" t="n"/>
-      <c r="AT3" s="266" t="n"/>
-      <c r="AU3" s="266" t="n"/>
-      <c r="AV3" s="267" t="n"/>
-      <c r="AW3" s="268" t="inlineStr">
+      <c r="AR3" s="364" t="n"/>
+      <c r="AS3" s="364" t="n"/>
+      <c r="AT3" s="364" t="n"/>
+      <c r="AU3" s="364" t="n"/>
+      <c r="AV3" s="365" t="n"/>
+      <c r="AW3" s="366" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="266" t="n"/>
-      <c r="AY3" s="266" t="n"/>
-      <c r="AZ3" s="266" t="n"/>
-      <c r="BA3" s="266" t="n"/>
-      <c r="BB3" s="266" t="n"/>
-      <c r="BC3" s="266" t="n"/>
-      <c r="BD3" s="269" t="n"/>
+      <c r="AX3" s="364" t="n"/>
+      <c r="AY3" s="364" t="n"/>
+      <c r="AZ3" s="364" t="n"/>
+      <c r="BA3" s="364" t="n"/>
+      <c r="BB3" s="364" t="n"/>
+      <c r="BC3" s="364" t="n"/>
+      <c r="BD3" s="367" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="262" t="n"/>
-      <c r="B4" s="263" t="n"/>
-      <c r="C4" s="263" t="n"/>
-      <c r="D4" s="263" t="n"/>
-      <c r="E4" s="263" t="n"/>
-      <c r="F4" s="263" t="n"/>
-      <c r="G4" s="263" t="n"/>
-      <c r="H4" s="263" t="n"/>
-      <c r="I4" s="263" t="n"/>
-      <c r="J4" s="263" t="n"/>
-      <c r="K4" s="264" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="K4" s="11" t="n"/>
       <c r="L4" s="270" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="263" t="n"/>
-      <c r="N4" s="263" t="n"/>
-      <c r="O4" s="263" t="n"/>
-      <c r="P4" s="263" t="n"/>
-      <c r="Q4" s="263" t="n"/>
-      <c r="R4" s="263" t="n"/>
-      <c r="S4" s="263" t="n"/>
-      <c r="T4" s="263" t="n"/>
-      <c r="U4" s="263" t="n"/>
-      <c r="V4" s="263" t="n"/>
-      <c r="W4" s="263" t="n"/>
-      <c r="X4" s="263" t="n"/>
-      <c r="Y4" s="263" t="n"/>
-      <c r="Z4" s="263" t="n"/>
-      <c r="AA4" s="263" t="n"/>
-      <c r="AB4" s="263" t="n"/>
-      <c r="AC4" s="263" t="n"/>
-      <c r="AD4" s="263" t="n"/>
-      <c r="AE4" s="263" t="n"/>
-      <c r="AF4" s="263" t="n"/>
-      <c r="AG4" s="263" t="n"/>
-      <c r="AH4" s="263" t="n"/>
-      <c r="AI4" s="263" t="n"/>
-      <c r="AJ4" s="263" t="n"/>
-      <c r="AK4" s="263" t="n"/>
-      <c r="AL4" s="263" t="n"/>
-      <c r="AM4" s="263" t="n"/>
-      <c r="AN4" s="263" t="n"/>
-      <c r="AO4" s="263" t="n"/>
-      <c r="AP4" s="263" t="n"/>
-      <c r="AQ4" s="265" t="inlineStr">
+      <c r="AQ4" s="363" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="266" t="n"/>
-      <c r="AS4" s="266" t="n"/>
-      <c r="AT4" s="266" t="n"/>
-      <c r="AU4" s="266" t="n"/>
-      <c r="AV4" s="267" t="n"/>
-      <c r="AW4" s="268" t="inlineStr">
+      <c r="AR4" s="364" t="n"/>
+      <c r="AS4" s="364" t="n"/>
+      <c r="AT4" s="364" t="n"/>
+      <c r="AU4" s="364" t="n"/>
+      <c r="AV4" s="365" t="n"/>
+      <c r="AW4" s="366" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AX4" s="266" t="n"/>
-      <c r="AY4" s="266" t="n"/>
-      <c r="AZ4" s="266" t="n"/>
-      <c r="BA4" s="266" t="n"/>
-      <c r="BB4" s="266" t="n"/>
-      <c r="BC4" s="266" t="n"/>
-      <c r="BD4" s="269" t="n"/>
+      <c r="AX4" s="364" t="n"/>
+      <c r="AY4" s="364" t="n"/>
+      <c r="AZ4" s="364" t="n"/>
+      <c r="BA4" s="364" t="n"/>
+      <c r="BB4" s="364" t="n"/>
+      <c r="BC4" s="364" t="n"/>
+      <c r="BD4" s="367" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="271" t="n"/>
-      <c r="B5" s="272" t="n"/>
-      <c r="C5" s="272" t="n"/>
-      <c r="D5" s="272" t="n"/>
-      <c r="E5" s="272" t="n"/>
-      <c r="F5" s="272" t="n"/>
-      <c r="G5" s="272" t="n"/>
-      <c r="H5" s="272" t="n"/>
-      <c r="I5" s="272" t="n"/>
-      <c r="J5" s="272" t="n"/>
-      <c r="K5" s="273" t="n"/>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="18" t="n"/>
       <c r="L5" s="50" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="272" t="n"/>
-      <c r="N5" s="272" t="n"/>
-      <c r="O5" s="272" t="n"/>
-      <c r="P5" s="272" t="n"/>
-      <c r="Q5" s="272" t="n"/>
-      <c r="R5" s="272" t="n"/>
-      <c r="S5" s="272" t="n"/>
-      <c r="T5" s="272" t="n"/>
-      <c r="U5" s="272" t="n"/>
-      <c r="V5" s="272" t="n"/>
-      <c r="W5" s="272" t="n"/>
-      <c r="X5" s="272" t="n"/>
-      <c r="Y5" s="272" t="n"/>
-      <c r="Z5" s="272" t="n"/>
-      <c r="AA5" s="272" t="n"/>
-      <c r="AB5" s="272" t="n"/>
-      <c r="AC5" s="272" t="n"/>
-      <c r="AD5" s="272" t="n"/>
-      <c r="AE5" s="272" t="n"/>
-      <c r="AF5" s="272" t="n"/>
-      <c r="AG5" s="272" t="n"/>
-      <c r="AH5" s="272" t="n"/>
-      <c r="AI5" s="272" t="n"/>
-      <c r="AJ5" s="272" t="n"/>
-      <c r="AK5" s="272" t="n"/>
-      <c r="AL5" s="272" t="n"/>
-      <c r="AM5" s="272" t="n"/>
-      <c r="AN5" s="272" t="n"/>
-      <c r="AO5" s="272" t="n"/>
-      <c r="AP5" s="272" t="n"/>
-      <c r="AQ5" s="274" t="inlineStr">
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="17" t="n"/>
+      <c r="P5" s="17" t="n"/>
+      <c r="Q5" s="17" t="n"/>
+      <c r="R5" s="17" t="n"/>
+      <c r="S5" s="17" t="n"/>
+      <c r="T5" s="17" t="n"/>
+      <c r="U5" s="17" t="n"/>
+      <c r="V5" s="17" t="n"/>
+      <c r="W5" s="17" t="n"/>
+      <c r="X5" s="17" t="n"/>
+      <c r="Y5" s="17" t="n"/>
+      <c r="Z5" s="17" t="n"/>
+      <c r="AA5" s="17" t="n"/>
+      <c r="AB5" s="17" t="n"/>
+      <c r="AC5" s="17" t="n"/>
+      <c r="AD5" s="17" t="n"/>
+      <c r="AE5" s="17" t="n"/>
+      <c r="AF5" s="17" t="n"/>
+      <c r="AG5" s="17" t="n"/>
+      <c r="AH5" s="17" t="n"/>
+      <c r="AI5" s="17" t="n"/>
+      <c r="AJ5" s="17" t="n"/>
+      <c r="AK5" s="17" t="n"/>
+      <c r="AL5" s="17" t="n"/>
+      <c r="AM5" s="17" t="n"/>
+      <c r="AN5" s="17" t="n"/>
+      <c r="AO5" s="17" t="n"/>
+      <c r="AP5" s="17" t="n"/>
+      <c r="AQ5" s="368" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="275" t="n"/>
-      <c r="AS5" s="275" t="n"/>
-      <c r="AT5" s="275" t="n"/>
-      <c r="AU5" s="275" t="n"/>
-      <c r="AV5" s="276" t="n"/>
-      <c r="AW5" s="277" t="inlineStr">
+      <c r="AR5" s="369" t="n"/>
+      <c r="AS5" s="369" t="n"/>
+      <c r="AT5" s="369" t="n"/>
+      <c r="AU5" s="369" t="n"/>
+      <c r="AV5" s="370" t="n"/>
+      <c r="AW5" s="371" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="275" t="n"/>
-      <c r="AY5" s="275" t="n"/>
-      <c r="AZ5" s="275" t="n"/>
-      <c r="BA5" s="275" t="n"/>
-      <c r="BB5" s="275" t="n"/>
-      <c r="BC5" s="275" t="n"/>
-      <c r="BD5" s="278" t="n"/>
+      <c r="AX5" s="369" t="n"/>
+      <c r="AY5" s="369" t="n"/>
+      <c r="AZ5" s="369" t="n"/>
+      <c r="BA5" s="369" t="n"/>
+      <c r="BB5" s="369" t="n"/>
+      <c r="BC5" s="369" t="n"/>
+      <c r="BD5" s="372" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="279" t="n"/>
@@ -6368,760 +6409,760 @@
       <c r="BD6" s="279" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="280" t="inlineStr">
+      <c r="A7" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="281" t="n"/>
-      <c r="C7" s="281" t="n"/>
-      <c r="D7" s="281" t="n"/>
-      <c r="E7" s="281" t="n"/>
-      <c r="F7" s="281" t="n"/>
-      <c r="G7" s="281" t="n"/>
-      <c r="H7" s="281" t="n"/>
-      <c r="I7" s="281" t="n"/>
-      <c r="J7" s="281" t="n"/>
-      <c r="K7" s="281" t="n"/>
-      <c r="L7" s="281" t="n"/>
-      <c r="M7" s="281" t="n"/>
-      <c r="N7" s="281" t="n"/>
-      <c r="O7" s="281" t="n"/>
-      <c r="P7" s="281" t="n"/>
-      <c r="Q7" s="281" t="n"/>
-      <c r="R7" s="281" t="n"/>
-      <c r="S7" s="281" t="n"/>
-      <c r="T7" s="281" t="n"/>
-      <c r="U7" s="281" t="n"/>
-      <c r="V7" s="281" t="n"/>
-      <c r="W7" s="281" t="n"/>
-      <c r="X7" s="281" t="n"/>
-      <c r="Y7" s="281" t="n"/>
-      <c r="Z7" s="281" t="n"/>
-      <c r="AA7" s="281" t="n"/>
-      <c r="AB7" s="281" t="n"/>
-      <c r="AC7" s="281" t="n"/>
-      <c r="AD7" s="281" t="n"/>
-      <c r="AE7" s="281" t="n"/>
-      <c r="AF7" s="281" t="n"/>
-      <c r="AG7" s="281" t="n"/>
-      <c r="AH7" s="281" t="n"/>
-      <c r="AI7" s="281" t="n"/>
-      <c r="AJ7" s="281" t="n"/>
-      <c r="AK7" s="281" t="n"/>
-      <c r="AL7" s="281" t="n"/>
-      <c r="AM7" s="281" t="n"/>
-      <c r="AN7" s="281" t="n"/>
-      <c r="AO7" s="281" t="n"/>
-      <c r="AP7" s="281" t="n"/>
-      <c r="AQ7" s="281" t="n"/>
-      <c r="AR7" s="281" t="n"/>
-      <c r="AS7" s="281" t="n"/>
-      <c r="AT7" s="281" t="n"/>
-      <c r="AU7" s="281" t="n"/>
-      <c r="AV7" s="281" t="n"/>
-      <c r="AW7" s="281" t="n"/>
-      <c r="AX7" s="281" t="n"/>
-      <c r="AY7" s="281" t="n"/>
-      <c r="AZ7" s="281" t="n"/>
-      <c r="BA7" s="281" t="n"/>
-      <c r="BB7" s="281" t="n"/>
-      <c r="BC7" s="281" t="n"/>
-      <c r="BD7" s="282" t="n"/>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="22" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="22" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="22" t="n"/>
+      <c r="AF7" s="22" t="n"/>
+      <c r="AG7" s="22" t="n"/>
+      <c r="AH7" s="22" t="n"/>
+      <c r="AI7" s="22" t="n"/>
+      <c r="AJ7" s="22" t="n"/>
+      <c r="AK7" s="22" t="n"/>
+      <c r="AL7" s="22" t="n"/>
+      <c r="AM7" s="22" t="n"/>
+      <c r="AN7" s="22" t="n"/>
+      <c r="AO7" s="22" t="n"/>
+      <c r="AP7" s="22" t="n"/>
+      <c r="AQ7" s="22" t="n"/>
+      <c r="AR7" s="22" t="n"/>
+      <c r="AS7" s="22" t="n"/>
+      <c r="AT7" s="22" t="n"/>
+      <c r="AU7" s="22" t="n"/>
+      <c r="AV7" s="22" t="n"/>
+      <c r="AW7" s="22" t="n"/>
+      <c r="AX7" s="22" t="n"/>
+      <c r="AY7" s="22" t="n"/>
+      <c r="AZ7" s="22" t="n"/>
+      <c r="BA7" s="22" t="n"/>
+      <c r="BB7" s="22" t="n"/>
+      <c r="BC7" s="22" t="n"/>
+      <c r="BD7" s="23" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="283" t="inlineStr">
+      <c r="A8" s="374" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="284" t="n"/>
-      <c r="C8" s="284" t="n"/>
-      <c r="D8" s="284" t="n"/>
-      <c r="E8" s="284" t="n"/>
-      <c r="F8" s="284" t="n"/>
-      <c r="G8" s="284" t="n"/>
-      <c r="H8" s="284" t="n"/>
-      <c r="I8" s="284" t="n"/>
-      <c r="J8" s="285" t="n"/>
-      <c r="K8" s="320" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="38" t="inlineStr">
         <is>
           <t>Access-role master and effective rights remain in the live system + ANNEX-IT-001 / 025 control set; workbook captures request / review evidence only, not the source permission model.</t>
         </is>
       </c>
-      <c r="L8" s="284" t="n"/>
-      <c r="M8" s="284" t="n"/>
-      <c r="N8" s="284" t="n"/>
-      <c r="O8" s="284" t="n"/>
-      <c r="P8" s="284" t="n"/>
-      <c r="Q8" s="284" t="n"/>
-      <c r="R8" s="284" t="n"/>
-      <c r="S8" s="284" t="n"/>
-      <c r="T8" s="284" t="n"/>
-      <c r="U8" s="284" t="n"/>
-      <c r="V8" s="284" t="n"/>
-      <c r="W8" s="284" t="n"/>
-      <c r="X8" s="284" t="n"/>
-      <c r="Y8" s="284" t="n"/>
-      <c r="Z8" s="284" t="n"/>
-      <c r="AA8" s="284" t="n"/>
-      <c r="AB8" s="285" t="n"/>
-      <c r="AC8" s="321" t="inlineStr"/>
-      <c r="AD8" s="284" t="n"/>
-      <c r="AE8" s="284" t="n"/>
-      <c r="AF8" s="284" t="n"/>
-      <c r="AG8" s="284" t="n"/>
-      <c r="AH8" s="284" t="n"/>
-      <c r="AI8" s="284" t="n"/>
-      <c r="AJ8" s="284" t="n"/>
-      <c r="AK8" s="284" t="n"/>
-      <c r="AL8" s="285" t="n"/>
-      <c r="AM8" s="321" t="inlineStr"/>
-      <c r="AN8" s="284" t="n"/>
-      <c r="AO8" s="284" t="n"/>
-      <c r="AP8" s="284" t="n"/>
-      <c r="AQ8" s="284" t="n"/>
-      <c r="AR8" s="284" t="n"/>
-      <c r="AS8" s="284" t="n"/>
-      <c r="AT8" s="284" t="n"/>
-      <c r="AU8" s="284" t="n"/>
-      <c r="AV8" s="284" t="n"/>
-      <c r="AW8" s="284" t="n"/>
-      <c r="AX8" s="284" t="n"/>
-      <c r="AY8" s="284" t="n"/>
-      <c r="AZ8" s="284" t="n"/>
-      <c r="BA8" s="284" t="n"/>
-      <c r="BB8" s="284" t="n"/>
-      <c r="BC8" s="284" t="n"/>
-      <c r="BD8" s="322" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="403" t="inlineStr"/>
+      <c r="AD8" s="6" t="n"/>
+      <c r="AE8" s="6" t="n"/>
+      <c r="AF8" s="6" t="n"/>
+      <c r="AG8" s="6" t="n"/>
+      <c r="AH8" s="6" t="n"/>
+      <c r="AI8" s="6" t="n"/>
+      <c r="AJ8" s="6" t="n"/>
+      <c r="AK8" s="6" t="n"/>
+      <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="404" t="inlineStr"/>
+      <c r="AN8" s="6" t="n"/>
+      <c r="AO8" s="6" t="n"/>
+      <c r="AP8" s="6" t="n"/>
+      <c r="AQ8" s="6" t="n"/>
+      <c r="AR8" s="6" t="n"/>
+      <c r="AS8" s="6" t="n"/>
+      <c r="AT8" s="6" t="n"/>
+      <c r="AU8" s="6" t="n"/>
+      <c r="AV8" s="6" t="n"/>
+      <c r="AW8" s="6" t="n"/>
+      <c r="AX8" s="6" t="n"/>
+      <c r="AY8" s="6" t="n"/>
+      <c r="AZ8" s="6" t="n"/>
+      <c r="BA8" s="6" t="n"/>
+      <c r="BB8" s="6" t="n"/>
+      <c r="BC8" s="6" t="n"/>
+      <c r="BD8" s="9" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="291" t="inlineStr">
+      <c r="A9" s="378" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="272" t="n"/>
-      <c r="C9" s="272" t="n"/>
-      <c r="D9" s="272" t="n"/>
-      <c r="E9" s="272" t="n"/>
-      <c r="F9" s="272" t="n"/>
-      <c r="G9" s="272" t="n"/>
-      <c r="H9" s="272" t="n"/>
-      <c r="I9" s="272" t="n"/>
-      <c r="J9" s="292" t="n"/>
-      <c r="K9" s="325" t="inlineStr">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="52" t="n"/>
+      <c r="K9" s="408" t="inlineStr">
         <is>
           <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
         </is>
       </c>
-      <c r="L9" s="272" t="n"/>
-      <c r="M9" s="272" t="n"/>
-      <c r="N9" s="272" t="n"/>
-      <c r="O9" s="272" t="n"/>
-      <c r="P9" s="272" t="n"/>
-      <c r="Q9" s="272" t="n"/>
-      <c r="R9" s="272" t="n"/>
-      <c r="S9" s="272" t="n"/>
-      <c r="T9" s="272" t="n"/>
-      <c r="U9" s="272" t="n"/>
-      <c r="V9" s="272" t="n"/>
-      <c r="W9" s="272" t="n"/>
-      <c r="X9" s="272" t="n"/>
-      <c r="Y9" s="272" t="n"/>
-      <c r="Z9" s="272" t="n"/>
-      <c r="AA9" s="272" t="n"/>
-      <c r="AB9" s="292" t="n"/>
-      <c r="AC9" s="326" t="inlineStr"/>
-      <c r="AD9" s="272" t="n"/>
-      <c r="AE9" s="272" t="n"/>
-      <c r="AF9" s="272" t="n"/>
-      <c r="AG9" s="272" t="n"/>
-      <c r="AH9" s="272" t="n"/>
-      <c r="AI9" s="272" t="n"/>
-      <c r="AJ9" s="272" t="n"/>
-      <c r="AK9" s="272" t="n"/>
-      <c r="AL9" s="292" t="n"/>
-      <c r="AM9" s="326" t="inlineStr"/>
-      <c r="AN9" s="272" t="n"/>
-      <c r="AO9" s="272" t="n"/>
-      <c r="AP9" s="272" t="n"/>
-      <c r="AQ9" s="272" t="n"/>
-      <c r="AR9" s="272" t="n"/>
-      <c r="AS9" s="272" t="n"/>
-      <c r="AT9" s="272" t="n"/>
-      <c r="AU9" s="272" t="n"/>
-      <c r="AV9" s="272" t="n"/>
-      <c r="AW9" s="272" t="n"/>
-      <c r="AX9" s="272" t="n"/>
-      <c r="AY9" s="272" t="n"/>
-      <c r="AZ9" s="272" t="n"/>
-      <c r="BA9" s="272" t="n"/>
-      <c r="BB9" s="272" t="n"/>
-      <c r="BC9" s="272" t="n"/>
-      <c r="BD9" s="273" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="17" t="n"/>
+      <c r="P9" s="17" t="n"/>
+      <c r="Q9" s="17" t="n"/>
+      <c r="R9" s="17" t="n"/>
+      <c r="S9" s="17" t="n"/>
+      <c r="T9" s="17" t="n"/>
+      <c r="U9" s="17" t="n"/>
+      <c r="V9" s="17" t="n"/>
+      <c r="W9" s="17" t="n"/>
+      <c r="X9" s="17" t="n"/>
+      <c r="Y9" s="17" t="n"/>
+      <c r="Z9" s="17" t="n"/>
+      <c r="AA9" s="17" t="n"/>
+      <c r="AB9" s="52" t="n"/>
+      <c r="AC9" s="409" t="inlineStr"/>
+      <c r="AD9" s="17" t="n"/>
+      <c r="AE9" s="17" t="n"/>
+      <c r="AF9" s="17" t="n"/>
+      <c r="AG9" s="17" t="n"/>
+      <c r="AH9" s="17" t="n"/>
+      <c r="AI9" s="17" t="n"/>
+      <c r="AJ9" s="17" t="n"/>
+      <c r="AK9" s="17" t="n"/>
+      <c r="AL9" s="52" t="n"/>
+      <c r="AM9" s="410" t="inlineStr"/>
+      <c r="AN9" s="17" t="n"/>
+      <c r="AO9" s="17" t="n"/>
+      <c r="AP9" s="17" t="n"/>
+      <c r="AQ9" s="17" t="n"/>
+      <c r="AR9" s="17" t="n"/>
+      <c r="AS9" s="17" t="n"/>
+      <c r="AT9" s="17" t="n"/>
+      <c r="AU9" s="17" t="n"/>
+      <c r="AV9" s="17" t="n"/>
+      <c r="AW9" s="17" t="n"/>
+      <c r="AX9" s="17" t="n"/>
+      <c r="AY9" s="17" t="n"/>
+      <c r="AZ9" s="17" t="n"/>
+      <c r="BA9" s="17" t="n"/>
+      <c r="BB9" s="17" t="n"/>
+      <c r="BC9" s="17" t="n"/>
+      <c r="BD9" s="18" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="280" t="inlineStr">
+      <c r="A10" s="373" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B10" s="281" t="n"/>
-      <c r="C10" s="281" t="n"/>
-      <c r="D10" s="281" t="n"/>
-      <c r="E10" s="281" t="n"/>
-      <c r="F10" s="281" t="n"/>
-      <c r="G10" s="281" t="n"/>
-      <c r="H10" s="281" t="n"/>
-      <c r="I10" s="281" t="n"/>
-      <c r="J10" s="281" t="n"/>
-      <c r="K10" s="281" t="n"/>
-      <c r="L10" s="281" t="n"/>
-      <c r="M10" s="281" t="n"/>
-      <c r="N10" s="281" t="n"/>
-      <c r="O10" s="281" t="n"/>
-      <c r="P10" s="281" t="n"/>
-      <c r="Q10" s="281" t="n"/>
-      <c r="R10" s="281" t="n"/>
-      <c r="S10" s="281" t="n"/>
-      <c r="T10" s="281" t="n"/>
-      <c r="U10" s="281" t="n"/>
-      <c r="V10" s="281" t="n"/>
-      <c r="W10" s="281" t="n"/>
-      <c r="X10" s="281" t="n"/>
-      <c r="Y10" s="281" t="n"/>
-      <c r="Z10" s="281" t="n"/>
-      <c r="AA10" s="281" t="n"/>
-      <c r="AB10" s="281" t="n"/>
-      <c r="AC10" s="281" t="n"/>
-      <c r="AD10" s="281" t="n"/>
-      <c r="AE10" s="281" t="n"/>
-      <c r="AF10" s="281" t="n"/>
-      <c r="AG10" s="281" t="n"/>
-      <c r="AH10" s="281" t="n"/>
-      <c r="AI10" s="281" t="n"/>
-      <c r="AJ10" s="281" t="n"/>
-      <c r="AK10" s="281" t="n"/>
-      <c r="AL10" s="281" t="n"/>
-      <c r="AM10" s="281" t="n"/>
-      <c r="AN10" s="281" t="n"/>
-      <c r="AO10" s="281" t="n"/>
-      <c r="AP10" s="281" t="n"/>
-      <c r="AQ10" s="281" t="n"/>
-      <c r="AR10" s="281" t="n"/>
-      <c r="AS10" s="281" t="n"/>
-      <c r="AT10" s="281" t="n"/>
-      <c r="AU10" s="281" t="n"/>
-      <c r="AV10" s="281" t="n"/>
-      <c r="AW10" s="281" t="n"/>
-      <c r="AX10" s="281" t="n"/>
-      <c r="AY10" s="281" t="n"/>
-      <c r="AZ10" s="281" t="n"/>
-      <c r="BA10" s="281" t="n"/>
-      <c r="BB10" s="281" t="n"/>
-      <c r="BC10" s="281" t="n"/>
-      <c r="BD10" s="282" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="22" t="n"/>
+      <c r="U10" s="22" t="n"/>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="22" t="n"/>
+      <c r="Y10" s="22" t="n"/>
+      <c r="Z10" s="22" t="n"/>
+      <c r="AA10" s="22" t="n"/>
+      <c r="AB10" s="22" t="n"/>
+      <c r="AC10" s="22" t="n"/>
+      <c r="AD10" s="22" t="n"/>
+      <c r="AE10" s="22" t="n"/>
+      <c r="AF10" s="22" t="n"/>
+      <c r="AG10" s="22" t="n"/>
+      <c r="AH10" s="22" t="n"/>
+      <c r="AI10" s="22" t="n"/>
+      <c r="AJ10" s="22" t="n"/>
+      <c r="AK10" s="22" t="n"/>
+      <c r="AL10" s="22" t="n"/>
+      <c r="AM10" s="22" t="n"/>
+      <c r="AN10" s="22" t="n"/>
+      <c r="AO10" s="22" t="n"/>
+      <c r="AP10" s="22" t="n"/>
+      <c r="AQ10" s="22" t="n"/>
+      <c r="AR10" s="22" t="n"/>
+      <c r="AS10" s="22" t="n"/>
+      <c r="AT10" s="22" t="n"/>
+      <c r="AU10" s="22" t="n"/>
+      <c r="AV10" s="22" t="n"/>
+      <c r="AW10" s="22" t="n"/>
+      <c r="AX10" s="22" t="n"/>
+      <c r="AY10" s="22" t="n"/>
+      <c r="AZ10" s="22" t="n"/>
+      <c r="BA10" s="22" t="n"/>
+      <c r="BB10" s="22" t="n"/>
+      <c r="BC10" s="22" t="n"/>
+      <c r="BD10" s="23" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="327" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Evidence ID</t>
         </is>
       </c>
-      <c r="B11" s="284" t="n"/>
-      <c r="C11" s="284" t="n"/>
-      <c r="D11" s="284" t="n"/>
-      <c r="E11" s="284" t="n"/>
-      <c r="F11" s="284" t="n"/>
-      <c r="G11" s="284" t="n"/>
-      <c r="H11" s="285" t="n"/>
-      <c r="I11" s="328" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="411" t="inlineStr">
         <is>
           <t>Related Record</t>
         </is>
       </c>
-      <c r="J11" s="284" t="n"/>
-      <c r="K11" s="284" t="n"/>
-      <c r="L11" s="284" t="n"/>
-      <c r="M11" s="285" t="n"/>
-      <c r="N11" s="328" t="inlineStr">
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="411" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O11" s="284" t="n"/>
-      <c r="P11" s="284" t="n"/>
-      <c r="Q11" s="284" t="n"/>
-      <c r="R11" s="284" t="n"/>
-      <c r="S11" s="284" t="n"/>
-      <c r="T11" s="284" t="n"/>
-      <c r="U11" s="284" t="n"/>
-      <c r="V11" s="284" t="n"/>
-      <c r="W11" s="284" t="n"/>
-      <c r="X11" s="285" t="n"/>
-      <c r="Y11" s="328" t="inlineStr">
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
+      <c r="T11" s="6" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="7" t="n"/>
+      <c r="Y11" s="411" t="inlineStr">
         <is>
           <t>Source System</t>
         </is>
       </c>
-      <c r="Z11" s="284" t="n"/>
-      <c r="AA11" s="284" t="n"/>
-      <c r="AB11" s="284" t="n"/>
-      <c r="AC11" s="285" t="n"/>
-      <c r="AD11" s="328" t="inlineStr">
+      <c r="Z11" s="6" t="n"/>
+      <c r="AA11" s="6" t="n"/>
+      <c r="AB11" s="6" t="n"/>
+      <c r="AC11" s="7" t="n"/>
+      <c r="AD11" s="411" t="inlineStr">
         <is>
           <t>Reference Path or Link</t>
         </is>
       </c>
-      <c r="AE11" s="284" t="n"/>
-      <c r="AF11" s="284" t="n"/>
-      <c r="AG11" s="284" t="n"/>
-      <c r="AH11" s="284" t="n"/>
-      <c r="AI11" s="284" t="n"/>
-      <c r="AJ11" s="285" t="n"/>
-      <c r="AK11" s="328" t="inlineStr">
+      <c r="AE11" s="6" t="n"/>
+      <c r="AF11" s="6" t="n"/>
+      <c r="AG11" s="6" t="n"/>
+      <c r="AH11" s="6" t="n"/>
+      <c r="AI11" s="6" t="n"/>
+      <c r="AJ11" s="7" t="n"/>
+      <c r="AK11" s="411" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AL11" s="284" t="n"/>
-      <c r="AM11" s="284" t="n"/>
-      <c r="AN11" s="284" t="n"/>
-      <c r="AO11" s="284" t="n"/>
-      <c r="AP11" s="285" t="n"/>
-      <c r="AQ11" s="328" t="inlineStr">
+      <c r="AL11" s="6" t="n"/>
+      <c r="AM11" s="6" t="n"/>
+      <c r="AN11" s="6" t="n"/>
+      <c r="AO11" s="6" t="n"/>
+      <c r="AP11" s="7" t="n"/>
+      <c r="AQ11" s="411" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="AR11" s="284" t="n"/>
-      <c r="AS11" s="284" t="n"/>
-      <c r="AT11" s="284" t="n"/>
-      <c r="AU11" s="285" t="n"/>
-      <c r="AV11" s="328" t="inlineStr">
+      <c r="AR11" s="6" t="n"/>
+      <c r="AS11" s="6" t="n"/>
+      <c r="AT11" s="6" t="n"/>
+      <c r="AU11" s="7" t="n"/>
+      <c r="AV11" s="412" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AW11" s="284" t="n"/>
-      <c r="AX11" s="284" t="n"/>
-      <c r="AY11" s="284" t="n"/>
-      <c r="AZ11" s="284" t="n"/>
-      <c r="BA11" s="284" t="n"/>
-      <c r="BB11" s="284" t="n"/>
-      <c r="BC11" s="284" t="n"/>
-      <c r="BD11" s="322" t="n"/>
+      <c r="AW11" s="6" t="n"/>
+      <c r="AX11" s="6" t="n"/>
+      <c r="AY11" s="6" t="n"/>
+      <c r="AZ11" s="6" t="n"/>
+      <c r="BA11" s="6" t="n"/>
+      <c r="BB11" s="6" t="n"/>
+      <c r="BC11" s="6" t="n"/>
+      <c r="BD11" s="9" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="337" t="n"/>
-      <c r="B12" s="284" t="n"/>
-      <c r="C12" s="284" t="n"/>
-      <c r="D12" s="284" t="n"/>
-      <c r="E12" s="284" t="n"/>
-      <c r="F12" s="284" t="n"/>
-      <c r="G12" s="284" t="n"/>
-      <c r="H12" s="285" t="n"/>
-      <c r="I12" s="286" t="n"/>
-      <c r="J12" s="287" t="n"/>
-      <c r="K12" s="287" t="n"/>
-      <c r="L12" s="287" t="n"/>
-      <c r="M12" s="288" t="n"/>
-      <c r="N12" s="286" t="n"/>
-      <c r="O12" s="287" t="n"/>
-      <c r="P12" s="287" t="n"/>
-      <c r="Q12" s="287" t="n"/>
-      <c r="R12" s="287" t="n"/>
-      <c r="S12" s="287" t="n"/>
-      <c r="T12" s="287" t="n"/>
-      <c r="U12" s="287" t="n"/>
-      <c r="V12" s="287" t="n"/>
-      <c r="W12" s="287" t="n"/>
-      <c r="X12" s="288" t="n"/>
-      <c r="Y12" s="286" t="n"/>
-      <c r="Z12" s="287" t="n"/>
-      <c r="AA12" s="287" t="n"/>
-      <c r="AB12" s="287" t="n"/>
-      <c r="AC12" s="288" t="n"/>
-      <c r="AD12" s="286" t="n"/>
-      <c r="AE12" s="287" t="n"/>
-      <c r="AF12" s="287" t="n"/>
-      <c r="AG12" s="287" t="n"/>
-      <c r="AH12" s="287" t="n"/>
-      <c r="AI12" s="287" t="n"/>
-      <c r="AJ12" s="288" t="n"/>
-      <c r="AK12" s="330" t="n"/>
-      <c r="AL12" s="287" t="n"/>
-      <c r="AM12" s="287" t="n"/>
-      <c r="AN12" s="287" t="n"/>
-      <c r="AO12" s="287" t="n"/>
-      <c r="AP12" s="288" t="n"/>
-      <c r="AQ12" s="286" t="n"/>
-      <c r="AR12" s="287" t="n"/>
-      <c r="AS12" s="287" t="n"/>
-      <c r="AT12" s="287" t="n"/>
-      <c r="AU12" s="288" t="n"/>
-      <c r="AV12" s="286" t="n"/>
-      <c r="AW12" s="287" t="n"/>
-      <c r="AX12" s="287" t="n"/>
-      <c r="AY12" s="287" t="n"/>
-      <c r="AZ12" s="287" t="n"/>
-      <c r="BA12" s="287" t="n"/>
-      <c r="BB12" s="287" t="n"/>
-      <c r="BC12" s="287" t="n"/>
-      <c r="BD12" s="290" t="n"/>
+      <c r="A12" s="421" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="26" t="n"/>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="27" t="n"/>
+      <c r="N12" s="25" t="n"/>
+      <c r="O12" s="26" t="n"/>
+      <c r="P12" s="26" t="n"/>
+      <c r="Q12" s="26" t="n"/>
+      <c r="R12" s="26" t="n"/>
+      <c r="S12" s="26" t="n"/>
+      <c r="T12" s="26" t="n"/>
+      <c r="U12" s="26" t="n"/>
+      <c r="V12" s="26" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="27" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="26" t="n"/>
+      <c r="AB12" s="26" t="n"/>
+      <c r="AC12" s="27" t="n"/>
+      <c r="AD12" s="25" t="n"/>
+      <c r="AE12" s="26" t="n"/>
+      <c r="AF12" s="26" t="n"/>
+      <c r="AG12" s="26" t="n"/>
+      <c r="AH12" s="26" t="n"/>
+      <c r="AI12" s="26" t="n"/>
+      <c r="AJ12" s="27" t="n"/>
+      <c r="AK12" s="414" t="n"/>
+      <c r="AL12" s="26" t="n"/>
+      <c r="AM12" s="26" t="n"/>
+      <c r="AN12" s="26" t="n"/>
+      <c r="AO12" s="26" t="n"/>
+      <c r="AP12" s="27" t="n"/>
+      <c r="AQ12" s="25" t="n"/>
+      <c r="AR12" s="26" t="n"/>
+      <c r="AS12" s="26" t="n"/>
+      <c r="AT12" s="26" t="n"/>
+      <c r="AU12" s="27" t="n"/>
+      <c r="AV12" s="376" t="n"/>
+      <c r="AW12" s="26" t="n"/>
+      <c r="AX12" s="26" t="n"/>
+      <c r="AY12" s="26" t="n"/>
+      <c r="AZ12" s="26" t="n"/>
+      <c r="BA12" s="26" t="n"/>
+      <c r="BB12" s="26" t="n"/>
+      <c r="BC12" s="26" t="n"/>
+      <c r="BD12" s="377" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="338" t="n"/>
-      <c r="B13" s="306" t="n"/>
-      <c r="C13" s="306" t="n"/>
-      <c r="D13" s="306" t="n"/>
-      <c r="E13" s="306" t="n"/>
-      <c r="F13" s="306" t="n"/>
-      <c r="G13" s="306" t="n"/>
-      <c r="H13" s="307" t="n"/>
-      <c r="I13" s="332" t="n"/>
-      <c r="J13" s="309" t="n"/>
-      <c r="K13" s="309" t="n"/>
-      <c r="L13" s="309" t="n"/>
-      <c r="M13" s="310" t="n"/>
-      <c r="N13" s="332" t="n"/>
-      <c r="O13" s="309" t="n"/>
-      <c r="P13" s="309" t="n"/>
-      <c r="Q13" s="309" t="n"/>
-      <c r="R13" s="309" t="n"/>
-      <c r="S13" s="309" t="n"/>
-      <c r="T13" s="309" t="n"/>
-      <c r="U13" s="309" t="n"/>
-      <c r="V13" s="309" t="n"/>
-      <c r="W13" s="309" t="n"/>
-      <c r="X13" s="310" t="n"/>
-      <c r="Y13" s="332" t="n"/>
-      <c r="Z13" s="309" t="n"/>
-      <c r="AA13" s="309" t="n"/>
-      <c r="AB13" s="309" t="n"/>
-      <c r="AC13" s="310" t="n"/>
-      <c r="AD13" s="332" t="n"/>
-      <c r="AE13" s="309" t="n"/>
-      <c r="AF13" s="309" t="n"/>
-      <c r="AG13" s="309" t="n"/>
-      <c r="AH13" s="309" t="n"/>
-      <c r="AI13" s="309" t="n"/>
-      <c r="AJ13" s="310" t="n"/>
-      <c r="AK13" s="333" t="n"/>
-      <c r="AL13" s="309" t="n"/>
-      <c r="AM13" s="309" t="n"/>
-      <c r="AN13" s="309" t="n"/>
-      <c r="AO13" s="309" t="n"/>
-      <c r="AP13" s="310" t="n"/>
-      <c r="AQ13" s="332" t="n"/>
-      <c r="AR13" s="309" t="n"/>
-      <c r="AS13" s="309" t="n"/>
-      <c r="AT13" s="309" t="n"/>
-      <c r="AU13" s="310" t="n"/>
-      <c r="AV13" s="332" t="n"/>
-      <c r="AW13" s="309" t="n"/>
-      <c r="AX13" s="309" t="n"/>
-      <c r="AY13" s="309" t="n"/>
-      <c r="AZ13" s="309" t="n"/>
-      <c r="BA13" s="309" t="n"/>
-      <c r="BB13" s="309" t="n"/>
-      <c r="BC13" s="309" t="n"/>
-      <c r="BD13" s="312" t="n"/>
+      <c r="A13" s="422" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="29" t="n"/>
+      <c r="I13" s="43" t="n"/>
+      <c r="J13" s="35" t="n"/>
+      <c r="K13" s="35" t="n"/>
+      <c r="L13" s="35" t="n"/>
+      <c r="M13" s="36" t="n"/>
+      <c r="N13" s="43" t="n"/>
+      <c r="O13" s="35" t="n"/>
+      <c r="P13" s="35" t="n"/>
+      <c r="Q13" s="35" t="n"/>
+      <c r="R13" s="35" t="n"/>
+      <c r="S13" s="35" t="n"/>
+      <c r="T13" s="35" t="n"/>
+      <c r="U13" s="35" t="n"/>
+      <c r="V13" s="35" t="n"/>
+      <c r="W13" s="35" t="n"/>
+      <c r="X13" s="36" t="n"/>
+      <c r="Y13" s="43" t="n"/>
+      <c r="Z13" s="35" t="n"/>
+      <c r="AA13" s="35" t="n"/>
+      <c r="AB13" s="35" t="n"/>
+      <c r="AC13" s="36" t="n"/>
+      <c r="AD13" s="43" t="n"/>
+      <c r="AE13" s="35" t="n"/>
+      <c r="AF13" s="35" t="n"/>
+      <c r="AG13" s="35" t="n"/>
+      <c r="AH13" s="35" t="n"/>
+      <c r="AI13" s="35" t="n"/>
+      <c r="AJ13" s="36" t="n"/>
+      <c r="AK13" s="42" t="n"/>
+      <c r="AL13" s="35" t="n"/>
+      <c r="AM13" s="35" t="n"/>
+      <c r="AN13" s="35" t="n"/>
+      <c r="AO13" s="35" t="n"/>
+      <c r="AP13" s="36" t="n"/>
+      <c r="AQ13" s="43" t="n"/>
+      <c r="AR13" s="35" t="n"/>
+      <c r="AS13" s="35" t="n"/>
+      <c r="AT13" s="35" t="n"/>
+      <c r="AU13" s="36" t="n"/>
+      <c r="AV13" s="416" t="n"/>
+      <c r="AW13" s="35" t="n"/>
+      <c r="AX13" s="35" t="n"/>
+      <c r="AY13" s="35" t="n"/>
+      <c r="AZ13" s="35" t="n"/>
+      <c r="BA13" s="35" t="n"/>
+      <c r="BB13" s="35" t="n"/>
+      <c r="BC13" s="35" t="n"/>
+      <c r="BD13" s="396" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="338" t="n"/>
-      <c r="B14" s="306" t="n"/>
-      <c r="C14" s="306" t="n"/>
-      <c r="D14" s="306" t="n"/>
-      <c r="E14" s="306" t="n"/>
-      <c r="F14" s="306" t="n"/>
-      <c r="G14" s="306" t="n"/>
-      <c r="H14" s="307" t="n"/>
-      <c r="I14" s="308" t="n"/>
-      <c r="J14" s="309" t="n"/>
-      <c r="K14" s="309" t="n"/>
-      <c r="L14" s="309" t="n"/>
-      <c r="M14" s="310" t="n"/>
-      <c r="N14" s="308" t="n"/>
-      <c r="O14" s="309" t="n"/>
-      <c r="P14" s="309" t="n"/>
-      <c r="Q14" s="309" t="n"/>
-      <c r="R14" s="309" t="n"/>
-      <c r="S14" s="309" t="n"/>
-      <c r="T14" s="309" t="n"/>
-      <c r="U14" s="309" t="n"/>
-      <c r="V14" s="309" t="n"/>
-      <c r="W14" s="309" t="n"/>
-      <c r="X14" s="310" t="n"/>
-      <c r="Y14" s="308" t="n"/>
-      <c r="Z14" s="309" t="n"/>
-      <c r="AA14" s="309" t="n"/>
-      <c r="AB14" s="309" t="n"/>
-      <c r="AC14" s="310" t="n"/>
-      <c r="AD14" s="308" t="n"/>
-      <c r="AE14" s="309" t="n"/>
-      <c r="AF14" s="309" t="n"/>
-      <c r="AG14" s="309" t="n"/>
-      <c r="AH14" s="309" t="n"/>
-      <c r="AI14" s="309" t="n"/>
-      <c r="AJ14" s="310" t="n"/>
-      <c r="AK14" s="333" t="n"/>
-      <c r="AL14" s="309" t="n"/>
-      <c r="AM14" s="309" t="n"/>
-      <c r="AN14" s="309" t="n"/>
-      <c r="AO14" s="309" t="n"/>
-      <c r="AP14" s="310" t="n"/>
-      <c r="AQ14" s="308" t="n"/>
-      <c r="AR14" s="309" t="n"/>
-      <c r="AS14" s="309" t="n"/>
-      <c r="AT14" s="309" t="n"/>
-      <c r="AU14" s="310" t="n"/>
-      <c r="AV14" s="308" t="n"/>
-      <c r="AW14" s="309" t="n"/>
-      <c r="AX14" s="309" t="n"/>
-      <c r="AY14" s="309" t="n"/>
-      <c r="AZ14" s="309" t="n"/>
-      <c r="BA14" s="309" t="n"/>
-      <c r="BB14" s="309" t="n"/>
-      <c r="BC14" s="309" t="n"/>
-      <c r="BD14" s="312" t="n"/>
+      <c r="A14" s="422" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="29" t="n"/>
+      <c r="I14" s="41" t="n"/>
+      <c r="J14" s="35" t="n"/>
+      <c r="K14" s="35" t="n"/>
+      <c r="L14" s="35" t="n"/>
+      <c r="M14" s="36" t="n"/>
+      <c r="N14" s="41" t="n"/>
+      <c r="O14" s="35" t="n"/>
+      <c r="P14" s="35" t="n"/>
+      <c r="Q14" s="35" t="n"/>
+      <c r="R14" s="35" t="n"/>
+      <c r="S14" s="35" t="n"/>
+      <c r="T14" s="35" t="n"/>
+      <c r="U14" s="35" t="n"/>
+      <c r="V14" s="35" t="n"/>
+      <c r="W14" s="35" t="n"/>
+      <c r="X14" s="36" t="n"/>
+      <c r="Y14" s="41" t="n"/>
+      <c r="Z14" s="35" t="n"/>
+      <c r="AA14" s="35" t="n"/>
+      <c r="AB14" s="35" t="n"/>
+      <c r="AC14" s="36" t="n"/>
+      <c r="AD14" s="41" t="n"/>
+      <c r="AE14" s="35" t="n"/>
+      <c r="AF14" s="35" t="n"/>
+      <c r="AG14" s="35" t="n"/>
+      <c r="AH14" s="35" t="n"/>
+      <c r="AI14" s="35" t="n"/>
+      <c r="AJ14" s="36" t="n"/>
+      <c r="AK14" s="42" t="n"/>
+      <c r="AL14" s="35" t="n"/>
+      <c r="AM14" s="35" t="n"/>
+      <c r="AN14" s="35" t="n"/>
+      <c r="AO14" s="35" t="n"/>
+      <c r="AP14" s="36" t="n"/>
+      <c r="AQ14" s="41" t="n"/>
+      <c r="AR14" s="35" t="n"/>
+      <c r="AS14" s="35" t="n"/>
+      <c r="AT14" s="35" t="n"/>
+      <c r="AU14" s="36" t="n"/>
+      <c r="AV14" s="395" t="n"/>
+      <c r="AW14" s="35" t="n"/>
+      <c r="AX14" s="35" t="n"/>
+      <c r="AY14" s="35" t="n"/>
+      <c r="AZ14" s="35" t="n"/>
+      <c r="BA14" s="35" t="n"/>
+      <c r="BB14" s="35" t="n"/>
+      <c r="BC14" s="35" t="n"/>
+      <c r="BD14" s="396" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="338" t="n"/>
-      <c r="B15" s="306" t="n"/>
-      <c r="C15" s="306" t="n"/>
-      <c r="D15" s="306" t="n"/>
-      <c r="E15" s="306" t="n"/>
-      <c r="F15" s="306" t="n"/>
-      <c r="G15" s="306" t="n"/>
-      <c r="H15" s="307" t="n"/>
-      <c r="I15" s="332" t="n"/>
-      <c r="J15" s="309" t="n"/>
-      <c r="K15" s="309" t="n"/>
-      <c r="L15" s="309" t="n"/>
-      <c r="M15" s="310" t="n"/>
-      <c r="N15" s="332" t="n"/>
-      <c r="O15" s="309" t="n"/>
-      <c r="P15" s="309" t="n"/>
-      <c r="Q15" s="309" t="n"/>
-      <c r="R15" s="309" t="n"/>
-      <c r="S15" s="309" t="n"/>
-      <c r="T15" s="309" t="n"/>
-      <c r="U15" s="309" t="n"/>
-      <c r="V15" s="309" t="n"/>
-      <c r="W15" s="309" t="n"/>
-      <c r="X15" s="310" t="n"/>
-      <c r="Y15" s="332" t="n"/>
-      <c r="Z15" s="309" t="n"/>
-      <c r="AA15" s="309" t="n"/>
-      <c r="AB15" s="309" t="n"/>
-      <c r="AC15" s="310" t="n"/>
-      <c r="AD15" s="332" t="n"/>
-      <c r="AE15" s="309" t="n"/>
-      <c r="AF15" s="309" t="n"/>
-      <c r="AG15" s="309" t="n"/>
-      <c r="AH15" s="309" t="n"/>
-      <c r="AI15" s="309" t="n"/>
-      <c r="AJ15" s="310" t="n"/>
-      <c r="AK15" s="333" t="n"/>
-      <c r="AL15" s="309" t="n"/>
-      <c r="AM15" s="309" t="n"/>
-      <c r="AN15" s="309" t="n"/>
-      <c r="AO15" s="309" t="n"/>
-      <c r="AP15" s="310" t="n"/>
-      <c r="AQ15" s="332" t="n"/>
-      <c r="AR15" s="309" t="n"/>
-      <c r="AS15" s="309" t="n"/>
-      <c r="AT15" s="309" t="n"/>
-      <c r="AU15" s="310" t="n"/>
-      <c r="AV15" s="332" t="n"/>
-      <c r="AW15" s="309" t="n"/>
-      <c r="AX15" s="309" t="n"/>
-      <c r="AY15" s="309" t="n"/>
-      <c r="AZ15" s="309" t="n"/>
-      <c r="BA15" s="309" t="n"/>
-      <c r="BB15" s="309" t="n"/>
-      <c r="BC15" s="309" t="n"/>
-      <c r="BD15" s="312" t="n"/>
+      <c r="A15" s="422" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="29" t="n"/>
+      <c r="I15" s="43" t="n"/>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
+      <c r="L15" s="35" t="n"/>
+      <c r="M15" s="36" t="n"/>
+      <c r="N15" s="43" t="n"/>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+      <c r="R15" s="35" t="n"/>
+      <c r="S15" s="35" t="n"/>
+      <c r="T15" s="35" t="n"/>
+      <c r="U15" s="35" t="n"/>
+      <c r="V15" s="35" t="n"/>
+      <c r="W15" s="35" t="n"/>
+      <c r="X15" s="36" t="n"/>
+      <c r="Y15" s="43" t="n"/>
+      <c r="Z15" s="35" t="n"/>
+      <c r="AA15" s="35" t="n"/>
+      <c r="AB15" s="35" t="n"/>
+      <c r="AC15" s="36" t="n"/>
+      <c r="AD15" s="43" t="n"/>
+      <c r="AE15" s="35" t="n"/>
+      <c r="AF15" s="35" t="n"/>
+      <c r="AG15" s="35" t="n"/>
+      <c r="AH15" s="35" t="n"/>
+      <c r="AI15" s="35" t="n"/>
+      <c r="AJ15" s="36" t="n"/>
+      <c r="AK15" s="42" t="n"/>
+      <c r="AL15" s="35" t="n"/>
+      <c r="AM15" s="35" t="n"/>
+      <c r="AN15" s="35" t="n"/>
+      <c r="AO15" s="35" t="n"/>
+      <c r="AP15" s="36" t="n"/>
+      <c r="AQ15" s="43" t="n"/>
+      <c r="AR15" s="35" t="n"/>
+      <c r="AS15" s="35" t="n"/>
+      <c r="AT15" s="35" t="n"/>
+      <c r="AU15" s="36" t="n"/>
+      <c r="AV15" s="416" t="n"/>
+      <c r="AW15" s="35" t="n"/>
+      <c r="AX15" s="35" t="n"/>
+      <c r="AY15" s="35" t="n"/>
+      <c r="AZ15" s="35" t="n"/>
+      <c r="BA15" s="35" t="n"/>
+      <c r="BB15" s="35" t="n"/>
+      <c r="BC15" s="35" t="n"/>
+      <c r="BD15" s="396" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="338" t="n"/>
-      <c r="B16" s="306" t="n"/>
-      <c r="C16" s="306" t="n"/>
-      <c r="D16" s="306" t="n"/>
-      <c r="E16" s="306" t="n"/>
-      <c r="F16" s="306" t="n"/>
-      <c r="G16" s="306" t="n"/>
-      <c r="H16" s="307" t="n"/>
-      <c r="I16" s="308" t="n"/>
-      <c r="J16" s="309" t="n"/>
-      <c r="K16" s="309" t="n"/>
-      <c r="L16" s="309" t="n"/>
-      <c r="M16" s="310" t="n"/>
-      <c r="N16" s="308" t="n"/>
-      <c r="O16" s="309" t="n"/>
-      <c r="P16" s="309" t="n"/>
-      <c r="Q16" s="309" t="n"/>
-      <c r="R16" s="309" t="n"/>
-      <c r="S16" s="309" t="n"/>
-      <c r="T16" s="309" t="n"/>
-      <c r="U16" s="309" t="n"/>
-      <c r="V16" s="309" t="n"/>
-      <c r="W16" s="309" t="n"/>
-      <c r="X16" s="310" t="n"/>
-      <c r="Y16" s="308" t="n"/>
-      <c r="Z16" s="309" t="n"/>
-      <c r="AA16" s="309" t="n"/>
-      <c r="AB16" s="309" t="n"/>
-      <c r="AC16" s="310" t="n"/>
-      <c r="AD16" s="308" t="n"/>
-      <c r="AE16" s="309" t="n"/>
-      <c r="AF16" s="309" t="n"/>
-      <c r="AG16" s="309" t="n"/>
-      <c r="AH16" s="309" t="n"/>
-      <c r="AI16" s="309" t="n"/>
-      <c r="AJ16" s="310" t="n"/>
-      <c r="AK16" s="333" t="n"/>
-      <c r="AL16" s="309" t="n"/>
-      <c r="AM16" s="309" t="n"/>
-      <c r="AN16" s="309" t="n"/>
-      <c r="AO16" s="309" t="n"/>
-      <c r="AP16" s="310" t="n"/>
-      <c r="AQ16" s="308" t="n"/>
-      <c r="AR16" s="309" t="n"/>
-      <c r="AS16" s="309" t="n"/>
-      <c r="AT16" s="309" t="n"/>
-      <c r="AU16" s="310" t="n"/>
-      <c r="AV16" s="308" t="n"/>
-      <c r="AW16" s="309" t="n"/>
-      <c r="AX16" s="309" t="n"/>
-      <c r="AY16" s="309" t="n"/>
-      <c r="AZ16" s="309" t="n"/>
-      <c r="BA16" s="309" t="n"/>
-      <c r="BB16" s="309" t="n"/>
-      <c r="BC16" s="309" t="n"/>
-      <c r="BD16" s="312" t="n"/>
+      <c r="A16" s="422" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="29" t="n"/>
+      <c r="I16" s="41" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="36" t="n"/>
+      <c r="N16" s="41" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+      <c r="R16" s="35" t="n"/>
+      <c r="S16" s="35" t="n"/>
+      <c r="T16" s="35" t="n"/>
+      <c r="U16" s="35" t="n"/>
+      <c r="V16" s="35" t="n"/>
+      <c r="W16" s="35" t="n"/>
+      <c r="X16" s="36" t="n"/>
+      <c r="Y16" s="41" t="n"/>
+      <c r="Z16" s="35" t="n"/>
+      <c r="AA16" s="35" t="n"/>
+      <c r="AB16" s="35" t="n"/>
+      <c r="AC16" s="36" t="n"/>
+      <c r="AD16" s="41" t="n"/>
+      <c r="AE16" s="35" t="n"/>
+      <c r="AF16" s="35" t="n"/>
+      <c r="AG16" s="35" t="n"/>
+      <c r="AH16" s="35" t="n"/>
+      <c r="AI16" s="35" t="n"/>
+      <c r="AJ16" s="36" t="n"/>
+      <c r="AK16" s="42" t="n"/>
+      <c r="AL16" s="35" t="n"/>
+      <c r="AM16" s="35" t="n"/>
+      <c r="AN16" s="35" t="n"/>
+      <c r="AO16" s="35" t="n"/>
+      <c r="AP16" s="36" t="n"/>
+      <c r="AQ16" s="41" t="n"/>
+      <c r="AR16" s="35" t="n"/>
+      <c r="AS16" s="35" t="n"/>
+      <c r="AT16" s="35" t="n"/>
+      <c r="AU16" s="36" t="n"/>
+      <c r="AV16" s="395" t="n"/>
+      <c r="AW16" s="35" t="n"/>
+      <c r="AX16" s="35" t="n"/>
+      <c r="AY16" s="35" t="n"/>
+      <c r="AZ16" s="35" t="n"/>
+      <c r="BA16" s="35" t="n"/>
+      <c r="BB16" s="35" t="n"/>
+      <c r="BC16" s="35" t="n"/>
+      <c r="BD16" s="396" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="339" t="n"/>
-      <c r="B17" s="272" t="n"/>
-      <c r="C17" s="272" t="n"/>
-      <c r="D17" s="272" t="n"/>
-      <c r="E17" s="272" t="n"/>
-      <c r="F17" s="272" t="n"/>
-      <c r="G17" s="272" t="n"/>
-      <c r="H17" s="292" t="n"/>
-      <c r="I17" s="335" t="n"/>
-      <c r="J17" s="294" t="n"/>
-      <c r="K17" s="294" t="n"/>
-      <c r="L17" s="294" t="n"/>
-      <c r="M17" s="295" t="n"/>
-      <c r="N17" s="335" t="n"/>
-      <c r="O17" s="294" t="n"/>
-      <c r="P17" s="294" t="n"/>
-      <c r="Q17" s="294" t="n"/>
-      <c r="R17" s="294" t="n"/>
-      <c r="S17" s="294" t="n"/>
-      <c r="T17" s="294" t="n"/>
-      <c r="U17" s="294" t="n"/>
-      <c r="V17" s="294" t="n"/>
-      <c r="W17" s="294" t="n"/>
-      <c r="X17" s="295" t="n"/>
-      <c r="Y17" s="335" t="n"/>
-      <c r="Z17" s="294" t="n"/>
-      <c r="AA17" s="294" t="n"/>
-      <c r="AB17" s="294" t="n"/>
-      <c r="AC17" s="295" t="n"/>
-      <c r="AD17" s="335" t="n"/>
-      <c r="AE17" s="294" t="n"/>
-      <c r="AF17" s="294" t="n"/>
-      <c r="AG17" s="294" t="n"/>
-      <c r="AH17" s="294" t="n"/>
-      <c r="AI17" s="294" t="n"/>
-      <c r="AJ17" s="295" t="n"/>
-      <c r="AK17" s="336" t="n"/>
-      <c r="AL17" s="294" t="n"/>
-      <c r="AM17" s="294" t="n"/>
-      <c r="AN17" s="294" t="n"/>
-      <c r="AO17" s="294" t="n"/>
-      <c r="AP17" s="295" t="n"/>
-      <c r="AQ17" s="335" t="n"/>
-      <c r="AR17" s="294" t="n"/>
-      <c r="AS17" s="294" t="n"/>
-      <c r="AT17" s="294" t="n"/>
-      <c r="AU17" s="295" t="n"/>
-      <c r="AV17" s="335" t="n"/>
-      <c r="AW17" s="294" t="n"/>
-      <c r="AX17" s="294" t="n"/>
-      <c r="AY17" s="294" t="n"/>
-      <c r="AZ17" s="294" t="n"/>
-      <c r="BA17" s="294" t="n"/>
-      <c r="BB17" s="294" t="n"/>
-      <c r="BC17" s="294" t="n"/>
-      <c r="BD17" s="297" t="n"/>
+      <c r="A17" s="423" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="52" t="n"/>
+      <c r="I17" s="418" t="n"/>
+      <c r="J17" s="380" t="n"/>
+      <c r="K17" s="380" t="n"/>
+      <c r="L17" s="380" t="n"/>
+      <c r="M17" s="381" t="n"/>
+      <c r="N17" s="418" t="n"/>
+      <c r="O17" s="380" t="n"/>
+      <c r="P17" s="380" t="n"/>
+      <c r="Q17" s="380" t="n"/>
+      <c r="R17" s="380" t="n"/>
+      <c r="S17" s="380" t="n"/>
+      <c r="T17" s="380" t="n"/>
+      <c r="U17" s="380" t="n"/>
+      <c r="V17" s="380" t="n"/>
+      <c r="W17" s="380" t="n"/>
+      <c r="X17" s="381" t="n"/>
+      <c r="Y17" s="418" t="n"/>
+      <c r="Z17" s="380" t="n"/>
+      <c r="AA17" s="380" t="n"/>
+      <c r="AB17" s="380" t="n"/>
+      <c r="AC17" s="381" t="n"/>
+      <c r="AD17" s="418" t="n"/>
+      <c r="AE17" s="380" t="n"/>
+      <c r="AF17" s="380" t="n"/>
+      <c r="AG17" s="380" t="n"/>
+      <c r="AH17" s="380" t="n"/>
+      <c r="AI17" s="380" t="n"/>
+      <c r="AJ17" s="381" t="n"/>
+      <c r="AK17" s="419" t="n"/>
+      <c r="AL17" s="380" t="n"/>
+      <c r="AM17" s="380" t="n"/>
+      <c r="AN17" s="380" t="n"/>
+      <c r="AO17" s="380" t="n"/>
+      <c r="AP17" s="381" t="n"/>
+      <c r="AQ17" s="418" t="n"/>
+      <c r="AR17" s="380" t="n"/>
+      <c r="AS17" s="380" t="n"/>
+      <c r="AT17" s="380" t="n"/>
+      <c r="AU17" s="381" t="n"/>
+      <c r="AV17" s="420" t="n"/>
+      <c r="AW17" s="380" t="n"/>
+      <c r="AX17" s="380" t="n"/>
+      <c r="AY17" s="380" t="n"/>
+      <c r="AZ17" s="380" t="n"/>
+      <c r="BA17" s="380" t="n"/>
+      <c r="BB17" s="380" t="n"/>
+      <c r="BC17" s="380" t="n"/>
+      <c r="BD17" s="384" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="280" t="inlineStr">
+      <c r="A18" s="373" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B18" s="281" t="n"/>
-      <c r="C18" s="281" t="n"/>
-      <c r="D18" s="281" t="n"/>
-      <c r="E18" s="281" t="n"/>
-      <c r="F18" s="281" t="n"/>
-      <c r="G18" s="281" t="n"/>
-      <c r="H18" s="281" t="n"/>
-      <c r="I18" s="281" t="n"/>
-      <c r="J18" s="281" t="n"/>
-      <c r="K18" s="281" t="n"/>
-      <c r="L18" s="281" t="n"/>
-      <c r="M18" s="281" t="n"/>
-      <c r="N18" s="281" t="n"/>
-      <c r="O18" s="281" t="n"/>
-      <c r="P18" s="281" t="n"/>
-      <c r="Q18" s="281" t="n"/>
-      <c r="R18" s="281" t="n"/>
-      <c r="S18" s="281" t="n"/>
-      <c r="T18" s="281" t="n"/>
-      <c r="U18" s="281" t="n"/>
-      <c r="V18" s="281" t="n"/>
-      <c r="W18" s="281" t="n"/>
-      <c r="X18" s="281" t="n"/>
-      <c r="Y18" s="281" t="n"/>
-      <c r="Z18" s="281" t="n"/>
-      <c r="AA18" s="281" t="n"/>
-      <c r="AB18" s="281" t="n"/>
-      <c r="AC18" s="281" t="n"/>
-      <c r="AD18" s="281" t="n"/>
-      <c r="AE18" s="281" t="n"/>
-      <c r="AF18" s="281" t="n"/>
-      <c r="AG18" s="281" t="n"/>
-      <c r="AH18" s="281" t="n"/>
-      <c r="AI18" s="281" t="n"/>
-      <c r="AJ18" s="281" t="n"/>
-      <c r="AK18" s="281" t="n"/>
-      <c r="AL18" s="281" t="n"/>
-      <c r="AM18" s="281" t="n"/>
-      <c r="AN18" s="281" t="n"/>
-      <c r="AO18" s="281" t="n"/>
-      <c r="AP18" s="281" t="n"/>
-      <c r="AQ18" s="281" t="n"/>
-      <c r="AR18" s="281" t="n"/>
-      <c r="AS18" s="281" t="n"/>
-      <c r="AT18" s="281" t="n"/>
-      <c r="AU18" s="281" t="n"/>
-      <c r="AV18" s="281" t="n"/>
-      <c r="AW18" s="281" t="n"/>
-      <c r="AX18" s="281" t="n"/>
-      <c r="AY18" s="281" t="n"/>
-      <c r="AZ18" s="281" t="n"/>
-      <c r="BA18" s="281" t="n"/>
-      <c r="BB18" s="281" t="n"/>
-      <c r="BC18" s="281" t="n"/>
-      <c r="BD18" s="282" t="n"/>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="22" t="n"/>
+      <c r="R18" s="22" t="n"/>
+      <c r="S18" s="22" t="n"/>
+      <c r="T18" s="22" t="n"/>
+      <c r="U18" s="22" t="n"/>
+      <c r="V18" s="22" t="n"/>
+      <c r="W18" s="22" t="n"/>
+      <c r="X18" s="22" t="n"/>
+      <c r="Y18" s="22" t="n"/>
+      <c r="Z18" s="22" t="n"/>
+      <c r="AA18" s="22" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+      <c r="AE18" s="22" t="n"/>
+      <c r="AF18" s="22" t="n"/>
+      <c r="AG18" s="22" t="n"/>
+      <c r="AH18" s="22" t="n"/>
+      <c r="AI18" s="22" t="n"/>
+      <c r="AJ18" s="22" t="n"/>
+      <c r="AK18" s="22" t="n"/>
+      <c r="AL18" s="22" t="n"/>
+      <c r="AM18" s="22" t="n"/>
+      <c r="AN18" s="22" t="n"/>
+      <c r="AO18" s="22" t="n"/>
+      <c r="AP18" s="22" t="n"/>
+      <c r="AQ18" s="22" t="n"/>
+      <c r="AR18" s="22" t="n"/>
+      <c r="AS18" s="22" t="n"/>
+      <c r="AT18" s="22" t="n"/>
+      <c r="AU18" s="22" t="n"/>
+      <c r="AV18" s="22" t="n"/>
+      <c r="AW18" s="22" t="n"/>
+      <c r="AX18" s="22" t="n"/>
+      <c r="AY18" s="22" t="n"/>
+      <c r="AZ18" s="22" t="n"/>
+      <c r="BA18" s="22" t="n"/>
+      <c r="BB18" s="22" t="n"/>
+      <c r="BC18" s="22" t="n"/>
+      <c r="BD18" s="23" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -7290,528 +7331,356 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="255" t="n"/>
-      <c r="B1" s="256" t="n"/>
-      <c r="C1" s="256" t="n"/>
-      <c r="D1" s="256" t="n"/>
-      <c r="E1" s="256" t="n"/>
-      <c r="F1" s="256" t="n"/>
-      <c r="G1" s="256" t="n"/>
-      <c r="H1" s="256" t="n"/>
-      <c r="I1" s="256" t="n"/>
-      <c r="J1" s="256" t="n"/>
-      <c r="K1" s="257" t="n"/>
+      <c r="A1" s="359" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="n"/>
       <c r="L1" s="340" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW — CONTROLLED LOOKUP LISTS</t>
         </is>
       </c>
-      <c r="M1" s="256" t="n"/>
-      <c r="N1" s="256" t="n"/>
-      <c r="O1" s="256" t="n"/>
-      <c r="P1" s="256" t="n"/>
-      <c r="Q1" s="256" t="n"/>
-      <c r="R1" s="256" t="n"/>
-      <c r="S1" s="256" t="n"/>
-      <c r="T1" s="256" t="n"/>
-      <c r="U1" s="256" t="n"/>
-      <c r="V1" s="256" t="n"/>
-      <c r="W1" s="256" t="n"/>
-      <c r="X1" s="256" t="n"/>
-      <c r="Y1" s="256" t="n"/>
-      <c r="Z1" s="256" t="n"/>
-      <c r="AA1" s="256" t="n"/>
-      <c r="AB1" s="256" t="n"/>
-      <c r="AC1" s="256" t="n"/>
-      <c r="AD1" s="256" t="n"/>
-      <c r="AE1" s="256" t="n"/>
-      <c r="AF1" s="256" t="n"/>
-      <c r="AG1" s="256" t="n"/>
-      <c r="AH1" s="256" t="n"/>
-      <c r="AI1" s="256" t="n"/>
-      <c r="AJ1" s="256" t="n"/>
-      <c r="AK1" s="256" t="n"/>
-      <c r="AL1" s="256" t="n"/>
-      <c r="AM1" s="256" t="n"/>
-      <c r="AN1" s="256" t="n"/>
-      <c r="AO1" s="256" t="n"/>
-      <c r="AP1" s="256" t="n"/>
-      <c r="AQ1" s="341" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="424" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="256" t="n"/>
-      <c r="AS1" s="256" t="n"/>
-      <c r="AT1" s="256" t="n"/>
-      <c r="AU1" s="256" t="n"/>
-      <c r="AV1" s="260" t="n"/>
-      <c r="AW1" s="342" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="361" t="n"/>
+      <c r="AW1" s="425" t="inlineStr">
         <is>
           <t>FRM-111</t>
         </is>
       </c>
-      <c r="AX1" s="256" t="n"/>
-      <c r="AY1" s="256" t="n"/>
-      <c r="AZ1" s="256" t="n"/>
-      <c r="BA1" s="256" t="n"/>
-      <c r="BB1" s="256" t="n"/>
-      <c r="BC1" s="256" t="n"/>
-      <c r="BD1" s="257" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="262" t="n"/>
-      <c r="B2" s="263" t="n"/>
-      <c r="C2" s="263" t="n"/>
-      <c r="D2" s="263" t="n"/>
-      <c r="E2" s="263" t="n"/>
-      <c r="F2" s="263" t="n"/>
-      <c r="G2" s="263" t="n"/>
-      <c r="H2" s="263" t="n"/>
-      <c r="I2" s="263" t="n"/>
-      <c r="J2" s="263" t="n"/>
-      <c r="K2" s="264" t="n"/>
-      <c r="L2" s="262" t="n"/>
-      <c r="M2" s="263" t="n"/>
-      <c r="N2" s="263" t="n"/>
-      <c r="O2" s="263" t="n"/>
-      <c r="P2" s="263" t="n"/>
-      <c r="Q2" s="263" t="n"/>
-      <c r="R2" s="263" t="n"/>
-      <c r="S2" s="263" t="n"/>
-      <c r="T2" s="263" t="n"/>
-      <c r="U2" s="263" t="n"/>
-      <c r="V2" s="263" t="n"/>
-      <c r="W2" s="263" t="n"/>
-      <c r="X2" s="263" t="n"/>
-      <c r="Y2" s="263" t="n"/>
-      <c r="Z2" s="263" t="n"/>
-      <c r="AA2" s="263" t="n"/>
-      <c r="AB2" s="263" t="n"/>
-      <c r="AC2" s="263" t="n"/>
-      <c r="AD2" s="263" t="n"/>
-      <c r="AE2" s="263" t="n"/>
-      <c r="AF2" s="263" t="n"/>
-      <c r="AG2" s="263" t="n"/>
-      <c r="AH2" s="263" t="n"/>
-      <c r="AI2" s="263" t="n"/>
-      <c r="AJ2" s="263" t="n"/>
-      <c r="AK2" s="263" t="n"/>
-      <c r="AL2" s="263" t="n"/>
-      <c r="AM2" s="263" t="n"/>
-      <c r="AN2" s="263" t="n"/>
-      <c r="AO2" s="263" t="n"/>
-      <c r="AP2" s="263" t="n"/>
-      <c r="AQ2" s="343" t="inlineStr">
+      <c r="A2" s="10" t="n"/>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="AQ2" s="426" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="266" t="n"/>
-      <c r="AS2" s="266" t="n"/>
-      <c r="AT2" s="266" t="n"/>
-      <c r="AU2" s="266" t="n"/>
-      <c r="AV2" s="267" t="n"/>
-      <c r="AW2" s="344" t="inlineStr">
+      <c r="AR2" s="364" t="n"/>
+      <c r="AS2" s="364" t="n"/>
+      <c r="AT2" s="364" t="n"/>
+      <c r="AU2" s="364" t="n"/>
+      <c r="AV2" s="365" t="n"/>
+      <c r="AW2" s="427" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="266" t="n"/>
-      <c r="AY2" s="266" t="n"/>
-      <c r="AZ2" s="266" t="n"/>
-      <c r="BA2" s="266" t="n"/>
-      <c r="BB2" s="266" t="n"/>
-      <c r="BC2" s="266" t="n"/>
-      <c r="BD2" s="269" t="n"/>
+      <c r="AX2" s="364" t="n"/>
+      <c r="AY2" s="364" t="n"/>
+      <c r="AZ2" s="364" t="n"/>
+      <c r="BA2" s="364" t="n"/>
+      <c r="BB2" s="364" t="n"/>
+      <c r="BC2" s="364" t="n"/>
+      <c r="BD2" s="367" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="262" t="n"/>
-      <c r="B3" s="263" t="n"/>
-      <c r="C3" s="263" t="n"/>
-      <c r="D3" s="263" t="n"/>
-      <c r="E3" s="263" t="n"/>
-      <c r="F3" s="263" t="n"/>
-      <c r="G3" s="263" t="n"/>
-      <c r="H3" s="263" t="n"/>
-      <c r="I3" s="263" t="n"/>
-      <c r="J3" s="263" t="n"/>
-      <c r="K3" s="264" t="n"/>
-      <c r="L3" s="262" t="n"/>
-      <c r="M3" s="263" t="n"/>
-      <c r="N3" s="263" t="n"/>
-      <c r="O3" s="263" t="n"/>
-      <c r="P3" s="263" t="n"/>
-      <c r="Q3" s="263" t="n"/>
-      <c r="R3" s="263" t="n"/>
-      <c r="S3" s="263" t="n"/>
-      <c r="T3" s="263" t="n"/>
-      <c r="U3" s="263" t="n"/>
-      <c r="V3" s="263" t="n"/>
-      <c r="W3" s="263" t="n"/>
-      <c r="X3" s="263" t="n"/>
-      <c r="Y3" s="263" t="n"/>
-      <c r="Z3" s="263" t="n"/>
-      <c r="AA3" s="263" t="n"/>
-      <c r="AB3" s="263" t="n"/>
-      <c r="AC3" s="263" t="n"/>
-      <c r="AD3" s="263" t="n"/>
-      <c r="AE3" s="263" t="n"/>
-      <c r="AF3" s="263" t="n"/>
-      <c r="AG3" s="263" t="n"/>
-      <c r="AH3" s="263" t="n"/>
-      <c r="AI3" s="263" t="n"/>
-      <c r="AJ3" s="263" t="n"/>
-      <c r="AK3" s="263" t="n"/>
-      <c r="AL3" s="263" t="n"/>
-      <c r="AM3" s="263" t="n"/>
-      <c r="AN3" s="263" t="n"/>
-      <c r="AO3" s="263" t="n"/>
-      <c r="AP3" s="263" t="n"/>
-      <c r="AQ3" s="343" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="AQ3" s="426" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="266" t="n"/>
-      <c r="AS3" s="266" t="n"/>
-      <c r="AT3" s="266" t="n"/>
-      <c r="AU3" s="266" t="n"/>
-      <c r="AV3" s="267" t="n"/>
-      <c r="AW3" s="344" t="inlineStr">
+      <c r="AR3" s="364" t="n"/>
+      <c r="AS3" s="364" t="n"/>
+      <c r="AT3" s="364" t="n"/>
+      <c r="AU3" s="364" t="n"/>
+      <c r="AV3" s="365" t="n"/>
+      <c r="AW3" s="427" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="266" t="n"/>
-      <c r="AY3" s="266" t="n"/>
-      <c r="AZ3" s="266" t="n"/>
-      <c r="BA3" s="266" t="n"/>
-      <c r="BB3" s="266" t="n"/>
-      <c r="BC3" s="266" t="n"/>
-      <c r="BD3" s="269" t="n"/>
+      <c r="AX3" s="364" t="n"/>
+      <c r="AY3" s="364" t="n"/>
+      <c r="AZ3" s="364" t="n"/>
+      <c r="BA3" s="364" t="n"/>
+      <c r="BB3" s="364" t="n"/>
+      <c r="BC3" s="364" t="n"/>
+      <c r="BD3" s="367" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="262" t="n"/>
-      <c r="B4" s="263" t="n"/>
-      <c r="C4" s="263" t="n"/>
-      <c r="D4" s="263" t="n"/>
-      <c r="E4" s="263" t="n"/>
-      <c r="F4" s="263" t="n"/>
-      <c r="G4" s="263" t="n"/>
-      <c r="H4" s="263" t="n"/>
-      <c r="I4" s="263" t="n"/>
-      <c r="J4" s="263" t="n"/>
-      <c r="K4" s="264" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="K4" s="11" t="n"/>
       <c r="L4" s="49" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="263" t="n"/>
-      <c r="N4" s="263" t="n"/>
-      <c r="O4" s="263" t="n"/>
-      <c r="P4" s="263" t="n"/>
-      <c r="Q4" s="263" t="n"/>
-      <c r="R4" s="263" t="n"/>
-      <c r="S4" s="263" t="n"/>
-      <c r="T4" s="263" t="n"/>
-      <c r="U4" s="263" t="n"/>
-      <c r="V4" s="263" t="n"/>
-      <c r="W4" s="263" t="n"/>
-      <c r="X4" s="263" t="n"/>
-      <c r="Y4" s="263" t="n"/>
-      <c r="Z4" s="263" t="n"/>
-      <c r="AA4" s="263" t="n"/>
-      <c r="AB4" s="263" t="n"/>
-      <c r="AC4" s="263" t="n"/>
-      <c r="AD4" s="263" t="n"/>
-      <c r="AE4" s="263" t="n"/>
-      <c r="AF4" s="263" t="n"/>
-      <c r="AG4" s="263" t="n"/>
-      <c r="AH4" s="263" t="n"/>
-      <c r="AI4" s="263" t="n"/>
-      <c r="AJ4" s="263" t="n"/>
-      <c r="AK4" s="263" t="n"/>
-      <c r="AL4" s="263" t="n"/>
-      <c r="AM4" s="263" t="n"/>
-      <c r="AN4" s="263" t="n"/>
-      <c r="AO4" s="263" t="n"/>
-      <c r="AP4" s="263" t="n"/>
-      <c r="AQ4" s="343" t="inlineStr">
+      <c r="AQ4" s="426" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="266" t="n"/>
-      <c r="AS4" s="266" t="n"/>
-      <c r="AT4" s="266" t="n"/>
-      <c r="AU4" s="266" t="n"/>
-      <c r="AV4" s="267" t="n"/>
-      <c r="AW4" s="344" t="inlineStr">
+      <c r="AR4" s="364" t="n"/>
+      <c r="AS4" s="364" t="n"/>
+      <c r="AT4" s="364" t="n"/>
+      <c r="AU4" s="364" t="n"/>
+      <c r="AV4" s="365" t="n"/>
+      <c r="AW4" s="427" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AX4" s="266" t="n"/>
-      <c r="AY4" s="266" t="n"/>
-      <c r="AZ4" s="266" t="n"/>
-      <c r="BA4" s="266" t="n"/>
-      <c r="BB4" s="266" t="n"/>
-      <c r="BC4" s="266" t="n"/>
-      <c r="BD4" s="269" t="n"/>
+      <c r="AX4" s="364" t="n"/>
+      <c r="AY4" s="364" t="n"/>
+      <c r="AZ4" s="364" t="n"/>
+      <c r="BA4" s="364" t="n"/>
+      <c r="BB4" s="364" t="n"/>
+      <c r="BC4" s="364" t="n"/>
+      <c r="BD4" s="367" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="271" t="n"/>
-      <c r="B5" s="272" t="n"/>
-      <c r="C5" s="272" t="n"/>
-      <c r="D5" s="272" t="n"/>
-      <c r="E5" s="272" t="n"/>
-      <c r="F5" s="272" t="n"/>
-      <c r="G5" s="272" t="n"/>
-      <c r="H5" s="272" t="n"/>
-      <c r="I5" s="272" t="n"/>
-      <c r="J5" s="272" t="n"/>
-      <c r="K5" s="273" t="n"/>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="18" t="n"/>
       <c r="L5" s="50" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="272" t="n"/>
-      <c r="N5" s="272" t="n"/>
-      <c r="O5" s="272" t="n"/>
-      <c r="P5" s="272" t="n"/>
-      <c r="Q5" s="272" t="n"/>
-      <c r="R5" s="272" t="n"/>
-      <c r="S5" s="272" t="n"/>
-      <c r="T5" s="272" t="n"/>
-      <c r="U5" s="272" t="n"/>
-      <c r="V5" s="272" t="n"/>
-      <c r="W5" s="272" t="n"/>
-      <c r="X5" s="272" t="n"/>
-      <c r="Y5" s="272" t="n"/>
-      <c r="Z5" s="272" t="n"/>
-      <c r="AA5" s="272" t="n"/>
-      <c r="AB5" s="272" t="n"/>
-      <c r="AC5" s="272" t="n"/>
-      <c r="AD5" s="272" t="n"/>
-      <c r="AE5" s="272" t="n"/>
-      <c r="AF5" s="272" t="n"/>
-      <c r="AG5" s="272" t="n"/>
-      <c r="AH5" s="272" t="n"/>
-      <c r="AI5" s="272" t="n"/>
-      <c r="AJ5" s="272" t="n"/>
-      <c r="AK5" s="272" t="n"/>
-      <c r="AL5" s="272" t="n"/>
-      <c r="AM5" s="272" t="n"/>
-      <c r="AN5" s="272" t="n"/>
-      <c r="AO5" s="272" t="n"/>
-      <c r="AP5" s="272" t="n"/>
-      <c r="AQ5" s="345" t="inlineStr">
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="17" t="n"/>
+      <c r="P5" s="17" t="n"/>
+      <c r="Q5" s="17" t="n"/>
+      <c r="R5" s="17" t="n"/>
+      <c r="S5" s="17" t="n"/>
+      <c r="T5" s="17" t="n"/>
+      <c r="U5" s="17" t="n"/>
+      <c r="V5" s="17" t="n"/>
+      <c r="W5" s="17" t="n"/>
+      <c r="X5" s="17" t="n"/>
+      <c r="Y5" s="17" t="n"/>
+      <c r="Z5" s="17" t="n"/>
+      <c r="AA5" s="17" t="n"/>
+      <c r="AB5" s="17" t="n"/>
+      <c r="AC5" s="17" t="n"/>
+      <c r="AD5" s="17" t="n"/>
+      <c r="AE5" s="17" t="n"/>
+      <c r="AF5" s="17" t="n"/>
+      <c r="AG5" s="17" t="n"/>
+      <c r="AH5" s="17" t="n"/>
+      <c r="AI5" s="17" t="n"/>
+      <c r="AJ5" s="17" t="n"/>
+      <c r="AK5" s="17" t="n"/>
+      <c r="AL5" s="17" t="n"/>
+      <c r="AM5" s="17" t="n"/>
+      <c r="AN5" s="17" t="n"/>
+      <c r="AO5" s="17" t="n"/>
+      <c r="AP5" s="17" t="n"/>
+      <c r="AQ5" s="428" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="275" t="n"/>
-      <c r="AS5" s="275" t="n"/>
-      <c r="AT5" s="275" t="n"/>
-      <c r="AU5" s="275" t="n"/>
-      <c r="AV5" s="276" t="n"/>
-      <c r="AW5" s="346" t="inlineStr">
+      <c r="AR5" s="369" t="n"/>
+      <c r="AS5" s="369" t="n"/>
+      <c r="AT5" s="369" t="n"/>
+      <c r="AU5" s="369" t="n"/>
+      <c r="AV5" s="370" t="n"/>
+      <c r="AW5" s="429" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="275" t="n"/>
-      <c r="AY5" s="275" t="n"/>
-      <c r="AZ5" s="275" t="n"/>
-      <c r="BA5" s="275" t="n"/>
-      <c r="BB5" s="275" t="n"/>
-      <c r="BC5" s="275" t="n"/>
-      <c r="BD5" s="278" t="n"/>
+      <c r="AX5" s="369" t="n"/>
+      <c r="AY5" s="369" t="n"/>
+      <c r="AZ5" s="369" t="n"/>
+      <c r="BA5" s="369" t="n"/>
+      <c r="BB5" s="369" t="n"/>
+      <c r="BC5" s="369" t="n"/>
+      <c r="BD5" s="372" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
       <c r="A6" s="347" t="n"/>
-      <c r="B6" s="263" t="n"/>
-      <c r="C6" s="263" t="n"/>
-      <c r="D6" s="263" t="n"/>
-      <c r="E6" s="263" t="n"/>
-      <c r="F6" s="263" t="n"/>
-      <c r="G6" s="263" t="n"/>
-      <c r="H6" s="263" t="n"/>
-      <c r="I6" s="263" t="n"/>
-      <c r="J6" s="263" t="n"/>
-      <c r="K6" s="263" t="n"/>
-      <c r="L6" s="263" t="n"/>
-      <c r="M6" s="263" t="n"/>
-      <c r="N6" s="263" t="n"/>
-      <c r="O6" s="263" t="n"/>
-      <c r="P6" s="263" t="n"/>
-      <c r="Q6" s="263" t="n"/>
-      <c r="R6" s="263" t="n"/>
-      <c r="S6" s="263" t="n"/>
-      <c r="T6" s="263" t="n"/>
-      <c r="U6" s="263" t="n"/>
-      <c r="V6" s="263" t="n"/>
-      <c r="W6" s="263" t="n"/>
-      <c r="X6" s="263" t="n"/>
-      <c r="Y6" s="263" t="n"/>
-      <c r="Z6" s="263" t="n"/>
-      <c r="AA6" s="263" t="n"/>
-      <c r="AB6" s="263" t="n"/>
-      <c r="AC6" s="263" t="n"/>
-      <c r="AD6" s="263" t="n"/>
-      <c r="AE6" s="263" t="n"/>
-      <c r="AF6" s="263" t="n"/>
-      <c r="AG6" s="263" t="n"/>
-      <c r="AH6" s="263" t="n"/>
-      <c r="AI6" s="263" t="n"/>
-      <c r="AJ6" s="263" t="n"/>
-      <c r="AK6" s="263" t="n"/>
-      <c r="AL6" s="263" t="n"/>
-      <c r="AM6" s="263" t="n"/>
-      <c r="AN6" s="263" t="n"/>
-      <c r="AO6" s="263" t="n"/>
-      <c r="AP6" s="263" t="n"/>
-      <c r="AQ6" s="263" t="n"/>
-      <c r="AR6" s="263" t="n"/>
-      <c r="AS6" s="263" t="n"/>
-      <c r="AT6" s="263" t="n"/>
-      <c r="AU6" s="263" t="n"/>
-      <c r="AV6" s="263" t="n"/>
-      <c r="AW6" s="263" t="n"/>
-      <c r="AX6" s="263" t="n"/>
-      <c r="AY6" s="263" t="n"/>
-      <c r="AZ6" s="263" t="n"/>
-      <c r="BA6" s="263" t="n"/>
-      <c r="BB6" s="263" t="n"/>
-      <c r="BC6" s="263" t="n"/>
-      <c r="BD6" s="263" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="348" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
         </is>
       </c>
-      <c r="B7" s="281" t="n"/>
-      <c r="C7" s="281" t="n"/>
-      <c r="D7" s="281" t="n"/>
-      <c r="E7" s="281" t="n"/>
-      <c r="F7" s="281" t="n"/>
-      <c r="G7" s="281" t="n"/>
-      <c r="H7" s="281" t="n"/>
-      <c r="I7" s="281" t="n"/>
-      <c r="J7" s="281" t="n"/>
-      <c r="K7" s="281" t="n"/>
-      <c r="L7" s="281" t="n"/>
-      <c r="M7" s="281" t="n"/>
-      <c r="N7" s="281" t="n"/>
-      <c r="O7" s="281" t="n"/>
-      <c r="P7" s="281" t="n"/>
-      <c r="Q7" s="281" t="n"/>
-      <c r="R7" s="281" t="n"/>
-      <c r="S7" s="281" t="n"/>
-      <c r="T7" s="281" t="n"/>
-      <c r="U7" s="281" t="n"/>
-      <c r="V7" s="281" t="n"/>
-      <c r="W7" s="281" t="n"/>
-      <c r="X7" s="281" t="n"/>
-      <c r="Y7" s="281" t="n"/>
-      <c r="Z7" s="281" t="n"/>
-      <c r="AA7" s="281" t="n"/>
-      <c r="AB7" s="281" t="n"/>
-      <c r="AC7" s="281" t="n"/>
-      <c r="AD7" s="281" t="n"/>
-      <c r="AE7" s="281" t="n"/>
-      <c r="AF7" s="281" t="n"/>
-      <c r="AG7" s="281" t="n"/>
-      <c r="AH7" s="281" t="n"/>
-      <c r="AI7" s="281" t="n"/>
-      <c r="AJ7" s="281" t="n"/>
-      <c r="AK7" s="281" t="n"/>
-      <c r="AL7" s="281" t="n"/>
-      <c r="AM7" s="281" t="n"/>
-      <c r="AN7" s="281" t="n"/>
-      <c r="AO7" s="281" t="n"/>
-      <c r="AP7" s="281" t="n"/>
-      <c r="AQ7" s="281" t="n"/>
-      <c r="AR7" s="281" t="n"/>
-      <c r="AS7" s="281" t="n"/>
-      <c r="AT7" s="281" t="n"/>
-      <c r="AU7" s="281" t="n"/>
-      <c r="AV7" s="281" t="n"/>
-      <c r="AW7" s="281" t="n"/>
-      <c r="AX7" s="281" t="n"/>
-      <c r="AY7" s="281" t="n"/>
-      <c r="AZ7" s="281" t="n"/>
-      <c r="BA7" s="281" t="n"/>
-      <c r="BB7" s="281" t="n"/>
-      <c r="BC7" s="281" t="n"/>
-      <c r="BD7" s="282" t="n"/>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="22" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="22" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="22" t="n"/>
+      <c r="AF7" s="22" t="n"/>
+      <c r="AG7" s="22" t="n"/>
+      <c r="AH7" s="22" t="n"/>
+      <c r="AI7" s="22" t="n"/>
+      <c r="AJ7" s="22" t="n"/>
+      <c r="AK7" s="22" t="n"/>
+      <c r="AL7" s="22" t="n"/>
+      <c r="AM7" s="22" t="n"/>
+      <c r="AN7" s="22" t="n"/>
+      <c r="AO7" s="22" t="n"/>
+      <c r="AP7" s="22" t="n"/>
+      <c r="AQ7" s="22" t="n"/>
+      <c r="AR7" s="22" t="n"/>
+      <c r="AS7" s="22" t="n"/>
+      <c r="AT7" s="22" t="n"/>
+      <c r="AU7" s="22" t="n"/>
+      <c r="AV7" s="22" t="n"/>
+      <c r="AW7" s="22" t="n"/>
+      <c r="AX7" s="22" t="n"/>
+      <c r="AY7" s="22" t="n"/>
+      <c r="AZ7" s="22" t="n"/>
+      <c r="BA7" s="22" t="n"/>
+      <c r="BB7" s="22" t="n"/>
+      <c r="BC7" s="22" t="n"/>
+      <c r="BD7" s="23" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="349" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="281" t="n"/>
-      <c r="C8" s="281" t="n"/>
-      <c r="D8" s="281" t="n"/>
-      <c r="E8" s="281" t="n"/>
-      <c r="F8" s="281" t="n"/>
-      <c r="G8" s="281" t="n"/>
-      <c r="H8" s="281" t="n"/>
-      <c r="I8" s="281" t="n"/>
-      <c r="J8" s="281" t="n"/>
-      <c r="K8" s="281" t="n"/>
-      <c r="L8" s="281" t="n"/>
-      <c r="M8" s="281" t="n"/>
-      <c r="N8" s="281" t="n"/>
-      <c r="O8" s="281" t="n"/>
-      <c r="P8" s="281" t="n"/>
-      <c r="Q8" s="281" t="n"/>
-      <c r="R8" s="281" t="n"/>
-      <c r="S8" s="281" t="n"/>
-      <c r="T8" s="281" t="n"/>
-      <c r="U8" s="281" t="n"/>
-      <c r="V8" s="281" t="n"/>
-      <c r="W8" s="281" t="n"/>
-      <c r="X8" s="281" t="n"/>
-      <c r="Y8" s="281" t="n"/>
-      <c r="Z8" s="281" t="n"/>
-      <c r="AA8" s="281" t="n"/>
-      <c r="AB8" s="281" t="n"/>
-      <c r="AC8" s="281" t="n"/>
-      <c r="AD8" s="281" t="n"/>
-      <c r="AE8" s="281" t="n"/>
-      <c r="AF8" s="281" t="n"/>
-      <c r="AG8" s="281" t="n"/>
-      <c r="AH8" s="281" t="n"/>
-      <c r="AI8" s="281" t="n"/>
-      <c r="AJ8" s="281" t="n"/>
-      <c r="AK8" s="281" t="n"/>
-      <c r="AL8" s="281" t="n"/>
-      <c r="AM8" s="281" t="n"/>
-      <c r="AN8" s="281" t="n"/>
-      <c r="AO8" s="281" t="n"/>
-      <c r="AP8" s="281" t="n"/>
-      <c r="AQ8" s="281" t="n"/>
-      <c r="AR8" s="281" t="n"/>
-      <c r="AS8" s="281" t="n"/>
-      <c r="AT8" s="281" t="n"/>
-      <c r="AU8" s="281" t="n"/>
-      <c r="AV8" s="281" t="n"/>
-      <c r="AW8" s="281" t="n"/>
-      <c r="AX8" s="281" t="n"/>
-      <c r="AY8" s="281" t="n"/>
-      <c r="AZ8" s="281" t="n"/>
-      <c r="BA8" s="281" t="n"/>
-      <c r="BB8" s="281" t="n"/>
-      <c r="BC8" s="281" t="n"/>
-      <c r="BD8" s="282" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="22" t="n"/>
+      <c r="U8" s="22" t="n"/>
+      <c r="V8" s="22" t="n"/>
+      <c r="W8" s="22" t="n"/>
+      <c r="X8" s="22" t="n"/>
+      <c r="Y8" s="22" t="n"/>
+      <c r="Z8" s="22" t="n"/>
+      <c r="AA8" s="22" t="n"/>
+      <c r="AB8" s="22" t="n"/>
+      <c r="AC8" s="22" t="n"/>
+      <c r="AD8" s="22" t="n"/>
+      <c r="AE8" s="22" t="n"/>
+      <c r="AF8" s="22" t="n"/>
+      <c r="AG8" s="22" t="n"/>
+      <c r="AH8" s="22" t="n"/>
+      <c r="AI8" s="22" t="n"/>
+      <c r="AJ8" s="22" t="n"/>
+      <c r="AK8" s="22" t="n"/>
+      <c r="AL8" s="22" t="n"/>
+      <c r="AM8" s="22" t="n"/>
+      <c r="AN8" s="22" t="n"/>
+      <c r="AO8" s="22" t="n"/>
+      <c r="AP8" s="22" t="n"/>
+      <c r="AQ8" s="22" t="n"/>
+      <c r="AR8" s="22" t="n"/>
+      <c r="AS8" s="22" t="n"/>
+      <c r="AT8" s="22" t="n"/>
+      <c r="AU8" s="22" t="n"/>
+      <c r="AV8" s="22" t="n"/>
+      <c r="AW8" s="22" t="n"/>
+      <c r="AX8" s="22" t="n"/>
+      <c r="AY8" s="22" t="n"/>
+      <c r="AZ8" s="22" t="n"/>
+      <c r="BA8" s="22" t="n"/>
+      <c r="BB8" s="22" t="n"/>
+      <c r="BC8" s="22" t="n"/>
+      <c r="BD8" s="23" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="327" t="inlineStr">
@@ -9260,66 +9129,66 @@
       <c r="BD19" s="358" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="349" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="281" t="n"/>
-      <c r="C20" s="281" t="n"/>
-      <c r="D20" s="281" t="n"/>
-      <c r="E20" s="281" t="n"/>
-      <c r="F20" s="281" t="n"/>
-      <c r="G20" s="281" t="n"/>
-      <c r="H20" s="281" t="n"/>
-      <c r="I20" s="281" t="n"/>
-      <c r="J20" s="281" t="n"/>
-      <c r="K20" s="281" t="n"/>
-      <c r="L20" s="281" t="n"/>
-      <c r="M20" s="281" t="n"/>
-      <c r="N20" s="281" t="n"/>
-      <c r="O20" s="281" t="n"/>
-      <c r="P20" s="281" t="n"/>
-      <c r="Q20" s="281" t="n"/>
-      <c r="R20" s="281" t="n"/>
-      <c r="S20" s="281" t="n"/>
-      <c r="T20" s="281" t="n"/>
-      <c r="U20" s="281" t="n"/>
-      <c r="V20" s="281" t="n"/>
-      <c r="W20" s="281" t="n"/>
-      <c r="X20" s="281" t="n"/>
-      <c r="Y20" s="281" t="n"/>
-      <c r="Z20" s="281" t="n"/>
-      <c r="AA20" s="281" t="n"/>
-      <c r="AB20" s="281" t="n"/>
-      <c r="AC20" s="281" t="n"/>
-      <c r="AD20" s="281" t="n"/>
-      <c r="AE20" s="281" t="n"/>
-      <c r="AF20" s="281" t="n"/>
-      <c r="AG20" s="281" t="n"/>
-      <c r="AH20" s="281" t="n"/>
-      <c r="AI20" s="281" t="n"/>
-      <c r="AJ20" s="281" t="n"/>
-      <c r="AK20" s="281" t="n"/>
-      <c r="AL20" s="281" t="n"/>
-      <c r="AM20" s="281" t="n"/>
-      <c r="AN20" s="281" t="n"/>
-      <c r="AO20" s="281" t="n"/>
-      <c r="AP20" s="281" t="n"/>
-      <c r="AQ20" s="281" t="n"/>
-      <c r="AR20" s="281" t="n"/>
-      <c r="AS20" s="281" t="n"/>
-      <c r="AT20" s="281" t="n"/>
-      <c r="AU20" s="281" t="n"/>
-      <c r="AV20" s="281" t="n"/>
-      <c r="AW20" s="281" t="n"/>
-      <c r="AX20" s="281" t="n"/>
-      <c r="AY20" s="281" t="n"/>
-      <c r="AZ20" s="281" t="n"/>
-      <c r="BA20" s="281" t="n"/>
-      <c r="BB20" s="281" t="n"/>
-      <c r="BC20" s="281" t="n"/>
-      <c r="BD20" s="282" t="n"/>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+      <c r="U20" s="22" t="n"/>
+      <c r="V20" s="22" t="n"/>
+      <c r="W20" s="22" t="n"/>
+      <c r="X20" s="22" t="n"/>
+      <c r="Y20" s="22" t="n"/>
+      <c r="Z20" s="22" t="n"/>
+      <c r="AA20" s="22" t="n"/>
+      <c r="AB20" s="22" t="n"/>
+      <c r="AC20" s="22" t="n"/>
+      <c r="AD20" s="22" t="n"/>
+      <c r="AE20" s="22" t="n"/>
+      <c r="AF20" s="22" t="n"/>
+      <c r="AG20" s="22" t="n"/>
+      <c r="AH20" s="22" t="n"/>
+      <c r="AI20" s="22" t="n"/>
+      <c r="AJ20" s="22" t="n"/>
+      <c r="AK20" s="22" t="n"/>
+      <c r="AL20" s="22" t="n"/>
+      <c r="AM20" s="22" t="n"/>
+      <c r="AN20" s="22" t="n"/>
+      <c r="AO20" s="22" t="n"/>
+      <c r="AP20" s="22" t="n"/>
+      <c r="AQ20" s="22" t="n"/>
+      <c r="AR20" s="22" t="n"/>
+      <c r="AS20" s="22" t="n"/>
+      <c r="AT20" s="22" t="n"/>
+      <c r="AU20" s="22" t="n"/>
+      <c r="AV20" s="22" t="n"/>
+      <c r="AW20" s="22" t="n"/>
+      <c r="AX20" s="22" t="n"/>
+      <c r="AY20" s="22" t="n"/>
+      <c r="AZ20" s="22" t="n"/>
+      <c r="BA20" s="22" t="n"/>
+      <c r="BB20" s="22" t="n"/>
+      <c r="BC20" s="22" t="n"/>
+      <c r="BD20" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -26,10 +26,732 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+  <si>
+    <t>  1. CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>  1. REVIEW HEADER</t>
+  </si>
+  <si>
+    <t>  2. REVIEW SCOPE AND BASIS</t>
+  </si>
+  <si>
+    <t>  3. FINDINGS, ACTION AND ESCALATION</t>
+  </si>
+  <si>
+    <t>  4. DECISION AND CLOSEOUT</t>
+  </si>
+  <si>
+    <t>  REFERENCE / SOURCE CONTEXT</t>
+  </si>
+  <si>
+    <t>  SUPPORT TABLE</t>
+  </si>
+  <si>
+    <t>  SUPPORT TABLES</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ABSENT</t>
+  </si>
+  <si>
+    <t>ACCESS</t>
+  </si>
+  <si>
+    <t>ACCESS_ACTION_TYPE</t>
+  </si>
+  <si>
+    <t>ADJUST</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>ALL HANDS</t>
+  </si>
+  <si>
+    <t>ANNEX</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>APPROVER</t>
+  </si>
+  <si>
+    <t>ATTENDANCE_STATUS</t>
+  </si>
+  <si>
+    <t>AUDIENCE_CLASS</t>
+  </si>
+  <si>
+    <t>AUDIT_FINDING_SEVERITY</t>
+  </si>
+  <si>
+    <t>AUTHORITY_ROLE</t>
+  </si>
+  <si>
+    <t>AUTHORIZATION_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZED</t>
+  </si>
+  <si>
+    <t>Access Review ID</t>
+  </si>
+  <si>
+    <t>Access-role master and effective rights remain in the live system + ANNEX-IT-001 / 025 control set; workbook captures request / review evidence only, not the source permission model.</t>
+  </si>
+  <si>
+    <t>Account / Group</t>
+  </si>
+  <si>
+    <t>Account Population / Role Scope</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>BACKUP_FLAG</t>
+  </si>
+  <si>
+    <t>Boundary / SoR</t>
+  </si>
+  <si>
+    <t>CHANGE</t>
+  </si>
+  <si>
+    <t>CHANGE_PRIORITY</t>
+  </si>
+  <si>
+    <t>CHANGE_TYPE</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>COMMERCIAL_REFERENCE</t>
+  </si>
+  <si>
+    <t>COMM_CHANNEL</t>
+  </si>
+  <si>
+    <t>COMPETENCY_LEVEL</t>
+  </si>
+  <si>
+    <t>COMPLIANCE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CONFIGURATION</t>
+  </si>
+  <si>
+    <t>CONTAINED</t>
+  </si>
+  <si>
+    <t>CONTEXT_CLASS</t>
+  </si>
+  <si>
+    <t>CONTRACT</t>
+  </si>
+  <si>
+    <t>CONTRACT REVIEW</t>
+  </si>
+  <si>
+    <t>CONTRIBUTOR</t>
+  </si>
+  <si>
+    <t>CONTROL_METHOD</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>CREATE</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>CSR</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Containment Need</t>
+  </si>
+  <si>
+    <t>DAILY</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>DEPT</t>
+  </si>
+  <si>
+    <t>DETECTION</t>
+  </si>
+  <si>
+    <t>DIMENSIONAL</t>
+  </si>
+  <si>
+    <t>DOCUMENT</t>
+  </si>
+  <si>
+    <t>DOC_STATUS</t>
+  </si>
+  <si>
+    <t>DOC_TYPE</t>
+  </si>
+  <si>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Detailed actions / findings / decisions</t>
+  </si>
+  <si>
+    <t>Detailed finding / action sheet linked from the primary gate page.</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>EACH LOT</t>
+  </si>
+  <si>
+    <t>EFFECTIVE</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>ESCALATE</t>
+  </si>
+  <si>
+    <t>ESCALATED</t>
+  </si>
+  <si>
+    <t>ESCALATION</t>
+  </si>
+  <si>
+    <t>EXCUSED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Evidence ID</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>FIRST ARTICLE</t>
+  </si>
+  <si>
+    <t>FIRST OFF</t>
+  </si>
+  <si>
+    <t>FIRST PIECE</t>
+  </si>
+  <si>
+    <t>FMEA_RANK</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t>FRM-111</t>
+  </si>
+  <si>
+    <t>FUNCTION</t>
+  </si>
+  <si>
+    <t>FUNCTIONAL</t>
+  </si>
+  <si>
+    <t>Final Decision</t>
+  </si>
+  <si>
+    <t>Finding ID</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>GATE</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HOURLY</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IMPACT_LEVEL</t>
+  </si>
+  <si>
+    <t>IMPACT_SCOPE</t>
+  </si>
+  <si>
+    <t>IN PROCESS</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>IN-PROCESS</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>KPI-COST</t>
+  </si>
+  <si>
+    <t>KPI-DELIVERY</t>
+  </si>
+  <si>
+    <t>KPI-QUALITY</t>
+  </si>
+  <si>
+    <t>KPI-SAFETY</t>
+  </si>
+  <si>
+    <t>KPI-TRAINING</t>
+  </si>
+  <si>
+    <t>KPI_OWNER_SET</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>LESSON_CLASS</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>Link or Ref</t>
+  </si>
+  <si>
+    <t>MAJOR</t>
+  </si>
+  <si>
+    <t>MANAGEMENT</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MEETING</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MINOR</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>NOT AUTHORIZED</t>
+  </si>
+  <si>
+    <t>NOT TRAINED</t>
+  </si>
+  <si>
+    <t>NOTICE</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Review access against least-privilege and segregation-of-duty expectations, close dormant or inappropriate access with owner and due date, and keep evidence linked to the reviewed system snapshot.</t>
+  </si>
+  <si>
+    <t>NOTICE: Use one row per finding. Record objective evidence, severity, owner, due date and verification reference; avoid vague or conclusion-only wording.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OBSERVED</t>
+  </si>
+  <si>
+    <t>OBSOLETE</t>
+  </si>
+  <si>
+    <t>ON HOLD</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OWNER</t>
+  </si>
+  <si>
+    <t>Objective Evidence</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PEOPLE</t>
+  </si>
+  <si>
+    <t>PESTLE</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>POLICY</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>PRESENT</t>
+  </si>
+  <si>
+    <t>PREVENTION</t>
+  </si>
+  <si>
+    <t>PROCESS</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Per authority matrix</t>
+  </si>
+  <si>
+    <t>Periodic access review only; role master stays in system / ANNEX.</t>
+  </si>
+  <si>
+    <t>Prepared By</t>
+  </si>
+  <si>
+    <t>Privilege / SoD Exceptions</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QMS + IT</t>
+  </si>
+  <si>
+    <t>QUALITY</t>
+  </si>
+  <si>
+    <t>QUARTERLY ACCESS REVIEW</t>
+  </si>
+  <si>
+    <t>QUARTERLY ACCESS REVIEW — CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>QUARTERLY ACCESS REVIEW — EVIDENCE REFERENCE REGISTER</t>
+  </si>
+  <si>
+    <t>QUARTERLY ACCESS REVIEW — FINDINGS AND ACTIONS</t>
+  </si>
+  <si>
+    <t>QUOTE</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REACTION_CLASS</t>
+  </si>
+  <si>
+    <t>RECHECK</t>
+  </si>
+  <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t>RECOVERING</t>
+  </si>
+  <si>
+    <t>RECOVERY_STATUS</t>
+  </si>
+  <si>
+    <t>REGULATORY</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>REMOVE</t>
+  </si>
+  <si>
+    <t>REQUESTER</t>
+  </si>
+  <si>
+    <t>RESPONSE</t>
+  </si>
+  <si>
+    <t>RESTORED</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>REVIEWER</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>RISK_CATEGORY</t>
+  </si>
+  <si>
+    <t>ROLE</t>
+  </si>
+  <si>
+    <t>ROLE_ACCESS_PROFILE</t>
+  </si>
+  <si>
+    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
+  </si>
+  <si>
+    <t>Reference Path or Link</t>
+  </si>
+  <si>
+    <t>Related Record</t>
+  </si>
+  <si>
+    <t>Review Period</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Reviewer / Process Owner</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SAFETY</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SAMPLE_FREQUENCY</t>
+  </si>
+  <si>
+    <t>SEGREGATE</t>
+  </si>
+  <si>
+    <t>SHIFT</t>
+  </si>
+  <si>
+    <t>SHIPPING</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>SOP</t>
+  </si>
+  <si>
+    <t>SOP: SOP-104 | ANNEX: ANNEX-QMS-005, ANNEX-QMS-006, ANNEX-QMS-012, ANNEX-QMS-019, ANNEX-QMS-021, ANNEX-IT-001, ANNEX-IT-002</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>STOP</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>SUPERVISED</t>
+  </si>
+  <si>
+    <t>SUSPENDED</t>
+  </si>
+  <si>
+    <t>SWOT</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>See workbook secondary sheet</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Source Links</t>
+  </si>
+  <si>
+    <t>Source System</t>
+  </si>
+  <si>
+    <t>Source-of-Truth Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Support Sheet</t>
+  </si>
+  <si>
+    <t>System / Area</t>
+  </si>
+  <si>
+    <t>TRAINER</t>
+  </si>
+  <si>
+    <t>TRAINING</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VIEWER</t>
+  </si>
+  <si>
+    <t>VISUAL</t>
+  </si>
+  <si>
+    <t>WEEKLY</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,8 +862,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -198,8 +925,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="150">
+  <borders count="153">
     <border>
       <left/>
       <right/>
@@ -1824,11 +2556,45 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="430">
+  <cellXfs count="433">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2974,6 +3740,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4612,51 +5387,51 @@
       <c r="AM24" s="380" t="n"/>
       <c r="AN24" s="384" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="373" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="430" t="inlineStr">
         <is>
           <t>NOTICE: Review access against least-privilege and segregation-of-duty expectations, close dormant or inappropriate access with owner and due date, and keep evidence linked to the reviewed system snapshot.</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
-      <c r="J25" s="22" t="n"/>
-      <c r="K25" s="22" t="n"/>
-      <c r="L25" s="22" t="n"/>
-      <c r="M25" s="22" t="n"/>
-      <c r="N25" s="22" t="n"/>
-      <c r="O25" s="22" t="n"/>
-      <c r="P25" s="22" t="n"/>
-      <c r="Q25" s="22" t="n"/>
-      <c r="R25" s="22" t="n"/>
-      <c r="S25" s="22" t="n"/>
-      <c r="T25" s="22" t="n"/>
-      <c r="U25" s="22" t="n"/>
-      <c r="V25" s="22" t="n"/>
-      <c r="W25" s="22" t="n"/>
-      <c r="X25" s="22" t="n"/>
-      <c r="Y25" s="22" t="n"/>
-      <c r="Z25" s="22" t="n"/>
-      <c r="AA25" s="22" t="n"/>
-      <c r="AB25" s="22" t="n"/>
-      <c r="AC25" s="22" t="n"/>
-      <c r="AD25" s="22" t="n"/>
-      <c r="AE25" s="22" t="n"/>
-      <c r="AF25" s="22" t="n"/>
-      <c r="AG25" s="22" t="n"/>
-      <c r="AH25" s="22" t="n"/>
-      <c r="AI25" s="22" t="n"/>
-      <c r="AJ25" s="22" t="n"/>
-      <c r="AK25" s="22" t="n"/>
-      <c r="AL25" s="22" t="n"/>
-      <c r="AM25" s="22" t="n"/>
-      <c r="AN25" s="23" t="n"/>
+      <c r="B25" s="431" t="n"/>
+      <c r="C25" s="431" t="n"/>
+      <c r="D25" s="431" t="n"/>
+      <c r="E25" s="431" t="n"/>
+      <c r="F25" s="431" t="n"/>
+      <c r="G25" s="431" t="n"/>
+      <c r="H25" s="431" t="n"/>
+      <c r="I25" s="431" t="n"/>
+      <c r="J25" s="431" t="n"/>
+      <c r="K25" s="431" t="n"/>
+      <c r="L25" s="431" t="n"/>
+      <c r="M25" s="431" t="n"/>
+      <c r="N25" s="431" t="n"/>
+      <c r="O25" s="431" t="n"/>
+      <c r="P25" s="431" t="n"/>
+      <c r="Q25" s="431" t="n"/>
+      <c r="R25" s="431" t="n"/>
+      <c r="S25" s="431" t="n"/>
+      <c r="T25" s="431" t="n"/>
+      <c r="U25" s="431" t="n"/>
+      <c r="V25" s="431" t="n"/>
+      <c r="W25" s="431" t="n"/>
+      <c r="X25" s="431" t="n"/>
+      <c r="Y25" s="431" t="n"/>
+      <c r="Z25" s="431" t="n"/>
+      <c r="AA25" s="431" t="n"/>
+      <c r="AB25" s="431" t="n"/>
+      <c r="AC25" s="431" t="n"/>
+      <c r="AD25" s="431" t="n"/>
+      <c r="AE25" s="431" t="n"/>
+      <c r="AF25" s="431" t="n"/>
+      <c r="AG25" s="431" t="n"/>
+      <c r="AH25" s="431" t="n"/>
+      <c r="AI25" s="431" t="n"/>
+      <c r="AJ25" s="431" t="n"/>
+      <c r="AK25" s="431" t="n"/>
+      <c r="AL25" s="431" t="n"/>
+      <c r="AM25" s="431" t="n"/>
+      <c r="AN25" s="432" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -5871,67 +6646,67 @@
       <c r="BC18" s="380" t="n"/>
       <c r="BD18" s="384" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="373" t="inlineStr">
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="430" t="inlineStr">
         <is>
           <t>NOTICE: Use one row per finding. Record objective evidence, severity, owner, due date and verification reference; avoid vague or conclusion-only wording.</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
-      <c r="U19" s="22" t="n"/>
-      <c r="V19" s="22" t="n"/>
-      <c r="W19" s="22" t="n"/>
-      <c r="X19" s="22" t="n"/>
-      <c r="Y19" s="22" t="n"/>
-      <c r="Z19" s="22" t="n"/>
-      <c r="AA19" s="22" t="n"/>
-      <c r="AB19" s="22" t="n"/>
-      <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="22" t="n"/>
-      <c r="AE19" s="22" t="n"/>
-      <c r="AF19" s="22" t="n"/>
-      <c r="AG19" s="22" t="n"/>
-      <c r="AH19" s="22" t="n"/>
-      <c r="AI19" s="22" t="n"/>
-      <c r="AJ19" s="22" t="n"/>
-      <c r="AK19" s="22" t="n"/>
-      <c r="AL19" s="22" t="n"/>
-      <c r="AM19" s="22" t="n"/>
-      <c r="AN19" s="22" t="n"/>
-      <c r="AO19" s="22" t="n"/>
-      <c r="AP19" s="22" t="n"/>
-      <c r="AQ19" s="22" t="n"/>
-      <c r="AR19" s="22" t="n"/>
-      <c r="AS19" s="22" t="n"/>
-      <c r="AT19" s="22" t="n"/>
-      <c r="AU19" s="22" t="n"/>
-      <c r="AV19" s="22" t="n"/>
-      <c r="AW19" s="22" t="n"/>
-      <c r="AX19" s="22" t="n"/>
-      <c r="AY19" s="22" t="n"/>
-      <c r="AZ19" s="22" t="n"/>
-      <c r="BA19" s="22" t="n"/>
-      <c r="BB19" s="22" t="n"/>
-      <c r="BC19" s="22" t="n"/>
-      <c r="BD19" s="23" t="n"/>
+      <c r="B19" s="431" t="n"/>
+      <c r="C19" s="431" t="n"/>
+      <c r="D19" s="431" t="n"/>
+      <c r="E19" s="431" t="n"/>
+      <c r="F19" s="431" t="n"/>
+      <c r="G19" s="431" t="n"/>
+      <c r="H19" s="431" t="n"/>
+      <c r="I19" s="431" t="n"/>
+      <c r="J19" s="431" t="n"/>
+      <c r="K19" s="431" t="n"/>
+      <c r="L19" s="431" t="n"/>
+      <c r="M19" s="431" t="n"/>
+      <c r="N19" s="431" t="n"/>
+      <c r="O19" s="431" t="n"/>
+      <c r="P19" s="431" t="n"/>
+      <c r="Q19" s="431" t="n"/>
+      <c r="R19" s="431" t="n"/>
+      <c r="S19" s="431" t="n"/>
+      <c r="T19" s="431" t="n"/>
+      <c r="U19" s="431" t="n"/>
+      <c r="V19" s="431" t="n"/>
+      <c r="W19" s="431" t="n"/>
+      <c r="X19" s="431" t="n"/>
+      <c r="Y19" s="431" t="n"/>
+      <c r="Z19" s="431" t="n"/>
+      <c r="AA19" s="431" t="n"/>
+      <c r="AB19" s="431" t="n"/>
+      <c r="AC19" s="431" t="n"/>
+      <c r="AD19" s="431" t="n"/>
+      <c r="AE19" s="431" t="n"/>
+      <c r="AF19" s="431" t="n"/>
+      <c r="AG19" s="431" t="n"/>
+      <c r="AH19" s="431" t="n"/>
+      <c r="AI19" s="431" t="n"/>
+      <c r="AJ19" s="431" t="n"/>
+      <c r="AK19" s="431" t="n"/>
+      <c r="AL19" s="431" t="n"/>
+      <c r="AM19" s="431" t="n"/>
+      <c r="AN19" s="431" t="n"/>
+      <c r="AO19" s="431" t="n"/>
+      <c r="AP19" s="431" t="n"/>
+      <c r="AQ19" s="431" t="n"/>
+      <c r="AR19" s="431" t="n"/>
+      <c r="AS19" s="431" t="n"/>
+      <c r="AT19" s="431" t="n"/>
+      <c r="AU19" s="431" t="n"/>
+      <c r="AV19" s="431" t="n"/>
+      <c r="AW19" s="431" t="n"/>
+      <c r="AX19" s="431" t="n"/>
+      <c r="AY19" s="431" t="n"/>
+      <c r="AZ19" s="431" t="n"/>
+      <c r="BA19" s="431" t="n"/>
+      <c r="BB19" s="431" t="n"/>
+      <c r="BC19" s="431" t="n"/>
+      <c r="BD19" s="432" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -9,25 +9,22 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM111_Main" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM111_Findings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM111_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="3" state="veryHidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM111_Main'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FRM111_Main'!$A$1:$AN$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FRM111_Findings'!$1:$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'FRM111_Findings'!$A$1:$BD$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'FRM111_Evidence'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'FRM111_Evidence'!$A$1:$BD$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'zLISTS'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'zLISTS'!$A$1:$BD$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'zLISTS'!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'zLISTS'!$A$1:$BD$20</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" calcOnSave="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t>  1. CONTROLLED LOOKUP LISTS</t>
   </si>
@@ -131,9 +128,6 @@
     <t>Access Review ID</t>
   </si>
   <si>
-    <t>Access-role master and effective rights remain in the live system + ANNEX-IT-001 / 025 control set; workbook captures request / review evidence only, not the source permission model.</t>
-  </si>
-  <si>
     <t>Account / Group</t>
   </si>
   <si>
@@ -251,12 +245,6 @@
     <t>DRAFT</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Detailed actions / findings / decisions</t>
   </si>
   <si>
@@ -296,9 +284,6 @@
     <t>Eff. Date</t>
   </si>
   <si>
-    <t>Evidence ID</t>
-  </si>
-  <si>
     <t>Evidence Ref</t>
   </si>
   <si>
@@ -455,9 +440,6 @@
     <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
   </si>
   <si>
-    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
-  </si>
-  <si>
     <t>NOTICE: Review access against least-privilege and segregation-of-duty expectations, close dormant or inappropriate access with owner and due date, and keep evidence linked to the reviewed system snapshot.</t>
   </si>
   <si>
@@ -467,9 +449,6 @@
     <t>Name / Signature / Date</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>OBSERVED</t>
   </si>
   <si>
@@ -557,9 +536,6 @@
     <t>QUARTERLY ACCESS REVIEW — CONTROLLED LOOKUP LISTS</t>
   </si>
   <si>
-    <t>QUARTERLY ACCESS REVIEW — EVIDENCE REFERENCE REGISTER</t>
-  </si>
-  <si>
     <t>QUARTERLY ACCESS REVIEW — FINDINGS AND ACTIONS</t>
   </si>
   <si>
@@ -620,15 +596,6 @@
     <t>ROLE_ACCESS_PROFILE</t>
   </si>
   <si>
-    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
-  </si>
-  <si>
-    <t>Reference Path or Link</t>
-  </si>
-  <si>
-    <t>Related Record</t>
-  </si>
-  <si>
     <t>Review Period</t>
   </si>
   <si>
@@ -696,9 +663,6 @@
   </si>
   <si>
     <t>Source Links</t>
-  </si>
-  <si>
-    <t>Source System</t>
   </si>
   <si>
     <t>Source-of-Truth Date</t>
@@ -931,7 +895,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="153">
+  <borders count="158">
     <border>
       <left/>
       <right/>
@@ -2590,11 +2554,69 @@
         <color rgb="00F9A825"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="433">
+  <cellXfs count="436">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3750,6 +3772,11 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3893,39 +3920,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
-    </from>
-    <ext cx="1394316" cy="402206"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -6839,1211 +6833,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BD18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col width="2.33" customWidth="1" min="5" max="5"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
-    <col width="2.33" customWidth="1" min="41" max="41"/>
-    <col width="2.33" customWidth="1" min="42" max="42"/>
-    <col width="2.33" customWidth="1" min="43" max="43"/>
-    <col width="2.33" customWidth="1" min="44" max="44"/>
-    <col width="2.33" customWidth="1" min="45" max="45"/>
-    <col width="2.33" customWidth="1" min="46" max="46"/>
-    <col width="2.33" customWidth="1" min="47" max="47"/>
-    <col width="2.33" customWidth="1" min="48" max="48"/>
-    <col width="2.33" customWidth="1" min="49" max="49"/>
-    <col width="2.33" customWidth="1" min="50" max="50"/>
-    <col width="2.33" customWidth="1" min="51" max="51"/>
-    <col width="2.33" customWidth="1" min="52" max="52"/>
-    <col width="2.33" customWidth="1" min="53" max="53"/>
-    <col width="2.33" customWidth="1" min="54" max="54"/>
-    <col width="2.33" customWidth="1" min="55" max="55"/>
-    <col width="2.33" customWidth="1" min="56" max="56"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="359" t="n"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="258" t="inlineStr">
-        <is>
-          <t>QUARTERLY ACCESS REVIEW — EVIDENCE REFERENCE REGISTER</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="2" t="n"/>
-      <c r="AI1" s="2" t="n"/>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="2" t="n"/>
-      <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
-      <c r="AQ1" s="360" t="inlineStr">
-        <is>
-          <t>Form Code</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="n"/>
-      <c r="AS1" s="2" t="n"/>
-      <c r="AT1" s="2" t="n"/>
-      <c r="AU1" s="2" t="n"/>
-      <c r="AV1" s="361" t="n"/>
-      <c r="AW1" s="362" t="inlineStr">
-        <is>
-          <t>FRM-111</t>
-        </is>
-      </c>
-      <c r="AX1" s="2" t="n"/>
-      <c r="AY1" s="2" t="n"/>
-      <c r="AZ1" s="2" t="n"/>
-      <c r="BA1" s="2" t="n"/>
-      <c r="BB1" s="2" t="n"/>
-      <c r="BC1" s="2" t="n"/>
-      <c r="BD1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="363" t="inlineStr">
-        <is>
-          <t>Revision</t>
-        </is>
-      </c>
-      <c r="AR2" s="364" t="n"/>
-      <c r="AS2" s="364" t="n"/>
-      <c r="AT2" s="364" t="n"/>
-      <c r="AU2" s="364" t="n"/>
-      <c r="AV2" s="365" t="n"/>
-      <c r="AW2" s="366" t="inlineStr">
-        <is>
-          <t>V0</t>
-        </is>
-      </c>
-      <c r="AX2" s="364" t="n"/>
-      <c r="AY2" s="364" t="n"/>
-      <c r="AZ2" s="364" t="n"/>
-      <c r="BA2" s="364" t="n"/>
-      <c r="BB2" s="364" t="n"/>
-      <c r="BC2" s="364" t="n"/>
-      <c r="BD2" s="367" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="363" t="inlineStr">
-        <is>
-          <t>Eff. Date</t>
-        </is>
-      </c>
-      <c r="AR3" s="364" t="n"/>
-      <c r="AS3" s="364" t="n"/>
-      <c r="AT3" s="364" t="n"/>
-      <c r="AU3" s="364" t="n"/>
-      <c r="AV3" s="365" t="n"/>
-      <c r="AW3" s="366" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="AX3" s="364" t="n"/>
-      <c r="AY3" s="364" t="n"/>
-      <c r="AZ3" s="364" t="n"/>
-      <c r="BA3" s="364" t="n"/>
-      <c r="BB3" s="364" t="n"/>
-      <c r="BC3" s="364" t="n"/>
-      <c r="BD3" s="367" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="270" t="inlineStr">
-        <is>
-          <t>Quality Management System · Controlled Document</t>
-        </is>
-      </c>
-      <c r="AQ4" s="363" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="AR4" s="364" t="n"/>
-      <c r="AS4" s="364" t="n"/>
-      <c r="AT4" s="364" t="n"/>
-      <c r="AU4" s="364" t="n"/>
-      <c r="AV4" s="365" t="n"/>
-      <c r="AW4" s="366" t="inlineStr">
-        <is>
-          <t>QMS + IT</t>
-        </is>
-      </c>
-      <c r="AX4" s="364" t="n"/>
-      <c r="AY4" s="364" t="n"/>
-      <c r="AZ4" s="364" t="n"/>
-      <c r="BA4" s="364" t="n"/>
-      <c r="BB4" s="364" t="n"/>
-      <c r="BC4" s="364" t="n"/>
-      <c r="BD4" s="367" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="50" t="inlineStr">
-        <is>
-          <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="368" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="AR5" s="369" t="n"/>
-      <c r="AS5" s="369" t="n"/>
-      <c r="AT5" s="369" t="n"/>
-      <c r="AU5" s="369" t="n"/>
-      <c r="AV5" s="370" t="n"/>
-      <c r="AW5" s="371" t="inlineStr">
-        <is>
-          <t>Per authority matrix</t>
-        </is>
-      </c>
-      <c r="AX5" s="369" t="n"/>
-      <c r="AY5" s="369" t="n"/>
-      <c r="AZ5" s="369" t="n"/>
-      <c r="BA5" s="369" t="n"/>
-      <c r="BB5" s="369" t="n"/>
-      <c r="BC5" s="369" t="n"/>
-      <c r="BD5" s="372" t="n"/>
-    </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="279" t="n"/>
-      <c r="B6" s="279" t="n"/>
-      <c r="C6" s="279" t="n"/>
-      <c r="D6" s="279" t="n"/>
-      <c r="E6" s="279" t="n"/>
-      <c r="F6" s="279" t="n"/>
-      <c r="G6" s="279" t="n"/>
-      <c r="H6" s="279" t="n"/>
-      <c r="I6" s="279" t="n"/>
-      <c r="J6" s="279" t="n"/>
-      <c r="K6" s="279" t="n"/>
-      <c r="L6" s="279" t="n"/>
-      <c r="M6" s="279" t="n"/>
-      <c r="N6" s="279" t="n"/>
-      <c r="O6" s="279" t="n"/>
-      <c r="P6" s="279" t="n"/>
-      <c r="Q6" s="279" t="n"/>
-      <c r="R6" s="279" t="n"/>
-      <c r="S6" s="279" t="n"/>
-      <c r="T6" s="279" t="n"/>
-      <c r="U6" s="279" t="n"/>
-      <c r="V6" s="279" t="n"/>
-      <c r="W6" s="279" t="n"/>
-      <c r="X6" s="279" t="n"/>
-      <c r="Y6" s="279" t="n"/>
-      <c r="Z6" s="279" t="n"/>
-      <c r="AA6" s="279" t="n"/>
-      <c r="AB6" s="279" t="n"/>
-      <c r="AC6" s="279" t="n"/>
-      <c r="AD6" s="279" t="n"/>
-      <c r="AE6" s="279" t="n"/>
-      <c r="AF6" s="279" t="n"/>
-      <c r="AG6" s="279" t="n"/>
-      <c r="AH6" s="279" t="n"/>
-      <c r="AI6" s="279" t="n"/>
-      <c r="AJ6" s="279" t="n"/>
-      <c r="AK6" s="279" t="n"/>
-      <c r="AL6" s="279" t="n"/>
-      <c r="AM6" s="279" t="n"/>
-      <c r="AN6" s="279" t="n"/>
-      <c r="AO6" s="279" t="n"/>
-      <c r="AP6" s="279" t="n"/>
-      <c r="AQ6" s="279" t="n"/>
-      <c r="AR6" s="279" t="n"/>
-      <c r="AS6" s="279" t="n"/>
-      <c r="AT6" s="279" t="n"/>
-      <c r="AU6" s="279" t="n"/>
-      <c r="AV6" s="279" t="n"/>
-      <c r="AW6" s="279" t="n"/>
-      <c r="AX6" s="279" t="n"/>
-      <c r="AY6" s="279" t="n"/>
-      <c r="AZ6" s="279" t="n"/>
-      <c r="BA6" s="279" t="n"/>
-      <c r="BB6" s="279" t="n"/>
-      <c r="BC6" s="279" t="n"/>
-      <c r="BD6" s="279" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="374" t="inlineStr">
-        <is>
-          <t>Source Links</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="38" t="inlineStr">
-        <is>
-          <t>Access-role master and effective rights remain in the live system + ANNEX-IT-001 / 025 control set; workbook captures request / review evidence only, not the source permission model.</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
-      <c r="S8" s="6" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="6" t="n"/>
-      <c r="V8" s="6" t="n"/>
-      <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="7" t="n"/>
-      <c r="AC8" s="403" t="inlineStr"/>
-      <c r="AD8" s="6" t="n"/>
-      <c r="AE8" s="6" t="n"/>
-      <c r="AF8" s="6" t="n"/>
-      <c r="AG8" s="6" t="n"/>
-      <c r="AH8" s="6" t="n"/>
-      <c r="AI8" s="6" t="n"/>
-      <c r="AJ8" s="6" t="n"/>
-      <c r="AK8" s="6" t="n"/>
-      <c r="AL8" s="7" t="n"/>
-      <c r="AM8" s="404" t="inlineStr"/>
-      <c r="AN8" s="6" t="n"/>
-      <c r="AO8" s="6" t="n"/>
-      <c r="AP8" s="6" t="n"/>
-      <c r="AQ8" s="6" t="n"/>
-      <c r="AR8" s="6" t="n"/>
-      <c r="AS8" s="6" t="n"/>
-      <c r="AT8" s="6" t="n"/>
-      <c r="AU8" s="6" t="n"/>
-      <c r="AV8" s="6" t="n"/>
-      <c r="AW8" s="6" t="n"/>
-      <c r="AX8" s="6" t="n"/>
-      <c r="AY8" s="6" t="n"/>
-      <c r="AZ8" s="6" t="n"/>
-      <c r="BA8" s="6" t="n"/>
-      <c r="BB8" s="6" t="n"/>
-      <c r="BC8" s="6" t="n"/>
-      <c r="BD8" s="9" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="378" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="17" t="n"/>
-      <c r="J9" s="52" t="n"/>
-      <c r="K9" s="408" t="inlineStr">
-        <is>
-          <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="17" t="n"/>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="17" t="n"/>
-      <c r="P9" s="17" t="n"/>
-      <c r="Q9" s="17" t="n"/>
-      <c r="R9" s="17" t="n"/>
-      <c r="S9" s="17" t="n"/>
-      <c r="T9" s="17" t="n"/>
-      <c r="U9" s="17" t="n"/>
-      <c r="V9" s="17" t="n"/>
-      <c r="W9" s="17" t="n"/>
-      <c r="X9" s="17" t="n"/>
-      <c r="Y9" s="17" t="n"/>
-      <c r="Z9" s="17" t="n"/>
-      <c r="AA9" s="17" t="n"/>
-      <c r="AB9" s="52" t="n"/>
-      <c r="AC9" s="409" t="inlineStr"/>
-      <c r="AD9" s="17" t="n"/>
-      <c r="AE9" s="17" t="n"/>
-      <c r="AF9" s="17" t="n"/>
-      <c r="AG9" s="17" t="n"/>
-      <c r="AH9" s="17" t="n"/>
-      <c r="AI9" s="17" t="n"/>
-      <c r="AJ9" s="17" t="n"/>
-      <c r="AK9" s="17" t="n"/>
-      <c r="AL9" s="52" t="n"/>
-      <c r="AM9" s="410" t="inlineStr"/>
-      <c r="AN9" s="17" t="n"/>
-      <c r="AO9" s="17" t="n"/>
-      <c r="AP9" s="17" t="n"/>
-      <c r="AQ9" s="17" t="n"/>
-      <c r="AR9" s="17" t="n"/>
-      <c r="AS9" s="17" t="n"/>
-      <c r="AT9" s="17" t="n"/>
-      <c r="AU9" s="17" t="n"/>
-      <c r="AV9" s="17" t="n"/>
-      <c r="AW9" s="17" t="n"/>
-      <c r="AX9" s="17" t="n"/>
-      <c r="AY9" s="17" t="n"/>
-      <c r="AZ9" s="17" t="n"/>
-      <c r="BA9" s="17" t="n"/>
-      <c r="BB9" s="17" t="n"/>
-      <c r="BC9" s="17" t="n"/>
-      <c r="BD9" s="18" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SUPPORT TABLE</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-      <c r="Q10" s="22" t="n"/>
-      <c r="R10" s="22" t="n"/>
-      <c r="S10" s="22" t="n"/>
-      <c r="T10" s="22" t="n"/>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="22" t="n"/>
-      <c r="W10" s="22" t="n"/>
-      <c r="X10" s="22" t="n"/>
-      <c r="Y10" s="22" t="n"/>
-      <c r="Z10" s="22" t="n"/>
-      <c r="AA10" s="22" t="n"/>
-      <c r="AB10" s="22" t="n"/>
-      <c r="AC10" s="22" t="n"/>
-      <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="22" t="n"/>
-      <c r="AF10" s="22" t="n"/>
-      <c r="AG10" s="22" t="n"/>
-      <c r="AH10" s="22" t="n"/>
-      <c r="AI10" s="22" t="n"/>
-      <c r="AJ10" s="22" t="n"/>
-      <c r="AK10" s="22" t="n"/>
-      <c r="AL10" s="22" t="n"/>
-      <c r="AM10" s="22" t="n"/>
-      <c r="AN10" s="22" t="n"/>
-      <c r="AO10" s="22" t="n"/>
-      <c r="AP10" s="22" t="n"/>
-      <c r="AQ10" s="22" t="n"/>
-      <c r="AR10" s="22" t="n"/>
-      <c r="AS10" s="22" t="n"/>
-      <c r="AT10" s="22" t="n"/>
-      <c r="AU10" s="22" t="n"/>
-      <c r="AV10" s="22" t="n"/>
-      <c r="AW10" s="22" t="n"/>
-      <c r="AX10" s="22" t="n"/>
-      <c r="AY10" s="22" t="n"/>
-      <c r="AZ10" s="22" t="n"/>
-      <c r="BA10" s="22" t="n"/>
-      <c r="BB10" s="22" t="n"/>
-      <c r="BC10" s="22" t="n"/>
-      <c r="BD10" s="23" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
-        <is>
-          <t>Evidence ID</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="411" t="inlineStr">
-        <is>
-          <t>Related Record</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="411" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n"/>
-      <c r="S11" s="6" t="n"/>
-      <c r="T11" s="6" t="n"/>
-      <c r="U11" s="6" t="n"/>
-      <c r="V11" s="6" t="n"/>
-      <c r="W11" s="6" t="n"/>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="411" t="inlineStr">
-        <is>
-          <t>Source System</t>
-        </is>
-      </c>
-      <c r="Z11" s="6" t="n"/>
-      <c r="AA11" s="6" t="n"/>
-      <c r="AB11" s="6" t="n"/>
-      <c r="AC11" s="7" t="n"/>
-      <c r="AD11" s="411" t="inlineStr">
-        <is>
-          <t>Reference Path or Link</t>
-        </is>
-      </c>
-      <c r="AE11" s="6" t="n"/>
-      <c r="AF11" s="6" t="n"/>
-      <c r="AG11" s="6" t="n"/>
-      <c r="AH11" s="6" t="n"/>
-      <c r="AI11" s="6" t="n"/>
-      <c r="AJ11" s="7" t="n"/>
-      <c r="AK11" s="411" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="AL11" s="6" t="n"/>
-      <c r="AM11" s="6" t="n"/>
-      <c r="AN11" s="6" t="n"/>
-      <c r="AO11" s="6" t="n"/>
-      <c r="AP11" s="7" t="n"/>
-      <c r="AQ11" s="411" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AR11" s="6" t="n"/>
-      <c r="AS11" s="6" t="n"/>
-      <c r="AT11" s="6" t="n"/>
-      <c r="AU11" s="7" t="n"/>
-      <c r="AV11" s="412" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="AW11" s="6" t="n"/>
-      <c r="AX11" s="6" t="n"/>
-      <c r="AY11" s="6" t="n"/>
-      <c r="AZ11" s="6" t="n"/>
-      <c r="BA11" s="6" t="n"/>
-      <c r="BB11" s="6" t="n"/>
-      <c r="BC11" s="6" t="n"/>
-      <c r="BD11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="421" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="25" t="n"/>
-      <c r="O12" s="26" t="n"/>
-      <c r="P12" s="26" t="n"/>
-      <c r="Q12" s="26" t="n"/>
-      <c r="R12" s="26" t="n"/>
-      <c r="S12" s="26" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="26" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="27" t="n"/>
-      <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="26" t="n"/>
-      <c r="AB12" s="26" t="n"/>
-      <c r="AC12" s="27" t="n"/>
-      <c r="AD12" s="25" t="n"/>
-      <c r="AE12" s="26" t="n"/>
-      <c r="AF12" s="26" t="n"/>
-      <c r="AG12" s="26" t="n"/>
-      <c r="AH12" s="26" t="n"/>
-      <c r="AI12" s="26" t="n"/>
-      <c r="AJ12" s="27" t="n"/>
-      <c r="AK12" s="414" t="n"/>
-      <c r="AL12" s="26" t="n"/>
-      <c r="AM12" s="26" t="n"/>
-      <c r="AN12" s="26" t="n"/>
-      <c r="AO12" s="26" t="n"/>
-      <c r="AP12" s="27" t="n"/>
-      <c r="AQ12" s="25" t="n"/>
-      <c r="AR12" s="26" t="n"/>
-      <c r="AS12" s="26" t="n"/>
-      <c r="AT12" s="26" t="n"/>
-      <c r="AU12" s="27" t="n"/>
-      <c r="AV12" s="376" t="n"/>
-      <c r="AW12" s="26" t="n"/>
-      <c r="AX12" s="26" t="n"/>
-      <c r="AY12" s="26" t="n"/>
-      <c r="AZ12" s="26" t="n"/>
-      <c r="BA12" s="26" t="n"/>
-      <c r="BB12" s="26" t="n"/>
-      <c r="BC12" s="26" t="n"/>
-      <c r="BD12" s="377" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="422" t="n"/>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="43" t="n"/>
-      <c r="J13" s="35" t="n"/>
-      <c r="K13" s="35" t="n"/>
-      <c r="L13" s="35" t="n"/>
-      <c r="M13" s="36" t="n"/>
-      <c r="N13" s="43" t="n"/>
-      <c r="O13" s="35" t="n"/>
-      <c r="P13" s="35" t="n"/>
-      <c r="Q13" s="35" t="n"/>
-      <c r="R13" s="35" t="n"/>
-      <c r="S13" s="35" t="n"/>
-      <c r="T13" s="35" t="n"/>
-      <c r="U13" s="35" t="n"/>
-      <c r="V13" s="35" t="n"/>
-      <c r="W13" s="35" t="n"/>
-      <c r="X13" s="36" t="n"/>
-      <c r="Y13" s="43" t="n"/>
-      <c r="Z13" s="35" t="n"/>
-      <c r="AA13" s="35" t="n"/>
-      <c r="AB13" s="35" t="n"/>
-      <c r="AC13" s="36" t="n"/>
-      <c r="AD13" s="43" t="n"/>
-      <c r="AE13" s="35" t="n"/>
-      <c r="AF13" s="35" t="n"/>
-      <c r="AG13" s="35" t="n"/>
-      <c r="AH13" s="35" t="n"/>
-      <c r="AI13" s="35" t="n"/>
-      <c r="AJ13" s="36" t="n"/>
-      <c r="AK13" s="42" t="n"/>
-      <c r="AL13" s="35" t="n"/>
-      <c r="AM13" s="35" t="n"/>
-      <c r="AN13" s="35" t="n"/>
-      <c r="AO13" s="35" t="n"/>
-      <c r="AP13" s="36" t="n"/>
-      <c r="AQ13" s="43" t="n"/>
-      <c r="AR13" s="35" t="n"/>
-      <c r="AS13" s="35" t="n"/>
-      <c r="AT13" s="35" t="n"/>
-      <c r="AU13" s="36" t="n"/>
-      <c r="AV13" s="416" t="n"/>
-      <c r="AW13" s="35" t="n"/>
-      <c r="AX13" s="35" t="n"/>
-      <c r="AY13" s="35" t="n"/>
-      <c r="AZ13" s="35" t="n"/>
-      <c r="BA13" s="35" t="n"/>
-      <c r="BB13" s="35" t="n"/>
-      <c r="BC13" s="35" t="n"/>
-      <c r="BD13" s="396" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="422" t="n"/>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="41" t="n"/>
-      <c r="J14" s="35" t="n"/>
-      <c r="K14" s="35" t="n"/>
-      <c r="L14" s="35" t="n"/>
-      <c r="M14" s="36" t="n"/>
-      <c r="N14" s="41" t="n"/>
-      <c r="O14" s="35" t="n"/>
-      <c r="P14" s="35" t="n"/>
-      <c r="Q14" s="35" t="n"/>
-      <c r="R14" s="35" t="n"/>
-      <c r="S14" s="35" t="n"/>
-      <c r="T14" s="35" t="n"/>
-      <c r="U14" s="35" t="n"/>
-      <c r="V14" s="35" t="n"/>
-      <c r="W14" s="35" t="n"/>
-      <c r="X14" s="36" t="n"/>
-      <c r="Y14" s="41" t="n"/>
-      <c r="Z14" s="35" t="n"/>
-      <c r="AA14" s="35" t="n"/>
-      <c r="AB14" s="35" t="n"/>
-      <c r="AC14" s="36" t="n"/>
-      <c r="AD14" s="41" t="n"/>
-      <c r="AE14" s="35" t="n"/>
-      <c r="AF14" s="35" t="n"/>
-      <c r="AG14" s="35" t="n"/>
-      <c r="AH14" s="35" t="n"/>
-      <c r="AI14" s="35" t="n"/>
-      <c r="AJ14" s="36" t="n"/>
-      <c r="AK14" s="42" t="n"/>
-      <c r="AL14" s="35" t="n"/>
-      <c r="AM14" s="35" t="n"/>
-      <c r="AN14" s="35" t="n"/>
-      <c r="AO14" s="35" t="n"/>
-      <c r="AP14" s="36" t="n"/>
-      <c r="AQ14" s="41" t="n"/>
-      <c r="AR14" s="35" t="n"/>
-      <c r="AS14" s="35" t="n"/>
-      <c r="AT14" s="35" t="n"/>
-      <c r="AU14" s="36" t="n"/>
-      <c r="AV14" s="395" t="n"/>
-      <c r="AW14" s="35" t="n"/>
-      <c r="AX14" s="35" t="n"/>
-      <c r="AY14" s="35" t="n"/>
-      <c r="AZ14" s="35" t="n"/>
-      <c r="BA14" s="35" t="n"/>
-      <c r="BB14" s="35" t="n"/>
-      <c r="BC14" s="35" t="n"/>
-      <c r="BD14" s="396" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="422" t="n"/>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="43" t="n"/>
-      <c r="J15" s="35" t="n"/>
-      <c r="K15" s="35" t="n"/>
-      <c r="L15" s="35" t="n"/>
-      <c r="M15" s="36" t="n"/>
-      <c r="N15" s="43" t="n"/>
-      <c r="O15" s="35" t="n"/>
-      <c r="P15" s="35" t="n"/>
-      <c r="Q15" s="35" t="n"/>
-      <c r="R15" s="35" t="n"/>
-      <c r="S15" s="35" t="n"/>
-      <c r="T15" s="35" t="n"/>
-      <c r="U15" s="35" t="n"/>
-      <c r="V15" s="35" t="n"/>
-      <c r="W15" s="35" t="n"/>
-      <c r="X15" s="36" t="n"/>
-      <c r="Y15" s="43" t="n"/>
-      <c r="Z15" s="35" t="n"/>
-      <c r="AA15" s="35" t="n"/>
-      <c r="AB15" s="35" t="n"/>
-      <c r="AC15" s="36" t="n"/>
-      <c r="AD15" s="43" t="n"/>
-      <c r="AE15" s="35" t="n"/>
-      <c r="AF15" s="35" t="n"/>
-      <c r="AG15" s="35" t="n"/>
-      <c r="AH15" s="35" t="n"/>
-      <c r="AI15" s="35" t="n"/>
-      <c r="AJ15" s="36" t="n"/>
-      <c r="AK15" s="42" t="n"/>
-      <c r="AL15" s="35" t="n"/>
-      <c r="AM15" s="35" t="n"/>
-      <c r="AN15" s="35" t="n"/>
-      <c r="AO15" s="35" t="n"/>
-      <c r="AP15" s="36" t="n"/>
-      <c r="AQ15" s="43" t="n"/>
-      <c r="AR15" s="35" t="n"/>
-      <c r="AS15" s="35" t="n"/>
-      <c r="AT15" s="35" t="n"/>
-      <c r="AU15" s="36" t="n"/>
-      <c r="AV15" s="416" t="n"/>
-      <c r="AW15" s="35" t="n"/>
-      <c r="AX15" s="35" t="n"/>
-      <c r="AY15" s="35" t="n"/>
-      <c r="AZ15" s="35" t="n"/>
-      <c r="BA15" s="35" t="n"/>
-      <c r="BB15" s="35" t="n"/>
-      <c r="BC15" s="35" t="n"/>
-      <c r="BD15" s="396" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="422" t="n"/>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="41" t="n"/>
-      <c r="J16" s="35" t="n"/>
-      <c r="K16" s="35" t="n"/>
-      <c r="L16" s="35" t="n"/>
-      <c r="M16" s="36" t="n"/>
-      <c r="N16" s="41" t="n"/>
-      <c r="O16" s="35" t="n"/>
-      <c r="P16" s="35" t="n"/>
-      <c r="Q16" s="35" t="n"/>
-      <c r="R16" s="35" t="n"/>
-      <c r="S16" s="35" t="n"/>
-      <c r="T16" s="35" t="n"/>
-      <c r="U16" s="35" t="n"/>
-      <c r="V16" s="35" t="n"/>
-      <c r="W16" s="35" t="n"/>
-      <c r="X16" s="36" t="n"/>
-      <c r="Y16" s="41" t="n"/>
-      <c r="Z16" s="35" t="n"/>
-      <c r="AA16" s="35" t="n"/>
-      <c r="AB16" s="35" t="n"/>
-      <c r="AC16" s="36" t="n"/>
-      <c r="AD16" s="41" t="n"/>
-      <c r="AE16" s="35" t="n"/>
-      <c r="AF16" s="35" t="n"/>
-      <c r="AG16" s="35" t="n"/>
-      <c r="AH16" s="35" t="n"/>
-      <c r="AI16" s="35" t="n"/>
-      <c r="AJ16" s="36" t="n"/>
-      <c r="AK16" s="42" t="n"/>
-      <c r="AL16" s="35" t="n"/>
-      <c r="AM16" s="35" t="n"/>
-      <c r="AN16" s="35" t="n"/>
-      <c r="AO16" s="35" t="n"/>
-      <c r="AP16" s="36" t="n"/>
-      <c r="AQ16" s="41" t="n"/>
-      <c r="AR16" s="35" t="n"/>
-      <c r="AS16" s="35" t="n"/>
-      <c r="AT16" s="35" t="n"/>
-      <c r="AU16" s="36" t="n"/>
-      <c r="AV16" s="395" t="n"/>
-      <c r="AW16" s="35" t="n"/>
-      <c r="AX16" s="35" t="n"/>
-      <c r="AY16" s="35" t="n"/>
-      <c r="AZ16" s="35" t="n"/>
-      <c r="BA16" s="35" t="n"/>
-      <c r="BB16" s="35" t="n"/>
-      <c r="BC16" s="35" t="n"/>
-      <c r="BD16" s="396" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="423" t="n"/>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="418" t="n"/>
-      <c r="J17" s="380" t="n"/>
-      <c r="K17" s="380" t="n"/>
-      <c r="L17" s="380" t="n"/>
-      <c r="M17" s="381" t="n"/>
-      <c r="N17" s="418" t="n"/>
-      <c r="O17" s="380" t="n"/>
-      <c r="P17" s="380" t="n"/>
-      <c r="Q17" s="380" t="n"/>
-      <c r="R17" s="380" t="n"/>
-      <c r="S17" s="380" t="n"/>
-      <c r="T17" s="380" t="n"/>
-      <c r="U17" s="380" t="n"/>
-      <c r="V17" s="380" t="n"/>
-      <c r="W17" s="380" t="n"/>
-      <c r="X17" s="381" t="n"/>
-      <c r="Y17" s="418" t="n"/>
-      <c r="Z17" s="380" t="n"/>
-      <c r="AA17" s="380" t="n"/>
-      <c r="AB17" s="380" t="n"/>
-      <c r="AC17" s="381" t="n"/>
-      <c r="AD17" s="418" t="n"/>
-      <c r="AE17" s="380" t="n"/>
-      <c r="AF17" s="380" t="n"/>
-      <c r="AG17" s="380" t="n"/>
-      <c r="AH17" s="380" t="n"/>
-      <c r="AI17" s="380" t="n"/>
-      <c r="AJ17" s="381" t="n"/>
-      <c r="AK17" s="419" t="n"/>
-      <c r="AL17" s="380" t="n"/>
-      <c r="AM17" s="380" t="n"/>
-      <c r="AN17" s="380" t="n"/>
-      <c r="AO17" s="380" t="n"/>
-      <c r="AP17" s="381" t="n"/>
-      <c r="AQ17" s="418" t="n"/>
-      <c r="AR17" s="380" t="n"/>
-      <c r="AS17" s="380" t="n"/>
-      <c r="AT17" s="380" t="n"/>
-      <c r="AU17" s="381" t="n"/>
-      <c r="AV17" s="420" t="n"/>
-      <c r="AW17" s="380" t="n"/>
-      <c r="AX17" s="380" t="n"/>
-      <c r="AY17" s="380" t="n"/>
-      <c r="AZ17" s="380" t="n"/>
-      <c r="BA17" s="380" t="n"/>
-      <c r="BB17" s="380" t="n"/>
-      <c r="BC17" s="380" t="n"/>
-      <c r="BD17" s="384" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="373" t="inlineStr">
-        <is>
-          <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="22" t="n"/>
-      <c r="R18" s="22" t="n"/>
-      <c r="S18" s="22" t="n"/>
-      <c r="T18" s="22" t="n"/>
-      <c r="U18" s="22" t="n"/>
-      <c r="V18" s="22" t="n"/>
-      <c r="W18" s="22" t="n"/>
-      <c r="X18" s="22" t="n"/>
-      <c r="Y18" s="22" t="n"/>
-      <c r="Z18" s="22" t="n"/>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="22" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="22" t="n"/>
-      <c r="AE18" s="22" t="n"/>
-      <c r="AF18" s="22" t="n"/>
-      <c r="AG18" s="22" t="n"/>
-      <c r="AH18" s="22" t="n"/>
-      <c r="AI18" s="22" t="n"/>
-      <c r="AJ18" s="22" t="n"/>
-      <c r="AK18" s="22" t="n"/>
-      <c r="AL18" s="22" t="n"/>
-      <c r="AM18" s="22" t="n"/>
-      <c r="AN18" s="22" t="n"/>
-      <c r="AO18" s="22" t="n"/>
-      <c r="AP18" s="22" t="n"/>
-      <c r="AQ18" s="22" t="n"/>
-      <c r="AR18" s="22" t="n"/>
-      <c r="AS18" s="22" t="n"/>
-      <c r="AT18" s="22" t="n"/>
-      <c r="AU18" s="22" t="n"/>
-      <c r="AV18" s="22" t="n"/>
-      <c r="AW18" s="22" t="n"/>
-      <c r="AX18" s="22" t="n"/>
-      <c r="AY18" s="22" t="n"/>
-      <c r="AZ18" s="22" t="n"/>
-      <c r="BA18" s="22" t="n"/>
-      <c r="BB18" s="22" t="n"/>
-      <c r="BC18" s="22" t="n"/>
-      <c r="BD18" s="23" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="81">
-    <mergeCell ref="AV17:BD17"/>
-    <mergeCell ref="AV11:BD11"/>
-    <mergeCell ref="N11:X11"/>
-    <mergeCell ref="AQ11:AU11"/>
-    <mergeCell ref="AW2:BD2"/>
-    <mergeCell ref="AD16:AJ16"/>
-    <mergeCell ref="AK11:AP11"/>
-    <mergeCell ref="AQ5:AV5"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="N12:X12"/>
-    <mergeCell ref="AW3:BD3"/>
-    <mergeCell ref="AQ12:AU12"/>
-    <mergeCell ref="AQ4:AV4"/>
-    <mergeCell ref="N14:X14"/>
-    <mergeCell ref="AV15:BD15"/>
-    <mergeCell ref="AW5:BD5"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="I17:M17"/>
-    <mergeCell ref="AV16:BD16"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="AD11:AJ11"/>
-    <mergeCell ref="L4:AP4"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="L1:AP3"/>
-    <mergeCell ref="N16:X16"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="AQ2:AV2"/>
-    <mergeCell ref="AK16:AP16"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="Y14:AC14"/>
-    <mergeCell ref="A1:K5"/>
-    <mergeCell ref="I12:M12"/>
-    <mergeCell ref="A7:BD7"/>
-    <mergeCell ref="I14:M14"/>
-    <mergeCell ref="AQ14:AU14"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="N13:X13"/>
-    <mergeCell ref="AM8:BD8"/>
-    <mergeCell ref="AQ13:AU13"/>
-    <mergeCell ref="A18:BD18"/>
-    <mergeCell ref="K9:AB9"/>
-    <mergeCell ref="AK13:AP13"/>
-    <mergeCell ref="N15:X15"/>
-    <mergeCell ref="AQ15:AU15"/>
-    <mergeCell ref="L5:AP5"/>
-    <mergeCell ref="AK15:AP15"/>
-    <mergeCell ref="AC9:AL9"/>
-    <mergeCell ref="AQ16:AU16"/>
-    <mergeCell ref="K8:AB8"/>
-    <mergeCell ref="AW4:BD4"/>
-    <mergeCell ref="AD12:AJ12"/>
-    <mergeCell ref="AQ1:AV1"/>
-    <mergeCell ref="AD14:AJ14"/>
-    <mergeCell ref="Y17:AC17"/>
-    <mergeCell ref="N17:X17"/>
-    <mergeCell ref="AQ17:AU17"/>
-    <mergeCell ref="AD13:AJ13"/>
-    <mergeCell ref="AW1:BD1"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="AD15:AJ15"/>
-    <mergeCell ref="AC8:AL8"/>
-    <mergeCell ref="I13:M13"/>
-    <mergeCell ref="AV12:BD12"/>
-    <mergeCell ref="AQ3:AV3"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="AK14:AP14"/>
-    <mergeCell ref="AV14:BD14"/>
-    <mergeCell ref="A10:BD10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="Y15:AC15"/>
-    <mergeCell ref="AM9:BD9"/>
-    <mergeCell ref="AV13:BD13"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="AD17:AJ17"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="Y16:AC16"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="AK17:AP17"/>
-    <mergeCell ref="AK12:AP12"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-111  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:BD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -21,695 +21,6 @@
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" calcOnSave="1" forceFullCalc="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
-  <si>
-    <t>  1. CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>  1. REVIEW HEADER</t>
-  </si>
-  <si>
-    <t>  2. REVIEW SCOPE AND BASIS</t>
-  </si>
-  <si>
-    <t>  3. FINDINGS, ACTION AND ESCALATION</t>
-  </si>
-  <si>
-    <t>  4. DECISION AND CLOSEOUT</t>
-  </si>
-  <si>
-    <t>  REFERENCE / SOURCE CONTEXT</t>
-  </si>
-  <si>
-    <t>  SUPPORT TABLE</t>
-  </si>
-  <si>
-    <t>  SUPPORT TABLES</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>ACCESS</t>
-  </si>
-  <si>
-    <t>ACCESS_ACTION_TYPE</t>
-  </si>
-  <si>
-    <t>ADJUST</t>
-  </si>
-  <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
-    <t>ALL HANDS</t>
-  </si>
-  <si>
-    <t>ANNEX</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>APPROVER</t>
-  </si>
-  <si>
-    <t>ATTENDANCE_STATUS</t>
-  </si>
-  <si>
-    <t>AUDIENCE_CLASS</t>
-  </si>
-  <si>
-    <t>AUDIT_FINDING_SEVERITY</t>
-  </si>
-  <si>
-    <t>AUTHORITY_ROLE</t>
-  </si>
-  <si>
-    <t>AUTHORIZATION_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZED</t>
-  </si>
-  <si>
-    <t>Access Review ID</t>
-  </si>
-  <si>
-    <t>Account / Group</t>
-  </si>
-  <si>
-    <t>Account Population / Role Scope</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>BACKUP_FLAG</t>
-  </si>
-  <si>
-    <t>Boundary / SoR</t>
-  </si>
-  <si>
-    <t>CHANGE</t>
-  </si>
-  <si>
-    <t>CHANGE_PRIORITY</t>
-  </si>
-  <si>
-    <t>CHANGE_TYPE</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>COMMERCIAL_REFERENCE</t>
-  </si>
-  <si>
-    <t>COMM_CHANNEL</t>
-  </si>
-  <si>
-    <t>COMPETENCY_LEVEL</t>
-  </si>
-  <si>
-    <t>COMPLIANCE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CONFIGURATION</t>
-  </si>
-  <si>
-    <t>CONTAINED</t>
-  </si>
-  <si>
-    <t>CONTEXT_CLASS</t>
-  </si>
-  <si>
-    <t>CONTRACT</t>
-  </si>
-  <si>
-    <t>CONTRACT REVIEW</t>
-  </si>
-  <si>
-    <t>CONTRIBUTOR</t>
-  </si>
-  <si>
-    <t>CONTROL_METHOD</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>CREATE</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>CSR</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Containment Need</t>
-  </si>
-  <si>
-    <t>DAILY</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>DELIVERY</t>
-  </si>
-  <si>
-    <t>DEPT</t>
-  </si>
-  <si>
-    <t>DETECTION</t>
-  </si>
-  <si>
-    <t>DIMENSIONAL</t>
-  </si>
-  <si>
-    <t>DOCUMENT</t>
-  </si>
-  <si>
-    <t>DOC_STATUS</t>
-  </si>
-  <si>
-    <t>DOC_TYPE</t>
-  </si>
-  <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
-    <t>Detailed actions / findings / decisions</t>
-  </si>
-  <si>
-    <t>Detailed finding / action sheet linked from the primary gate page.</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>EACH LOT</t>
-  </si>
-  <si>
-    <t>EFFECTIVE</t>
-  </si>
-  <si>
-    <t>EMAIL</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>ESCALATE</t>
-  </si>
-  <si>
-    <t>ESCALATED</t>
-  </si>
-  <si>
-    <t>ESCALATION</t>
-  </si>
-  <si>
-    <t>EXCUSED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FINAL</t>
-  </si>
-  <si>
-    <t>FIRST ARTICLE</t>
-  </si>
-  <si>
-    <t>FIRST OFF</t>
-  </si>
-  <si>
-    <t>FIRST PIECE</t>
-  </si>
-  <si>
-    <t>FMEA_RANK</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>FRM-111</t>
-  </si>
-  <si>
-    <t>FUNCTION</t>
-  </si>
-  <si>
-    <t>FUNCTIONAL</t>
-  </si>
-  <si>
-    <t>Final Decision</t>
-  </si>
-  <si>
-    <t>Finding ID</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>GATE</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HOURLY</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>IMPACT_LEVEL</t>
-  </si>
-  <si>
-    <t>IMPACT_SCOPE</t>
-  </si>
-  <si>
-    <t>IN PROCESS</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>IN-PROCESS</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>KPI-COST</t>
-  </si>
-  <si>
-    <t>KPI-DELIVERY</t>
-  </si>
-  <si>
-    <t>KPI-QUALITY</t>
-  </si>
-  <si>
-    <t>KPI-SAFETY</t>
-  </si>
-  <si>
-    <t>KPI-TRAINING</t>
-  </si>
-  <si>
-    <t>KPI_OWNER_SET</t>
-  </si>
-  <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>LESSON_CLASS</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>Link or Ref</t>
-  </si>
-  <si>
-    <t>MAJOR</t>
-  </si>
-  <si>
-    <t>MANAGEMENT</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MEETING</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MINOR</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>NOT AUTHORIZED</t>
-  </si>
-  <si>
-    <t>NOT TRAINED</t>
-  </si>
-  <si>
-    <t>NOTICE</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
-  </si>
-  <si>
-    <t>NOTICE: Review access against least-privilege and segregation-of-duty expectations, close dormant or inappropriate access with owner and due date, and keep evidence linked to the reviewed system snapshot.</t>
-  </si>
-  <si>
-    <t>NOTICE: Use one row per finding. Record objective evidence, severity, owner, due date and verification reference; avoid vague or conclusion-only wording.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>OBSERVED</t>
-  </si>
-  <si>
-    <t>OBSOLETE</t>
-  </si>
-  <si>
-    <t>ON HOLD</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OWNER</t>
-  </si>
-  <si>
-    <t>Objective Evidence</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PEOPLE</t>
-  </si>
-  <si>
-    <t>PESTLE</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>POLICY</t>
-  </si>
-  <si>
-    <t>PORTAL</t>
-  </si>
-  <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
-    <t>PREVENTION</t>
-  </si>
-  <si>
-    <t>PROCESS</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Per authority matrix</t>
-  </si>
-  <si>
-    <t>Periodic access review only; role master stays in system / ANNEX.</t>
-  </si>
-  <si>
-    <t>Prepared By</t>
-  </si>
-  <si>
-    <t>Privilege / SoD Exceptions</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>QMS + IT</t>
-  </si>
-  <si>
-    <t>QUALITY</t>
-  </si>
-  <si>
-    <t>QUARTERLY ACCESS REVIEW</t>
-  </si>
-  <si>
-    <t>QUARTERLY ACCESS REVIEW — CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>QUARTERLY ACCESS REVIEW — FINDINGS AND ACTIONS</t>
-  </si>
-  <si>
-    <t>QUOTE</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>REACTION_CLASS</t>
-  </si>
-  <si>
-    <t>RECHECK</t>
-  </si>
-  <si>
-    <t>RECORD</t>
-  </si>
-  <si>
-    <t>RECOVERING</t>
-  </si>
-  <si>
-    <t>RECOVERY_STATUS</t>
-  </si>
-  <si>
-    <t>REGULATORY</t>
-  </si>
-  <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
-    <t>REMOVE</t>
-  </si>
-  <si>
-    <t>REQUESTER</t>
-  </si>
-  <si>
-    <t>RESPONSE</t>
-  </si>
-  <si>
-    <t>RESTORED</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>REVIEWER</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>RISK_CATEGORY</t>
-  </si>
-  <si>
-    <t>ROLE</t>
-  </si>
-  <si>
-    <t>ROLE_ACCESS_PROFILE</t>
-  </si>
-  <si>
-    <t>Review Period</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Reviewer / Process Owner</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SAFETY</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SAMPLE_FREQUENCY</t>
-  </si>
-  <si>
-    <t>SEGREGATE</t>
-  </si>
-  <si>
-    <t>SHIFT</t>
-  </si>
-  <si>
-    <t>SHIPPING</t>
-  </si>
-  <si>
-    <t>SO</t>
-  </si>
-  <si>
-    <t>SOP</t>
-  </si>
-  <si>
-    <t>SOP: SOP-104 | ANNEX: ANNEX-QMS-005, ANNEX-QMS-006, ANNEX-QMS-012, ANNEX-QMS-019, ANNEX-QMS-021, ANNEX-IT-001, ANNEX-IT-002</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>STOP</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>SUPERVISED</t>
-  </si>
-  <si>
-    <t>SUSPENDED</t>
-  </si>
-  <si>
-    <t>SWOT</t>
-  </si>
-  <si>
-    <t>SYSTEM</t>
-  </si>
-  <si>
-    <t>See workbook secondary sheet</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Source Links</t>
-  </si>
-  <si>
-    <t>Source-of-Truth Date</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Support Sheet</t>
-  </si>
-  <si>
-    <t>System / Area</t>
-  </si>
-  <si>
-    <t>TRAINER</t>
-  </si>
-  <si>
-    <t>TRAINING</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VIEWER</t>
-  </si>
-  <si>
-    <t>VISUAL</t>
-  </si>
-  <si>
-    <t>WEEKLY</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7184,67 +6495,67 @@
       <c r="BC7" s="22" t="n"/>
       <c r="BD7" s="23" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="430" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="22" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="22" t="n"/>
-      <c r="R8" s="22" t="n"/>
-      <c r="S8" s="22" t="n"/>
-      <c r="T8" s="22" t="n"/>
-      <c r="U8" s="22" t="n"/>
-      <c r="V8" s="22" t="n"/>
-      <c r="W8" s="22" t="n"/>
-      <c r="X8" s="22" t="n"/>
-      <c r="Y8" s="22" t="n"/>
-      <c r="Z8" s="22" t="n"/>
-      <c r="AA8" s="22" t="n"/>
-      <c r="AB8" s="22" t="n"/>
-      <c r="AC8" s="22" t="n"/>
-      <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="22" t="n"/>
-      <c r="AF8" s="22" t="n"/>
-      <c r="AG8" s="22" t="n"/>
-      <c r="AH8" s="22" t="n"/>
-      <c r="AI8" s="22" t="n"/>
-      <c r="AJ8" s="22" t="n"/>
-      <c r="AK8" s="22" t="n"/>
-      <c r="AL8" s="22" t="n"/>
-      <c r="AM8" s="22" t="n"/>
-      <c r="AN8" s="22" t="n"/>
-      <c r="AO8" s="22" t="n"/>
-      <c r="AP8" s="22" t="n"/>
-      <c r="AQ8" s="22" t="n"/>
-      <c r="AR8" s="22" t="n"/>
-      <c r="AS8" s="22" t="n"/>
-      <c r="AT8" s="22" t="n"/>
-      <c r="AU8" s="22" t="n"/>
-      <c r="AV8" s="22" t="n"/>
-      <c r="AW8" s="22" t="n"/>
-      <c r="AX8" s="22" t="n"/>
-      <c r="AY8" s="22" t="n"/>
-      <c r="AZ8" s="22" t="n"/>
-      <c r="BA8" s="22" t="n"/>
-      <c r="BB8" s="22" t="n"/>
-      <c r="BC8" s="22" t="n"/>
-      <c r="BD8" s="23" t="n"/>
+      <c r="B8" s="431" t="n"/>
+      <c r="C8" s="431" t="n"/>
+      <c r="D8" s="431" t="n"/>
+      <c r="E8" s="431" t="n"/>
+      <c r="F8" s="431" t="n"/>
+      <c r="G8" s="431" t="n"/>
+      <c r="H8" s="431" t="n"/>
+      <c r="I8" s="431" t="n"/>
+      <c r="J8" s="431" t="n"/>
+      <c r="K8" s="431" t="n"/>
+      <c r="L8" s="431" t="n"/>
+      <c r="M8" s="431" t="n"/>
+      <c r="N8" s="431" t="n"/>
+      <c r="O8" s="431" t="n"/>
+      <c r="P8" s="431" t="n"/>
+      <c r="Q8" s="431" t="n"/>
+      <c r="R8" s="431" t="n"/>
+      <c r="S8" s="431" t="n"/>
+      <c r="T8" s="431" t="n"/>
+      <c r="U8" s="431" t="n"/>
+      <c r="V8" s="431" t="n"/>
+      <c r="W8" s="431" t="n"/>
+      <c r="X8" s="431" t="n"/>
+      <c r="Y8" s="431" t="n"/>
+      <c r="Z8" s="431" t="n"/>
+      <c r="AA8" s="431" t="n"/>
+      <c r="AB8" s="431" t="n"/>
+      <c r="AC8" s="431" t="n"/>
+      <c r="AD8" s="431" t="n"/>
+      <c r="AE8" s="431" t="n"/>
+      <c r="AF8" s="431" t="n"/>
+      <c r="AG8" s="431" t="n"/>
+      <c r="AH8" s="431" t="n"/>
+      <c r="AI8" s="431" t="n"/>
+      <c r="AJ8" s="431" t="n"/>
+      <c r="AK8" s="431" t="n"/>
+      <c r="AL8" s="431" t="n"/>
+      <c r="AM8" s="431" t="n"/>
+      <c r="AN8" s="431" t="n"/>
+      <c r="AO8" s="431" t="n"/>
+      <c r="AP8" s="431" t="n"/>
+      <c r="AQ8" s="431" t="n"/>
+      <c r="AR8" s="431" t="n"/>
+      <c r="AS8" s="431" t="n"/>
+      <c r="AT8" s="431" t="n"/>
+      <c r="AU8" s="431" t="n"/>
+      <c r="AV8" s="431" t="n"/>
+      <c r="AW8" s="431" t="n"/>
+      <c r="AX8" s="431" t="n"/>
+      <c r="AY8" s="431" t="n"/>
+      <c r="AZ8" s="431" t="n"/>
+      <c r="BA8" s="431" t="n"/>
+      <c r="BB8" s="431" t="n"/>
+      <c r="BC8" s="431" t="n"/>
+      <c r="BD8" s="432" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="327" t="inlineStr">
@@ -8692,67 +8003,67 @@
       <c r="BC19" s="357" t="n"/>
       <c r="BD19" s="358" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="430" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="22" t="n"/>
-      <c r="U20" s="22" t="n"/>
-      <c r="V20" s="22" t="n"/>
-      <c r="W20" s="22" t="n"/>
-      <c r="X20" s="22" t="n"/>
-      <c r="Y20" s="22" t="n"/>
-      <c r="Z20" s="22" t="n"/>
-      <c r="AA20" s="22" t="n"/>
-      <c r="AB20" s="22" t="n"/>
-      <c r="AC20" s="22" t="n"/>
-      <c r="AD20" s="22" t="n"/>
-      <c r="AE20" s="22" t="n"/>
-      <c r="AF20" s="22" t="n"/>
-      <c r="AG20" s="22" t="n"/>
-      <c r="AH20" s="22" t="n"/>
-      <c r="AI20" s="22" t="n"/>
-      <c r="AJ20" s="22" t="n"/>
-      <c r="AK20" s="22" t="n"/>
-      <c r="AL20" s="22" t="n"/>
-      <c r="AM20" s="22" t="n"/>
-      <c r="AN20" s="22" t="n"/>
-      <c r="AO20" s="22" t="n"/>
-      <c r="AP20" s="22" t="n"/>
-      <c r="AQ20" s="22" t="n"/>
-      <c r="AR20" s="22" t="n"/>
-      <c r="AS20" s="22" t="n"/>
-      <c r="AT20" s="22" t="n"/>
-      <c r="AU20" s="22" t="n"/>
-      <c r="AV20" s="22" t="n"/>
-      <c r="AW20" s="22" t="n"/>
-      <c r="AX20" s="22" t="n"/>
-      <c r="AY20" s="22" t="n"/>
-      <c r="AZ20" s="22" t="n"/>
-      <c r="BA20" s="22" t="n"/>
-      <c r="BB20" s="22" t="n"/>
-      <c r="BC20" s="22" t="n"/>
-      <c r="BD20" s="23" t="n"/>
+      <c r="B20" s="431" t="n"/>
+      <c r="C20" s="431" t="n"/>
+      <c r="D20" s="431" t="n"/>
+      <c r="E20" s="431" t="n"/>
+      <c r="F20" s="431" t="n"/>
+      <c r="G20" s="431" t="n"/>
+      <c r="H20" s="431" t="n"/>
+      <c r="I20" s="431" t="n"/>
+      <c r="J20" s="431" t="n"/>
+      <c r="K20" s="431" t="n"/>
+      <c r="L20" s="431" t="n"/>
+      <c r="M20" s="431" t="n"/>
+      <c r="N20" s="431" t="n"/>
+      <c r="O20" s="431" t="n"/>
+      <c r="P20" s="431" t="n"/>
+      <c r="Q20" s="431" t="n"/>
+      <c r="R20" s="431" t="n"/>
+      <c r="S20" s="431" t="n"/>
+      <c r="T20" s="431" t="n"/>
+      <c r="U20" s="431" t="n"/>
+      <c r="V20" s="431" t="n"/>
+      <c r="W20" s="431" t="n"/>
+      <c r="X20" s="431" t="n"/>
+      <c r="Y20" s="431" t="n"/>
+      <c r="Z20" s="431" t="n"/>
+      <c r="AA20" s="431" t="n"/>
+      <c r="AB20" s="431" t="n"/>
+      <c r="AC20" s="431" t="n"/>
+      <c r="AD20" s="431" t="n"/>
+      <c r="AE20" s="431" t="n"/>
+      <c r="AF20" s="431" t="n"/>
+      <c r="AG20" s="431" t="n"/>
+      <c r="AH20" s="431" t="n"/>
+      <c r="AI20" s="431" t="n"/>
+      <c r="AJ20" s="431" t="n"/>
+      <c r="AK20" s="431" t="n"/>
+      <c r="AL20" s="431" t="n"/>
+      <c r="AM20" s="431" t="n"/>
+      <c r="AN20" s="431" t="n"/>
+      <c r="AO20" s="431" t="n"/>
+      <c r="AP20" s="431" t="n"/>
+      <c r="AQ20" s="431" t="n"/>
+      <c r="AR20" s="431" t="n"/>
+      <c r="AS20" s="431" t="n"/>
+      <c r="AT20" s="431" t="n"/>
+      <c r="AU20" s="431" t="n"/>
+      <c r="AV20" s="431" t="n"/>
+      <c r="AW20" s="431" t="n"/>
+      <c r="AX20" s="431" t="n"/>
+      <c r="AY20" s="431" t="n"/>
+      <c r="AZ20" s="431" t="n"/>
+      <c r="BA20" s="431" t="n"/>
+      <c r="BB20" s="431" t="n"/>
+      <c r="BC20" s="431" t="n"/>
+      <c r="BD20" s="432" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -206,7 +206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="158">
+  <borders count="160">
     <border>
       <left/>
       <right/>
@@ -1923,11 +1923,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="436">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3088,6 +3112,98 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3169,11 +3285,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>253512</colOff>
-      <row>0</row>
-      <rowOff>340740</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="941616" cy="271620"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3187,9 +3303,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3202,11 +3315,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3220,9 +3333,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3235,11 +3345,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3253,9 +3363,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3597,7 +3704,7 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="359" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -3606,7 +3713,7 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="258" t="inlineStr">
+      <c r="I1" s="472" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW</t>
         </is>
@@ -3631,7 +3738,7 @@
       <c r="AA1" s="2" t="n"/>
       <c r="AB1" s="2" t="n"/>
       <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
+      <c r="AD1" s="3" t="n"/>
       <c r="AE1" s="360" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -3652,219 +3759,296 @@
       <c r="AN1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="AE2" s="363" t="inlineStr">
+      <c r="A2" s="436" t="n"/>
+      <c r="B2" s="437" t="n"/>
+      <c r="C2" s="437" t="n"/>
+      <c r="D2" s="437" t="n"/>
+      <c r="E2" s="437" t="n"/>
+      <c r="F2" s="437" t="n"/>
+      <c r="G2" s="437" t="n"/>
+      <c r="H2" s="438" t="n"/>
+      <c r="I2" s="437" t="n"/>
+      <c r="J2" s="437" t="n"/>
+      <c r="K2" s="437" t="n"/>
+      <c r="L2" s="437" t="n"/>
+      <c r="M2" s="437" t="n"/>
+      <c r="N2" s="437" t="n"/>
+      <c r="O2" s="437" t="n"/>
+      <c r="P2" s="437" t="n"/>
+      <c r="Q2" s="437" t="n"/>
+      <c r="R2" s="437" t="n"/>
+      <c r="S2" s="437" t="n"/>
+      <c r="T2" s="437" t="n"/>
+      <c r="U2" s="437" t="n"/>
+      <c r="V2" s="437" t="n"/>
+      <c r="W2" s="437" t="n"/>
+      <c r="X2" s="437" t="n"/>
+      <c r="Y2" s="437" t="n"/>
+      <c r="Z2" s="437" t="n"/>
+      <c r="AA2" s="437" t="n"/>
+      <c r="AB2" s="437" t="n"/>
+      <c r="AC2" s="437" t="n"/>
+      <c r="AD2" s="438" t="n"/>
+      <c r="AE2" s="439" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="364" t="n"/>
-      <c r="AG2" s="364" t="n"/>
-      <c r="AH2" s="365" t="n"/>
-      <c r="AI2" s="366" t="inlineStr">
+      <c r="AF2" s="440" t="n"/>
+      <c r="AG2" s="440" t="n"/>
+      <c r="AH2" s="441" t="n"/>
+      <c r="AI2" s="442" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="364" t="n"/>
-      <c r="AK2" s="364" t="n"/>
-      <c r="AL2" s="364" t="n"/>
-      <c r="AM2" s="364" t="n"/>
-      <c r="AN2" s="367" t="n"/>
+      <c r="AJ2" s="443" t="n"/>
+      <c r="AK2" s="443" t="n"/>
+      <c r="AL2" s="443" t="n"/>
+      <c r="AM2" s="443" t="n"/>
+      <c r="AN2" s="444" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="AE3" s="363" t="inlineStr">
+      <c r="A3" s="445" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="446" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="54" t="n"/>
+      <c r="Y3" s="54" t="n"/>
+      <c r="Z3" s="54" t="n"/>
+      <c r="AA3" s="54" t="n"/>
+      <c r="AB3" s="54" t="n"/>
+      <c r="AC3" s="54" t="n"/>
+      <c r="AD3" s="446" t="n"/>
+      <c r="AE3" s="447" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="364" t="n"/>
-      <c r="AG3" s="364" t="n"/>
-      <c r="AH3" s="365" t="n"/>
-      <c r="AI3" s="366" t="inlineStr">
+      <c r="AF3" s="448" t="n"/>
+      <c r="AG3" s="448" t="n"/>
+      <c r="AH3" s="449" t="n"/>
+      <c r="AI3" s="323" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="364" t="n"/>
-      <c r="AK3" s="364" t="n"/>
-      <c r="AL3" s="364" t="n"/>
-      <c r="AM3" s="364" t="n"/>
-      <c r="AN3" s="367" t="n"/>
+      <c r="AJ3" s="450" t="n"/>
+      <c r="AK3" s="450" t="n"/>
+      <c r="AL3" s="450" t="n"/>
+      <c r="AM3" s="450" t="n"/>
+      <c r="AN3" s="451" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="270" t="inlineStr">
+      <c r="A4" s="445" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="446" t="n"/>
+      <c r="I4" s="452" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="363" t="inlineStr">
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="54" t="n"/>
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="54" t="n"/>
+      <c r="Q4" s="54" t="n"/>
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
+      <c r="AA4" s="54" t="n"/>
+      <c r="AB4" s="54" t="n"/>
+      <c r="AC4" s="54" t="n"/>
+      <c r="AD4" s="446" t="n"/>
+      <c r="AE4" s="447" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="364" t="n"/>
-      <c r="AG4" s="364" t="n"/>
-      <c r="AH4" s="365" t="n"/>
-      <c r="AI4" s="366" t="inlineStr">
+      <c r="AF4" s="448" t="n"/>
+      <c r="AG4" s="448" t="n"/>
+      <c r="AH4" s="449" t="n"/>
+      <c r="AI4" s="323" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AJ4" s="364" t="n"/>
-      <c r="AK4" s="364" t="n"/>
-      <c r="AL4" s="364" t="n"/>
-      <c r="AM4" s="364" t="n"/>
-      <c r="AN4" s="367" t="n"/>
+      <c r="AJ4" s="450" t="n"/>
+      <c r="AK4" s="450" t="n"/>
+      <c r="AL4" s="450" t="n"/>
+      <c r="AM4" s="450" t="n"/>
+      <c r="AN4" s="451" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="50" t="inlineStr">
+      <c r="A5" s="445" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="446" t="n"/>
+      <c r="I5" s="453" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="368" t="inlineStr">
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="54" t="n"/>
+      <c r="L5" s="54" t="n"/>
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="54" t="n"/>
+      <c r="R5" s="54" t="n"/>
+      <c r="S5" s="54" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
+      <c r="X5" s="54" t="n"/>
+      <c r="Y5" s="54" t="n"/>
+      <c r="Z5" s="54" t="n"/>
+      <c r="AA5" s="54" t="n"/>
+      <c r="AB5" s="54" t="n"/>
+      <c r="AC5" s="54" t="n"/>
+      <c r="AD5" s="446" t="n"/>
+      <c r="AE5" s="447" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="369" t="n"/>
-      <c r="AG5" s="369" t="n"/>
-      <c r="AH5" s="370" t="n"/>
-      <c r="AI5" s="371" t="inlineStr">
+      <c r="AF5" s="448" t="n"/>
+      <c r="AG5" s="448" t="n"/>
+      <c r="AH5" s="449" t="n"/>
+      <c r="AI5" s="323" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AJ5" s="369" t="n"/>
-      <c r="AK5" s="369" t="n"/>
-      <c r="AL5" s="369" t="n"/>
-      <c r="AM5" s="369" t="n"/>
-      <c r="AN5" s="372" t="n"/>
+      <c r="AJ5" s="450" t="n"/>
+      <c r="AK5" s="450" t="n"/>
+      <c r="AL5" s="450" t="n"/>
+      <c r="AM5" s="450" t="n"/>
+      <c r="AN5" s="451" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="279" t="n"/>
-      <c r="B6" s="279" t="n"/>
-      <c r="C6" s="279" t="n"/>
-      <c r="D6" s="279" t="n"/>
-      <c r="E6" s="279" t="n"/>
-      <c r="F6" s="279" t="n"/>
-      <c r="G6" s="279" t="n"/>
-      <c r="H6" s="279" t="n"/>
-      <c r="I6" s="279" t="n"/>
-      <c r="J6" s="279" t="n"/>
-      <c r="K6" s="279" t="n"/>
-      <c r="L6" s="279" t="n"/>
-      <c r="M6" s="279" t="n"/>
-      <c r="N6" s="279" t="n"/>
-      <c r="O6" s="279" t="n"/>
-      <c r="P6" s="279" t="n"/>
-      <c r="Q6" s="279" t="n"/>
-      <c r="R6" s="279" t="n"/>
-      <c r="S6" s="279" t="n"/>
-      <c r="T6" s="279" t="n"/>
-      <c r="U6" s="279" t="n"/>
-      <c r="V6" s="279" t="n"/>
-      <c r="W6" s="279" t="n"/>
-      <c r="X6" s="279" t="n"/>
-      <c r="Y6" s="279" t="n"/>
-      <c r="Z6" s="279" t="n"/>
-      <c r="AA6" s="279" t="n"/>
-      <c r="AB6" s="279" t="n"/>
-      <c r="AC6" s="279" t="n"/>
-      <c r="AD6" s="279" t="n"/>
-      <c r="AE6" s="279" t="n"/>
-      <c r="AF6" s="279" t="n"/>
-      <c r="AG6" s="279" t="n"/>
-      <c r="AH6" s="279" t="n"/>
-      <c r="AI6" s="279" t="n"/>
-      <c r="AJ6" s="279" t="n"/>
-      <c r="AK6" s="279" t="n"/>
-      <c r="AL6" s="279" t="n"/>
-      <c r="AM6" s="279" t="n"/>
-      <c r="AN6" s="279" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="454" t="n"/>
+      <c r="B6" s="455" t="n"/>
+      <c r="C6" s="455" t="n"/>
+      <c r="D6" s="455" t="n"/>
+      <c r="E6" s="455" t="n"/>
+      <c r="F6" s="455" t="n"/>
+      <c r="G6" s="455" t="n"/>
+      <c r="H6" s="456" t="n"/>
+      <c r="I6" s="455" t="n"/>
+      <c r="J6" s="455" t="n"/>
+      <c r="K6" s="455" t="n"/>
+      <c r="L6" s="455" t="n"/>
+      <c r="M6" s="455" t="n"/>
+      <c r="N6" s="455" t="n"/>
+      <c r="O6" s="455" t="n"/>
+      <c r="P6" s="455" t="n"/>
+      <c r="Q6" s="455" t="n"/>
+      <c r="R6" s="455" t="n"/>
+      <c r="S6" s="455" t="n"/>
+      <c r="T6" s="455" t="n"/>
+      <c r="U6" s="455" t="n"/>
+      <c r="V6" s="455" t="n"/>
+      <c r="W6" s="455" t="n"/>
+      <c r="X6" s="455" t="n"/>
+      <c r="Y6" s="455" t="n"/>
+      <c r="Z6" s="455" t="n"/>
+      <c r="AA6" s="455" t="n"/>
+      <c r="AB6" s="455" t="n"/>
+      <c r="AC6" s="455" t="n"/>
+      <c r="AD6" s="456" t="n"/>
+      <c r="AE6" s="457" t="n"/>
+      <c r="AF6" s="457" t="n"/>
+      <c r="AG6" s="457" t="n"/>
+      <c r="AH6" s="458" t="n"/>
+      <c r="AI6" s="459" t="n"/>
+      <c r="AJ6" s="459" t="n"/>
+      <c r="AK6" s="459" t="n"/>
+      <c r="AL6" s="459" t="n"/>
+      <c r="AM6" s="459" t="n"/>
+      <c r="AN6" s="460" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REVIEW HEADER</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="461" t="n"/>
+      <c r="B7" s="462" t="n"/>
+      <c r="C7" s="462" t="n"/>
+      <c r="D7" s="462" t="n"/>
+      <c r="E7" s="462" t="n"/>
+      <c r="F7" s="462" t="n"/>
+      <c r="G7" s="462" t="n"/>
+      <c r="H7" s="462" t="n"/>
+      <c r="I7" s="462" t="n"/>
+      <c r="J7" s="462" t="n"/>
+      <c r="K7" s="462" t="n"/>
+      <c r="L7" s="462" t="n"/>
+      <c r="M7" s="462" t="n"/>
+      <c r="N7" s="462" t="n"/>
+      <c r="O7" s="462" t="n"/>
+      <c r="P7" s="462" t="n"/>
+      <c r="Q7" s="462" t="n"/>
+      <c r="R7" s="462" t="n"/>
+      <c r="S7" s="462" t="n"/>
+      <c r="T7" s="462" t="n"/>
+      <c r="U7" s="462" t="n"/>
+      <c r="V7" s="462" t="n"/>
+      <c r="W7" s="462" t="n"/>
+      <c r="X7" s="462" t="n"/>
+      <c r="Y7" s="462" t="n"/>
+      <c r="Z7" s="462" t="n"/>
+      <c r="AA7" s="462" t="n"/>
+      <c r="AB7" s="462" t="n"/>
+      <c r="AC7" s="462" t="n"/>
+      <c r="AD7" s="462" t="n"/>
+      <c r="AE7" s="462" t="n"/>
+      <c r="AF7" s="462" t="n"/>
+      <c r="AG7" s="462" t="n"/>
+      <c r="AH7" s="462" t="n"/>
+      <c r="AI7" s="462" t="n"/>
+      <c r="AJ7" s="462" t="n"/>
+      <c r="AK7" s="462" t="n"/>
+      <c r="AL7" s="462" t="n"/>
+      <c r="AM7" s="462" t="n"/>
+      <c r="AN7" s="462" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="374" t="inlineStr">
@@ -4693,50 +4877,50 @@
       <c r="AN24" s="384" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="430" t="inlineStr">
+      <c r="A25" s="349" t="inlineStr">
         <is>
           <t>NOTICE: Review access against least-privilege and segregation-of-duty expectations, close dormant or inappropriate access with owner and due date, and keep evidence linked to the reviewed system snapshot.</t>
         </is>
       </c>
-      <c r="B25" s="431" t="n"/>
-      <c r="C25" s="431" t="n"/>
-      <c r="D25" s="431" t="n"/>
-      <c r="E25" s="431" t="n"/>
-      <c r="F25" s="431" t="n"/>
-      <c r="G25" s="431" t="n"/>
-      <c r="H25" s="431" t="n"/>
-      <c r="I25" s="431" t="n"/>
-      <c r="J25" s="431" t="n"/>
-      <c r="K25" s="431" t="n"/>
-      <c r="L25" s="431" t="n"/>
-      <c r="M25" s="431" t="n"/>
-      <c r="N25" s="431" t="n"/>
-      <c r="O25" s="431" t="n"/>
-      <c r="P25" s="431" t="n"/>
-      <c r="Q25" s="431" t="n"/>
-      <c r="R25" s="431" t="n"/>
-      <c r="S25" s="431" t="n"/>
-      <c r="T25" s="431" t="n"/>
-      <c r="U25" s="431" t="n"/>
-      <c r="V25" s="431" t="n"/>
-      <c r="W25" s="431" t="n"/>
-      <c r="X25" s="431" t="n"/>
-      <c r="Y25" s="431" t="n"/>
-      <c r="Z25" s="431" t="n"/>
-      <c r="AA25" s="431" t="n"/>
-      <c r="AB25" s="431" t="n"/>
-      <c r="AC25" s="431" t="n"/>
-      <c r="AD25" s="431" t="n"/>
-      <c r="AE25" s="431" t="n"/>
-      <c r="AF25" s="431" t="n"/>
-      <c r="AG25" s="431" t="n"/>
-      <c r="AH25" s="431" t="n"/>
-      <c r="AI25" s="431" t="n"/>
-      <c r="AJ25" s="431" t="n"/>
-      <c r="AK25" s="431" t="n"/>
-      <c r="AL25" s="431" t="n"/>
-      <c r="AM25" s="431" t="n"/>
-      <c r="AN25" s="432" t="n"/>
+      <c r="B25" s="463" t="n"/>
+      <c r="C25" s="463" t="n"/>
+      <c r="D25" s="463" t="n"/>
+      <c r="E25" s="463" t="n"/>
+      <c r="F25" s="463" t="n"/>
+      <c r="G25" s="463" t="n"/>
+      <c r="H25" s="463" t="n"/>
+      <c r="I25" s="463" t="n"/>
+      <c r="J25" s="463" t="n"/>
+      <c r="K25" s="463" t="n"/>
+      <c r="L25" s="463" t="n"/>
+      <c r="M25" s="463" t="n"/>
+      <c r="N25" s="463" t="n"/>
+      <c r="O25" s="463" t="n"/>
+      <c r="P25" s="463" t="n"/>
+      <c r="Q25" s="463" t="n"/>
+      <c r="R25" s="463" t="n"/>
+      <c r="S25" s="463" t="n"/>
+      <c r="T25" s="463" t="n"/>
+      <c r="U25" s="463" t="n"/>
+      <c r="V25" s="463" t="n"/>
+      <c r="W25" s="463" t="n"/>
+      <c r="X25" s="463" t="n"/>
+      <c r="Y25" s="463" t="n"/>
+      <c r="Z25" s="463" t="n"/>
+      <c r="AA25" s="463" t="n"/>
+      <c r="AB25" s="463" t="n"/>
+      <c r="AC25" s="463" t="n"/>
+      <c r="AD25" s="463" t="n"/>
+      <c r="AE25" s="463" t="n"/>
+      <c r="AF25" s="463" t="n"/>
+      <c r="AG25" s="463" t="n"/>
+      <c r="AH25" s="463" t="n"/>
+      <c r="AI25" s="463" t="n"/>
+      <c r="AJ25" s="463" t="n"/>
+      <c r="AK25" s="463" t="n"/>
+      <c r="AL25" s="463" t="n"/>
+      <c r="AM25" s="463" t="n"/>
+      <c r="AN25" s="464" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -4904,7 +5088,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="359" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -4916,7 +5100,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="258" t="inlineStr">
+      <c r="L1" s="472" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW — FINDINGS AND ACTIONS</t>
         </is>
@@ -4950,7 +5134,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="360" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -4975,279 +5159,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="363" t="inlineStr">
+      <c r="A2" s="436" t="n"/>
+      <c r="B2" s="437" t="n"/>
+      <c r="C2" s="437" t="n"/>
+      <c r="D2" s="437" t="n"/>
+      <c r="E2" s="437" t="n"/>
+      <c r="F2" s="437" t="n"/>
+      <c r="G2" s="437" t="n"/>
+      <c r="H2" s="437" t="n"/>
+      <c r="I2" s="437" t="n"/>
+      <c r="J2" s="437" t="n"/>
+      <c r="K2" s="438" t="n"/>
+      <c r="L2" s="437" t="n"/>
+      <c r="M2" s="437" t="n"/>
+      <c r="N2" s="437" t="n"/>
+      <c r="O2" s="437" t="n"/>
+      <c r="P2" s="437" t="n"/>
+      <c r="Q2" s="437" t="n"/>
+      <c r="R2" s="437" t="n"/>
+      <c r="S2" s="437" t="n"/>
+      <c r="T2" s="437" t="n"/>
+      <c r="U2" s="437" t="n"/>
+      <c r="V2" s="437" t="n"/>
+      <c r="W2" s="437" t="n"/>
+      <c r="X2" s="437" t="n"/>
+      <c r="Y2" s="437" t="n"/>
+      <c r="Z2" s="437" t="n"/>
+      <c r="AA2" s="437" t="n"/>
+      <c r="AB2" s="437" t="n"/>
+      <c r="AC2" s="437" t="n"/>
+      <c r="AD2" s="437" t="n"/>
+      <c r="AE2" s="437" t="n"/>
+      <c r="AF2" s="437" t="n"/>
+      <c r="AG2" s="437" t="n"/>
+      <c r="AH2" s="437" t="n"/>
+      <c r="AI2" s="437" t="n"/>
+      <c r="AJ2" s="437" t="n"/>
+      <c r="AK2" s="437" t="n"/>
+      <c r="AL2" s="437" t="n"/>
+      <c r="AM2" s="437" t="n"/>
+      <c r="AN2" s="437" t="n"/>
+      <c r="AO2" s="437" t="n"/>
+      <c r="AP2" s="438" t="n"/>
+      <c r="AQ2" s="439" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="364" t="n"/>
-      <c r="AS2" s="364" t="n"/>
-      <c r="AT2" s="364" t="n"/>
-      <c r="AU2" s="364" t="n"/>
-      <c r="AV2" s="365" t="n"/>
-      <c r="AW2" s="366" t="inlineStr">
+      <c r="AR2" s="440" t="n"/>
+      <c r="AS2" s="440" t="n"/>
+      <c r="AT2" s="440" t="n"/>
+      <c r="AU2" s="440" t="n"/>
+      <c r="AV2" s="441" t="n"/>
+      <c r="AW2" s="442" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="364" t="n"/>
-      <c r="AY2" s="364" t="n"/>
-      <c r="AZ2" s="364" t="n"/>
-      <c r="BA2" s="364" t="n"/>
-      <c r="BB2" s="364" t="n"/>
-      <c r="BC2" s="364" t="n"/>
-      <c r="BD2" s="367" t="n"/>
+      <c r="AX2" s="443" t="n"/>
+      <c r="AY2" s="443" t="n"/>
+      <c r="AZ2" s="443" t="n"/>
+      <c r="BA2" s="443" t="n"/>
+      <c r="BB2" s="443" t="n"/>
+      <c r="BC2" s="443" t="n"/>
+      <c r="BD2" s="444" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="363" t="inlineStr">
+      <c r="A3" s="445" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="446" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="54" t="n"/>
+      <c r="Y3" s="54" t="n"/>
+      <c r="Z3" s="54" t="n"/>
+      <c r="AA3" s="54" t="n"/>
+      <c r="AB3" s="54" t="n"/>
+      <c r="AC3" s="54" t="n"/>
+      <c r="AD3" s="54" t="n"/>
+      <c r="AE3" s="54" t="n"/>
+      <c r="AF3" s="54" t="n"/>
+      <c r="AG3" s="54" t="n"/>
+      <c r="AH3" s="54" t="n"/>
+      <c r="AI3" s="54" t="n"/>
+      <c r="AJ3" s="54" t="n"/>
+      <c r="AK3" s="54" t="n"/>
+      <c r="AL3" s="54" t="n"/>
+      <c r="AM3" s="54" t="n"/>
+      <c r="AN3" s="54" t="n"/>
+      <c r="AO3" s="54" t="n"/>
+      <c r="AP3" s="446" t="n"/>
+      <c r="AQ3" s="447" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="364" t="n"/>
-      <c r="AS3" s="364" t="n"/>
-      <c r="AT3" s="364" t="n"/>
-      <c r="AU3" s="364" t="n"/>
-      <c r="AV3" s="365" t="n"/>
-      <c r="AW3" s="366" t="inlineStr">
+      <c r="AR3" s="448" t="n"/>
+      <c r="AS3" s="448" t="n"/>
+      <c r="AT3" s="448" t="n"/>
+      <c r="AU3" s="448" t="n"/>
+      <c r="AV3" s="449" t="n"/>
+      <c r="AW3" s="323" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="364" t="n"/>
-      <c r="AY3" s="364" t="n"/>
-      <c r="AZ3" s="364" t="n"/>
-      <c r="BA3" s="364" t="n"/>
-      <c r="BB3" s="364" t="n"/>
-      <c r="BC3" s="364" t="n"/>
-      <c r="BD3" s="367" t="n"/>
+      <c r="AX3" s="450" t="n"/>
+      <c r="AY3" s="450" t="n"/>
+      <c r="AZ3" s="450" t="n"/>
+      <c r="BA3" s="450" t="n"/>
+      <c r="BB3" s="450" t="n"/>
+      <c r="BC3" s="450" t="n"/>
+      <c r="BD3" s="451" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="270" t="inlineStr">
+      <c r="A4" s="445" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="446" t="n"/>
+      <c r="L4" s="452" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="363" t="inlineStr">
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="54" t="n"/>
+      <c r="Q4" s="54" t="n"/>
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
+      <c r="AA4" s="54" t="n"/>
+      <c r="AB4" s="54" t="n"/>
+      <c r="AC4" s="54" t="n"/>
+      <c r="AD4" s="54" t="n"/>
+      <c r="AE4" s="54" t="n"/>
+      <c r="AF4" s="54" t="n"/>
+      <c r="AG4" s="54" t="n"/>
+      <c r="AH4" s="54" t="n"/>
+      <c r="AI4" s="54" t="n"/>
+      <c r="AJ4" s="54" t="n"/>
+      <c r="AK4" s="54" t="n"/>
+      <c r="AL4" s="54" t="n"/>
+      <c r="AM4" s="54" t="n"/>
+      <c r="AN4" s="54" t="n"/>
+      <c r="AO4" s="54" t="n"/>
+      <c r="AP4" s="446" t="n"/>
+      <c r="AQ4" s="447" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="364" t="n"/>
-      <c r="AS4" s="364" t="n"/>
-      <c r="AT4" s="364" t="n"/>
-      <c r="AU4" s="364" t="n"/>
-      <c r="AV4" s="365" t="n"/>
-      <c r="AW4" s="366" t="inlineStr">
+      <c r="AR4" s="448" t="n"/>
+      <c r="AS4" s="448" t="n"/>
+      <c r="AT4" s="448" t="n"/>
+      <c r="AU4" s="448" t="n"/>
+      <c r="AV4" s="449" t="n"/>
+      <c r="AW4" s="323" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AX4" s="364" t="n"/>
-      <c r="AY4" s="364" t="n"/>
-      <c r="AZ4" s="364" t="n"/>
-      <c r="BA4" s="364" t="n"/>
-      <c r="BB4" s="364" t="n"/>
-      <c r="BC4" s="364" t="n"/>
-      <c r="BD4" s="367" t="n"/>
+      <c r="AX4" s="450" t="n"/>
+      <c r="AY4" s="450" t="n"/>
+      <c r="AZ4" s="450" t="n"/>
+      <c r="BA4" s="450" t="n"/>
+      <c r="BB4" s="450" t="n"/>
+      <c r="BC4" s="450" t="n"/>
+      <c r="BD4" s="451" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="A5" s="445" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="446" t="n"/>
+      <c r="L5" s="453" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="368" t="inlineStr">
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="54" t="n"/>
+      <c r="R5" s="54" t="n"/>
+      <c r="S5" s="54" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
+      <c r="X5" s="54" t="n"/>
+      <c r="Y5" s="54" t="n"/>
+      <c r="Z5" s="54" t="n"/>
+      <c r="AA5" s="54" t="n"/>
+      <c r="AB5" s="54" t="n"/>
+      <c r="AC5" s="54" t="n"/>
+      <c r="AD5" s="54" t="n"/>
+      <c r="AE5" s="54" t="n"/>
+      <c r="AF5" s="54" t="n"/>
+      <c r="AG5" s="54" t="n"/>
+      <c r="AH5" s="54" t="n"/>
+      <c r="AI5" s="54" t="n"/>
+      <c r="AJ5" s="54" t="n"/>
+      <c r="AK5" s="54" t="n"/>
+      <c r="AL5" s="54" t="n"/>
+      <c r="AM5" s="54" t="n"/>
+      <c r="AN5" s="54" t="n"/>
+      <c r="AO5" s="54" t="n"/>
+      <c r="AP5" s="446" t="n"/>
+      <c r="AQ5" s="447" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="369" t="n"/>
-      <c r="AS5" s="369" t="n"/>
-      <c r="AT5" s="369" t="n"/>
-      <c r="AU5" s="369" t="n"/>
-      <c r="AV5" s="370" t="n"/>
-      <c r="AW5" s="371" t="inlineStr">
+      <c r="AR5" s="448" t="n"/>
+      <c r="AS5" s="448" t="n"/>
+      <c r="AT5" s="448" t="n"/>
+      <c r="AU5" s="448" t="n"/>
+      <c r="AV5" s="449" t="n"/>
+      <c r="AW5" s="323" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="369" t="n"/>
-      <c r="AY5" s="369" t="n"/>
-      <c r="AZ5" s="369" t="n"/>
-      <c r="BA5" s="369" t="n"/>
-      <c r="BB5" s="369" t="n"/>
-      <c r="BC5" s="369" t="n"/>
-      <c r="BD5" s="372" t="n"/>
+      <c r="AX5" s="450" t="n"/>
+      <c r="AY5" s="450" t="n"/>
+      <c r="AZ5" s="450" t="n"/>
+      <c r="BA5" s="450" t="n"/>
+      <c r="BB5" s="450" t="n"/>
+      <c r="BC5" s="450" t="n"/>
+      <c r="BD5" s="451" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="279" t="n"/>
-      <c r="B6" s="279" t="n"/>
-      <c r="C6" s="279" t="n"/>
-      <c r="D6" s="279" t="n"/>
-      <c r="E6" s="279" t="n"/>
-      <c r="F6" s="279" t="n"/>
-      <c r="G6" s="279" t="n"/>
-      <c r="H6" s="279" t="n"/>
-      <c r="I6" s="279" t="n"/>
-      <c r="J6" s="279" t="n"/>
-      <c r="K6" s="279" t="n"/>
-      <c r="L6" s="279" t="n"/>
-      <c r="M6" s="279" t="n"/>
-      <c r="N6" s="279" t="n"/>
-      <c r="O6" s="279" t="n"/>
-      <c r="P6" s="279" t="n"/>
-      <c r="Q6" s="279" t="n"/>
-      <c r="R6" s="279" t="n"/>
-      <c r="S6" s="279" t="n"/>
-      <c r="T6" s="279" t="n"/>
-      <c r="U6" s="279" t="n"/>
-      <c r="V6" s="279" t="n"/>
-      <c r="W6" s="279" t="n"/>
-      <c r="X6" s="279" t="n"/>
-      <c r="Y6" s="279" t="n"/>
-      <c r="Z6" s="279" t="n"/>
-      <c r="AA6" s="279" t="n"/>
-      <c r="AB6" s="279" t="n"/>
-      <c r="AC6" s="279" t="n"/>
-      <c r="AD6" s="279" t="n"/>
-      <c r="AE6" s="279" t="n"/>
-      <c r="AF6" s="279" t="n"/>
-      <c r="AG6" s="279" t="n"/>
-      <c r="AH6" s="279" t="n"/>
-      <c r="AI6" s="279" t="n"/>
-      <c r="AJ6" s="279" t="n"/>
-      <c r="AK6" s="279" t="n"/>
-      <c r="AL6" s="279" t="n"/>
-      <c r="AM6" s="279" t="n"/>
-      <c r="AN6" s="279" t="n"/>
-      <c r="AO6" s="279" t="n"/>
-      <c r="AP6" s="279" t="n"/>
-      <c r="AQ6" s="279" t="n"/>
-      <c r="AR6" s="279" t="n"/>
-      <c r="AS6" s="279" t="n"/>
-      <c r="AT6" s="279" t="n"/>
-      <c r="AU6" s="279" t="n"/>
-      <c r="AV6" s="279" t="n"/>
-      <c r="AW6" s="279" t="n"/>
-      <c r="AX6" s="279" t="n"/>
-      <c r="AY6" s="279" t="n"/>
-      <c r="AZ6" s="279" t="n"/>
-      <c r="BA6" s="279" t="n"/>
-      <c r="BB6" s="279" t="n"/>
-      <c r="BC6" s="279" t="n"/>
-      <c r="BD6" s="279" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="454" t="n"/>
+      <c r="B6" s="455" t="n"/>
+      <c r="C6" s="455" t="n"/>
+      <c r="D6" s="455" t="n"/>
+      <c r="E6" s="455" t="n"/>
+      <c r="F6" s="455" t="n"/>
+      <c r="G6" s="455" t="n"/>
+      <c r="H6" s="455" t="n"/>
+      <c r="I6" s="455" t="n"/>
+      <c r="J6" s="455" t="n"/>
+      <c r="K6" s="456" t="n"/>
+      <c r="L6" s="455" t="n"/>
+      <c r="M6" s="455" t="n"/>
+      <c r="N6" s="455" t="n"/>
+      <c r="O6" s="455" t="n"/>
+      <c r="P6" s="455" t="n"/>
+      <c r="Q6" s="455" t="n"/>
+      <c r="R6" s="455" t="n"/>
+      <c r="S6" s="455" t="n"/>
+      <c r="T6" s="455" t="n"/>
+      <c r="U6" s="455" t="n"/>
+      <c r="V6" s="455" t="n"/>
+      <c r="W6" s="455" t="n"/>
+      <c r="X6" s="455" t="n"/>
+      <c r="Y6" s="455" t="n"/>
+      <c r="Z6" s="455" t="n"/>
+      <c r="AA6" s="455" t="n"/>
+      <c r="AB6" s="455" t="n"/>
+      <c r="AC6" s="455" t="n"/>
+      <c r="AD6" s="455" t="n"/>
+      <c r="AE6" s="455" t="n"/>
+      <c r="AF6" s="455" t="n"/>
+      <c r="AG6" s="455" t="n"/>
+      <c r="AH6" s="455" t="n"/>
+      <c r="AI6" s="455" t="n"/>
+      <c r="AJ6" s="455" t="n"/>
+      <c r="AK6" s="455" t="n"/>
+      <c r="AL6" s="455" t="n"/>
+      <c r="AM6" s="455" t="n"/>
+      <c r="AN6" s="455" t="n"/>
+      <c r="AO6" s="455" t="n"/>
+      <c r="AP6" s="456" t="n"/>
+      <c r="AQ6" s="457" t="n"/>
+      <c r="AR6" s="457" t="n"/>
+      <c r="AS6" s="457" t="n"/>
+      <c r="AT6" s="457" t="n"/>
+      <c r="AU6" s="457" t="n"/>
+      <c r="AV6" s="458" t="n"/>
+      <c r="AW6" s="459" t="n"/>
+      <c r="AX6" s="459" t="n"/>
+      <c r="AY6" s="459" t="n"/>
+      <c r="AZ6" s="459" t="n"/>
+      <c r="BA6" s="459" t="n"/>
+      <c r="BB6" s="459" t="n"/>
+      <c r="BC6" s="459" t="n"/>
+      <c r="BD6" s="460" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="461" t="n"/>
+      <c r="B7" s="462" t="n"/>
+      <c r="C7" s="462" t="n"/>
+      <c r="D7" s="462" t="n"/>
+      <c r="E7" s="462" t="n"/>
+      <c r="F7" s="462" t="n"/>
+      <c r="G7" s="462" t="n"/>
+      <c r="H7" s="462" t="n"/>
+      <c r="I7" s="462" t="n"/>
+      <c r="J7" s="462" t="n"/>
+      <c r="K7" s="462" t="n"/>
+      <c r="L7" s="462" t="n"/>
+      <c r="M7" s="462" t="n"/>
+      <c r="N7" s="462" t="n"/>
+      <c r="O7" s="462" t="n"/>
+      <c r="P7" s="462" t="n"/>
+      <c r="Q7" s="462" t="n"/>
+      <c r="R7" s="462" t="n"/>
+      <c r="S7" s="462" t="n"/>
+      <c r="T7" s="462" t="n"/>
+      <c r="U7" s="462" t="n"/>
+      <c r="V7" s="462" t="n"/>
+      <c r="W7" s="462" t="n"/>
+      <c r="X7" s="462" t="n"/>
+      <c r="Y7" s="462" t="n"/>
+      <c r="Z7" s="462" t="n"/>
+      <c r="AA7" s="462" t="n"/>
+      <c r="AB7" s="462" t="n"/>
+      <c r="AC7" s="462" t="n"/>
+      <c r="AD7" s="462" t="n"/>
+      <c r="AE7" s="462" t="n"/>
+      <c r="AF7" s="462" t="n"/>
+      <c r="AG7" s="462" t="n"/>
+      <c r="AH7" s="462" t="n"/>
+      <c r="AI7" s="462" t="n"/>
+      <c r="AJ7" s="462" t="n"/>
+      <c r="AK7" s="462" t="n"/>
+      <c r="AL7" s="462" t="n"/>
+      <c r="AM7" s="462" t="n"/>
+      <c r="AN7" s="462" t="n"/>
+      <c r="AO7" s="462" t="n"/>
+      <c r="AP7" s="462" t="n"/>
+      <c r="AQ7" s="462" t="n"/>
+      <c r="AR7" s="462" t="n"/>
+      <c r="AS7" s="462" t="n"/>
+      <c r="AT7" s="462" t="n"/>
+      <c r="AU7" s="462" t="n"/>
+      <c r="AV7" s="462" t="n"/>
+      <c r="AW7" s="462" t="n"/>
+      <c r="AX7" s="462" t="n"/>
+      <c r="AY7" s="462" t="n"/>
+      <c r="AZ7" s="462" t="n"/>
+      <c r="BA7" s="462" t="n"/>
+      <c r="BB7" s="462" t="n"/>
+      <c r="BC7" s="462" t="n"/>
+      <c r="BD7" s="462" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="374" t="inlineStr">
@@ -5952,66 +6249,66 @@
       <c r="BD18" s="384" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="430" t="inlineStr">
+      <c r="A19" s="349" t="inlineStr">
         <is>
           <t>NOTICE: Use one row per finding. Record objective evidence, severity, owner, due date and verification reference; avoid vague or conclusion-only wording.</t>
         </is>
       </c>
-      <c r="B19" s="431" t="n"/>
-      <c r="C19" s="431" t="n"/>
-      <c r="D19" s="431" t="n"/>
-      <c r="E19" s="431" t="n"/>
-      <c r="F19" s="431" t="n"/>
-      <c r="G19" s="431" t="n"/>
-      <c r="H19" s="431" t="n"/>
-      <c r="I19" s="431" t="n"/>
-      <c r="J19" s="431" t="n"/>
-      <c r="K19" s="431" t="n"/>
-      <c r="L19" s="431" t="n"/>
-      <c r="M19" s="431" t="n"/>
-      <c r="N19" s="431" t="n"/>
-      <c r="O19" s="431" t="n"/>
-      <c r="P19" s="431" t="n"/>
-      <c r="Q19" s="431" t="n"/>
-      <c r="R19" s="431" t="n"/>
-      <c r="S19" s="431" t="n"/>
-      <c r="T19" s="431" t="n"/>
-      <c r="U19" s="431" t="n"/>
-      <c r="V19" s="431" t="n"/>
-      <c r="W19" s="431" t="n"/>
-      <c r="X19" s="431" t="n"/>
-      <c r="Y19" s="431" t="n"/>
-      <c r="Z19" s="431" t="n"/>
-      <c r="AA19" s="431" t="n"/>
-      <c r="AB19" s="431" t="n"/>
-      <c r="AC19" s="431" t="n"/>
-      <c r="AD19" s="431" t="n"/>
-      <c r="AE19" s="431" t="n"/>
-      <c r="AF19" s="431" t="n"/>
-      <c r="AG19" s="431" t="n"/>
-      <c r="AH19" s="431" t="n"/>
-      <c r="AI19" s="431" t="n"/>
-      <c r="AJ19" s="431" t="n"/>
-      <c r="AK19" s="431" t="n"/>
-      <c r="AL19" s="431" t="n"/>
-      <c r="AM19" s="431" t="n"/>
-      <c r="AN19" s="431" t="n"/>
-      <c r="AO19" s="431" t="n"/>
-      <c r="AP19" s="431" t="n"/>
-      <c r="AQ19" s="431" t="n"/>
-      <c r="AR19" s="431" t="n"/>
-      <c r="AS19" s="431" t="n"/>
-      <c r="AT19" s="431" t="n"/>
-      <c r="AU19" s="431" t="n"/>
-      <c r="AV19" s="431" t="n"/>
-      <c r="AW19" s="431" t="n"/>
-      <c r="AX19" s="431" t="n"/>
-      <c r="AY19" s="431" t="n"/>
-      <c r="AZ19" s="431" t="n"/>
-      <c r="BA19" s="431" t="n"/>
-      <c r="BB19" s="431" t="n"/>
-      <c r="BC19" s="431" t="n"/>
-      <c r="BD19" s="432" t="n"/>
+      <c r="B19" s="463" t="n"/>
+      <c r="C19" s="463" t="n"/>
+      <c r="D19" s="463" t="n"/>
+      <c r="E19" s="463" t="n"/>
+      <c r="F19" s="463" t="n"/>
+      <c r="G19" s="463" t="n"/>
+      <c r="H19" s="463" t="n"/>
+      <c r="I19" s="463" t="n"/>
+      <c r="J19" s="463" t="n"/>
+      <c r="K19" s="463" t="n"/>
+      <c r="L19" s="463" t="n"/>
+      <c r="M19" s="463" t="n"/>
+      <c r="N19" s="463" t="n"/>
+      <c r="O19" s="463" t="n"/>
+      <c r="P19" s="463" t="n"/>
+      <c r="Q19" s="463" t="n"/>
+      <c r="R19" s="463" t="n"/>
+      <c r="S19" s="463" t="n"/>
+      <c r="T19" s="463" t="n"/>
+      <c r="U19" s="463" t="n"/>
+      <c r="V19" s="463" t="n"/>
+      <c r="W19" s="463" t="n"/>
+      <c r="X19" s="463" t="n"/>
+      <c r="Y19" s="463" t="n"/>
+      <c r="Z19" s="463" t="n"/>
+      <c r="AA19" s="463" t="n"/>
+      <c r="AB19" s="463" t="n"/>
+      <c r="AC19" s="463" t="n"/>
+      <c r="AD19" s="463" t="n"/>
+      <c r="AE19" s="463" t="n"/>
+      <c r="AF19" s="463" t="n"/>
+      <c r="AG19" s="463" t="n"/>
+      <c r="AH19" s="463" t="n"/>
+      <c r="AI19" s="463" t="n"/>
+      <c r="AJ19" s="463" t="n"/>
+      <c r="AK19" s="463" t="n"/>
+      <c r="AL19" s="463" t="n"/>
+      <c r="AM19" s="463" t="n"/>
+      <c r="AN19" s="463" t="n"/>
+      <c r="AO19" s="463" t="n"/>
+      <c r="AP19" s="463" t="n"/>
+      <c r="AQ19" s="463" t="n"/>
+      <c r="AR19" s="463" t="n"/>
+      <c r="AS19" s="463" t="n"/>
+      <c r="AT19" s="463" t="n"/>
+      <c r="AU19" s="463" t="n"/>
+      <c r="AV19" s="463" t="n"/>
+      <c r="AW19" s="463" t="n"/>
+      <c r="AX19" s="463" t="n"/>
+      <c r="AY19" s="463" t="n"/>
+      <c r="AZ19" s="463" t="n"/>
+      <c r="BA19" s="463" t="n"/>
+      <c r="BB19" s="463" t="n"/>
+      <c r="BC19" s="463" t="n"/>
+      <c r="BD19" s="464" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -6205,7 +6502,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="359" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -6217,7 +6514,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="340" t="inlineStr">
+      <c r="L1" s="473" t="inlineStr">
         <is>
           <t>QUARTERLY ACCESS REVIEW — CONTROLLED LOOKUP LISTS</t>
         </is>
@@ -6251,7 +6548,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="424" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6276,286 +6573,454 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="426" t="inlineStr">
+      <c r="A2" s="436" t="n"/>
+      <c r="B2" s="437" t="n"/>
+      <c r="C2" s="437" t="n"/>
+      <c r="D2" s="437" t="n"/>
+      <c r="E2" s="437" t="n"/>
+      <c r="F2" s="437" t="n"/>
+      <c r="G2" s="437" t="n"/>
+      <c r="H2" s="437" t="n"/>
+      <c r="I2" s="437" t="n"/>
+      <c r="J2" s="437" t="n"/>
+      <c r="K2" s="438" t="n"/>
+      <c r="L2" s="437" t="n"/>
+      <c r="M2" s="437" t="n"/>
+      <c r="N2" s="437" t="n"/>
+      <c r="O2" s="437" t="n"/>
+      <c r="P2" s="437" t="n"/>
+      <c r="Q2" s="437" t="n"/>
+      <c r="R2" s="437" t="n"/>
+      <c r="S2" s="437" t="n"/>
+      <c r="T2" s="437" t="n"/>
+      <c r="U2" s="437" t="n"/>
+      <c r="V2" s="437" t="n"/>
+      <c r="W2" s="437" t="n"/>
+      <c r="X2" s="437" t="n"/>
+      <c r="Y2" s="437" t="n"/>
+      <c r="Z2" s="437" t="n"/>
+      <c r="AA2" s="437" t="n"/>
+      <c r="AB2" s="437" t="n"/>
+      <c r="AC2" s="437" t="n"/>
+      <c r="AD2" s="437" t="n"/>
+      <c r="AE2" s="437" t="n"/>
+      <c r="AF2" s="437" t="n"/>
+      <c r="AG2" s="437" t="n"/>
+      <c r="AH2" s="437" t="n"/>
+      <c r="AI2" s="437" t="n"/>
+      <c r="AJ2" s="437" t="n"/>
+      <c r="AK2" s="437" t="n"/>
+      <c r="AL2" s="437" t="n"/>
+      <c r="AM2" s="437" t="n"/>
+      <c r="AN2" s="437" t="n"/>
+      <c r="AO2" s="437" t="n"/>
+      <c r="AP2" s="438" t="n"/>
+      <c r="AQ2" s="439" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="364" t="n"/>
-      <c r="AS2" s="364" t="n"/>
-      <c r="AT2" s="364" t="n"/>
-      <c r="AU2" s="364" t="n"/>
-      <c r="AV2" s="365" t="n"/>
-      <c r="AW2" s="427" t="inlineStr">
+      <c r="AR2" s="440" t="n"/>
+      <c r="AS2" s="440" t="n"/>
+      <c r="AT2" s="440" t="n"/>
+      <c r="AU2" s="440" t="n"/>
+      <c r="AV2" s="441" t="n"/>
+      <c r="AW2" s="442" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="364" t="n"/>
-      <c r="AY2" s="364" t="n"/>
-      <c r="AZ2" s="364" t="n"/>
-      <c r="BA2" s="364" t="n"/>
-      <c r="BB2" s="364" t="n"/>
-      <c r="BC2" s="364" t="n"/>
-      <c r="BD2" s="367" t="n"/>
+      <c r="AX2" s="443" t="n"/>
+      <c r="AY2" s="443" t="n"/>
+      <c r="AZ2" s="443" t="n"/>
+      <c r="BA2" s="443" t="n"/>
+      <c r="BB2" s="443" t="n"/>
+      <c r="BC2" s="443" t="n"/>
+      <c r="BD2" s="444" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="426" t="inlineStr">
+      <c r="A3" s="445" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="446" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="54" t="n"/>
+      <c r="Y3" s="54" t="n"/>
+      <c r="Z3" s="54" t="n"/>
+      <c r="AA3" s="54" t="n"/>
+      <c r="AB3" s="54" t="n"/>
+      <c r="AC3" s="54" t="n"/>
+      <c r="AD3" s="54" t="n"/>
+      <c r="AE3" s="54" t="n"/>
+      <c r="AF3" s="54" t="n"/>
+      <c r="AG3" s="54" t="n"/>
+      <c r="AH3" s="54" t="n"/>
+      <c r="AI3" s="54" t="n"/>
+      <c r="AJ3" s="54" t="n"/>
+      <c r="AK3" s="54" t="n"/>
+      <c r="AL3" s="54" t="n"/>
+      <c r="AM3" s="54" t="n"/>
+      <c r="AN3" s="54" t="n"/>
+      <c r="AO3" s="54" t="n"/>
+      <c r="AP3" s="446" t="n"/>
+      <c r="AQ3" s="447" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="364" t="n"/>
-      <c r="AS3" s="364" t="n"/>
-      <c r="AT3" s="364" t="n"/>
-      <c r="AU3" s="364" t="n"/>
-      <c r="AV3" s="365" t="n"/>
-      <c r="AW3" s="427" t="inlineStr">
+      <c r="AR3" s="448" t="n"/>
+      <c r="AS3" s="448" t="n"/>
+      <c r="AT3" s="448" t="n"/>
+      <c r="AU3" s="448" t="n"/>
+      <c r="AV3" s="449" t="n"/>
+      <c r="AW3" s="323" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="364" t="n"/>
-      <c r="AY3" s="364" t="n"/>
-      <c r="AZ3" s="364" t="n"/>
-      <c r="BA3" s="364" t="n"/>
-      <c r="BB3" s="364" t="n"/>
-      <c r="BC3" s="364" t="n"/>
-      <c r="BD3" s="367" t="n"/>
+      <c r="AX3" s="450" t="n"/>
+      <c r="AY3" s="450" t="n"/>
+      <c r="AZ3" s="450" t="n"/>
+      <c r="BA3" s="450" t="n"/>
+      <c r="BB3" s="450" t="n"/>
+      <c r="BC3" s="450" t="n"/>
+      <c r="BD3" s="451" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="A4" s="445" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="446" t="n"/>
+      <c r="L4" s="452" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="426" t="inlineStr">
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="54" t="n"/>
+      <c r="Q4" s="54" t="n"/>
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
+      <c r="AA4" s="54" t="n"/>
+      <c r="AB4" s="54" t="n"/>
+      <c r="AC4" s="54" t="n"/>
+      <c r="AD4" s="54" t="n"/>
+      <c r="AE4" s="54" t="n"/>
+      <c r="AF4" s="54" t="n"/>
+      <c r="AG4" s="54" t="n"/>
+      <c r="AH4" s="54" t="n"/>
+      <c r="AI4" s="54" t="n"/>
+      <c r="AJ4" s="54" t="n"/>
+      <c r="AK4" s="54" t="n"/>
+      <c r="AL4" s="54" t="n"/>
+      <c r="AM4" s="54" t="n"/>
+      <c r="AN4" s="54" t="n"/>
+      <c r="AO4" s="54" t="n"/>
+      <c r="AP4" s="446" t="n"/>
+      <c r="AQ4" s="447" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="364" t="n"/>
-      <c r="AS4" s="364" t="n"/>
-      <c r="AT4" s="364" t="n"/>
-      <c r="AU4" s="364" t="n"/>
-      <c r="AV4" s="365" t="n"/>
-      <c r="AW4" s="427" t="inlineStr">
+      <c r="AR4" s="448" t="n"/>
+      <c r="AS4" s="448" t="n"/>
+      <c r="AT4" s="448" t="n"/>
+      <c r="AU4" s="448" t="n"/>
+      <c r="AV4" s="449" t="n"/>
+      <c r="AW4" s="323" t="inlineStr">
         <is>
           <t>QMS + IT</t>
         </is>
       </c>
-      <c r="AX4" s="364" t="n"/>
-      <c r="AY4" s="364" t="n"/>
-      <c r="AZ4" s="364" t="n"/>
-      <c r="BA4" s="364" t="n"/>
-      <c r="BB4" s="364" t="n"/>
-      <c r="BC4" s="364" t="n"/>
-      <c r="BD4" s="367" t="n"/>
+      <c r="AX4" s="450" t="n"/>
+      <c r="AY4" s="450" t="n"/>
+      <c r="AZ4" s="450" t="n"/>
+      <c r="BA4" s="450" t="n"/>
+      <c r="BB4" s="450" t="n"/>
+      <c r="BC4" s="450" t="n"/>
+      <c r="BD4" s="451" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="A5" s="445" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="446" t="n"/>
+      <c r="L5" s="453" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="428" t="inlineStr">
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="54" t="n"/>
+      <c r="R5" s="54" t="n"/>
+      <c r="S5" s="54" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
+      <c r="X5" s="54" t="n"/>
+      <c r="Y5" s="54" t="n"/>
+      <c r="Z5" s="54" t="n"/>
+      <c r="AA5" s="54" t="n"/>
+      <c r="AB5" s="54" t="n"/>
+      <c r="AC5" s="54" t="n"/>
+      <c r="AD5" s="54" t="n"/>
+      <c r="AE5" s="54" t="n"/>
+      <c r="AF5" s="54" t="n"/>
+      <c r="AG5" s="54" t="n"/>
+      <c r="AH5" s="54" t="n"/>
+      <c r="AI5" s="54" t="n"/>
+      <c r="AJ5" s="54" t="n"/>
+      <c r="AK5" s="54" t="n"/>
+      <c r="AL5" s="54" t="n"/>
+      <c r="AM5" s="54" t="n"/>
+      <c r="AN5" s="54" t="n"/>
+      <c r="AO5" s="54" t="n"/>
+      <c r="AP5" s="446" t="n"/>
+      <c r="AQ5" s="447" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="369" t="n"/>
-      <c r="AS5" s="369" t="n"/>
-      <c r="AT5" s="369" t="n"/>
-      <c r="AU5" s="369" t="n"/>
-      <c r="AV5" s="370" t="n"/>
-      <c r="AW5" s="429" t="inlineStr">
+      <c r="AR5" s="448" t="n"/>
+      <c r="AS5" s="448" t="n"/>
+      <c r="AT5" s="448" t="n"/>
+      <c r="AU5" s="448" t="n"/>
+      <c r="AV5" s="449" t="n"/>
+      <c r="AW5" s="323" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="369" t="n"/>
-      <c r="AY5" s="369" t="n"/>
-      <c r="AZ5" s="369" t="n"/>
-      <c r="BA5" s="369" t="n"/>
-      <c r="BB5" s="369" t="n"/>
-      <c r="BC5" s="369" t="n"/>
-      <c r="BD5" s="372" t="n"/>
+      <c r="AX5" s="450" t="n"/>
+      <c r="AY5" s="450" t="n"/>
+      <c r="AZ5" s="450" t="n"/>
+      <c r="BA5" s="450" t="n"/>
+      <c r="BB5" s="450" t="n"/>
+      <c r="BC5" s="450" t="n"/>
+      <c r="BD5" s="451" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="347" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="454" t="n"/>
+      <c r="B6" s="465" t="n"/>
+      <c r="C6" s="465" t="n"/>
+      <c r="D6" s="465" t="n"/>
+      <c r="E6" s="465" t="n"/>
+      <c r="F6" s="465" t="n"/>
+      <c r="G6" s="465" t="n"/>
+      <c r="H6" s="465" t="n"/>
+      <c r="I6" s="465" t="n"/>
+      <c r="J6" s="465" t="n"/>
+      <c r="K6" s="466" t="n"/>
+      <c r="L6" s="465" t="n"/>
+      <c r="M6" s="465" t="n"/>
+      <c r="N6" s="465" t="n"/>
+      <c r="O6" s="465" t="n"/>
+      <c r="P6" s="465" t="n"/>
+      <c r="Q6" s="465" t="n"/>
+      <c r="R6" s="465" t="n"/>
+      <c r="S6" s="465" t="n"/>
+      <c r="T6" s="465" t="n"/>
+      <c r="U6" s="465" t="n"/>
+      <c r="V6" s="465" t="n"/>
+      <c r="W6" s="465" t="n"/>
+      <c r="X6" s="465" t="n"/>
+      <c r="Y6" s="465" t="n"/>
+      <c r="Z6" s="465" t="n"/>
+      <c r="AA6" s="465" t="n"/>
+      <c r="AB6" s="465" t="n"/>
+      <c r="AC6" s="465" t="n"/>
+      <c r="AD6" s="465" t="n"/>
+      <c r="AE6" s="465" t="n"/>
+      <c r="AF6" s="465" t="n"/>
+      <c r="AG6" s="465" t="n"/>
+      <c r="AH6" s="465" t="n"/>
+      <c r="AI6" s="465" t="n"/>
+      <c r="AJ6" s="465" t="n"/>
+      <c r="AK6" s="465" t="n"/>
+      <c r="AL6" s="465" t="n"/>
+      <c r="AM6" s="465" t="n"/>
+      <c r="AN6" s="465" t="n"/>
+      <c r="AO6" s="465" t="n"/>
+      <c r="AP6" s="466" t="n"/>
+      <c r="AQ6" s="467" t="n"/>
+      <c r="AR6" s="467" t="n"/>
+      <c r="AS6" s="467" t="n"/>
+      <c r="AT6" s="467" t="n"/>
+      <c r="AU6" s="467" t="n"/>
+      <c r="AV6" s="468" t="n"/>
+      <c r="AW6" s="469" t="n"/>
+      <c r="AX6" s="469" t="n"/>
+      <c r="AY6" s="469" t="n"/>
+      <c r="AZ6" s="469" t="n"/>
+      <c r="BA6" s="469" t="n"/>
+      <c r="BB6" s="469" t="n"/>
+      <c r="BC6" s="469" t="n"/>
+      <c r="BD6" s="470" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="471" t="n"/>
+      <c r="B7" s="462" t="n"/>
+      <c r="C7" s="462" t="n"/>
+      <c r="D7" s="462" t="n"/>
+      <c r="E7" s="462" t="n"/>
+      <c r="F7" s="462" t="n"/>
+      <c r="G7" s="462" t="n"/>
+      <c r="H7" s="462" t="n"/>
+      <c r="I7" s="462" t="n"/>
+      <c r="J7" s="462" t="n"/>
+      <c r="K7" s="462" t="n"/>
+      <c r="L7" s="462" t="n"/>
+      <c r="M7" s="462" t="n"/>
+      <c r="N7" s="462" t="n"/>
+      <c r="O7" s="462" t="n"/>
+      <c r="P7" s="462" t="n"/>
+      <c r="Q7" s="462" t="n"/>
+      <c r="R7" s="462" t="n"/>
+      <c r="S7" s="462" t="n"/>
+      <c r="T7" s="462" t="n"/>
+      <c r="U7" s="462" t="n"/>
+      <c r="V7" s="462" t="n"/>
+      <c r="W7" s="462" t="n"/>
+      <c r="X7" s="462" t="n"/>
+      <c r="Y7" s="462" t="n"/>
+      <c r="Z7" s="462" t="n"/>
+      <c r="AA7" s="462" t="n"/>
+      <c r="AB7" s="462" t="n"/>
+      <c r="AC7" s="462" t="n"/>
+      <c r="AD7" s="462" t="n"/>
+      <c r="AE7" s="462" t="n"/>
+      <c r="AF7" s="462" t="n"/>
+      <c r="AG7" s="462" t="n"/>
+      <c r="AH7" s="462" t="n"/>
+      <c r="AI7" s="462" t="n"/>
+      <c r="AJ7" s="462" t="n"/>
+      <c r="AK7" s="462" t="n"/>
+      <c r="AL7" s="462" t="n"/>
+      <c r="AM7" s="462" t="n"/>
+      <c r="AN7" s="462" t="n"/>
+      <c r="AO7" s="462" t="n"/>
+      <c r="AP7" s="462" t="n"/>
+      <c r="AQ7" s="462" t="n"/>
+      <c r="AR7" s="462" t="n"/>
+      <c r="AS7" s="462" t="n"/>
+      <c r="AT7" s="462" t="n"/>
+      <c r="AU7" s="462" t="n"/>
+      <c r="AV7" s="462" t="n"/>
+      <c r="AW7" s="462" t="n"/>
+      <c r="AX7" s="462" t="n"/>
+      <c r="AY7" s="462" t="n"/>
+      <c r="AZ7" s="462" t="n"/>
+      <c r="BA7" s="462" t="n"/>
+      <c r="BB7" s="462" t="n"/>
+      <c r="BC7" s="462" t="n"/>
+      <c r="BD7" s="462" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="430" t="inlineStr">
+      <c r="A8" s="349" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="431" t="n"/>
-      <c r="C8" s="431" t="n"/>
-      <c r="D8" s="431" t="n"/>
-      <c r="E8" s="431" t="n"/>
-      <c r="F8" s="431" t="n"/>
-      <c r="G8" s="431" t="n"/>
-      <c r="H8" s="431" t="n"/>
-      <c r="I8" s="431" t="n"/>
-      <c r="J8" s="431" t="n"/>
-      <c r="K8" s="431" t="n"/>
-      <c r="L8" s="431" t="n"/>
-      <c r="M8" s="431" t="n"/>
-      <c r="N8" s="431" t="n"/>
-      <c r="O8" s="431" t="n"/>
-      <c r="P8" s="431" t="n"/>
-      <c r="Q8" s="431" t="n"/>
-      <c r="R8" s="431" t="n"/>
-      <c r="S8" s="431" t="n"/>
-      <c r="T8" s="431" t="n"/>
-      <c r="U8" s="431" t="n"/>
-      <c r="V8" s="431" t="n"/>
-      <c r="W8" s="431" t="n"/>
-      <c r="X8" s="431" t="n"/>
-      <c r="Y8" s="431" t="n"/>
-      <c r="Z8" s="431" t="n"/>
-      <c r="AA8" s="431" t="n"/>
-      <c r="AB8" s="431" t="n"/>
-      <c r="AC8" s="431" t="n"/>
-      <c r="AD8" s="431" t="n"/>
-      <c r="AE8" s="431" t="n"/>
-      <c r="AF8" s="431" t="n"/>
-      <c r="AG8" s="431" t="n"/>
-      <c r="AH8" s="431" t="n"/>
-      <c r="AI8" s="431" t="n"/>
-      <c r="AJ8" s="431" t="n"/>
-      <c r="AK8" s="431" t="n"/>
-      <c r="AL8" s="431" t="n"/>
-      <c r="AM8" s="431" t="n"/>
-      <c r="AN8" s="431" t="n"/>
-      <c r="AO8" s="431" t="n"/>
-      <c r="AP8" s="431" t="n"/>
-      <c r="AQ8" s="431" t="n"/>
-      <c r="AR8" s="431" t="n"/>
-      <c r="AS8" s="431" t="n"/>
-      <c r="AT8" s="431" t="n"/>
-      <c r="AU8" s="431" t="n"/>
-      <c r="AV8" s="431" t="n"/>
-      <c r="AW8" s="431" t="n"/>
-      <c r="AX8" s="431" t="n"/>
-      <c r="AY8" s="431" t="n"/>
-      <c r="AZ8" s="431" t="n"/>
-      <c r="BA8" s="431" t="n"/>
-      <c r="BB8" s="431" t="n"/>
-      <c r="BC8" s="431" t="n"/>
-      <c r="BD8" s="432" t="n"/>
+      <c r="B8" s="463" t="n"/>
+      <c r="C8" s="463" t="n"/>
+      <c r="D8" s="463" t="n"/>
+      <c r="E8" s="463" t="n"/>
+      <c r="F8" s="463" t="n"/>
+      <c r="G8" s="463" t="n"/>
+      <c r="H8" s="463" t="n"/>
+      <c r="I8" s="463" t="n"/>
+      <c r="J8" s="463" t="n"/>
+      <c r="K8" s="463" t="n"/>
+      <c r="L8" s="463" t="n"/>
+      <c r="M8" s="463" t="n"/>
+      <c r="N8" s="463" t="n"/>
+      <c r="O8" s="463" t="n"/>
+      <c r="P8" s="463" t="n"/>
+      <c r="Q8" s="463" t="n"/>
+      <c r="R8" s="463" t="n"/>
+      <c r="S8" s="463" t="n"/>
+      <c r="T8" s="463" t="n"/>
+      <c r="U8" s="463" t="n"/>
+      <c r="V8" s="463" t="n"/>
+      <c r="W8" s="463" t="n"/>
+      <c r="X8" s="463" t="n"/>
+      <c r="Y8" s="463" t="n"/>
+      <c r="Z8" s="463" t="n"/>
+      <c r="AA8" s="463" t="n"/>
+      <c r="AB8" s="463" t="n"/>
+      <c r="AC8" s="463" t="n"/>
+      <c r="AD8" s="463" t="n"/>
+      <c r="AE8" s="463" t="n"/>
+      <c r="AF8" s="463" t="n"/>
+      <c r="AG8" s="463" t="n"/>
+      <c r="AH8" s="463" t="n"/>
+      <c r="AI8" s="463" t="n"/>
+      <c r="AJ8" s="463" t="n"/>
+      <c r="AK8" s="463" t="n"/>
+      <c r="AL8" s="463" t="n"/>
+      <c r="AM8" s="463" t="n"/>
+      <c r="AN8" s="463" t="n"/>
+      <c r="AO8" s="463" t="n"/>
+      <c r="AP8" s="463" t="n"/>
+      <c r="AQ8" s="463" t="n"/>
+      <c r="AR8" s="463" t="n"/>
+      <c r="AS8" s="463" t="n"/>
+      <c r="AT8" s="463" t="n"/>
+      <c r="AU8" s="463" t="n"/>
+      <c r="AV8" s="463" t="n"/>
+      <c r="AW8" s="463" t="n"/>
+      <c r="AX8" s="463" t="n"/>
+      <c r="AY8" s="463" t="n"/>
+      <c r="AZ8" s="463" t="n"/>
+      <c r="BA8" s="463" t="n"/>
+      <c r="BB8" s="463" t="n"/>
+      <c r="BC8" s="463" t="n"/>
+      <c r="BD8" s="464" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="327" t="inlineStr">
@@ -8004,66 +8469,66 @@
       <c r="BD19" s="358" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="430" t="inlineStr">
+      <c r="A20" s="349" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="431" t="n"/>
-      <c r="C20" s="431" t="n"/>
-      <c r="D20" s="431" t="n"/>
-      <c r="E20" s="431" t="n"/>
-      <c r="F20" s="431" t="n"/>
-      <c r="G20" s="431" t="n"/>
-      <c r="H20" s="431" t="n"/>
-      <c r="I20" s="431" t="n"/>
-      <c r="J20" s="431" t="n"/>
-      <c r="K20" s="431" t="n"/>
-      <c r="L20" s="431" t="n"/>
-      <c r="M20" s="431" t="n"/>
-      <c r="N20" s="431" t="n"/>
-      <c r="O20" s="431" t="n"/>
-      <c r="P20" s="431" t="n"/>
-      <c r="Q20" s="431" t="n"/>
-      <c r="R20" s="431" t="n"/>
-      <c r="S20" s="431" t="n"/>
-      <c r="T20" s="431" t="n"/>
-      <c r="U20" s="431" t="n"/>
-      <c r="V20" s="431" t="n"/>
-      <c r="W20" s="431" t="n"/>
-      <c r="X20" s="431" t="n"/>
-      <c r="Y20" s="431" t="n"/>
-      <c r="Z20" s="431" t="n"/>
-      <c r="AA20" s="431" t="n"/>
-      <c r="AB20" s="431" t="n"/>
-      <c r="AC20" s="431" t="n"/>
-      <c r="AD20" s="431" t="n"/>
-      <c r="AE20" s="431" t="n"/>
-      <c r="AF20" s="431" t="n"/>
-      <c r="AG20" s="431" t="n"/>
-      <c r="AH20" s="431" t="n"/>
-      <c r="AI20" s="431" t="n"/>
-      <c r="AJ20" s="431" t="n"/>
-      <c r="AK20" s="431" t="n"/>
-      <c r="AL20" s="431" t="n"/>
-      <c r="AM20" s="431" t="n"/>
-      <c r="AN20" s="431" t="n"/>
-      <c r="AO20" s="431" t="n"/>
-      <c r="AP20" s="431" t="n"/>
-      <c r="AQ20" s="431" t="n"/>
-      <c r="AR20" s="431" t="n"/>
-      <c r="AS20" s="431" t="n"/>
-      <c r="AT20" s="431" t="n"/>
-      <c r="AU20" s="431" t="n"/>
-      <c r="AV20" s="431" t="n"/>
-      <c r="AW20" s="431" t="n"/>
-      <c r="AX20" s="431" t="n"/>
-      <c r="AY20" s="431" t="n"/>
-      <c r="AZ20" s="431" t="n"/>
-      <c r="BA20" s="431" t="n"/>
-      <c r="BB20" s="431" t="n"/>
-      <c r="BC20" s="431" t="n"/>
-      <c r="BD20" s="432" t="n"/>
+      <c r="B20" s="463" t="n"/>
+      <c r="C20" s="463" t="n"/>
+      <c r="D20" s="463" t="n"/>
+      <c r="E20" s="463" t="n"/>
+      <c r="F20" s="463" t="n"/>
+      <c r="G20" s="463" t="n"/>
+      <c r="H20" s="463" t="n"/>
+      <c r="I20" s="463" t="n"/>
+      <c r="J20" s="463" t="n"/>
+      <c r="K20" s="463" t="n"/>
+      <c r="L20" s="463" t="n"/>
+      <c r="M20" s="463" t="n"/>
+      <c r="N20" s="463" t="n"/>
+      <c r="O20" s="463" t="n"/>
+      <c r="P20" s="463" t="n"/>
+      <c r="Q20" s="463" t="n"/>
+      <c r="R20" s="463" t="n"/>
+      <c r="S20" s="463" t="n"/>
+      <c r="T20" s="463" t="n"/>
+      <c r="U20" s="463" t="n"/>
+      <c r="V20" s="463" t="n"/>
+      <c r="W20" s="463" t="n"/>
+      <c r="X20" s="463" t="n"/>
+      <c r="Y20" s="463" t="n"/>
+      <c r="Z20" s="463" t="n"/>
+      <c r="AA20" s="463" t="n"/>
+      <c r="AB20" s="463" t="n"/>
+      <c r="AC20" s="463" t="n"/>
+      <c r="AD20" s="463" t="n"/>
+      <c r="AE20" s="463" t="n"/>
+      <c r="AF20" s="463" t="n"/>
+      <c r="AG20" s="463" t="n"/>
+      <c r="AH20" s="463" t="n"/>
+      <c r="AI20" s="463" t="n"/>
+      <c r="AJ20" s="463" t="n"/>
+      <c r="AK20" s="463" t="n"/>
+      <c r="AL20" s="463" t="n"/>
+      <c r="AM20" s="463" t="n"/>
+      <c r="AN20" s="463" t="n"/>
+      <c r="AO20" s="463" t="n"/>
+      <c r="AP20" s="463" t="n"/>
+      <c r="AQ20" s="463" t="n"/>
+      <c r="AR20" s="463" t="n"/>
+      <c r="AS20" s="463" t="n"/>
+      <c r="AT20" s="463" t="n"/>
+      <c r="AU20" s="463" t="n"/>
+      <c r="AV20" s="463" t="n"/>
+      <c r="AW20" s="463" t="n"/>
+      <c r="AX20" s="463" t="n"/>
+      <c r="AY20" s="463" t="n"/>
+      <c r="AZ20" s="463" t="n"/>
+      <c r="BA20" s="463" t="n"/>
+      <c r="BB20" s="463" t="n"/>
+      <c r="BC20" s="463" t="n"/>
+      <c r="BD20" s="464" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -840,6 +840,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2302,7 +2305,6 @@
       <c r="AN25" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="63">
     <mergeCell ref="U24:AA24"/>
     <mergeCell ref="A12:AN12"/>
@@ -3472,7 +3474,6 @@
       <c r="BD19" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="93">
     <mergeCell ref="K16:R16"/>
     <mergeCell ref="Y14:AD14"/>
@@ -4624,7 +4625,6 @@
       <c r="BD18" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="82">
     <mergeCell ref="AV17:BD17"/>
     <mergeCell ref="AV11:BD11"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -1320,7 +1320,7 @@
       <c r="AH4" s="29" t="n"/>
       <c r="AI4" s="47" t="inlineStr">
         <is>
-          <t>QMS + IT</t>
+          <t>IT / QMS</t>
         </is>
       </c>
       <c r="AJ4" s="14" t="n"/>
@@ -1374,7 +1374,7 @@
       <c r="AH5" s="52" t="n"/>
       <c r="AI5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AJ5" s="17" t="n"/>
@@ -2641,7 +2641,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>QMS + IT</t>
+          <t>IT / QMS</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -2711,7 +2711,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -3836,7 +3836,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>QMS + IT</t>
+          <t>IT / QMS</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -3906,7 +3906,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -4961,7 +4961,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>QMS + IT</t>
+          <t>IT / QMS</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM111_Findings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM111_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM111_Main'!$1:$6</definedName>
@@ -826,7 +828,7 @@
       <row>0</row>
       <rowOff>257175</rowOff>
     </from>
-    <ext cx="1552575" cy="438150"/>
+    <ext cx="5238750" cy="1514475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1139,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -1251,7 +1253,7 @@
       <c r="AH2" s="29" t="n"/>
       <c r="AI2" s="47" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AJ2" s="14" t="n"/>
@@ -1294,7 +1296,7 @@
       <c r="AH3" s="29" t="n"/>
       <c r="AI3" s="47" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AJ3" s="14" t="n"/>
@@ -1320,7 +1322,7 @@
       <c r="AH4" s="29" t="n"/>
       <c r="AI4" s="47" t="inlineStr">
         <is>
-          <t>IT / QMS</t>
+          <t>QMS + IT</t>
         </is>
       </c>
       <c r="AJ4" s="14" t="n"/>
@@ -1374,7 +1376,7 @@
       <c r="AH5" s="52" t="n"/>
       <c r="AI5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AJ5" s="17" t="n"/>
@@ -1435,7 +1437,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>Access Review ID</t>
+          <t>Linked FRM-141</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -1459,7 +1461,7 @@
       <c r="T8" s="27" t="n"/>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>System / Area</t>
+          <t>Ref: SOP-101</t>
         </is>
       </c>
       <c r="V8" s="6" t="n"/>
@@ -1468,7 +1470,11 @@
       <c r="Y8" s="6" t="n"/>
       <c r="Z8" s="6" t="n"/>
       <c r="AA8" s="7" t="n"/>
-      <c r="AB8" s="25" t="n"/>
+      <c r="AB8" s="25" t="inlineStr">
+        <is>
+          <t>Retain: 5 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AC8" s="26" t="n"/>
       <c r="AD8" s="26" t="n"/>
       <c r="AE8" s="26" t="n"/>
@@ -2305,6 +2311,7 @@
       <c r="AN25" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="63">
     <mergeCell ref="U24:AA24"/>
     <mergeCell ref="A12:AN12"/>
@@ -2641,7 +2648,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>IT / QMS</t>
+          <t>QMS + IT</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -2711,7 +2718,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -3474,6 +3481,7 @@
       <c r="BD19" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="93">
     <mergeCell ref="K16:R16"/>
     <mergeCell ref="Y14:AD14"/>
@@ -3836,7 +3844,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>IT / QMS</t>
+          <t>QMS + IT</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -3906,7 +3914,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -4625,6 +4633,7 @@
       <c r="BD18" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="82">
     <mergeCell ref="AV17:BD17"/>
     <mergeCell ref="AV11:BD11"/>
@@ -4961,7 +4970,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>IT / QMS</t>
+          <t>QMS + IT</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -5031,7 +5040,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -6457,4 +6466,97 @@
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-141; Parent ref: SOP-101</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-111_Quarterly_Access_Review.xlsx
@@ -4953,6 +4953,81 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Kỳ xem xét
+Ghi quý và năm.
+Ví dụ: Q1-2026, Q2-2026</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày xem xét
+Ngày thực hiện rà soát quyền truy cập.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Người xem xét
+IT admin hoặc người được ủy quyền.</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t>Hệ thống được xem xét
+Liệt kê các hệ thống: M365, Epicor, CNC network...
+Ví dụ: M365 + Epicor ERP + CNC DNC server</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Danh sách user hoạt động
+So sánh danh sách user hệ thống với danh sách nhân viên HR.
+Nhân viên đã nghỉ phải bị vô hiệu hóa tài khoản trong 24h.</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Mức quyền phù hợp
+Kiểm tra từng user không có quyền vượt quá yêu cầu công việc.
+Ví dụ: operator không cần quyền admin hệ thống.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Quyền truy cập thư mục
+Kiểm tra các thư mục chia sẻ chỉ cho phép nhóm được ủy quyền.</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Tài khoản dịch vụ
+Tài khoản dùng cho hệ thống tự động (backup, sync...).
+Mỗi tài khoản phải có mục đích rõ ràng.</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Khắc phục phát hiện
+Mọi vấn đề phát hiện phải có hành động và người chịu trách nhiệm.</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Lưu hồ sơ xem xét
+Lưu biên bản xem xét làm bằng chứng cho audit.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5862,8 +5937,9 @@
       <c r="AN13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="inlineStr">
@@ -5918,8 +5994,9 @@
       <c r="AN14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="492" t="inlineStr">
@@ -5974,8 +6051,9 @@
       <c r="AN15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="492" t="inlineStr">
@@ -6030,8 +6108,9 @@
       <c r="AN16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="492" t="inlineStr">
@@ -6063,7 +6142,7 @@
       <c r="U17" s="491" t="n"/>
       <c r="V17" s="495" t="inlineStr">
         <is>
-          <t>All service accounts have documented purpose.</t>
+          <t>All service accounts documented.</t>
         </is>
       </c>
       <c r="W17" s="493" t="n"/>
@@ -6086,8 +6165,9 @@
       <c r="AN17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="inlineStr">
@@ -6142,8 +6222,9 @@
       <c r="AN18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="inlineStr">
@@ -6198,8 +6279,9 @@
       <c r="AN19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="500" t="n"/>
@@ -6242,8 +6324,9 @@
       <c r="AN20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="502" t="n">
-        <v>8</v>
+      <c r="A21" s="502">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="482" t="n"/>
       <c r="C21" s="503" t="n"/>
@@ -6719,6 +6802,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
